--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>814.1</v>
+        <v>279.4</v>
       </c>
       <c r="E2" t="n">
-        <v>548.8</v>
+        <v>209.71</v>
       </c>
       <c r="F2" t="n">
-        <v>48.34</v>
+        <v>33.23</v>
       </c>
       <c r="G2" t="n">
-        <v>659.2</v>
+        <v>241.57</v>
       </c>
       <c r="H2" t="n">
-        <v>23.5</v>
+        <v>15.66</v>
       </c>
       <c r="I2" t="n">
-        <v>67.94</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="K2" t="n">
         <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>79.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="N2" t="n">
-        <v>814.1</v>
+        <v>279.4</v>
       </c>
       <c r="O2" t="n">
-        <v>122</v>
+        <v>357</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99320.2</v>
+        <v>99745.8</v>
       </c>
       <c r="R2" t="n">
-        <v>9.93</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>732.6900000000001</v>
+        <v>251.46</v>
       </c>
       <c r="T2" t="n">
-        <v>9932.02</v>
+        <v>9974.58</v>
       </c>
       <c r="U2" t="n">
-        <v>968.78</v>
+        <v>329.69</v>
       </c>
       <c r="V2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>18870.84</v>
+        <v>17954.24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>596.7</v>
+        <v>238.48</v>
       </c>
       <c r="E3" t="n">
-        <v>493.23</v>
+        <v>205.82</v>
       </c>
       <c r="F3" t="n">
-        <v>20.98</v>
+        <v>15.87</v>
       </c>
       <c r="G3" t="n">
-        <v>539</v>
+        <v>245.38</v>
       </c>
       <c r="H3" t="n">
-        <v>10.71</v>
+        <v>-2.81</v>
       </c>
       <c r="I3" t="n">
-        <v>65.02</v>
+        <v>63.09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.25</v>
+        <v>2.37</v>
       </c>
       <c r="K3" t="n">
         <v>70</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>79.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="N3" t="n">
-        <v>596.7</v>
+        <v>238.48</v>
       </c>
       <c r="O3" t="n">
-        <v>167</v>
+        <v>419</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99648.89999999999</v>
+        <v>99923.12</v>
       </c>
       <c r="R3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>537.03</v>
+        <v>214.63</v>
       </c>
       <c r="T3" t="n">
-        <v>9964.889999999999</v>
+        <v>9992.309999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>710.0700000000001</v>
+        <v>286.18</v>
       </c>
       <c r="V3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W3" t="n">
-        <v>18933.29</v>
+        <v>19984.62</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>957.15</v>
+        <v>597.9</v>
       </c>
       <c r="E4" t="n">
-        <v>644.87</v>
+        <v>493.76</v>
       </c>
       <c r="F4" t="n">
-        <v>48.43</v>
+        <v>21.09</v>
       </c>
       <c r="G4" t="n">
-        <v>720</v>
+        <v>539</v>
       </c>
       <c r="H4" t="n">
-        <v>32.94</v>
+        <v>10.93</v>
       </c>
       <c r="I4" t="n">
-        <v>64.95</v>
+        <v>65.45</v>
       </c>
       <c r="J4" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>78.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>957.15</v>
+        <v>597.9</v>
       </c>
       <c r="O4" t="n">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99543.60000000001</v>
+        <v>99849.3</v>
       </c>
       <c r="R4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>861.4400000000001</v>
+        <v>538.11</v>
       </c>
       <c r="T4" t="n">
-        <v>9954.360000000001</v>
+        <v>9984.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1158.15</v>
+        <v>723.46</v>
       </c>
       <c r="V4" t="n">
         <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>20904.16</v>
+        <v>20968.35</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>618.6</v>
+        <v>333.6</v>
       </c>
       <c r="E5" t="n">
-        <v>520.8099999999999</v>
+        <v>244.63</v>
       </c>
       <c r="F5" t="n">
-        <v>18.78</v>
+        <v>36.37</v>
       </c>
       <c r="G5" t="n">
-        <v>570</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>8.529999999999999</v>
+        <v>51.36</v>
       </c>
       <c r="I5" t="n">
-        <v>64.95999999999999</v>
+        <v>60.89</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>0.39</v>
       </c>
       <c r="K5" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>77.5</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>618.6</v>
+        <v>333.6</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>299</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99594.60000000001</v>
+        <v>99746.39999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>556.74</v>
+        <v>300.24</v>
       </c>
       <c r="T5" t="n">
-        <v>9959.459999999999</v>
+        <v>9974.639999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>742.3200000000001</v>
+        <v>393.65</v>
       </c>
       <c r="V5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>19918.92</v>
+        <v>17954.35</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.86</v>
+        <v>85</v>
       </c>
       <c r="E6" t="n">
-        <v>9.609999999999999</v>
+        <v>73.14</v>
       </c>
       <c r="F6" t="n">
-        <v>23.41</v>
+        <v>16.21</v>
       </c>
       <c r="G6" t="n">
-        <v>11.38</v>
+        <v>58.79</v>
       </c>
       <c r="H6" t="n">
-        <v>4.22</v>
+        <v>44.58</v>
       </c>
       <c r="I6" t="n">
-        <v>68.65000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>0.74</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>77</v>
+        <v>76.75</v>
       </c>
       <c r="N6" t="n">
-        <v>11.86</v>
+        <v>85</v>
       </c>
       <c r="O6" t="n">
-        <v>8431</v>
+        <v>1176</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99991.66</v>
+        <v>99960</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>10.67</v>
+        <v>76.5</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.17</v>
+        <v>9996</v>
       </c>
       <c r="U6" t="n">
-        <v>14.35</v>
+        <v>99.45</v>
       </c>
       <c r="V6" t="n">
-        <v>20.99</v>
+        <v>17</v>
       </c>
       <c r="W6" t="n">
-        <v>20988.25</v>
+        <v>16993.2</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>340.1</v>
+        <v>985.3</v>
       </c>
       <c r="E7" t="n">
-        <v>243.84</v>
+        <v>647.29</v>
       </c>
       <c r="F7" t="n">
-        <v>39.48</v>
+        <v>52.22</v>
       </c>
       <c r="G7" t="n">
-        <v>220.4</v>
+        <v>720</v>
       </c>
       <c r="H7" t="n">
-        <v>54.31</v>
+        <v>36.85</v>
       </c>
       <c r="I7" t="n">
-        <v>67.16</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.67</v>
+        <v>1.39</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>76.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>340.1</v>
+        <v>985.3</v>
       </c>
       <c r="O7" t="n">
-        <v>294</v>
+        <v>101</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99989.39999999999</v>
+        <v>99515.3</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>306.09</v>
+        <v>886.77</v>
       </c>
       <c r="T7" t="n">
-        <v>9998.940000000001</v>
+        <v>9951.530000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>401.32</v>
+        <v>1172.51</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>17998.09</v>
+        <v>18907.91</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85.95</v>
+        <v>1114.2</v>
       </c>
       <c r="E8" t="n">
-        <v>73.02</v>
+        <v>1054.95</v>
       </c>
       <c r="F8" t="n">
-        <v>17.71</v>
+        <v>5.62</v>
       </c>
       <c r="G8" t="n">
-        <v>58.79</v>
+        <v>1128.1</v>
       </c>
       <c r="H8" t="n">
-        <v>46.2</v>
+        <v>-1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>62.05</v>
+        <v>53.31</v>
       </c>
       <c r="J8" t="n">
-        <v>0.84</v>
+        <v>2.85</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>68.75</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="M8" t="n">
-        <v>76.75</v>
+        <v>75.25</v>
       </c>
       <c r="N8" t="n">
-        <v>85.95</v>
+        <v>1114.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1163</v>
+        <v>89</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99959.85000000001</v>
+        <v>99163.8</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="S8" t="n">
-        <v>77.36</v>
+        <v>1002.78</v>
       </c>
       <c r="T8" t="n">
-        <v>9995.98</v>
+        <v>9916.379999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>100.56</v>
+        <v>1292.47</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>16993.17</v>
+        <v>15866.21</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1149,68 +1149,68 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62.81</v>
+        <v>62.17</v>
       </c>
       <c r="E9" t="n">
-        <v>49.72</v>
+        <v>49.73</v>
       </c>
       <c r="F9" t="n">
-        <v>26.32</v>
+        <v>25.02</v>
       </c>
       <c r="G9" t="n">
         <v>62.84</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.05</v>
+        <v>-1.07</v>
       </c>
       <c r="I9" t="n">
-        <v>75.44</v>
+        <v>72.87</v>
       </c>
       <c r="J9" t="n">
-        <v>3.16</v>
+        <v>1.06</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
+        <v>58.75</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>76</v>
+        <v>75.25</v>
       </c>
       <c r="N9" t="n">
-        <v>62.81</v>
+        <v>62.17</v>
       </c>
       <c r="O9" t="n">
-        <v>1592</v>
+        <v>1608</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99993.52</v>
+        <v>99969.36</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>56.53</v>
+        <v>55.95</v>
       </c>
       <c r="T9" t="n">
-        <v>9999.35</v>
+        <v>9996.940000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>72.86</v>
+        <v>71.5</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>15.01</v>
       </c>
       <c r="W9" t="n">
-        <v>15998.96</v>
+        <v>15005.4</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89.04000000000001</v>
+        <v>135.89</v>
       </c>
       <c r="E10" t="n">
-        <v>86.5</v>
+        <v>103.74</v>
       </c>
       <c r="F10" t="n">
-        <v>2.94</v>
+        <v>30.99</v>
       </c>
       <c r="G10" t="n">
-        <v>53</v>
+        <v>133.9</v>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>40.78</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>7.28</v>
+        <v>2.46</v>
       </c>
       <c r="K10" t="n">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M10" t="n">
-        <v>75.95</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>89.04000000000001</v>
+        <v>135.89</v>
       </c>
       <c r="O10" t="n">
-        <v>1123</v>
+        <v>735</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99991.92</v>
+        <v>99879.14999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>80.14</v>
+        <v>122.3</v>
       </c>
       <c r="T10" t="n">
-        <v>9999.190000000001</v>
+        <v>9987.92</v>
       </c>
       <c r="U10" t="n">
-        <v>107.74</v>
+        <v>161.71</v>
       </c>
       <c r="V10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>20998.3</v>
+        <v>18977.04</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>236.01</v>
+        <v>805.1</v>
       </c>
       <c r="E11" t="n">
-        <v>205.62</v>
+        <v>550</v>
       </c>
       <c r="F11" t="n">
-        <v>14.78</v>
+        <v>46.38</v>
       </c>
       <c r="G11" t="n">
-        <v>245.38</v>
+        <v>659.2</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.82</v>
+        <v>22.13</v>
       </c>
       <c r="I11" t="n">
-        <v>61.53</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>0.64</v>
       </c>
       <c r="K11" t="n">
-        <v>58.75</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>75.25</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>236.01</v>
+        <v>805.1</v>
       </c>
       <c r="O11" t="n">
-        <v>423</v>
+        <v>124</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99832.23</v>
+        <v>99832.39999999999</v>
       </c>
       <c r="R11" t="n">
         <v>9.98</v>
       </c>
       <c r="S11" t="n">
-        <v>212.41</v>
+        <v>724.59</v>
       </c>
       <c r="T11" t="n">
-        <v>9983.219999999999</v>
+        <v>9983.24</v>
       </c>
       <c r="U11" t="n">
-        <v>276.13</v>
+        <v>950.02</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>16971.48</v>
+        <v>17969.83</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>279.4</v>
+        <v>60.17</v>
       </c>
       <c r="E2" t="n">
-        <v>209.71</v>
+        <v>49.72</v>
       </c>
       <c r="F2" t="n">
-        <v>33.23</v>
+        <v>21.02</v>
       </c>
       <c r="G2" t="n">
-        <v>241.57</v>
+        <v>62.84</v>
       </c>
       <c r="H2" t="n">
-        <v>15.66</v>
+        <v>-4.25</v>
       </c>
       <c r="I2" t="n">
-        <v>72.59999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N2" t="n">
-        <v>279.4</v>
+        <v>60.17</v>
       </c>
       <c r="O2" t="n">
-        <v>357</v>
+        <v>1661</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99745.8</v>
+        <v>99942.37</v>
       </c>
       <c r="R2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>251.46</v>
+        <v>54.15</v>
       </c>
       <c r="T2" t="n">
-        <v>9974.58</v>
+        <v>9994.24</v>
       </c>
       <c r="U2" t="n">
-        <v>329.69</v>
+        <v>72.81</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>21.01</v>
       </c>
       <c r="W2" t="n">
-        <v>17954.24</v>
+        <v>20997.89</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>238.48</v>
+        <v>264.26</v>
       </c>
       <c r="E3" t="n">
-        <v>205.82</v>
+        <v>211.38</v>
       </c>
       <c r="F3" t="n">
-        <v>15.87</v>
+        <v>25.02</v>
       </c>
       <c r="G3" t="n">
-        <v>245.38</v>
+        <v>249</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.81</v>
+        <v>6.13</v>
       </c>
       <c r="I3" t="n">
-        <v>63.09</v>
+        <v>59.54</v>
       </c>
       <c r="J3" t="n">
-        <v>2.37</v>
+        <v>0.49</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>82</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>238.48</v>
+        <v>264.26</v>
       </c>
       <c r="O3" t="n">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99923.12</v>
+        <v>99890.28</v>
       </c>
       <c r="R3" t="n">
         <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>214.63</v>
+        <v>237.83</v>
       </c>
       <c r="T3" t="n">
-        <v>9992.309999999999</v>
+        <v>9989.030000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>286.18</v>
+        <v>311.83</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>19984.62</v>
+        <v>17980.25</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>597.9</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>493.76</v>
+        <v>73.27</v>
       </c>
       <c r="F4" t="n">
-        <v>21.09</v>
+        <v>15.72</v>
       </c>
       <c r="G4" t="n">
-        <v>539</v>
+        <v>58.79</v>
       </c>
       <c r="H4" t="n">
-        <v>10.93</v>
+        <v>44.23</v>
       </c>
       <c r="I4" t="n">
-        <v>65.45</v>
+        <v>57.59</v>
       </c>
       <c r="J4" t="n">
-        <v>1.87</v>
+        <v>0.62</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>81.09999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N4" t="n">
-        <v>597.9</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>1179</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99849.3</v>
+        <v>99967.41</v>
       </c>
       <c r="R4" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>538.11</v>
+        <v>76.31</v>
       </c>
       <c r="T4" t="n">
-        <v>9984.93</v>
+        <v>9996.74</v>
       </c>
       <c r="U4" t="n">
-        <v>723.46</v>
+        <v>99.2</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>16.99</v>
       </c>
       <c r="W4" t="n">
-        <v>20968.35</v>
+        <v>16984.46</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>333.6</v>
+        <v>740.55</v>
       </c>
       <c r="E5" t="n">
-        <v>244.63</v>
+        <v>629.55</v>
       </c>
       <c r="F5" t="n">
-        <v>36.37</v>
+        <v>17.63</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>629.9</v>
       </c>
       <c r="H5" t="n">
-        <v>51.36</v>
+        <v>17.57</v>
       </c>
       <c r="I5" t="n">
-        <v>60.89</v>
+        <v>44.72</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39</v>
+        <v>2.57</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>333.6</v>
+        <v>740.55</v>
       </c>
       <c r="O5" t="n">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99746.39999999999</v>
+        <v>99974.25</v>
       </c>
       <c r="R5" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>300.24</v>
+        <v>666.5</v>
       </c>
       <c r="T5" t="n">
-        <v>9974.639999999999</v>
+        <v>9997.42</v>
       </c>
       <c r="U5" t="n">
-        <v>393.65</v>
+        <v>866.4400000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>17954.35</v>
+        <v>16995.62</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>85</v>
+        <v>141.44</v>
       </c>
       <c r="E6" t="n">
-        <v>73.14</v>
+        <v>95.23</v>
       </c>
       <c r="F6" t="n">
-        <v>16.21</v>
+        <v>48.52</v>
       </c>
       <c r="G6" t="n">
-        <v>58.79</v>
+        <v>114</v>
       </c>
       <c r="H6" t="n">
-        <v>44.58</v>
+        <v>24.07</v>
       </c>
       <c r="I6" t="n">
-        <v>58.4</v>
+        <v>64.36</v>
       </c>
       <c r="J6" t="n">
-        <v>0.74</v>
+        <v>0.08</v>
       </c>
       <c r="K6" t="n">
         <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>76.75</v>
+        <v>73.55</v>
       </c>
       <c r="N6" t="n">
-        <v>85</v>
+        <v>141.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1176</v>
+        <v>707</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99960</v>
+        <v>99998.08</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>76.5</v>
+        <v>127.3</v>
       </c>
       <c r="T6" t="n">
-        <v>9996</v>
+        <v>9999.809999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>99.45</v>
+        <v>166.9</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>16993.2</v>
+        <v>17999.65</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>985.3</v>
+        <v>19.88</v>
       </c>
       <c r="E7" t="n">
-        <v>647.29</v>
+        <v>15.2</v>
       </c>
       <c r="F7" t="n">
-        <v>52.22</v>
+        <v>30.81</v>
       </c>
       <c r="G7" t="n">
-        <v>720</v>
+        <v>17.4</v>
       </c>
       <c r="H7" t="n">
-        <v>36.85</v>
+        <v>14.25</v>
       </c>
       <c r="I7" t="n">
-        <v>67.29000000000001</v>
+        <v>53.53</v>
       </c>
       <c r="J7" t="n">
-        <v>1.39</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>57.5</v>
       </c>
       <c r="L7" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>75.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>985.3</v>
+        <v>19.88</v>
       </c>
       <c r="O7" t="n">
-        <v>101</v>
+        <v>5030</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99515.3</v>
+        <v>99996.39999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>886.77</v>
+        <v>17.89</v>
       </c>
       <c r="T7" t="n">
-        <v>9951.530000000001</v>
+        <v>9999.639999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1172.51</v>
+        <v>22.86</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>14.99</v>
       </c>
       <c r="W7" t="n">
-        <v>18907.91</v>
+        <v>14989.46</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>RADHIKAJWE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1114.2</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1054.95</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>5.62</v>
+        <v>32.46</v>
       </c>
       <c r="G8" t="n">
-        <v>1128.1</v>
+        <v>85.06</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.23</v>
+        <v>3.41</v>
       </c>
       <c r="I8" t="n">
-        <v>53.31</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="K8" t="n">
-        <v>68.75</v>
+        <v>70</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>75.25</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>1114.2</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>89</v>
+        <v>1136</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99163.8</v>
+        <v>99922.56</v>
       </c>
       <c r="R8" t="n">
-        <v>9.92</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>1002.78</v>
+        <v>79.16</v>
       </c>
       <c r="T8" t="n">
-        <v>9916.379999999999</v>
+        <v>9992.26</v>
       </c>
       <c r="U8" t="n">
-        <v>1292.47</v>
+        <v>102.03</v>
       </c>
       <c r="V8" t="n">
         <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>15866.21</v>
+        <v>15987.61</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62.17</v>
+        <v>344.15</v>
       </c>
       <c r="E9" t="n">
-        <v>49.73</v>
+        <v>298.55</v>
       </c>
       <c r="F9" t="n">
-        <v>25.02</v>
+        <v>15.28</v>
       </c>
       <c r="G9" t="n">
-        <v>62.84</v>
+        <v>220</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.07</v>
+        <v>56.43</v>
       </c>
       <c r="I9" t="n">
-        <v>72.87</v>
+        <v>45.43</v>
       </c>
       <c r="J9" t="n">
-        <v>1.06</v>
+        <v>0.74</v>
       </c>
       <c r="K9" t="n">
-        <v>58.75</v>
+        <v>52.5</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>75.25</v>
+        <v>71.5</v>
       </c>
       <c r="N9" t="n">
-        <v>62.17</v>
+        <v>344.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1608</v>
+        <v>290</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99969.36</v>
+        <v>99803.5</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S9" t="n">
-        <v>55.95</v>
+        <v>309.74</v>
       </c>
       <c r="T9" t="n">
-        <v>9996.940000000001</v>
+        <v>9980.35</v>
       </c>
       <c r="U9" t="n">
-        <v>71.5</v>
+        <v>392.33</v>
       </c>
       <c r="V9" t="n">
-        <v>15.01</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>15005.4</v>
+        <v>13972.49</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>INDNIPPON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>135.89</v>
+        <v>1122.3</v>
       </c>
       <c r="E10" t="n">
-        <v>103.74</v>
+        <v>886.72</v>
       </c>
       <c r="F10" t="n">
-        <v>30.99</v>
+        <v>26.57</v>
       </c>
       <c r="G10" t="n">
-        <v>133.9</v>
+        <v>1099.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="I10" t="n">
-        <v>66.65000000000001</v>
+        <v>53.27</v>
       </c>
       <c r="J10" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>71.25</v>
       </c>
       <c r="L10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M10" t="n">
-        <v>74.59999999999999</v>
+        <v>70.75</v>
       </c>
       <c r="N10" t="n">
-        <v>135.89</v>
+        <v>1122.3</v>
       </c>
       <c r="O10" t="n">
-        <v>735</v>
+        <v>89</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99879.14999999999</v>
+        <v>99884.7</v>
       </c>
       <c r="R10" t="n">
         <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>122.3</v>
+        <v>1010.07</v>
       </c>
       <c r="T10" t="n">
-        <v>9987.92</v>
+        <v>9988.469999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>161.71</v>
+        <v>1301.87</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>18977.04</v>
+        <v>15981.55</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>805.1</v>
+        <v>368.5</v>
       </c>
       <c r="E11" t="n">
-        <v>550</v>
+        <v>322.39</v>
       </c>
       <c r="F11" t="n">
-        <v>46.38</v>
+        <v>14.3</v>
       </c>
       <c r="G11" t="n">
-        <v>659.2</v>
+        <v>386</v>
       </c>
       <c r="H11" t="n">
-        <v>22.13</v>
+        <v>-4.53</v>
       </c>
       <c r="I11" t="n">
-        <v>65.43000000000001</v>
+        <v>54.57</v>
       </c>
       <c r="J11" t="n">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>50</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>74.34999999999999</v>
+        <v>70</v>
       </c>
       <c r="N11" t="n">
-        <v>805.1</v>
+        <v>368.5</v>
       </c>
       <c r="O11" t="n">
-        <v>124</v>
+        <v>271</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99832.39999999999</v>
+        <v>99863.5</v>
       </c>
       <c r="R11" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>724.59</v>
+        <v>331.65</v>
       </c>
       <c r="T11" t="n">
-        <v>9983.24</v>
+        <v>9986.35</v>
       </c>
       <c r="U11" t="n">
-        <v>950.02</v>
+        <v>420.09</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>17969.83</v>
+        <v>13980.89</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60.17</v>
+        <v>1353.4</v>
       </c>
       <c r="E2" t="n">
-        <v>49.72</v>
+        <v>952.3200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>21.02</v>
+        <v>42.12</v>
       </c>
       <c r="G2" t="n">
-        <v>62.84</v>
+        <v>993.8</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.25</v>
+        <v>36.18</v>
       </c>
       <c r="I2" t="n">
-        <v>65.84</v>
+        <v>63.97</v>
       </c>
       <c r="J2" t="n">
-        <v>1.77</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M2" t="n">
-        <v>79</v>
+        <v>80.2</v>
       </c>
       <c r="N2" t="n">
-        <v>60.17</v>
+        <v>1353.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1661</v>
+        <v>73</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99942.37</v>
+        <v>98798.2</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>54.15</v>
+        <v>1218.06</v>
       </c>
       <c r="T2" t="n">
-        <v>9994.24</v>
+        <v>9879.82</v>
       </c>
       <c r="U2" t="n">
-        <v>72.81</v>
+        <v>1637.61</v>
       </c>
       <c r="V2" t="n">
-        <v>21.01</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>20997.89</v>
+        <v>20747.62</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>264.26</v>
+        <v>133.56</v>
       </c>
       <c r="E3" t="n">
-        <v>211.38</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>25.02</v>
+        <v>37.09</v>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>108.59</v>
       </c>
       <c r="H3" t="n">
-        <v>6.13</v>
+        <v>22.99</v>
       </c>
       <c r="I3" t="n">
-        <v>59.54</v>
+        <v>63.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.49</v>
+        <v>1.37</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>78.8</v>
       </c>
       <c r="N3" t="n">
-        <v>264.26</v>
+        <v>133.56</v>
       </c>
       <c r="O3" t="n">
-        <v>378</v>
+        <v>748</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99890.28</v>
+        <v>99902.88</v>
       </c>
       <c r="R3" t="n">
         <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>237.83</v>
+        <v>120.2</v>
       </c>
       <c r="T3" t="n">
-        <v>9989.030000000001</v>
+        <v>9990.290000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>311.83</v>
+        <v>158.94</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
-        <v>17980.25</v>
+        <v>18981.55</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,34 +719,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84.79000000000001</v>
+        <v>331.25</v>
       </c>
       <c r="E4" t="n">
-        <v>73.27</v>
+        <v>246.02</v>
       </c>
       <c r="F4" t="n">
-        <v>15.72</v>
+        <v>34.64</v>
       </c>
       <c r="G4" t="n">
-        <v>58.79</v>
+        <v>220.4</v>
       </c>
       <c r="H4" t="n">
-        <v>44.23</v>
+        <v>50.29</v>
       </c>
       <c r="I4" t="n">
-        <v>57.59</v>
+        <v>58.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="K4" t="n">
         <v>61.25</v>
@@ -758,34 +758,34 @@
         <v>76.75</v>
       </c>
       <c r="N4" t="n">
-        <v>84.79000000000001</v>
+        <v>331.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1179</v>
+        <v>301</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99967.41</v>
+        <v>99706.25</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>76.31</v>
+        <v>298.12</v>
       </c>
       <c r="T4" t="n">
-        <v>9996.74</v>
+        <v>9970.620000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>99.2</v>
+        <v>390.88</v>
       </c>
       <c r="V4" t="n">
-        <v>16.99</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>16984.46</v>
+        <v>17947.12</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>740.55</v>
+        <v>84.56</v>
       </c>
       <c r="E5" t="n">
-        <v>629.55</v>
+        <v>73.41</v>
       </c>
       <c r="F5" t="n">
-        <v>17.63</v>
+        <v>15.2</v>
       </c>
       <c r="G5" t="n">
-        <v>629.9</v>
+        <v>58.79</v>
       </c>
       <c r="H5" t="n">
-        <v>17.57</v>
+        <v>43.83</v>
       </c>
       <c r="I5" t="n">
-        <v>44.72</v>
+        <v>56.66</v>
       </c>
       <c r="J5" t="n">
-        <v>2.57</v>
+        <v>0.74</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>74.34999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>740.55</v>
+        <v>84.56</v>
       </c>
       <c r="O5" t="n">
-        <v>135</v>
+        <v>1182</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99974.25</v>
+        <v>99949.92</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>666.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>9997.42</v>
+        <v>9994.99</v>
       </c>
       <c r="U5" t="n">
-        <v>866.4400000000001</v>
+        <v>98.94</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>17.01</v>
       </c>
       <c r="W5" t="n">
-        <v>16995.62</v>
+        <v>17001.48</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>JMA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>141.44</v>
+        <v>97.14</v>
       </c>
       <c r="E6" t="n">
-        <v>95.23</v>
+        <v>85.47</v>
       </c>
       <c r="F6" t="n">
-        <v>48.52</v>
+        <v>13.65</v>
       </c>
       <c r="G6" t="n">
-        <v>114</v>
+        <v>97.5</v>
       </c>
       <c r="H6" t="n">
-        <v>24.07</v>
+        <v>-0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>64.36</v>
+        <v>63.41</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08</v>
+        <v>5.05</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>73.75</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>73.55</v>
+        <v>75.45</v>
       </c>
       <c r="N6" t="n">
-        <v>141.44</v>
+        <v>97.14</v>
       </c>
       <c r="O6" t="n">
-        <v>707</v>
+        <v>1029</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99998.08</v>
+        <v>99957.06</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>127.3</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.809999999999</v>
+        <v>9995.709999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>166.9</v>
+        <v>114.63</v>
       </c>
       <c r="V6" t="n">
         <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>17999.65</v>
+        <v>17992.27</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.88</v>
+        <v>1128.7</v>
       </c>
       <c r="E7" t="n">
-        <v>15.2</v>
+        <v>1055.6</v>
       </c>
       <c r="F7" t="n">
-        <v>30.81</v>
+        <v>6.92</v>
       </c>
       <c r="G7" t="n">
-        <v>17.4</v>
+        <v>1128.1</v>
       </c>
       <c r="H7" t="n">
-        <v>14.25</v>
+        <v>0.05</v>
       </c>
       <c r="I7" t="n">
-        <v>53.53</v>
+        <v>54.71</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="K7" t="n">
-        <v>57.5</v>
+        <v>68.75</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>72.09999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="N7" t="n">
-        <v>19.88</v>
+        <v>1128.7</v>
       </c>
       <c r="O7" t="n">
-        <v>5030</v>
+        <v>88</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99996.39999999999</v>
+        <v>99325.60000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="S7" t="n">
-        <v>17.89</v>
+        <v>1015.83</v>
       </c>
       <c r="T7" t="n">
-        <v>9999.639999999999</v>
+        <v>9932.559999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>22.86</v>
+        <v>1309.29</v>
       </c>
       <c r="V7" t="n">
-        <v>14.99</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>14989.46</v>
+        <v>15892.1</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RADHIKAJWE</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.95999999999999</v>
+        <v>574.6</v>
       </c>
       <c r="E8" t="n">
-        <v>66.40000000000001</v>
+        <v>494.68</v>
       </c>
       <c r="F8" t="n">
-        <v>32.46</v>
+        <v>16.16</v>
       </c>
       <c r="G8" t="n">
-        <v>85.06</v>
+        <v>539</v>
       </c>
       <c r="H8" t="n">
-        <v>3.41</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>70.04000000000001</v>
+        <v>51.52</v>
       </c>
       <c r="J8" t="n">
-        <v>2.35</v>
+        <v>1.15</v>
       </c>
       <c r="K8" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>71.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>87.95999999999999</v>
+        <v>574.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1136</v>
+        <v>174</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99922.56</v>
+        <v>99980.39999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>79.16</v>
+        <v>517.14</v>
       </c>
       <c r="T8" t="n">
-        <v>9992.26</v>
+        <v>9998.040000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>102.03</v>
+        <v>655.04</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>15987.61</v>
+        <v>13997.26</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>344.15</v>
+        <v>803</v>
       </c>
       <c r="E9" t="n">
-        <v>298.55</v>
+        <v>551.1900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>15.28</v>
+        <v>45.68</v>
       </c>
       <c r="G9" t="n">
-        <v>220</v>
+        <v>659.2</v>
       </c>
       <c r="H9" t="n">
-        <v>56.43</v>
+        <v>21.81</v>
       </c>
       <c r="I9" t="n">
-        <v>45.43</v>
+        <v>64.62</v>
       </c>
       <c r="J9" t="n">
-        <v>0.74</v>
+        <v>0.32</v>
       </c>
       <c r="K9" t="n">
-        <v>52.5</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>71.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>344.15</v>
+        <v>803</v>
       </c>
       <c r="O9" t="n">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99803.5</v>
+        <v>99572</v>
       </c>
       <c r="R9" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>309.74</v>
+        <v>722.7</v>
       </c>
       <c r="T9" t="n">
-        <v>9980.35</v>
+        <v>9957.200000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>392.33</v>
+        <v>947.54</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>13972.49</v>
+        <v>17922.96</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INDNIPPON</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1122.3</v>
+        <v>1389.1</v>
       </c>
       <c r="E10" t="n">
-        <v>886.72</v>
+        <v>1356.13</v>
       </c>
       <c r="F10" t="n">
-        <v>26.57</v>
+        <v>2.43</v>
       </c>
       <c r="G10" t="n">
-        <v>1099.9</v>
+        <v>1445</v>
       </c>
       <c r="H10" t="n">
-        <v>2.04</v>
+        <v>-3.87</v>
       </c>
       <c r="I10" t="n">
-        <v>53.27</v>
+        <v>39.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="K10" t="n">
-        <v>71.25</v>
+        <v>67.5</v>
       </c>
       <c r="L10" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>70.75</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>1122.3</v>
+        <v>1389.1</v>
       </c>
       <c r="O10" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99884.7</v>
+        <v>98626.10000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>1010.07</v>
+        <v>1250.19</v>
       </c>
       <c r="T10" t="n">
-        <v>9988.469999999999</v>
+        <v>9862.610000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1301.87</v>
+        <v>1680.81</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W10" t="n">
-        <v>15981.55</v>
+        <v>20711.48</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>368.5</v>
+        <v>15.52</v>
       </c>
       <c r="E11" t="n">
-        <v>322.39</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>14.3</v>
+        <v>29.37</v>
       </c>
       <c r="G11" t="n">
-        <v>386</v>
+        <v>12.8</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.53</v>
+        <v>21.25</v>
       </c>
       <c r="I11" t="n">
-        <v>54.57</v>
+        <v>66.09</v>
       </c>
       <c r="J11" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="K11" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N11" t="n">
-        <v>368.5</v>
+        <v>15.52</v>
       </c>
       <c r="O11" t="n">
-        <v>271</v>
+        <v>6443</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99863.5</v>
+        <v>99995.36</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>331.65</v>
+        <v>13.97</v>
       </c>
       <c r="T11" t="n">
-        <v>9986.35</v>
+        <v>9999.540000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>420.09</v>
+        <v>18.47</v>
       </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>19.01</v>
       </c>
       <c r="W11" t="n">
-        <v>13980.89</v>
+        <v>19009.12</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1353.4</v>
+        <v>756.55</v>
       </c>
       <c r="E2" t="n">
-        <v>952.3200000000001</v>
+        <v>631.97</v>
       </c>
       <c r="F2" t="n">
-        <v>42.12</v>
+        <v>19.71</v>
       </c>
       <c r="G2" t="n">
-        <v>993.8</v>
+        <v>629.9</v>
       </c>
       <c r="H2" t="n">
-        <v>36.18</v>
+        <v>20.11</v>
       </c>
       <c r="I2" t="n">
-        <v>63.97</v>
+        <v>50.51</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>1.27</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>80.2</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>1353.4</v>
+        <v>756.55</v>
       </c>
       <c r="O2" t="n">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>98798.2</v>
+        <v>99864.60000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1218.06</v>
+        <v>680.9</v>
       </c>
       <c r="T2" t="n">
-        <v>9879.82</v>
+        <v>9986.459999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1637.61</v>
+        <v>870.03</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>20747.62</v>
+        <v>14979.69</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>LAMBODHARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>133.56</v>
+        <v>137.22</v>
       </c>
       <c r="E3" t="n">
-        <v>97.43000000000001</v>
+        <v>112.4</v>
       </c>
       <c r="F3" t="n">
-        <v>37.09</v>
+        <v>22.09</v>
       </c>
       <c r="G3" t="n">
-        <v>108.59</v>
+        <v>136.41</v>
       </c>
       <c r="H3" t="n">
-        <v>22.99</v>
+        <v>0.59</v>
       </c>
       <c r="I3" t="n">
-        <v>63.15</v>
+        <v>60.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.37</v>
+        <v>0.19</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>78.8</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>133.56</v>
+        <v>137.22</v>
       </c>
       <c r="O3" t="n">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99902.88</v>
+        <v>99896.16</v>
       </c>
       <c r="R3" t="n">
         <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>120.2</v>
+        <v>123.5</v>
       </c>
       <c r="T3" t="n">
-        <v>9990.290000000001</v>
+        <v>9989.620000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>158.94</v>
+        <v>161.92</v>
       </c>
       <c r="V3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>18981.55</v>
+        <v>17981.31</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>331.25</v>
+        <v>346</v>
       </c>
       <c r="E4" t="n">
-        <v>246.02</v>
+        <v>299.48</v>
       </c>
       <c r="F4" t="n">
-        <v>34.64</v>
+        <v>15.53</v>
       </c>
       <c r="G4" t="n">
-        <v>220.4</v>
+        <v>220</v>
       </c>
       <c r="H4" t="n">
-        <v>50.29</v>
+        <v>57.27</v>
       </c>
       <c r="I4" t="n">
-        <v>58.4</v>
+        <v>47.36</v>
       </c>
       <c r="J4" t="n">
-        <v>0.68</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>57.5</v>
       </c>
       <c r="L4" t="n">
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>76.75</v>
+        <v>74.5</v>
       </c>
       <c r="N4" t="n">
-        <v>331.25</v>
+        <v>346</v>
       </c>
       <c r="O4" t="n">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99706.25</v>
+        <v>99994</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>298.12</v>
+        <v>311.4</v>
       </c>
       <c r="T4" t="n">
-        <v>9970.620000000001</v>
+        <v>9999.4</v>
       </c>
       <c r="U4" t="n">
-        <v>390.88</v>
+        <v>394.44</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W4" t="n">
-        <v>17947.12</v>
+        <v>13999.16</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>84.56</v>
+        <v>141.08</v>
       </c>
       <c r="E5" t="n">
-        <v>73.41</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>15.2</v>
+        <v>47.44</v>
       </c>
       <c r="G5" t="n">
-        <v>58.79</v>
+        <v>114</v>
       </c>
       <c r="H5" t="n">
-        <v>43.83</v>
+        <v>23.75</v>
       </c>
       <c r="I5" t="n">
-        <v>56.66</v>
+        <v>62.36</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>73.55</v>
       </c>
       <c r="N5" t="n">
-        <v>84.56</v>
+        <v>141.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1182</v>
+        <v>708</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99949.92</v>
+        <v>99884.64</v>
       </c>
       <c r="R5" t="n">
         <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>76.09999999999999</v>
+        <v>126.97</v>
       </c>
       <c r="T5" t="n">
-        <v>9994.99</v>
+        <v>9988.459999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>98.94</v>
+        <v>166.47</v>
       </c>
       <c r="V5" t="n">
-        <v>17.01</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>17001.48</v>
+        <v>17979.24</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JMA</t>
+          <t>STEELCITY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>97.14</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>85.47</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>13.65</v>
+        <v>9.41</v>
       </c>
       <c r="G6" t="n">
-        <v>97.5</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.37</v>
+        <v>-4.78</v>
       </c>
       <c r="I6" t="n">
-        <v>63.41</v>
+        <v>65.86</v>
       </c>
       <c r="J6" t="n">
-        <v>5.05</v>
+        <v>7.28</v>
       </c>
       <c r="K6" t="n">
-        <v>73.75</v>
+        <v>67.5</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>75.45</v>
+        <v>72.5</v>
       </c>
       <c r="N6" t="n">
-        <v>97.14</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>1029</v>
+        <v>1094</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99957.06</v>
+        <v>99991.60000000001</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>87.43000000000001</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>9995.709999999999</v>
+        <v>9999.16</v>
       </c>
       <c r="U6" t="n">
-        <v>114.63</v>
+        <v>108.77</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>17992.27</v>
+        <v>18998.4</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1128.7</v>
+        <v>370.05</v>
       </c>
       <c r="E7" t="n">
-        <v>1055.6</v>
+        <v>322.39</v>
       </c>
       <c r="F7" t="n">
-        <v>6.92</v>
+        <v>14.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1128.1</v>
+        <v>386</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>-4.13</v>
       </c>
       <c r="I7" t="n">
-        <v>54.71</v>
+        <v>55.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.52</v>
+        <v>0.71</v>
       </c>
       <c r="K7" t="n">
-        <v>68.75</v>
+        <v>53.75</v>
       </c>
       <c r="L7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>75.25</v>
+        <v>72.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1128.7</v>
+        <v>370.05</v>
       </c>
       <c r="O7" t="n">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99325.60000000001</v>
+        <v>99913.5</v>
       </c>
       <c r="R7" t="n">
-        <v>9.93</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>1015.83</v>
+        <v>333.04</v>
       </c>
       <c r="T7" t="n">
-        <v>9932.559999999999</v>
+        <v>9991.35</v>
       </c>
       <c r="U7" t="n">
-        <v>1309.29</v>
+        <v>432.96</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W7" t="n">
-        <v>15892.1</v>
+        <v>16985.29</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ANUHPHR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>574.6</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>494.68</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>16.16</v>
+        <v>16.2</v>
       </c>
       <c r="G8" t="n">
-        <v>539</v>
+        <v>86.81</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>5.07</v>
       </c>
       <c r="I8" t="n">
-        <v>51.52</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="K8" t="n">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="M8" t="n">
-        <v>75.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="N8" t="n">
-        <v>574.6</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>174</v>
+        <v>1096</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99980.39999999999</v>
+        <v>99966.16</v>
       </c>
       <c r="R8" t="n">
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>517.14</v>
+        <v>82.09</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.040000000001</v>
+        <v>9996.620000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>655.04</v>
+        <v>107.63</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>13997.26</v>
+        <v>17993.91</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>WENDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>803</v>
+        <v>8669.5</v>
       </c>
       <c r="E9" t="n">
-        <v>551.1900000000001</v>
+        <v>7411.08</v>
       </c>
       <c r="F9" t="n">
-        <v>45.68</v>
+        <v>16.98</v>
       </c>
       <c r="G9" t="n">
-        <v>659.2</v>
+        <v>8740</v>
       </c>
       <c r="H9" t="n">
-        <v>21.81</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>64.62</v>
+        <v>62.67</v>
       </c>
       <c r="J9" t="n">
-        <v>0.32</v>
+        <v>7.75</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>73.75</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>71.45</v>
       </c>
       <c r="N9" t="n">
-        <v>803</v>
+        <v>8669.5</v>
       </c>
       <c r="O9" t="n">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99572</v>
+        <v>95364.5</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>722.7</v>
+        <v>7802.55</v>
       </c>
       <c r="T9" t="n">
-        <v>9957.200000000001</v>
+        <v>9536.450000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>947.54</v>
+        <v>10230.01</v>
       </c>
       <c r="V9" t="n">
         <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>17922.96</v>
+        <v>17165.61</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1389.1</v>
+        <v>1127.7</v>
       </c>
       <c r="E10" t="n">
-        <v>1356.13</v>
+        <v>1056.09</v>
       </c>
       <c r="F10" t="n">
-        <v>2.43</v>
+        <v>6.78</v>
       </c>
       <c r="G10" t="n">
-        <v>1445</v>
+        <v>1128.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.87</v>
+        <v>-0.04</v>
       </c>
       <c r="I10" t="n">
-        <v>39.6</v>
+        <v>54.51</v>
       </c>
       <c r="J10" t="n">
-        <v>1.59</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>67.5</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>74.09999999999999</v>
+        <v>70.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1389.1</v>
+        <v>1127.7</v>
       </c>
       <c r="O10" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>98626.10000000001</v>
+        <v>99237.60000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>9.859999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="S10" t="n">
-        <v>1250.19</v>
+        <v>1014.93</v>
       </c>
       <c r="T10" t="n">
-        <v>9862.610000000001</v>
+        <v>9923.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1680.81</v>
+        <v>1274.3</v>
       </c>
       <c r="V10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
-        <v>20711.48</v>
+        <v>12900.89</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>NRAIL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.52</v>
+        <v>595.3</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>463.16</v>
       </c>
       <c r="F11" t="n">
-        <v>29.37</v>
+        <v>28.53</v>
       </c>
       <c r="G11" t="n">
-        <v>12.8</v>
+        <v>519</v>
       </c>
       <c r="H11" t="n">
-        <v>21.25</v>
+        <v>14.7</v>
       </c>
       <c r="I11" t="n">
-        <v>66.09</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="M11" t="n">
-        <v>74</v>
+        <v>70.7</v>
       </c>
       <c r="N11" t="n">
-        <v>15.52</v>
+        <v>595.3</v>
       </c>
       <c r="O11" t="n">
-        <v>6443</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99995.36</v>
+        <v>99415.10000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>13.97</v>
+        <v>535.77</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.540000000001</v>
+        <v>9941.51</v>
       </c>
       <c r="U11" t="n">
-        <v>18.47</v>
+        <v>708.41</v>
       </c>
       <c r="V11" t="n">
-        <v>19.01</v>
+        <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>19009.12</v>
+        <v>18888.87</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>756.55</v>
+        <v>84.2</v>
       </c>
       <c r="E2" t="n">
-        <v>631.97</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>19.71</v>
+        <v>14.32</v>
       </c>
       <c r="G2" t="n">
-        <v>629.9</v>
+        <v>58.79</v>
       </c>
       <c r="H2" t="n">
-        <v>20.11</v>
+        <v>43.22</v>
       </c>
       <c r="I2" t="n">
-        <v>50.51</v>
+        <v>55.13</v>
       </c>
       <c r="J2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="K2" t="n">
-        <v>66.25</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>77.34999999999999</v>
+        <v>82</v>
       </c>
       <c r="N2" t="n">
-        <v>756.55</v>
+        <v>84.2</v>
       </c>
       <c r="O2" t="n">
-        <v>132</v>
+        <v>1187</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99864.60000000001</v>
+        <v>99945.39999999999</v>
       </c>
       <c r="R2" t="n">
         <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>680.9</v>
+        <v>75.78</v>
       </c>
       <c r="T2" t="n">
-        <v>9986.459999999999</v>
+        <v>9994.540000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>870.03</v>
+        <v>99.36</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>14979.69</v>
+        <v>17990.17</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LAMBODHARA</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>137.22</v>
+        <v>1424</v>
       </c>
       <c r="E3" t="n">
-        <v>112.4</v>
+        <v>958.98</v>
       </c>
       <c r="F3" t="n">
-        <v>22.09</v>
+        <v>48.49</v>
       </c>
       <c r="G3" t="n">
-        <v>136.41</v>
+        <v>993.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59</v>
+        <v>43.29</v>
       </c>
       <c r="I3" t="n">
-        <v>60.3</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.19</v>
+        <v>2.74</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>80.2</v>
       </c>
       <c r="N3" t="n">
-        <v>137.22</v>
+        <v>1424</v>
       </c>
       <c r="O3" t="n">
-        <v>728</v>
+        <v>70</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99896.16</v>
+        <v>99680</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>123.5</v>
+        <v>1281.6</v>
       </c>
       <c r="T3" t="n">
-        <v>9989.620000000001</v>
+        <v>9968</v>
       </c>
       <c r="U3" t="n">
-        <v>161.92</v>
+        <v>1723.04</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>17981.31</v>
+        <v>20932.8</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>346</v>
+        <v>333.27</v>
       </c>
       <c r="E4" t="n">
-        <v>299.48</v>
+        <v>211.55</v>
       </c>
       <c r="F4" t="n">
-        <v>15.53</v>
+        <v>57.54</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>241.57</v>
       </c>
       <c r="H4" t="n">
-        <v>57.27</v>
+        <v>37.96</v>
       </c>
       <c r="I4" t="n">
-        <v>47.36</v>
+        <v>69.78</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="K4" t="n">
-        <v>57.5</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>74.5</v>
+        <v>78.7</v>
       </c>
       <c r="N4" t="n">
-        <v>346</v>
+        <v>333.27</v>
       </c>
       <c r="O4" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99994</v>
+        <v>99981</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>311.4</v>
+        <v>299.94</v>
       </c>
       <c r="T4" t="n">
-        <v>9999.4</v>
+        <v>9998.1</v>
       </c>
       <c r="U4" t="n">
-        <v>394.44</v>
+        <v>403.26</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>13999.16</v>
+        <v>20996.01</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>141.08</v>
+        <v>1505.7</v>
       </c>
       <c r="E5" t="n">
-        <v>95.68000000000001</v>
+        <v>1264.19</v>
       </c>
       <c r="F5" t="n">
-        <v>47.44</v>
+        <v>19.1</v>
       </c>
       <c r="G5" t="n">
-        <v>114</v>
+        <v>1513</v>
       </c>
       <c r="H5" t="n">
-        <v>23.75</v>
+        <v>-0.48</v>
       </c>
       <c r="I5" t="n">
-        <v>62.36</v>
+        <v>57.18</v>
       </c>
       <c r="J5" t="n">
-        <v>0.52</v>
+        <v>2.07</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>73.75</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M5" t="n">
-        <v>73.55</v>
+        <v>76.25</v>
       </c>
       <c r="N5" t="n">
-        <v>141.08</v>
+        <v>1505.7</v>
       </c>
       <c r="O5" t="n">
-        <v>708</v>
+        <v>66</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99884.64</v>
+        <v>99376.2</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.94</v>
       </c>
       <c r="S5" t="n">
-        <v>126.97</v>
+        <v>1355.13</v>
       </c>
       <c r="T5" t="n">
-        <v>9988.459999999999</v>
+        <v>9937.620000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>166.47</v>
+        <v>1806.84</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W5" t="n">
-        <v>17979.24</v>
+        <v>19875.24</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STEELCITY</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91.40000000000001</v>
+        <v>230.3</v>
       </c>
       <c r="E6" t="n">
-        <v>83.54000000000001</v>
+        <v>155.96</v>
       </c>
       <c r="F6" t="n">
-        <v>9.41</v>
+        <v>47.67</v>
       </c>
       <c r="G6" t="n">
-        <v>95.98999999999999</v>
+        <v>163.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.78</v>
+        <v>40.51</v>
       </c>
       <c r="I6" t="n">
-        <v>65.86</v>
+        <v>61.82</v>
       </c>
       <c r="J6" t="n">
-        <v>7.28</v>
+        <v>3.66</v>
       </c>
       <c r="K6" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>72.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>91.40000000000001</v>
+        <v>230.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1094</v>
+        <v>434</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99991.60000000001</v>
+        <v>99950.2</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>82.26000000000001</v>
+        <v>207.27</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.16</v>
+        <v>9995.02</v>
       </c>
       <c r="U6" t="n">
-        <v>108.77</v>
+        <v>274.06</v>
       </c>
       <c r="V6" t="n">
         <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>18998.4</v>
+        <v>18990.54</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>370.05</v>
+        <v>325.35</v>
       </c>
       <c r="E7" t="n">
-        <v>322.39</v>
+        <v>247.18</v>
       </c>
       <c r="F7" t="n">
-        <v>14.78</v>
+        <v>31.63</v>
       </c>
       <c r="G7" t="n">
-        <v>386</v>
+        <v>220.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.13</v>
+        <v>47.62</v>
       </c>
       <c r="I7" t="n">
-        <v>55.5</v>
+        <v>52.55</v>
       </c>
       <c r="J7" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="K7" t="n">
-        <v>53.75</v>
+        <v>57.5</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>72.25</v>
+        <v>74.5</v>
       </c>
       <c r="N7" t="n">
-        <v>370.05</v>
+        <v>325.35</v>
       </c>
       <c r="O7" t="n">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99913.5</v>
+        <v>99882.45</v>
       </c>
       <c r="R7" t="n">
         <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>333.04</v>
+        <v>292.82</v>
       </c>
       <c r="T7" t="n">
-        <v>9991.35</v>
+        <v>9988.25</v>
       </c>
       <c r="U7" t="n">
-        <v>432.96</v>
+        <v>374.15</v>
       </c>
       <c r="V7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>16985.29</v>
+        <v>14982.37</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANUHPHR</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>91.20999999999999</v>
+        <v>813</v>
       </c>
       <c r="E8" t="n">
-        <v>78.48999999999999</v>
+        <v>553.8099999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>16.2</v>
+        <v>46.8</v>
       </c>
       <c r="G8" t="n">
-        <v>86.81</v>
+        <v>659.2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.07</v>
+        <v>23.33</v>
       </c>
       <c r="I8" t="n">
-        <v>64.73999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="J8" t="n">
-        <v>1.57</v>
+        <v>0.72</v>
       </c>
       <c r="K8" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>71.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>91.20999999999999</v>
+        <v>813</v>
       </c>
       <c r="O8" t="n">
-        <v>1096</v>
+        <v>123</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99966.16</v>
+        <v>99999</v>
       </c>
       <c r="R8" t="n">
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>82.09</v>
+        <v>731.7</v>
       </c>
       <c r="T8" t="n">
-        <v>9996.620000000001</v>
+        <v>9999.9</v>
       </c>
       <c r="U8" t="n">
-        <v>107.63</v>
+        <v>959.34</v>
       </c>
       <c r="V8" t="n">
         <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>17993.91</v>
+        <v>17999.82</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WENDT</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8669.5</v>
+        <v>14.97</v>
       </c>
       <c r="E9" t="n">
-        <v>7411.08</v>
+        <v>12.04</v>
       </c>
       <c r="F9" t="n">
-        <v>16.98</v>
+        <v>24.29</v>
       </c>
       <c r="G9" t="n">
-        <v>8740</v>
+        <v>12.8</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>16.95</v>
       </c>
       <c r="I9" t="n">
-        <v>62.67</v>
+        <v>56.94</v>
       </c>
       <c r="J9" t="n">
-        <v>7.75</v>
+        <v>1.23</v>
       </c>
       <c r="K9" t="n">
-        <v>73.75</v>
+        <v>70</v>
       </c>
       <c r="L9" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M9" t="n">
-        <v>71.45</v>
+        <v>74</v>
       </c>
       <c r="N9" t="n">
-        <v>8669.5</v>
+        <v>14.97</v>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>6680</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>95364.5</v>
+        <v>99999.60000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>9.539999999999999</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>7802.55</v>
+        <v>13.47</v>
       </c>
       <c r="T9" t="n">
-        <v>9536.450000000001</v>
+        <v>9999.959999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>10230.01</v>
+        <v>17.81</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>18.97</v>
       </c>
       <c r="W9" t="n">
-        <v>17165.61</v>
+        <v>18969.92</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1127.7</v>
+        <v>226.37</v>
       </c>
       <c r="E10" t="n">
-        <v>1056.09</v>
+        <v>185.53</v>
       </c>
       <c r="F10" t="n">
-        <v>6.78</v>
+        <v>22.01</v>
       </c>
       <c r="G10" t="n">
-        <v>1128.1</v>
+        <v>205.9</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.04</v>
+        <v>9.94</v>
       </c>
       <c r="I10" t="n">
-        <v>54.51</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>0.36</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M10" t="n">
-        <v>70.75</v>
+        <v>73.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1127.7</v>
+        <v>226.37</v>
       </c>
       <c r="O10" t="n">
-        <v>88</v>
+        <v>441</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99237.60000000001</v>
+        <v>99829.17</v>
       </c>
       <c r="R10" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="S10" t="n">
-        <v>1014.93</v>
+        <v>203.73</v>
       </c>
       <c r="T10" t="n">
-        <v>9923.76</v>
+        <v>9982.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1274.3</v>
+        <v>267.12</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>12900.89</v>
+        <v>17969.25</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NRAIL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>595.3</v>
+        <v>140.92</v>
       </c>
       <c r="E11" t="n">
-        <v>463.16</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>28.53</v>
+        <v>46.9</v>
       </c>
       <c r="G11" t="n">
-        <v>519</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
-        <v>14.7</v>
+        <v>23.61</v>
       </c>
       <c r="I11" t="n">
-        <v>64.04000000000001</v>
+        <v>62.24</v>
       </c>
       <c r="J11" t="n">
-        <v>1.56</v>
+        <v>0.44</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>70.7</v>
+        <v>73.55</v>
       </c>
       <c r="N11" t="n">
-        <v>595.3</v>
+        <v>140.92</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>709</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99415.10000000001</v>
+        <v>99912.28</v>
       </c>
       <c r="R11" t="n">
-        <v>9.94</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>535.77</v>
+        <v>126.83</v>
       </c>
       <c r="T11" t="n">
-        <v>9941.51</v>
+        <v>9991.23</v>
       </c>
       <c r="U11" t="n">
-        <v>708.41</v>
+        <v>166.29</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>18888.87</v>
+        <v>17984.21</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>84.2</v>
+        <v>420.4</v>
       </c>
       <c r="E2" t="n">
-        <v>73.65000000000001</v>
+        <v>296.62</v>
       </c>
       <c r="F2" t="n">
-        <v>14.32</v>
+        <v>41.73</v>
       </c>
       <c r="G2" t="n">
-        <v>58.79</v>
+        <v>324.3</v>
       </c>
       <c r="H2" t="n">
-        <v>43.22</v>
+        <v>29.63</v>
       </c>
       <c r="I2" t="n">
-        <v>55.13</v>
+        <v>63.37</v>
       </c>
       <c r="J2" t="n">
-        <v>1.31</v>
+        <v>2.13</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="N2" t="n">
-        <v>84.2</v>
+        <v>420.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1187</v>
+        <v>237</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99945.39999999999</v>
+        <v>99634.8</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>75.78</v>
+        <v>378.36</v>
       </c>
       <c r="T2" t="n">
-        <v>9994.540000000001</v>
+        <v>9963.48</v>
       </c>
       <c r="U2" t="n">
-        <v>99.36</v>
+        <v>487.66</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W2" t="n">
-        <v>17990.17</v>
+        <v>15941.57</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1424</v>
+        <v>233.41</v>
       </c>
       <c r="E3" t="n">
-        <v>958.98</v>
+        <v>156.45</v>
       </c>
       <c r="F3" t="n">
-        <v>48.49</v>
+        <v>49.19</v>
       </c>
       <c r="G3" t="n">
-        <v>993.8</v>
+        <v>163.9</v>
       </c>
       <c r="H3" t="n">
-        <v>43.29</v>
+        <v>42.41</v>
       </c>
       <c r="I3" t="n">
-        <v>68.76000000000001</v>
+        <v>63.65</v>
       </c>
       <c r="J3" t="n">
-        <v>2.74</v>
+        <v>3.78</v>
       </c>
       <c r="K3" t="n">
         <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>80.2</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>1424</v>
+        <v>233.41</v>
       </c>
       <c r="O3" t="n">
-        <v>70</v>
+        <v>428</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99680</v>
+        <v>99899.48</v>
       </c>
       <c r="R3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>1281.6</v>
+        <v>210.07</v>
       </c>
       <c r="T3" t="n">
-        <v>9968</v>
+        <v>9989.950000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1723.04</v>
+        <v>270.76</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>20932.8</v>
+        <v>15983.92</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>333.27</v>
+        <v>838.55</v>
       </c>
       <c r="E4" t="n">
-        <v>211.55</v>
+        <v>555.33</v>
       </c>
       <c r="F4" t="n">
-        <v>57.54</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>241.57</v>
+        <v>659.2</v>
       </c>
       <c r="H4" t="n">
-        <v>37.96</v>
+        <v>27.21</v>
       </c>
       <c r="I4" t="n">
-        <v>69.78</v>
+        <v>68.66</v>
       </c>
       <c r="J4" t="n">
-        <v>1.52</v>
+        <v>7.01</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>78.7</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>333.27</v>
+        <v>838.55</v>
       </c>
       <c r="O4" t="n">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99981</v>
+        <v>99787.45</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>299.94</v>
+        <v>754.7</v>
       </c>
       <c r="T4" t="n">
-        <v>9998.1</v>
+        <v>9978.75</v>
       </c>
       <c r="U4" t="n">
-        <v>403.26</v>
+        <v>972.72</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>20996.01</v>
+        <v>15965.99</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>NRAIL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1505.7</v>
+        <v>638.85</v>
       </c>
       <c r="E5" t="n">
-        <v>1264.19</v>
+        <v>464.66</v>
       </c>
       <c r="F5" t="n">
-        <v>19.1</v>
+        <v>37.49</v>
       </c>
       <c r="G5" t="n">
-        <v>1513</v>
+        <v>519</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.48</v>
+        <v>23.09</v>
       </c>
       <c r="I5" t="n">
-        <v>57.18</v>
+        <v>69.52</v>
       </c>
       <c r="J5" t="n">
-        <v>2.07</v>
+        <v>3.56</v>
       </c>
       <c r="K5" t="n">
-        <v>73.75</v>
+        <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>76.25</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>1505.7</v>
+        <v>638.85</v>
       </c>
       <c r="O5" t="n">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99376.2</v>
+        <v>99660.60000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.94</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>1355.13</v>
+        <v>574.96</v>
       </c>
       <c r="T5" t="n">
-        <v>9937.620000000001</v>
+        <v>9966.059999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1806.84</v>
+        <v>741.0700000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>19875.24</v>
+        <v>15945.7</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>SHREEPUSHK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>230.3</v>
+        <v>501.45</v>
       </c>
       <c r="E6" t="n">
-        <v>155.96</v>
+        <v>373.46</v>
       </c>
       <c r="F6" t="n">
-        <v>47.67</v>
+        <v>34.27</v>
       </c>
       <c r="G6" t="n">
-        <v>163.9</v>
+        <v>476</v>
       </c>
       <c r="H6" t="n">
-        <v>40.51</v>
+        <v>5.35</v>
       </c>
       <c r="I6" t="n">
-        <v>61.82</v>
+        <v>66.86</v>
       </c>
       <c r="J6" t="n">
-        <v>3.66</v>
+        <v>2.1</v>
       </c>
       <c r="K6" t="n">
         <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>75.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>230.3</v>
+        <v>501.45</v>
       </c>
       <c r="O6" t="n">
-        <v>434</v>
+        <v>199</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99950.2</v>
+        <v>99788.55</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>207.27</v>
+        <v>451.3</v>
       </c>
       <c r="T6" t="n">
-        <v>9995.02</v>
+        <v>9978.860000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>274.06</v>
+        <v>581.6799999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>18990.54</v>
+        <v>15966.17</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>325.35</v>
+        <v>377.95</v>
       </c>
       <c r="E7" t="n">
-        <v>247.18</v>
+        <v>178.57</v>
       </c>
       <c r="F7" t="n">
-        <v>31.63</v>
+        <v>111.65</v>
       </c>
       <c r="G7" t="n">
-        <v>220.4</v>
+        <v>215.2</v>
       </c>
       <c r="H7" t="n">
-        <v>47.62</v>
+        <v>75.63</v>
       </c>
       <c r="I7" t="n">
-        <v>52.55</v>
+        <v>68.98</v>
       </c>
       <c r="J7" t="n">
-        <v>0.79</v>
+        <v>3.07</v>
       </c>
       <c r="K7" t="n">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>74.5</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>325.35</v>
+        <v>377.95</v>
       </c>
       <c r="O7" t="n">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99882.45</v>
+        <v>99778.8</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S7" t="n">
-        <v>292.82</v>
+        <v>340.16</v>
       </c>
       <c r="T7" t="n">
-        <v>9988.25</v>
+        <v>9977.879999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>374.15</v>
+        <v>438.42</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>14982.37</v>
+        <v>15964.61</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>813</v>
+        <v>140.17</v>
       </c>
       <c r="E8" t="n">
-        <v>553.8099999999999</v>
+        <v>104.11</v>
       </c>
       <c r="F8" t="n">
-        <v>46.8</v>
+        <v>34.64</v>
       </c>
       <c r="G8" t="n">
-        <v>659.2</v>
+        <v>133.9</v>
       </c>
       <c r="H8" t="n">
-        <v>23.33</v>
+        <v>4.68</v>
       </c>
       <c r="I8" t="n">
-        <v>64.94</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.72</v>
+        <v>2.8</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>74.34999999999999</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>813</v>
+        <v>140.17</v>
       </c>
       <c r="O8" t="n">
-        <v>123</v>
+        <v>713</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99999</v>
+        <v>99941.21000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>731.7</v>
+        <v>126.15</v>
       </c>
       <c r="T8" t="n">
-        <v>9999.9</v>
+        <v>9994.120000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>959.34</v>
+        <v>162.6</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>17999.82</v>
+        <v>15990.59</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.97</v>
+        <v>737.6</v>
       </c>
       <c r="E9" t="n">
-        <v>12.04</v>
+        <v>536.63</v>
       </c>
       <c r="F9" t="n">
-        <v>24.29</v>
+        <v>37.45</v>
       </c>
       <c r="G9" t="n">
-        <v>12.8</v>
+        <v>580</v>
       </c>
       <c r="H9" t="n">
-        <v>16.95</v>
+        <v>27.17</v>
       </c>
       <c r="I9" t="n">
-        <v>56.94</v>
+        <v>57.97</v>
       </c>
       <c r="J9" t="n">
-        <v>1.23</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>14.97</v>
+        <v>737.6</v>
       </c>
       <c r="O9" t="n">
-        <v>6680</v>
+        <v>135</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99999.60000000001</v>
+        <v>99576</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>13.47</v>
+        <v>663.84</v>
       </c>
       <c r="T9" t="n">
-        <v>9999.959999999999</v>
+        <v>9957.6</v>
       </c>
       <c r="U9" t="n">
-        <v>17.81</v>
+        <v>855.62</v>
       </c>
       <c r="V9" t="n">
-        <v>18.97</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>18969.92</v>
+        <v>15932.16</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>226.37</v>
+        <v>981.8</v>
       </c>
       <c r="E10" t="n">
-        <v>185.53</v>
+        <v>764.55</v>
       </c>
       <c r="F10" t="n">
-        <v>22.01</v>
+        <v>28.42</v>
       </c>
       <c r="G10" t="n">
-        <v>205.9</v>
+        <v>843.7</v>
       </c>
       <c r="H10" t="n">
-        <v>9.94</v>
+        <v>16.37</v>
       </c>
       <c r="I10" t="n">
-        <v>67.98999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36</v>
+        <v>1.54</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>72.5</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>73.55</v>
+        <v>43.5</v>
       </c>
       <c r="N10" t="n">
-        <v>226.37</v>
+        <v>981.8</v>
       </c>
       <c r="O10" t="n">
-        <v>441</v>
+        <v>101</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99829.17</v>
+        <v>99161.8</v>
       </c>
       <c r="R10" t="n">
-        <v>9.98</v>
+        <v>9.92</v>
       </c>
       <c r="S10" t="n">
-        <v>203.73</v>
+        <v>883.62</v>
       </c>
       <c r="T10" t="n">
-        <v>9982.92</v>
+        <v>9916.18</v>
       </c>
       <c r="U10" t="n">
-        <v>267.12</v>
+        <v>1138.89</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>17969.25</v>
+        <v>15865.89</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>140.92</v>
+        <v>529</v>
       </c>
       <c r="E11" t="n">
-        <v>95.93000000000001</v>
+        <v>373.5</v>
       </c>
       <c r="F11" t="n">
-        <v>46.9</v>
+        <v>41.63</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>472.15</v>
       </c>
       <c r="H11" t="n">
-        <v>23.61</v>
+        <v>12.04</v>
       </c>
       <c r="I11" t="n">
-        <v>62.24</v>
+        <v>59.83</v>
       </c>
       <c r="J11" t="n">
-        <v>0.44</v>
+        <v>1.69</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>73.55</v>
+        <v>43.5</v>
       </c>
       <c r="N11" t="n">
-        <v>140.92</v>
+        <v>529</v>
       </c>
       <c r="O11" t="n">
-        <v>709</v>
+        <v>189</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99912.28</v>
+        <v>99981</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>126.83</v>
+        <v>476.1</v>
       </c>
       <c r="T11" t="n">
-        <v>9991.23</v>
+        <v>9998.1</v>
       </c>
       <c r="U11" t="n">
-        <v>166.29</v>
+        <v>613.64</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>17984.21</v>
+        <v>15996.96</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>420.4</v>
+        <v>19.3</v>
       </c>
       <c r="E2" t="n">
-        <v>296.62</v>
+        <v>15.32</v>
       </c>
       <c r="F2" t="n">
-        <v>41.73</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>324.3</v>
+        <v>17.4</v>
       </c>
       <c r="H2" t="n">
-        <v>29.63</v>
+        <v>10.92</v>
       </c>
       <c r="I2" t="n">
-        <v>63.37</v>
+        <v>47.47</v>
       </c>
       <c r="J2" t="n">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>63.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>420.4</v>
+        <v>19.3</v>
       </c>
       <c r="O2" t="n">
-        <v>237</v>
+        <v>5181</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99634.8</v>
+        <v>99993.3</v>
       </c>
       <c r="R2" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>378.36</v>
+        <v>17.37</v>
       </c>
       <c r="T2" t="n">
-        <v>9963.48</v>
+        <v>9999.33</v>
       </c>
       <c r="U2" t="n">
-        <v>487.66</v>
+        <v>22.77</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>17.98</v>
       </c>
       <c r="W2" t="n">
-        <v>15941.57</v>
+        <v>17978.8</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>233.41</v>
+        <v>9158</v>
       </c>
       <c r="E3" t="n">
-        <v>156.45</v>
+        <v>6889.94</v>
       </c>
       <c r="F3" t="n">
-        <v>49.19</v>
+        <v>32.92</v>
       </c>
       <c r="G3" t="n">
-        <v>163.9</v>
+        <v>7071.5</v>
       </c>
       <c r="H3" t="n">
-        <v>42.41</v>
+        <v>29.51</v>
       </c>
       <c r="I3" t="n">
-        <v>63.65</v>
+        <v>57.41</v>
       </c>
       <c r="J3" t="n">
-        <v>3.78</v>
+        <v>1.88</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>75.5</v>
       </c>
       <c r="N3" t="n">
-        <v>233.41</v>
+        <v>9158</v>
       </c>
       <c r="O3" t="n">
-        <v>428</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99899.48</v>
+        <v>91580</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>9.16</v>
       </c>
       <c r="S3" t="n">
-        <v>210.07</v>
+        <v>8242.200000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>9989.950000000001</v>
+        <v>9158</v>
       </c>
       <c r="U3" t="n">
-        <v>270.76</v>
+        <v>11081.18</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>15983.92</v>
+        <v>19231.8</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>838.55</v>
+        <v>12.64</v>
       </c>
       <c r="E4" t="n">
-        <v>555.33</v>
+        <v>9.74</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>29.74</v>
       </c>
       <c r="G4" t="n">
-        <v>659.2</v>
+        <v>11.38</v>
       </c>
       <c r="H4" t="n">
-        <v>27.21</v>
+        <v>11.07</v>
       </c>
       <c r="I4" t="n">
-        <v>68.66</v>
+        <v>59.32</v>
       </c>
       <c r="J4" t="n">
-        <v>7.01</v>
+        <v>1.52</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>75.5</v>
       </c>
       <c r="N4" t="n">
-        <v>838.55</v>
+        <v>12.64</v>
       </c>
       <c r="O4" t="n">
-        <v>119</v>
+        <v>7911</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99787.45</v>
+        <v>99995.03999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>754.7</v>
+        <v>11.38</v>
       </c>
       <c r="T4" t="n">
-        <v>9978.75</v>
+        <v>9999.5</v>
       </c>
       <c r="U4" t="n">
-        <v>972.72</v>
+        <v>15.29</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>20.97</v>
       </c>
       <c r="W4" t="n">
-        <v>15965.99</v>
+        <v>20968.96</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NRAIL</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>638.85</v>
+        <v>28.79</v>
       </c>
       <c r="E5" t="n">
-        <v>464.66</v>
+        <v>19.22</v>
       </c>
       <c r="F5" t="n">
-        <v>37.49</v>
+        <v>49.76</v>
       </c>
       <c r="G5" t="n">
-        <v>519</v>
+        <v>21.25</v>
       </c>
       <c r="H5" t="n">
-        <v>23.09</v>
+        <v>35.48</v>
       </c>
       <c r="I5" t="n">
-        <v>69.52</v>
+        <v>62.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.56</v>
+        <v>3.83</v>
       </c>
       <c r="K5" t="n">
         <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
-        <v>638.85</v>
+        <v>28.79</v>
       </c>
       <c r="O5" t="n">
-        <v>156</v>
+        <v>3473</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99660.60000000001</v>
+        <v>99987.67</v>
       </c>
       <c r="R5" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>574.96</v>
+        <v>25.91</v>
       </c>
       <c r="T5" t="n">
-        <v>9966.059999999999</v>
+        <v>9998.77</v>
       </c>
       <c r="U5" t="n">
-        <v>741.0700000000001</v>
+        <v>34.26</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W5" t="n">
-        <v>15945.7</v>
+        <v>18997.66</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHREEPUSHK</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>501.45</v>
+        <v>1362.6</v>
       </c>
       <c r="E6" t="n">
-        <v>373.46</v>
+        <v>968.35</v>
       </c>
       <c r="F6" t="n">
-        <v>34.27</v>
+        <v>40.71</v>
       </c>
       <c r="G6" t="n">
-        <v>476</v>
+        <v>993.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5.35</v>
+        <v>37.11</v>
       </c>
       <c r="I6" t="n">
-        <v>66.86</v>
+        <v>59.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>74.95</v>
       </c>
       <c r="N6" t="n">
-        <v>501.45</v>
+        <v>1362.6</v>
       </c>
       <c r="O6" t="n">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99788.55</v>
+        <v>99469.8</v>
       </c>
       <c r="R6" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>451.3</v>
+        <v>1226.34</v>
       </c>
       <c r="T6" t="n">
-        <v>9978.860000000001</v>
+        <v>9946.98</v>
       </c>
       <c r="U6" t="n">
-        <v>581.6799999999999</v>
+        <v>1607.87</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>15966.17</v>
+        <v>17904.56</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>377.95</v>
+        <v>904.2</v>
       </c>
       <c r="E7" t="n">
-        <v>178.57</v>
+        <v>696.97</v>
       </c>
       <c r="F7" t="n">
-        <v>111.65</v>
+        <v>29.73</v>
       </c>
       <c r="G7" t="n">
-        <v>215.2</v>
+        <v>513.55</v>
       </c>
       <c r="H7" t="n">
-        <v>75.63</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>68.98</v>
+        <v>53.63</v>
       </c>
       <c r="J7" t="n">
-        <v>3.07</v>
+        <v>1.51</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>377.95</v>
+        <v>904.2</v>
       </c>
       <c r="O7" t="n">
-        <v>264</v>
+        <v>110</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99778.8</v>
+        <v>99462</v>
       </c>
       <c r="R7" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>340.16</v>
+        <v>813.78</v>
       </c>
       <c r="T7" t="n">
-        <v>9977.879999999999</v>
+        <v>9946.200000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>438.42</v>
+        <v>1066.96</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>15964.61</v>
+        <v>17903.16</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>140.17</v>
+        <v>219.94</v>
       </c>
       <c r="E8" t="n">
-        <v>104.11</v>
+        <v>186.12</v>
       </c>
       <c r="F8" t="n">
-        <v>34.64</v>
+        <v>18.17</v>
       </c>
       <c r="G8" t="n">
-        <v>133.9</v>
+        <v>205.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.68</v>
+        <v>6.82</v>
       </c>
       <c r="I8" t="n">
-        <v>67.65000000000001</v>
+        <v>58.52</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8</v>
+        <v>0.26</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>73.55</v>
       </c>
       <c r="N8" t="n">
-        <v>140.17</v>
+        <v>219.94</v>
       </c>
       <c r="O8" t="n">
-        <v>713</v>
+        <v>454</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99941.21000000001</v>
+        <v>99852.75999999999</v>
       </c>
       <c r="R8" t="n">
         <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>126.15</v>
+        <v>197.95</v>
       </c>
       <c r="T8" t="n">
-        <v>9994.120000000001</v>
+        <v>9985.280000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>162.6</v>
+        <v>257.33</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>15990.59</v>
+        <v>16974.97</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>737.6</v>
+        <v>222.57</v>
       </c>
       <c r="E9" t="n">
-        <v>536.63</v>
+        <v>157.37</v>
       </c>
       <c r="F9" t="n">
-        <v>37.45</v>
+        <v>41.43</v>
       </c>
       <c r="G9" t="n">
-        <v>580</v>
+        <v>163.9</v>
       </c>
       <c r="H9" t="n">
-        <v>27.17</v>
+        <v>35.8</v>
       </c>
       <c r="I9" t="n">
-        <v>57.97</v>
+        <v>53.44</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>71.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>737.6</v>
+        <v>222.57</v>
       </c>
       <c r="O9" t="n">
-        <v>135</v>
+        <v>449</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99576</v>
+        <v>99933.92999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>663.84</v>
+        <v>200.31</v>
       </c>
       <c r="T9" t="n">
-        <v>9957.6</v>
+        <v>9993.389999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>855.62</v>
+        <v>258.18</v>
       </c>
       <c r="V9" t="n">
         <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>15932.16</v>
+        <v>15989.43</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>981.8</v>
+        <v>367.15</v>
       </c>
       <c r="E10" t="n">
-        <v>764.55</v>
+        <v>322.34</v>
       </c>
       <c r="F10" t="n">
-        <v>28.42</v>
+        <v>13.9</v>
       </c>
       <c r="G10" t="n">
-        <v>843.7</v>
+        <v>386</v>
       </c>
       <c r="H10" t="n">
-        <v>16.37</v>
+        <v>-4.88</v>
       </c>
       <c r="I10" t="n">
-        <v>62.24</v>
+        <v>52.19</v>
       </c>
       <c r="J10" t="n">
-        <v>1.54</v>
+        <v>1.13</v>
       </c>
       <c r="K10" t="n">
-        <v>72.5</v>
+        <v>55</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>43.5</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
-        <v>981.8</v>
+        <v>367.15</v>
       </c>
       <c r="O10" t="n">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99161.8</v>
+        <v>99864.8</v>
       </c>
       <c r="R10" t="n">
-        <v>9.92</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>883.62</v>
+        <v>330.44</v>
       </c>
       <c r="T10" t="n">
-        <v>9916.18</v>
+        <v>9986.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1138.89</v>
+        <v>418.55</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>15865.89</v>
+        <v>13981.07</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>529</v>
+        <v>1889.6</v>
       </c>
       <c r="E11" t="n">
-        <v>373.5</v>
+        <v>1172.58</v>
       </c>
       <c r="F11" t="n">
-        <v>41.63</v>
+        <v>61.15</v>
       </c>
       <c r="G11" t="n">
-        <v>472.15</v>
+        <v>1250</v>
       </c>
       <c r="H11" t="n">
-        <v>12.04</v>
+        <v>51.17</v>
       </c>
       <c r="I11" t="n">
-        <v>59.83</v>
+        <v>57.18</v>
       </c>
       <c r="J11" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>66.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>43.5</v>
+        <v>72.55</v>
       </c>
       <c r="N11" t="n">
-        <v>529</v>
+        <v>1889.6</v>
       </c>
       <c r="O11" t="n">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99981</v>
+        <v>98259.2</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="S11" t="n">
-        <v>476.1</v>
+        <v>1700.64</v>
       </c>
       <c r="T11" t="n">
-        <v>9998.1</v>
+        <v>9825.92</v>
       </c>
       <c r="U11" t="n">
-        <v>613.64</v>
+        <v>2229.73</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>15996.96</v>
+        <v>17686.66</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.3</v>
+        <v>29.77</v>
       </c>
       <c r="E2" t="n">
-        <v>15.32</v>
+        <v>25.81</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>15.35</v>
       </c>
       <c r="G2" t="n">
-        <v>17.4</v>
+        <v>30.51</v>
       </c>
       <c r="H2" t="n">
-        <v>10.92</v>
+        <v>-2.43</v>
       </c>
       <c r="I2" t="n">
-        <v>47.47</v>
+        <v>68.69</v>
       </c>
       <c r="J2" t="n">
-        <v>1.71</v>
+        <v>4.91</v>
       </c>
       <c r="K2" t="n">
-        <v>63.75</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="M2" t="n">
-        <v>75.84999999999999</v>
+        <v>76</v>
       </c>
       <c r="N2" t="n">
-        <v>19.3</v>
+        <v>29.77</v>
       </c>
       <c r="O2" t="n">
-        <v>5181</v>
+        <v>3359</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99993.3</v>
+        <v>99997.42999999999</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>17.37</v>
+        <v>26.79</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.33</v>
+        <v>9999.74</v>
       </c>
       <c r="U2" t="n">
-        <v>22.77</v>
+        <v>35.72</v>
       </c>
       <c r="V2" t="n">
-        <v>17.98</v>
+        <v>19.99</v>
       </c>
       <c r="W2" t="n">
-        <v>17978.8</v>
+        <v>19989.49</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MOTISONS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9158</v>
+        <v>17.94</v>
       </c>
       <c r="E3" t="n">
-        <v>6889.94</v>
+        <v>14.09</v>
       </c>
       <c r="F3" t="n">
-        <v>32.92</v>
+        <v>27.34</v>
       </c>
       <c r="G3" t="n">
-        <v>7071.5</v>
+        <v>18.12</v>
       </c>
       <c r="H3" t="n">
-        <v>29.51</v>
+        <v>-0.99</v>
       </c>
       <c r="I3" t="n">
-        <v>57.41</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.88</v>
+        <v>4.72</v>
       </c>
       <c r="K3" t="n">
-        <v>72.5</v>
+        <v>73.75</v>
       </c>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="M3" t="n">
-        <v>75.5</v>
+        <v>71.45</v>
       </c>
       <c r="N3" t="n">
-        <v>9158</v>
+        <v>17.94</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>5574</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>91580</v>
+        <v>99997.56</v>
       </c>
       <c r="R3" t="n">
-        <v>9.16</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>8242.200000000001</v>
+        <v>16.15</v>
       </c>
       <c r="T3" t="n">
-        <v>9158</v>
+        <v>9999.76</v>
       </c>
       <c r="U3" t="n">
-        <v>11081.18</v>
+        <v>21.35</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>19.01</v>
       </c>
       <c r="W3" t="n">
-        <v>19231.8</v>
+        <v>19009.54</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.64</v>
+        <v>600.7</v>
       </c>
       <c r="E4" t="n">
-        <v>9.74</v>
+        <v>584.34</v>
       </c>
       <c r="F4" t="n">
-        <v>29.74</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>11.38</v>
+        <v>624.4</v>
       </c>
       <c r="H4" t="n">
-        <v>11.07</v>
+        <v>-3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>59.32</v>
+        <v>44.28</v>
       </c>
       <c r="J4" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>62.5</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>75.5</v>
+        <v>70.3</v>
       </c>
       <c r="N4" t="n">
-        <v>12.64</v>
+        <v>600.7</v>
       </c>
       <c r="O4" t="n">
-        <v>7911</v>
+        <v>166</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99995.03999999999</v>
+        <v>99716.2</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>11.38</v>
+        <v>540.63</v>
       </c>
       <c r="T4" t="n">
-        <v>9999.5</v>
+        <v>9971.620000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>15.29</v>
+        <v>708.83</v>
       </c>
       <c r="V4" t="n">
-        <v>20.97</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>20968.96</v>
+        <v>17948.92</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.79</v>
+        <v>370.95</v>
       </c>
       <c r="E5" t="n">
-        <v>19.22</v>
+        <v>322.37</v>
       </c>
       <c r="F5" t="n">
-        <v>49.76</v>
+        <v>15.07</v>
       </c>
       <c r="G5" t="n">
-        <v>21.25</v>
+        <v>386</v>
       </c>
       <c r="H5" t="n">
-        <v>35.48</v>
+        <v>-3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>62.3</v>
+        <v>54.66</v>
       </c>
       <c r="J5" t="n">
-        <v>3.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>28.79</v>
+        <v>370.95</v>
       </c>
       <c r="O5" t="n">
-        <v>3473</v>
+        <v>269</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99987.67</v>
+        <v>99785.55</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>25.91</v>
+        <v>333.86</v>
       </c>
       <c r="T5" t="n">
-        <v>9998.77</v>
+        <v>9978.559999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>34.26</v>
+        <v>422.88</v>
       </c>
       <c r="V5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>18997.66</v>
+        <v>13969.98</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1362.6</v>
+        <v>750</v>
       </c>
       <c r="E6" t="n">
-        <v>968.35</v>
+        <v>638.09</v>
       </c>
       <c r="F6" t="n">
-        <v>40.71</v>
+        <v>17.54</v>
       </c>
       <c r="G6" t="n">
-        <v>993.8</v>
+        <v>629.9</v>
       </c>
       <c r="H6" t="n">
-        <v>37.11</v>
+        <v>19.07</v>
       </c>
       <c r="I6" t="n">
-        <v>59.4</v>
+        <v>49.44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>66.25</v>
+        <v>52.5</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
-        <v>74.95</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>1362.6</v>
+        <v>750</v>
       </c>
       <c r="O6" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99469.8</v>
+        <v>99750</v>
       </c>
       <c r="R6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>1226.34</v>
+        <v>675</v>
       </c>
       <c r="T6" t="n">
-        <v>9946.98</v>
+        <v>9975</v>
       </c>
       <c r="U6" t="n">
-        <v>1607.87</v>
+        <v>855</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W6" t="n">
-        <v>17904.56</v>
+        <v>13965</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>904.2</v>
+        <v>80.8</v>
       </c>
       <c r="E7" t="n">
-        <v>696.97</v>
+        <v>74.11</v>
       </c>
       <c r="F7" t="n">
-        <v>29.73</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>513.55</v>
+        <v>58.79</v>
       </c>
       <c r="H7" t="n">
-        <v>76.06999999999999</v>
+        <v>37.44</v>
       </c>
       <c r="I7" t="n">
-        <v>53.63</v>
+        <v>43.72</v>
       </c>
       <c r="J7" t="n">
-        <v>1.51</v>
+        <v>0.95</v>
       </c>
       <c r="K7" t="n">
-        <v>68.75</v>
+        <v>47.5</v>
       </c>
       <c r="L7" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>74.84999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="N7" t="n">
-        <v>904.2</v>
+        <v>80.8</v>
       </c>
       <c r="O7" t="n">
-        <v>110</v>
+        <v>1237</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99462</v>
+        <v>99949.60000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.949999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>813.78</v>
+        <v>72.72</v>
       </c>
       <c r="T7" t="n">
-        <v>9946.200000000001</v>
+        <v>9994.959999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1066.96</v>
+        <v>91.3</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>17903.16</v>
+        <v>12993.45</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>219.94</v>
+        <v>88.94</v>
       </c>
       <c r="E8" t="n">
-        <v>186.12</v>
+        <v>87.31</v>
       </c>
       <c r="F8" t="n">
-        <v>18.17</v>
+        <v>1.86</v>
       </c>
       <c r="G8" t="n">
-        <v>205.9</v>
+        <v>53</v>
       </c>
       <c r="H8" t="n">
-        <v>6.82</v>
+        <v>67.81</v>
       </c>
       <c r="I8" t="n">
-        <v>58.52</v>
+        <v>42.45</v>
       </c>
       <c r="J8" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="M8" t="n">
-        <v>73.55</v>
+        <v>66.2</v>
       </c>
       <c r="N8" t="n">
-        <v>219.94</v>
+        <v>88.94</v>
       </c>
       <c r="O8" t="n">
-        <v>454</v>
+        <v>1124</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99852.75999999999</v>
+        <v>99968.56</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>197.95</v>
+        <v>80.05</v>
       </c>
       <c r="T8" t="n">
-        <v>9985.280000000001</v>
+        <v>9996.860000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>257.33</v>
+        <v>103.17</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>16974.97</v>
+        <v>15994.97</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>222.57</v>
+        <v>970.55</v>
       </c>
       <c r="E9" t="n">
-        <v>157.37</v>
+        <v>792.6900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>41.43</v>
+        <v>22.44</v>
       </c>
       <c r="G9" t="n">
-        <v>163.9</v>
+        <v>988.8</v>
       </c>
       <c r="H9" t="n">
-        <v>35.8</v>
+        <v>-1.85</v>
       </c>
       <c r="I9" t="n">
-        <v>53.44</v>
+        <v>60.99</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="K9" t="n">
-        <v>71.25</v>
+        <v>72.5</v>
       </c>
       <c r="L9" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>73.15000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>222.57</v>
+        <v>970.55</v>
       </c>
       <c r="O9" t="n">
-        <v>449</v>
+        <v>103</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99933.92999999999</v>
+        <v>99966.64999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>200.31</v>
+        <v>873.5</v>
       </c>
       <c r="T9" t="n">
-        <v>9993.389999999999</v>
+        <v>9996.67</v>
       </c>
       <c r="U9" t="n">
-        <v>258.18</v>
+        <v>1125.84</v>
       </c>
       <c r="V9" t="n">
         <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>15989.43</v>
+        <v>15994.66</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>367.15</v>
+        <v>18.41</v>
       </c>
       <c r="E10" t="n">
-        <v>322.34</v>
+        <v>15.06</v>
       </c>
       <c r="F10" t="n">
-        <v>13.9</v>
+        <v>22.23</v>
       </c>
       <c r="G10" t="n">
-        <v>386</v>
+        <v>19.28</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.88</v>
+        <v>-4.51</v>
       </c>
       <c r="I10" t="n">
-        <v>52.19</v>
+        <v>59.73</v>
       </c>
       <c r="J10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="K10" t="n">
-        <v>55</v>
+        <v>58.75</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>367.15</v>
+        <v>18.41</v>
       </c>
       <c r="O10" t="n">
-        <v>272</v>
+        <v>5431</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99864.8</v>
+        <v>99984.71000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>330.44</v>
+        <v>16.57</v>
       </c>
       <c r="T10" t="n">
-        <v>9986.48</v>
+        <v>9998.469999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>418.55</v>
+        <v>21.36</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>16.02</v>
       </c>
       <c r="W10" t="n">
-        <v>13981.07</v>
+        <v>16017.55</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1889.6</v>
+        <v>1077.7</v>
       </c>
       <c r="E11" t="n">
-        <v>1172.58</v>
+        <v>1056.83</v>
       </c>
       <c r="F11" t="n">
-        <v>61.15</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>1250</v>
+        <v>1128.1</v>
       </c>
       <c r="H11" t="n">
-        <v>51.17</v>
+        <v>-4.47</v>
       </c>
       <c r="I11" t="n">
-        <v>57.18</v>
+        <v>45.64</v>
       </c>
       <c r="J11" t="n">
-        <v>1.17</v>
+        <v>0.38</v>
       </c>
       <c r="K11" t="n">
-        <v>66.25</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="M11" t="n">
-        <v>72.55</v>
+        <v>64.75</v>
       </c>
       <c r="N11" t="n">
-        <v>1889.6</v>
+        <v>1077.7</v>
       </c>
       <c r="O11" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>98259.2</v>
+        <v>99148.39999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>9.83</v>
+        <v>9.91</v>
       </c>
       <c r="S11" t="n">
-        <v>1700.64</v>
+        <v>969.9299999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>9825.92</v>
+        <v>9914.84</v>
       </c>
       <c r="U11" t="n">
-        <v>2229.73</v>
+        <v>1250.13</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>17686.66</v>
+        <v>15863.74</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.77</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>25.81</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>15.35</v>
+        <v>12.52</v>
       </c>
       <c r="G2" t="n">
-        <v>30.51</v>
+        <v>58.79</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.43</v>
+        <v>42.1</v>
       </c>
       <c r="I2" t="n">
-        <v>68.69</v>
+        <v>53.16</v>
       </c>
       <c r="J2" t="n">
-        <v>4.91</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="L2" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>76</v>
+        <v>77.5</v>
       </c>
       <c r="N2" t="n">
-        <v>29.77</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>3359</v>
+        <v>1197</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99997.42999999999</v>
+        <v>99997.38</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>26.79</v>
+        <v>75.19</v>
       </c>
       <c r="T2" t="n">
         <v>9999.74</v>
       </c>
       <c r="U2" t="n">
-        <v>35.72</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>19.99</v>
+        <v>14.01</v>
       </c>
       <c r="W2" t="n">
-        <v>19989.49</v>
+        <v>14009.63</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MOTISONS</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.94</v>
+        <v>313.6</v>
       </c>
       <c r="E3" t="n">
-        <v>14.09</v>
+        <v>271.3</v>
       </c>
       <c r="F3" t="n">
-        <v>27.34</v>
+        <v>15.59</v>
       </c>
       <c r="G3" t="n">
-        <v>18.12</v>
+        <v>290</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.99</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>66.76000000000001</v>
+        <v>59.91</v>
       </c>
       <c r="J3" t="n">
-        <v>4.72</v>
+        <v>0.37</v>
       </c>
       <c r="K3" t="n">
-        <v>73.75</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>71.45</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>17.94</v>
+        <v>313.6</v>
       </c>
       <c r="O3" t="n">
-        <v>5574</v>
+        <v>318</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99997.56</v>
+        <v>99724.8</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>16.15</v>
+        <v>282.24</v>
       </c>
       <c r="T3" t="n">
-        <v>9999.76</v>
+        <v>9972.48</v>
       </c>
       <c r="U3" t="n">
-        <v>21.35</v>
+        <v>366.91</v>
       </c>
       <c r="V3" t="n">
-        <v>19.01</v>
+        <v>17</v>
       </c>
       <c r="W3" t="n">
-        <v>19009.54</v>
+        <v>16953.22</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>600.7</v>
+        <v>153.4</v>
       </c>
       <c r="E4" t="n">
-        <v>584.34</v>
+        <v>116.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>32.13</v>
       </c>
       <c r="G4" t="n">
-        <v>624.4</v>
+        <v>147.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.8</v>
+        <v>3.72</v>
       </c>
       <c r="I4" t="n">
-        <v>44.28</v>
+        <v>62.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1.18</v>
+        <v>0.1</v>
       </c>
       <c r="K4" t="n">
-        <v>62.5</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>70.3</v>
+        <v>76.75</v>
       </c>
       <c r="N4" t="n">
-        <v>600.7</v>
+        <v>153.4</v>
       </c>
       <c r="O4" t="n">
-        <v>166</v>
+        <v>651</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99716.2</v>
+        <v>99863.39999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>540.63</v>
+        <v>138.06</v>
       </c>
       <c r="T4" t="n">
-        <v>9971.620000000001</v>
+        <v>9986.34</v>
       </c>
       <c r="U4" t="n">
-        <v>708.83</v>
+        <v>181.01</v>
       </c>
       <c r="V4" t="n">
         <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>17948.92</v>
+        <v>17975.41</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>370.95</v>
+        <v>332.75</v>
       </c>
       <c r="E5" t="n">
-        <v>322.37</v>
+        <v>301.96</v>
       </c>
       <c r="F5" t="n">
-        <v>15.07</v>
+        <v>10.19</v>
       </c>
       <c r="G5" t="n">
-        <v>386</v>
+        <v>220</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.9</v>
+        <v>51.25</v>
       </c>
       <c r="I5" t="n">
-        <v>54.66</v>
+        <v>34.83</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>70</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>370.95</v>
+        <v>332.75</v>
       </c>
       <c r="O5" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99785.55</v>
+        <v>99825</v>
       </c>
       <c r="R5" t="n">
         <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>333.86</v>
+        <v>299.48</v>
       </c>
       <c r="T5" t="n">
-        <v>9978.559999999999</v>
+        <v>9982.5</v>
       </c>
       <c r="U5" t="n">
-        <v>422.88</v>
+        <v>389.32</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>13969.98</v>
+        <v>16970.25</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>218.35</v>
       </c>
       <c r="E6" t="n">
-        <v>638.09</v>
+        <v>186.5</v>
       </c>
       <c r="F6" t="n">
-        <v>17.54</v>
+        <v>17.08</v>
       </c>
       <c r="G6" t="n">
-        <v>629.9</v>
+        <v>205.9</v>
       </c>
       <c r="H6" t="n">
-        <v>19.07</v>
+        <v>6.05</v>
       </c>
       <c r="I6" t="n">
-        <v>49.44</v>
+        <v>56.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="K6" t="n">
-        <v>52.5</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>69.09999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="N6" t="n">
-        <v>750</v>
+        <v>218.35</v>
       </c>
       <c r="O6" t="n">
-        <v>133</v>
+        <v>457</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99750</v>
+        <v>99785.95</v>
       </c>
       <c r="R6" t="n">
         <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>675</v>
+        <v>196.52</v>
       </c>
       <c r="T6" t="n">
-        <v>9975</v>
+        <v>9978.59</v>
       </c>
       <c r="U6" t="n">
-        <v>855</v>
+        <v>255.47</v>
       </c>
       <c r="V6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W6" t="n">
-        <v>13965</v>
+        <v>16963.61</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80.8</v>
+        <v>136.6</v>
       </c>
       <c r="E7" t="n">
-        <v>74.11</v>
+        <v>97.33</v>
       </c>
       <c r="F7" t="n">
-        <v>9.029999999999999</v>
+        <v>40.35</v>
       </c>
       <c r="G7" t="n">
-        <v>58.79</v>
+        <v>114</v>
       </c>
       <c r="H7" t="n">
-        <v>37.44</v>
+        <v>19.82</v>
       </c>
       <c r="I7" t="n">
-        <v>43.72</v>
+        <v>56.99</v>
       </c>
       <c r="J7" t="n">
-        <v>0.95</v>
+        <v>0.17</v>
       </c>
       <c r="K7" t="n">
-        <v>47.5</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M7" t="n">
-        <v>68.5</v>
+        <v>73.55</v>
       </c>
       <c r="N7" t="n">
-        <v>80.8</v>
+        <v>136.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1237</v>
+        <v>732</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99949.60000000001</v>
+        <v>99991.2</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>72.72</v>
+        <v>122.94</v>
       </c>
       <c r="T7" t="n">
-        <v>9994.959999999999</v>
+        <v>9999.120000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>91.3</v>
+        <v>161.19</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>12993.45</v>
+        <v>17998.42</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88.94</v>
+        <v>30.39</v>
       </c>
       <c r="E8" t="n">
-        <v>87.31</v>
+        <v>19.37</v>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>56.89</v>
       </c>
       <c r="G8" t="n">
-        <v>53</v>
+        <v>21.25</v>
       </c>
       <c r="H8" t="n">
-        <v>67.81</v>
+        <v>43.01</v>
       </c>
       <c r="I8" t="n">
-        <v>42.45</v>
+        <v>69.37</v>
       </c>
       <c r="J8" t="n">
-        <v>0.19</v>
+        <v>1.92</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="L8" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="M8" t="n">
-        <v>66.2</v>
+        <v>73.5</v>
       </c>
       <c r="N8" t="n">
-        <v>88.94</v>
+        <v>30.39</v>
       </c>
       <c r="O8" t="n">
-        <v>1124</v>
+        <v>3290</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99968.56</v>
+        <v>99983.10000000001</v>
       </c>
       <c r="R8" t="n">
         <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>80.05</v>
+        <v>27.35</v>
       </c>
       <c r="T8" t="n">
-        <v>9996.860000000001</v>
+        <v>9998.309999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>103.17</v>
+        <v>36.16</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>18.99</v>
       </c>
       <c r="W8" t="n">
-        <v>15994.97</v>
+        <v>18986.79</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>970.55</v>
+        <v>235.79</v>
       </c>
       <c r="E9" t="n">
-        <v>792.6900000000001</v>
+        <v>206.92</v>
       </c>
       <c r="F9" t="n">
-        <v>22.44</v>
+        <v>13.95</v>
       </c>
       <c r="G9" t="n">
-        <v>988.8</v>
+        <v>245.38</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.85</v>
+        <v>-3.91</v>
       </c>
       <c r="I9" t="n">
-        <v>60.99</v>
+        <v>59.92</v>
       </c>
       <c r="J9" t="n">
-        <v>2.01</v>
+        <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>72.5</v>
+        <v>53.75</v>
       </c>
       <c r="L9" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>65.90000000000001</v>
+        <v>72.25</v>
       </c>
       <c r="N9" t="n">
-        <v>970.55</v>
+        <v>235.79</v>
       </c>
       <c r="O9" t="n">
-        <v>103</v>
+        <v>424</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99966.64999999999</v>
+        <v>99974.96000000001</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>873.5</v>
+        <v>212.21</v>
       </c>
       <c r="T9" t="n">
-        <v>9996.67</v>
+        <v>9997.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1125.84</v>
+        <v>275.87</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W9" t="n">
-        <v>15994.66</v>
+        <v>16995.74</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>MOTISONS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.41</v>
+        <v>18.3</v>
       </c>
       <c r="E10" t="n">
-        <v>15.06</v>
+        <v>14.1</v>
       </c>
       <c r="F10" t="n">
-        <v>22.23</v>
+        <v>29.81</v>
       </c>
       <c r="G10" t="n">
-        <v>19.28</v>
+        <v>18.12</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.51</v>
+        <v>0.99</v>
       </c>
       <c r="I10" t="n">
-        <v>59.73</v>
+        <v>68.69</v>
       </c>
       <c r="J10" t="n">
-        <v>1.08</v>
+        <v>2.22</v>
       </c>
       <c r="K10" t="n">
-        <v>58.75</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>64.84999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="N10" t="n">
-        <v>18.41</v>
+        <v>18.3</v>
       </c>
       <c r="O10" t="n">
-        <v>5431</v>
+        <v>5464</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99984.71000000001</v>
+        <v>99991.2</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>16.57</v>
+        <v>16.47</v>
       </c>
       <c r="T10" t="n">
-        <v>9998.469999999999</v>
+        <v>9999.120000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>21.36</v>
+        <v>21.78</v>
       </c>
       <c r="V10" t="n">
-        <v>16.02</v>
+        <v>19.02</v>
       </c>
       <c r="W10" t="n">
-        <v>16017.55</v>
+        <v>19018.33</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1077.7</v>
+        <v>283.47</v>
       </c>
       <c r="E11" t="n">
-        <v>1056.83</v>
+        <v>212.91</v>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>33.14</v>
       </c>
       <c r="G11" t="n">
-        <v>1128.1</v>
+        <v>241.57</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.47</v>
+        <v>17.34</v>
       </c>
       <c r="I11" t="n">
-        <v>45.64</v>
+        <v>52.44</v>
       </c>
       <c r="J11" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>57.5</v>
       </c>
       <c r="L11" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>64.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1077.7</v>
+        <v>283.47</v>
       </c>
       <c r="O11" t="n">
-        <v>92</v>
+        <v>352</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99148.39999999999</v>
+        <v>99781.44</v>
       </c>
       <c r="R11" t="n">
-        <v>9.91</v>
+        <v>9.98</v>
       </c>
       <c r="S11" t="n">
-        <v>969.9299999999999</v>
+        <v>255.12</v>
       </c>
       <c r="T11" t="n">
-        <v>9914.84</v>
+        <v>9978.139999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>1250.13</v>
+        <v>325.99</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>15863.74</v>
+        <v>14967.22</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,64 +558,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>83.54000000000001</v>
+        <v>588.9</v>
       </c>
       <c r="E2" t="n">
-        <v>74.23999999999999</v>
+        <v>497.04</v>
       </c>
       <c r="F2" t="n">
-        <v>12.52</v>
+        <v>18.48</v>
       </c>
       <c r="G2" t="n">
-        <v>58.79</v>
+        <v>539</v>
       </c>
       <c r="H2" t="n">
-        <v>42.1</v>
+        <v>9.26</v>
       </c>
       <c r="I2" t="n">
-        <v>53.16</v>
+        <v>57.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="K2" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>77.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>83.54000000000001</v>
+        <v>588.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1197</v>
+        <v>169</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99997.38</v>
+        <v>99524.10000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>75.19</v>
+        <v>530.01</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.74</v>
+        <v>9952.41</v>
       </c>
       <c r="U2" t="n">
-        <v>95.23999999999999</v>
+        <v>694.9</v>
       </c>
       <c r="V2" t="n">
-        <v>14.01</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>14009.63</v>
+        <v>17914.34</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NORTHARC</t>
+          <t>TREL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -643,64 +643,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>313.6</v>
+        <v>29.66</v>
       </c>
       <c r="E3" t="n">
-        <v>271.3</v>
+        <v>25.83</v>
       </c>
       <c r="F3" t="n">
-        <v>15.59</v>
+        <v>14.81</v>
       </c>
       <c r="G3" t="n">
-        <v>290</v>
+        <v>29.48</v>
       </c>
       <c r="H3" t="n">
-        <v>8.140000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="I3" t="n">
-        <v>59.91</v>
+        <v>68.41</v>
       </c>
       <c r="J3" t="n">
-        <v>0.37</v>
+        <v>3.61</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>79</v>
       </c>
       <c r="N3" t="n">
-        <v>313.6</v>
+        <v>29.66</v>
       </c>
       <c r="O3" t="n">
-        <v>318</v>
+        <v>3371</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99724.8</v>
+        <v>99983.86</v>
       </c>
       <c r="R3" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>282.24</v>
+        <v>26.69</v>
       </c>
       <c r="T3" t="n">
-        <v>9972.48</v>
+        <v>9998.389999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>366.91</v>
+        <v>35.59</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>19.99</v>
       </c>
       <c r="W3" t="n">
-        <v>16953.22</v>
+        <v>19986.77</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -728,64 +728,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>153.4</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>116.1</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>32.13</v>
+        <v>12.52</v>
       </c>
       <c r="G4" t="n">
-        <v>147.9</v>
+        <v>58.79</v>
       </c>
       <c r="H4" t="n">
-        <v>3.72</v>
+        <v>42.1</v>
       </c>
       <c r="I4" t="n">
-        <v>62.15</v>
+        <v>53.16</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>62.5</v>
       </c>
       <c r="L4" t="n">
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>76.75</v>
+        <v>77.5</v>
       </c>
       <c r="N4" t="n">
-        <v>153.4</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>651</v>
+        <v>1197</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99863.39999999999</v>
+        <v>99997.38</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>138.06</v>
+        <v>75.19</v>
       </c>
       <c r="T4" t="n">
-        <v>9986.34</v>
+        <v>9999.74</v>
       </c>
       <c r="U4" t="n">
-        <v>181.01</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>14.01</v>
       </c>
       <c r="W4" t="n">
-        <v>17975.41</v>
+        <v>14009.63</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,64 +898,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>218.35</v>
+        <v>2104.5</v>
       </c>
       <c r="E6" t="n">
-        <v>186.5</v>
+        <v>1186.88</v>
       </c>
       <c r="F6" t="n">
-        <v>17.08</v>
+        <v>77.31</v>
       </c>
       <c r="G6" t="n">
-        <v>205.9</v>
+        <v>1250</v>
       </c>
       <c r="H6" t="n">
-        <v>6.05</v>
+        <v>68.36</v>
       </c>
       <c r="I6" t="n">
-        <v>56.3</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.49</v>
+        <v>4.22</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
-        <v>73.55</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>218.35</v>
+        <v>2104.5</v>
       </c>
       <c r="O6" t="n">
-        <v>457</v>
+        <v>47</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99785.95</v>
+        <v>98911.5</v>
       </c>
       <c r="R6" t="n">
-        <v>9.98</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>196.52</v>
+        <v>1894.05</v>
       </c>
       <c r="T6" t="n">
-        <v>9978.59</v>
+        <v>9891.15</v>
       </c>
       <c r="U6" t="n">
-        <v>255.47</v>
+        <v>2504.36</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>16963.61</v>
+        <v>18793.19</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -983,64 +983,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>136.6</v>
+        <v>9375</v>
       </c>
       <c r="E7" t="n">
-        <v>97.33</v>
+        <v>6919.23</v>
       </c>
       <c r="F7" t="n">
-        <v>40.35</v>
+        <v>35.49</v>
       </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>7071.5</v>
       </c>
       <c r="H7" t="n">
-        <v>19.82</v>
+        <v>32.57</v>
       </c>
       <c r="I7" t="n">
-        <v>56.99</v>
+        <v>62.98</v>
       </c>
       <c r="J7" t="n">
-        <v>0.17</v>
+        <v>1.36</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>73.55</v>
+        <v>74</v>
       </c>
       <c r="N7" t="n">
-        <v>136.6</v>
+        <v>9375</v>
       </c>
       <c r="O7" t="n">
-        <v>732</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99991.2</v>
+        <v>93750</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>122.94</v>
+        <v>8437.5</v>
       </c>
       <c r="T7" t="n">
-        <v>9999.120000000001</v>
+        <v>9375</v>
       </c>
       <c r="U7" t="n">
-        <v>161.19</v>
+        <v>11156.25</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>17998.42</v>
+        <v>17812.5</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1068,64 +1068,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.39</v>
+        <v>218.35</v>
       </c>
       <c r="E8" t="n">
-        <v>19.37</v>
+        <v>186.5</v>
       </c>
       <c r="F8" t="n">
-        <v>56.89</v>
+        <v>17.08</v>
       </c>
       <c r="G8" t="n">
-        <v>21.25</v>
+        <v>205.9</v>
       </c>
       <c r="H8" t="n">
-        <v>43.01</v>
+        <v>6.05</v>
       </c>
       <c r="I8" t="n">
-        <v>69.37</v>
+        <v>56.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.92</v>
+        <v>0.49</v>
       </c>
       <c r="K8" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>73.5</v>
+        <v>73.55</v>
       </c>
       <c r="N8" t="n">
-        <v>30.39</v>
+        <v>218.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3290</v>
+        <v>457</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99983.10000000001</v>
+        <v>99785.95</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>27.35</v>
+        <v>196.52</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.309999999999</v>
+        <v>9978.59</v>
       </c>
       <c r="U8" t="n">
-        <v>36.16</v>
+        <v>255.47</v>
       </c>
       <c r="V8" t="n">
-        <v>18.99</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>18986.79</v>
+        <v>16963.61</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1153,64 +1153,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>235.79</v>
+        <v>136.6</v>
       </c>
       <c r="E9" t="n">
-        <v>206.92</v>
+        <v>97.33</v>
       </c>
       <c r="F9" t="n">
-        <v>13.95</v>
+        <v>40.35</v>
       </c>
       <c r="G9" t="n">
-        <v>245.38</v>
+        <v>114</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.91</v>
+        <v>19.82</v>
       </c>
       <c r="I9" t="n">
-        <v>59.92</v>
+        <v>56.99</v>
       </c>
       <c r="J9" t="n">
-        <v>0.95</v>
+        <v>0.17</v>
       </c>
       <c r="K9" t="n">
-        <v>53.75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M9" t="n">
-        <v>72.25</v>
+        <v>73.55</v>
       </c>
       <c r="N9" t="n">
-        <v>235.79</v>
+        <v>136.6</v>
       </c>
       <c r="O9" t="n">
-        <v>424</v>
+        <v>732</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99974.96000000001</v>
+        <v>99991.2</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>212.21</v>
+        <v>122.94</v>
       </c>
       <c r="T9" t="n">
-        <v>9997.5</v>
+        <v>9999.120000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>275.87</v>
+        <v>161.19</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>16995.74</v>
+        <v>17998.42</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MOTISONS</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1238,64 +1238,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.3</v>
+        <v>30.39</v>
       </c>
       <c r="E10" t="n">
-        <v>14.1</v>
+        <v>19.37</v>
       </c>
       <c r="F10" t="n">
-        <v>29.81</v>
+        <v>56.89</v>
       </c>
       <c r="G10" t="n">
-        <v>18.12</v>
+        <v>21.25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.99</v>
+        <v>43.01</v>
       </c>
       <c r="I10" t="n">
-        <v>68.69</v>
+        <v>69.37</v>
       </c>
       <c r="J10" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="K10" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="L10" t="n">
         <v>75</v>
       </c>
-      <c r="L10" t="n">
-        <v>68</v>
-      </c>
       <c r="M10" t="n">
-        <v>72.2</v>
+        <v>73.5</v>
       </c>
       <c r="N10" t="n">
-        <v>18.3</v>
+        <v>30.39</v>
       </c>
       <c r="O10" t="n">
-        <v>5464</v>
+        <v>3290</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99991.2</v>
+        <v>99983.10000000001</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>16.47</v>
+        <v>27.35</v>
       </c>
       <c r="T10" t="n">
-        <v>9999.120000000001</v>
+        <v>9998.309999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>21.78</v>
+        <v>36.16</v>
       </c>
       <c r="V10" t="n">
-        <v>19.02</v>
+        <v>18.99</v>
       </c>
       <c r="W10" t="n">
-        <v>19018.33</v>
+        <v>18986.79</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1323,64 +1323,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>283.47</v>
+        <v>895.75</v>
       </c>
       <c r="E11" t="n">
-        <v>212.91</v>
+        <v>702.7</v>
       </c>
       <c r="F11" t="n">
-        <v>33.14</v>
+        <v>27.47</v>
       </c>
       <c r="G11" t="n">
-        <v>241.57</v>
+        <v>513.55</v>
       </c>
       <c r="H11" t="n">
-        <v>17.34</v>
+        <v>74.42</v>
       </c>
       <c r="I11" t="n">
-        <v>52.44</v>
+        <v>50.95</v>
       </c>
       <c r="J11" t="n">
-        <v>0.22</v>
+        <v>1.47</v>
       </c>
       <c r="K11" t="n">
-        <v>57.5</v>
+        <v>66.25</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M11" t="n">
-        <v>72.09999999999999</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>283.47</v>
+        <v>895.75</v>
       </c>
       <c r="O11" t="n">
-        <v>352</v>
+        <v>111</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99781.44</v>
+        <v>99428.25</v>
       </c>
       <c r="R11" t="n">
-        <v>9.98</v>
+        <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>255.12</v>
+        <v>806.1799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>9978.139999999999</v>
+        <v>9942.83</v>
       </c>
       <c r="U11" t="n">
-        <v>325.99</v>
+        <v>1039.07</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>14967.22</v>
+        <v>15908.52</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>588.9</v>
+        <v>331.5</v>
       </c>
       <c r="E2" t="n">
-        <v>497.04</v>
+        <v>250.91</v>
       </c>
       <c r="F2" t="n">
-        <v>18.48</v>
+        <v>32.12</v>
       </c>
       <c r="G2" t="n">
-        <v>539</v>
+        <v>220.4</v>
       </c>
       <c r="H2" t="n">
-        <v>9.26</v>
+        <v>50.41</v>
       </c>
       <c r="I2" t="n">
-        <v>57.9</v>
+        <v>58.37</v>
       </c>
       <c r="J2" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>79.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="N2" t="n">
-        <v>588.9</v>
+        <v>331.5</v>
       </c>
       <c r="O2" t="n">
-        <v>169</v>
+        <v>301</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99524.10000000001</v>
+        <v>99781.5</v>
       </c>
       <c r="R2" t="n">
-        <v>9.949999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="S2" t="n">
-        <v>530.01</v>
+        <v>298.35</v>
       </c>
       <c r="T2" t="n">
-        <v>9952.41</v>
+        <v>9978.15</v>
       </c>
       <c r="U2" t="n">
-        <v>694.9</v>
+        <v>401.12</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>17914.34</v>
+        <v>20954.12</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TREL</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.66</v>
+        <v>598.7</v>
       </c>
       <c r="E3" t="n">
-        <v>25.83</v>
+        <v>497.96</v>
       </c>
       <c r="F3" t="n">
-        <v>14.81</v>
+        <v>20.23</v>
       </c>
       <c r="G3" t="n">
-        <v>29.48</v>
+        <v>539</v>
       </c>
       <c r="H3" t="n">
-        <v>0.61</v>
+        <v>11.08</v>
       </c>
       <c r="I3" t="n">
-        <v>68.41</v>
+        <v>61.13</v>
       </c>
       <c r="J3" t="n">
-        <v>3.61</v>
+        <v>1.91</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L3" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>79</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>29.66</v>
+        <v>598.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3371</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99983.86</v>
+        <v>99982.89999999999</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>26.69</v>
+        <v>538.83</v>
       </c>
       <c r="T3" t="n">
-        <v>9998.389999999999</v>
+        <v>9998.290000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>35.59</v>
+        <v>724.4299999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>19.99</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>19986.77</v>
+        <v>20996.41</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83.54000000000001</v>
+        <v>1468.1</v>
       </c>
       <c r="E4" t="n">
-        <v>74.23999999999999</v>
+        <v>981.9</v>
       </c>
       <c r="F4" t="n">
-        <v>12.52</v>
+        <v>49.52</v>
       </c>
       <c r="G4" t="n">
-        <v>58.79</v>
+        <v>993.8</v>
       </c>
       <c r="H4" t="n">
-        <v>42.1</v>
+        <v>47.73</v>
       </c>
       <c r="I4" t="n">
-        <v>53.16</v>
+        <v>67.09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="K4" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="N4" t="n">
-        <v>83.54000000000001</v>
+        <v>1468.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1197</v>
+        <v>68</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99997.38</v>
+        <v>99830.8</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>75.19</v>
+        <v>1321.29</v>
       </c>
       <c r="T4" t="n">
-        <v>9999.74</v>
+        <v>9983.08</v>
       </c>
       <c r="U4" t="n">
-        <v>95.23999999999999</v>
+        <v>1747.04</v>
       </c>
       <c r="V4" t="n">
-        <v>14.01</v>
+        <v>19</v>
       </c>
       <c r="W4" t="n">
-        <v>14009.63</v>
+        <v>18967.85</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>332.75</v>
+        <v>913.05</v>
       </c>
       <c r="E5" t="n">
-        <v>301.96</v>
+        <v>566.97</v>
       </c>
       <c r="F5" t="n">
-        <v>10.19</v>
+        <v>61.04</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>659.2</v>
       </c>
       <c r="H5" t="n">
-        <v>51.25</v>
+        <v>38.51</v>
       </c>
       <c r="I5" t="n">
-        <v>34.83</v>
+        <v>72.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>77.2</v>
       </c>
       <c r="N5" t="n">
-        <v>332.75</v>
+        <v>913.05</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>109</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99825</v>
+        <v>99522.45</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>299.48</v>
+        <v>821.74</v>
       </c>
       <c r="T5" t="n">
-        <v>9982.5</v>
+        <v>9952.25</v>
       </c>
       <c r="U5" t="n">
-        <v>389.32</v>
+        <v>1077.4</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>16970.25</v>
+        <v>17914.04</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2104.5</v>
+        <v>654.25</v>
       </c>
       <c r="E6" t="n">
-        <v>1186.88</v>
+        <v>526.22</v>
       </c>
       <c r="F6" t="n">
-        <v>77.31</v>
+        <v>24.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1250</v>
+        <v>570</v>
       </c>
       <c r="H6" t="n">
-        <v>68.36</v>
+        <v>14.78</v>
       </c>
       <c r="I6" t="n">
-        <v>69.51000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="J6" t="n">
-        <v>4.22</v>
+        <v>2.46</v>
       </c>
       <c r="K6" t="n">
         <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>74.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="N6" t="n">
-        <v>2104.5</v>
+        <v>654.25</v>
       </c>
       <c r="O6" t="n">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>98911.5</v>
+        <v>99446</v>
       </c>
       <c r="R6" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="S6" t="n">
-        <v>1894.05</v>
+        <v>588.83</v>
       </c>
       <c r="T6" t="n">
-        <v>9891.15</v>
+        <v>9944.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2504.36</v>
+        <v>791.64</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W6" t="n">
-        <v>18793.19</v>
+        <v>20883.66</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9375</v>
+        <v>13.58</v>
       </c>
       <c r="E7" t="n">
-        <v>6919.23</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>35.49</v>
+        <v>38.75</v>
       </c>
       <c r="G7" t="n">
-        <v>7071.5</v>
+        <v>11.38</v>
       </c>
       <c r="H7" t="n">
-        <v>32.57</v>
+        <v>19.33</v>
       </c>
       <c r="I7" t="n">
-        <v>62.98</v>
+        <v>65.64</v>
       </c>
       <c r="J7" t="n">
-        <v>1.36</v>
+        <v>1.89</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L7" t="n">
         <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>74</v>
+        <v>75.5</v>
       </c>
       <c r="N7" t="n">
-        <v>9375</v>
+        <v>13.58</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>7363</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>93750</v>
+        <v>99989.53999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.380000000000001</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>8437.5</v>
+        <v>12.22</v>
       </c>
       <c r="T7" t="n">
-        <v>9375</v>
+        <v>9998.950000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>11156.25</v>
+        <v>16.43</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>20.99</v>
       </c>
       <c r="W7" t="n">
-        <v>17812.5</v>
+        <v>20987.8</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>218.35</v>
+        <v>19.15</v>
       </c>
       <c r="E8" t="n">
-        <v>186.5</v>
+        <v>15.41</v>
       </c>
       <c r="F8" t="n">
-        <v>17.08</v>
+        <v>24.26</v>
       </c>
       <c r="G8" t="n">
-        <v>205.9</v>
+        <v>17.4</v>
       </c>
       <c r="H8" t="n">
-        <v>6.05</v>
+        <v>10.06</v>
       </c>
       <c r="I8" t="n">
-        <v>56.3</v>
+        <v>45.65</v>
       </c>
       <c r="J8" t="n">
-        <v>0.49</v>
+        <v>1.31</v>
       </c>
       <c r="K8" t="n">
         <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>73.55</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>218.35</v>
+        <v>19.15</v>
       </c>
       <c r="O8" t="n">
-        <v>457</v>
+        <v>5221</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99785.95</v>
+        <v>99982.14999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>196.52</v>
+        <v>17.24</v>
       </c>
       <c r="T8" t="n">
-        <v>9978.59</v>
+        <v>9998.219999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>255.47</v>
+        <v>22.21</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>15.98</v>
       </c>
       <c r="W8" t="n">
-        <v>16963.61</v>
+        <v>15977.15</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,34 +1144,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>136.6</v>
+        <v>130.23</v>
       </c>
       <c r="E9" t="n">
-        <v>97.33</v>
+        <v>99.05</v>
       </c>
       <c r="F9" t="n">
-        <v>40.35</v>
+        <v>31.48</v>
       </c>
       <c r="G9" t="n">
-        <v>114</v>
+        <v>108.59</v>
       </c>
       <c r="H9" t="n">
-        <v>19.82</v>
+        <v>19.93</v>
       </c>
       <c r="I9" t="n">
-        <v>56.99</v>
+        <v>56.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="K9" t="n">
         <v>61.25</v>
@@ -1183,34 +1183,34 @@
         <v>73.55</v>
       </c>
       <c r="N9" t="n">
-        <v>136.6</v>
+        <v>130.23</v>
       </c>
       <c r="O9" t="n">
-        <v>732</v>
+        <v>767</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99991.2</v>
+        <v>99886.41</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>122.94</v>
+        <v>117.21</v>
       </c>
       <c r="T9" t="n">
-        <v>9999.120000000001</v>
+        <v>9988.639999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>161.19</v>
+        <v>153.67</v>
       </c>
       <c r="V9" t="n">
         <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>17998.42</v>
+        <v>17979.55</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.39</v>
+        <v>218.58</v>
       </c>
       <c r="E10" t="n">
-        <v>19.37</v>
+        <v>186.94</v>
       </c>
       <c r="F10" t="n">
-        <v>56.89</v>
+        <v>16.92</v>
       </c>
       <c r="G10" t="n">
-        <v>21.25</v>
+        <v>205.9</v>
       </c>
       <c r="H10" t="n">
-        <v>43.01</v>
+        <v>6.16</v>
       </c>
       <c r="I10" t="n">
-        <v>69.37</v>
+        <v>56.49</v>
       </c>
       <c r="J10" t="n">
-        <v>1.92</v>
+        <v>0.23</v>
       </c>
       <c r="K10" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="M10" t="n">
-        <v>73.5</v>
+        <v>73.55</v>
       </c>
       <c r="N10" t="n">
-        <v>30.39</v>
+        <v>218.58</v>
       </c>
       <c r="O10" t="n">
-        <v>3290</v>
+        <v>457</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99983.10000000001</v>
+        <v>99891.06</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>27.35</v>
+        <v>196.72</v>
       </c>
       <c r="T10" t="n">
-        <v>9998.309999999999</v>
+        <v>9989.110000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>36.16</v>
+        <v>255.74</v>
       </c>
       <c r="V10" t="n">
-        <v>18.99</v>
+        <v>17</v>
       </c>
       <c r="W10" t="n">
-        <v>18986.79</v>
+        <v>16981.48</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>895.75</v>
+        <v>137.82</v>
       </c>
       <c r="E11" t="n">
-        <v>702.7</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>27.47</v>
+        <v>40.93</v>
       </c>
       <c r="G11" t="n">
-        <v>513.55</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
-        <v>74.42</v>
+        <v>20.89</v>
       </c>
       <c r="I11" t="n">
-        <v>50.95</v>
+        <v>57.12</v>
       </c>
       <c r="J11" t="n">
-        <v>1.47</v>
+        <v>0.11</v>
       </c>
       <c r="K11" t="n">
-        <v>66.25</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>73.34999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="N11" t="n">
-        <v>895.75</v>
+        <v>137.82</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>725</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99428.25</v>
+        <v>99919.5</v>
       </c>
       <c r="R11" t="n">
-        <v>9.94</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>806.1799999999999</v>
+        <v>124.04</v>
       </c>
       <c r="T11" t="n">
-        <v>9942.83</v>
+        <v>9991.950000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1039.07</v>
+        <v>162.63</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>15908.52</v>
+        <v>17985.51</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>OMAXAUTO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>331.5</v>
+        <v>209.94</v>
       </c>
       <c r="E2" t="n">
-        <v>250.91</v>
+        <v>159.72</v>
       </c>
       <c r="F2" t="n">
-        <v>32.12</v>
+        <v>31.44</v>
       </c>
       <c r="G2" t="n">
-        <v>220.4</v>
+        <v>165.8</v>
       </c>
       <c r="H2" t="n">
-        <v>50.41</v>
+        <v>26.62</v>
       </c>
       <c r="I2" t="n">
-        <v>58.37</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.54</v>
+        <v>2.87</v>
       </c>
       <c r="K2" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>83.5</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>331.5</v>
+        <v>209.94</v>
       </c>
       <c r="O2" t="n">
-        <v>301</v>
+        <v>476</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99781.5</v>
+        <v>99931.44</v>
       </c>
       <c r="R2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>298.35</v>
+        <v>188.95</v>
       </c>
       <c r="T2" t="n">
-        <v>9978.15</v>
+        <v>9993.139999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>401.12</v>
+        <v>254.03</v>
       </c>
       <c r="V2" t="n">
         <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>20954.12</v>
+        <v>20985.6</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>598.7</v>
+        <v>205.65</v>
       </c>
       <c r="E3" t="n">
-        <v>497.96</v>
+        <v>172.22</v>
       </c>
       <c r="F3" t="n">
-        <v>20.23</v>
+        <v>19.41</v>
       </c>
       <c r="G3" t="n">
-        <v>539</v>
+        <v>204.4</v>
       </c>
       <c r="H3" t="n">
-        <v>11.08</v>
+        <v>0.61</v>
       </c>
       <c r="I3" t="n">
-        <v>61.13</v>
+        <v>56.34</v>
       </c>
       <c r="J3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="K3" t="n">
         <v>72.5</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>81.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="N3" t="n">
-        <v>598.7</v>
+        <v>205.65</v>
       </c>
       <c r="O3" t="n">
-        <v>167</v>
+        <v>486</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99982.89999999999</v>
+        <v>99945.89999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>538.83</v>
+        <v>185.08</v>
       </c>
       <c r="T3" t="n">
-        <v>9998.290000000001</v>
+        <v>9994.59</v>
       </c>
       <c r="U3" t="n">
-        <v>724.4299999999999</v>
+        <v>246.78</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W3" t="n">
-        <v>20996.41</v>
+        <v>19989.18</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1468.1</v>
+        <v>546.6</v>
       </c>
       <c r="E4" t="n">
-        <v>981.9</v>
+        <v>451.4</v>
       </c>
       <c r="F4" t="n">
-        <v>49.52</v>
+        <v>21.09</v>
       </c>
       <c r="G4" t="n">
-        <v>993.8</v>
+        <v>552.5</v>
       </c>
       <c r="H4" t="n">
-        <v>47.73</v>
+        <v>-1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>67.09</v>
+        <v>55.14</v>
       </c>
       <c r="J4" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>67.5</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M4" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1468.1</v>
+        <v>546.6</v>
       </c>
       <c r="O4" t="n">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99830.8</v>
+        <v>99481.2</v>
       </c>
       <c r="R4" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1321.29</v>
+        <v>491.94</v>
       </c>
       <c r="T4" t="n">
-        <v>9983.08</v>
+        <v>9948.120000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1747.04</v>
+        <v>650.45</v>
       </c>
       <c r="V4" t="n">
         <v>19</v>
       </c>
       <c r="W4" t="n">
-        <v>18967.85</v>
+        <v>18901.43</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>913.05</v>
+        <v>1053</v>
       </c>
       <c r="E5" t="n">
-        <v>566.97</v>
+        <v>1005.49</v>
       </c>
       <c r="F5" t="n">
-        <v>61.04</v>
+        <v>4.73</v>
       </c>
       <c r="G5" t="n">
-        <v>659.2</v>
+        <v>1039.2</v>
       </c>
       <c r="H5" t="n">
-        <v>38.51</v>
+        <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>72.2</v>
+        <v>48.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="K5" t="n">
-        <v>70</v>
+        <v>63.75</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>77.2</v>
+        <v>75.05</v>
       </c>
       <c r="N5" t="n">
-        <v>913.05</v>
+        <v>1053</v>
       </c>
       <c r="O5" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99522.45</v>
+        <v>98982</v>
       </c>
       <c r="R5" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="S5" t="n">
-        <v>821.74</v>
+        <v>947.7</v>
       </c>
       <c r="T5" t="n">
-        <v>9952.25</v>
+        <v>9898.200000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1077.4</v>
+        <v>1221.48</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>17914.04</v>
+        <v>15837.12</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>654.25</v>
+        <v>1890.9</v>
       </c>
       <c r="E6" t="n">
-        <v>526.22</v>
+        <v>1578.75</v>
       </c>
       <c r="F6" t="n">
-        <v>24.33</v>
+        <v>19.77</v>
       </c>
       <c r="G6" t="n">
-        <v>570</v>
+        <v>1612</v>
       </c>
       <c r="H6" t="n">
-        <v>14.78</v>
+        <v>17.3</v>
       </c>
       <c r="I6" t="n">
-        <v>68.25</v>
+        <v>58.85</v>
       </c>
       <c r="J6" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="K6" t="n">
         <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
-        <v>77</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>654.25</v>
+        <v>1890.9</v>
       </c>
       <c r="O6" t="n">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99446</v>
+        <v>98326.8</v>
       </c>
       <c r="R6" t="n">
-        <v>9.94</v>
+        <v>9.83</v>
       </c>
       <c r="S6" t="n">
-        <v>588.83</v>
+        <v>1701.81</v>
       </c>
       <c r="T6" t="n">
-        <v>9944.6</v>
+        <v>9832.68</v>
       </c>
       <c r="U6" t="n">
-        <v>791.64</v>
+        <v>2231.26</v>
       </c>
       <c r="V6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>20883.66</v>
+        <v>17698.82</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.58</v>
+        <v>84.11</v>
       </c>
       <c r="E7" t="n">
-        <v>9.789999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F7" t="n">
-        <v>38.75</v>
+        <v>12.7</v>
       </c>
       <c r="G7" t="n">
-        <v>11.38</v>
+        <v>58.79</v>
       </c>
       <c r="H7" t="n">
-        <v>19.33</v>
+        <v>43.07</v>
       </c>
       <c r="I7" t="n">
-        <v>65.64</v>
+        <v>54.86</v>
       </c>
       <c r="J7" t="n">
-        <v>1.89</v>
+        <v>0.82</v>
       </c>
       <c r="K7" t="n">
-        <v>72.5</v>
+        <v>57.5</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>75.5</v>
+        <v>74.5</v>
       </c>
       <c r="N7" t="n">
-        <v>13.58</v>
+        <v>84.11</v>
       </c>
       <c r="O7" t="n">
-        <v>7363</v>
+        <v>1188</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99989.53999999999</v>
+        <v>99922.67999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>12.22</v>
+        <v>75.7</v>
       </c>
       <c r="T7" t="n">
-        <v>9998.950000000001</v>
+        <v>9992.27</v>
       </c>
       <c r="U7" t="n">
-        <v>16.43</v>
+        <v>95.89</v>
       </c>
       <c r="V7" t="n">
-        <v>20.99</v>
+        <v>14.01</v>
       </c>
       <c r="W7" t="n">
-        <v>20987.8</v>
+        <v>13999.17</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.15</v>
+        <v>377.95</v>
       </c>
       <c r="E8" t="n">
-        <v>15.41</v>
+        <v>322.77</v>
       </c>
       <c r="F8" t="n">
-        <v>24.26</v>
+        <v>17.09</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
+        <v>386</v>
       </c>
       <c r="H8" t="n">
-        <v>10.06</v>
+        <v>-2.09</v>
       </c>
       <c r="I8" t="n">
-        <v>45.65</v>
+        <v>58.54</v>
       </c>
       <c r="J8" t="n">
-        <v>1.31</v>
+        <v>0.19</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>56.25</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>74.34999999999999</v>
+        <v>73.75</v>
       </c>
       <c r="N8" t="n">
-        <v>19.15</v>
+        <v>377.95</v>
       </c>
       <c r="O8" t="n">
-        <v>5221</v>
+        <v>264</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99982.14999999999</v>
+        <v>99778.8</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>17.24</v>
+        <v>340.16</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.219999999999</v>
+        <v>9977.879999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>22.21</v>
+        <v>442.2</v>
       </c>
       <c r="V8" t="n">
-        <v>15.98</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>15977.15</v>
+        <v>16962.4</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,34 +1144,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>130.23</v>
+        <v>223.69</v>
       </c>
       <c r="E9" t="n">
-        <v>99.05</v>
+        <v>187.21</v>
       </c>
       <c r="F9" t="n">
-        <v>31.48</v>
+        <v>19.48</v>
       </c>
       <c r="G9" t="n">
-        <v>108.59</v>
+        <v>205.9</v>
       </c>
       <c r="H9" t="n">
-        <v>19.93</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>56.3</v>
+        <v>62.48</v>
       </c>
       <c r="J9" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
         <v>61.25</v>
@@ -1183,34 +1183,34 @@
         <v>73.55</v>
       </c>
       <c r="N9" t="n">
-        <v>130.23</v>
+        <v>223.69</v>
       </c>
       <c r="O9" t="n">
-        <v>767</v>
+        <v>447</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99886.41</v>
+        <v>99989.42999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>117.21</v>
+        <v>201.32</v>
       </c>
       <c r="T9" t="n">
-        <v>9988.639999999999</v>
+        <v>9998.940000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>153.67</v>
+        <v>261.72</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W9" t="n">
-        <v>17979.55</v>
+        <v>16998.2</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,34 +1229,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>218.58</v>
+        <v>130.49</v>
       </c>
       <c r="E10" t="n">
-        <v>186.94</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>16.92</v>
+        <v>31.47</v>
       </c>
       <c r="G10" t="n">
-        <v>205.9</v>
+        <v>108.59</v>
       </c>
       <c r="H10" t="n">
-        <v>6.16</v>
+        <v>20.17</v>
       </c>
       <c r="I10" t="n">
-        <v>56.49</v>
+        <v>56.63</v>
       </c>
       <c r="J10" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
@@ -1268,34 +1268,34 @@
         <v>73.55</v>
       </c>
       <c r="N10" t="n">
-        <v>218.58</v>
+        <v>130.49</v>
       </c>
       <c r="O10" t="n">
-        <v>457</v>
+        <v>766</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99891.06</v>
+        <v>99955.34</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>196.72</v>
+        <v>117.44</v>
       </c>
       <c r="T10" t="n">
-        <v>9989.110000000001</v>
+        <v>9995.530000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>255.74</v>
+        <v>153.98</v>
       </c>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>16981.48</v>
+        <v>17991.96</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GANDHITUBE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>137.82</v>
+        <v>995.05</v>
       </c>
       <c r="E11" t="n">
-        <v>97.79000000000001</v>
+        <v>838.36</v>
       </c>
       <c r="F11" t="n">
-        <v>40.93</v>
+        <v>18.69</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>1031.8</v>
       </c>
       <c r="H11" t="n">
-        <v>20.89</v>
+        <v>-3.56</v>
       </c>
       <c r="I11" t="n">
-        <v>57.12</v>
+        <v>73.53</v>
       </c>
       <c r="J11" t="n">
-        <v>0.11</v>
+        <v>1.25</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>57.5</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>73.55</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>137.82</v>
+        <v>995.05</v>
       </c>
       <c r="O11" t="n">
-        <v>725</v>
+        <v>100</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99919.5</v>
+        <v>99505</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>124.04</v>
+        <v>895.54</v>
       </c>
       <c r="T11" t="n">
-        <v>9991.950000000001</v>
+        <v>9950.5</v>
       </c>
       <c r="U11" t="n">
-        <v>162.63</v>
+        <v>1144.31</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>17985.51</v>
+        <v>14925.75</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OMAXAUTO</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>209.94</v>
+        <v>224.98</v>
       </c>
       <c r="E2" t="n">
-        <v>159.72</v>
+        <v>204.63</v>
       </c>
       <c r="F2" t="n">
-        <v>31.44</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>165.8</v>
+        <v>221.5</v>
       </c>
       <c r="H2" t="n">
-        <v>26.62</v>
+        <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>66.45999999999999</v>
+        <v>45.83</v>
       </c>
       <c r="J2" t="n">
-        <v>2.87</v>
+        <v>4.24</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>79.75</v>
       </c>
       <c r="N2" t="n">
-        <v>209.94</v>
+        <v>224.98</v>
       </c>
       <c r="O2" t="n">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99931.44</v>
+        <v>99891.12</v>
       </c>
       <c r="R2" t="n">
         <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>188.95</v>
+        <v>202.48</v>
       </c>
       <c r="T2" t="n">
-        <v>9993.139999999999</v>
+        <v>9989.110000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>254.03</v>
+        <v>260.98</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W2" t="n">
-        <v>20985.6</v>
+        <v>15982.58</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>205.65</v>
+        <v>371.95</v>
       </c>
       <c r="E3" t="n">
-        <v>172.22</v>
+        <v>322.89</v>
       </c>
       <c r="F3" t="n">
-        <v>19.41</v>
+        <v>15.19</v>
       </c>
       <c r="G3" t="n">
-        <v>204.4</v>
+        <v>386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.61</v>
+        <v>-3.64</v>
       </c>
       <c r="I3" t="n">
-        <v>56.34</v>
+        <v>53.31</v>
       </c>
       <c r="J3" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="K3" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>83.5</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>205.65</v>
+        <v>371.95</v>
       </c>
       <c r="O3" t="n">
-        <v>486</v>
+        <v>268</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99945.89999999999</v>
+        <v>99682.60000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>185.08</v>
+        <v>334.76</v>
       </c>
       <c r="T3" t="n">
-        <v>9994.59</v>
+        <v>9968.26</v>
       </c>
       <c r="U3" t="n">
-        <v>246.78</v>
+        <v>435.18</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="W3" t="n">
-        <v>19989.18</v>
+        <v>16946.04</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>546.6</v>
+        <v>329.5</v>
       </c>
       <c r="E4" t="n">
-        <v>451.4</v>
+        <v>303.38</v>
       </c>
       <c r="F4" t="n">
-        <v>21.09</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>552.5</v>
+        <v>220</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.07</v>
+        <v>49.77</v>
       </c>
       <c r="I4" t="n">
-        <v>55.14</v>
+        <v>35.44</v>
       </c>
       <c r="J4" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="K4" t="n">
-        <v>67.5</v>
+        <v>56.25</v>
       </c>
       <c r="L4" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>77.3</v>
+        <v>73.75</v>
       </c>
       <c r="N4" t="n">
-        <v>546.6</v>
+        <v>329.5</v>
       </c>
       <c r="O4" t="n">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99481.2</v>
+        <v>99838.5</v>
       </c>
       <c r="R4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>491.94</v>
+        <v>296.55</v>
       </c>
       <c r="T4" t="n">
-        <v>9948.120000000001</v>
+        <v>9983.85</v>
       </c>
       <c r="U4" t="n">
-        <v>650.45</v>
+        <v>375.63</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W4" t="n">
-        <v>18901.43</v>
+        <v>13977.39</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1053</v>
+        <v>19.26</v>
       </c>
       <c r="E5" t="n">
-        <v>1005.49</v>
+        <v>15.46</v>
       </c>
       <c r="F5" t="n">
-        <v>4.73</v>
+        <v>24.57</v>
       </c>
       <c r="G5" t="n">
-        <v>1039.2</v>
+        <v>17.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>10.69</v>
       </c>
       <c r="I5" t="n">
-        <v>48.2</v>
+        <v>47.42</v>
       </c>
       <c r="J5" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>63.75</v>
+        <v>57.5</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>75.05</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1053</v>
+        <v>19.26</v>
       </c>
       <c r="O5" t="n">
-        <v>94</v>
+        <v>5192</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>98982</v>
+        <v>99997.92</v>
       </c>
       <c r="R5" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>947.7</v>
+        <v>17.33</v>
       </c>
       <c r="T5" t="n">
-        <v>9898.200000000001</v>
+        <v>9999.790000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1221.48</v>
+        <v>22.15</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>15.01</v>
       </c>
       <c r="W5" t="n">
-        <v>15837.12</v>
+        <v>15009.69</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1890.9</v>
+        <v>1868.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1578.75</v>
+        <v>1653.52</v>
       </c>
       <c r="F6" t="n">
-        <v>19.77</v>
+        <v>12.99</v>
       </c>
       <c r="G6" t="n">
-        <v>1612</v>
+        <v>1876</v>
       </c>
       <c r="H6" t="n">
-        <v>17.3</v>
+        <v>-0.41</v>
       </c>
       <c r="I6" t="n">
-        <v>58.85</v>
+        <v>58.49</v>
       </c>
       <c r="J6" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>71.25</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M6" t="n">
-        <v>74.59999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1890.9</v>
+        <v>1868.3</v>
       </c>
       <c r="O6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>98326.8</v>
+        <v>99019.89999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>9.83</v>
+        <v>9.9</v>
       </c>
       <c r="S6" t="n">
-        <v>1701.81</v>
+        <v>1681.47</v>
       </c>
       <c r="T6" t="n">
-        <v>9832.68</v>
+        <v>9901.99</v>
       </c>
       <c r="U6" t="n">
-        <v>2231.26</v>
+        <v>2204.59</v>
       </c>
       <c r="V6" t="n">
         <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>17698.82</v>
+        <v>17823.58</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84.11</v>
+        <v>733.1</v>
       </c>
       <c r="E7" t="n">
-        <v>74.63</v>
+        <v>644.99</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7</v>
+        <v>13.66</v>
       </c>
       <c r="G7" t="n">
-        <v>58.79</v>
+        <v>629.9</v>
       </c>
       <c r="H7" t="n">
-        <v>43.07</v>
+        <v>16.38</v>
       </c>
       <c r="I7" t="n">
-        <v>54.86</v>
+        <v>45.92</v>
       </c>
       <c r="J7" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="K7" t="n">
-        <v>57.5</v>
+        <v>52.5</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>74.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>84.11</v>
+        <v>733.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1188</v>
+        <v>136</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99922.67999999999</v>
+        <v>99701.60000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>75.7</v>
+        <v>659.79</v>
       </c>
       <c r="T7" t="n">
-        <v>9992.27</v>
+        <v>9970.16</v>
       </c>
       <c r="U7" t="n">
-        <v>95.89</v>
+        <v>835.73</v>
       </c>
       <c r="V7" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>13999.17</v>
+        <v>13958.22</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>LINCOLN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>377.95</v>
+        <v>594.65</v>
       </c>
       <c r="E8" t="n">
-        <v>322.77</v>
+        <v>587.33</v>
       </c>
       <c r="F8" t="n">
-        <v>17.09</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>386</v>
+        <v>624.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.09</v>
+        <v>-4.76</v>
       </c>
       <c r="I8" t="n">
-        <v>58.54</v>
+        <v>42.51</v>
       </c>
       <c r="J8" t="n">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="K8" t="n">
-        <v>56.25</v>
+        <v>57.5</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>73.75</v>
+        <v>67.3</v>
       </c>
       <c r="N8" t="n">
-        <v>377.95</v>
+        <v>594.65</v>
       </c>
       <c r="O8" t="n">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99778.8</v>
+        <v>99901.2</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>340.16</v>
+        <v>535.1799999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>9977.879999999999</v>
+        <v>9990.120000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>442.2</v>
+        <v>701.6900000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>16962.4</v>
+        <v>17982.22</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>223.69</v>
+        <v>1478.8</v>
       </c>
       <c r="E9" t="n">
-        <v>187.21</v>
+        <v>1268.47</v>
       </c>
       <c r="F9" t="n">
-        <v>19.48</v>
+        <v>16.58</v>
       </c>
       <c r="G9" t="n">
-        <v>205.9</v>
+        <v>1513</v>
       </c>
       <c r="H9" t="n">
-        <v>8.640000000000001</v>
+        <v>-2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>62.48</v>
+        <v>49.66</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>1.97</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>58.75</v>
       </c>
       <c r="L9" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M9" t="n">
-        <v>73.55</v>
+        <v>67.25</v>
       </c>
       <c r="N9" t="n">
-        <v>223.69</v>
+        <v>1478.8</v>
       </c>
       <c r="O9" t="n">
-        <v>447</v>
+        <v>67</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99989.42999999999</v>
+        <v>99079.60000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="S9" t="n">
-        <v>201.32</v>
+        <v>1330.92</v>
       </c>
       <c r="T9" t="n">
-        <v>9998.940000000001</v>
+        <v>9907.959999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>261.72</v>
+        <v>1730.2</v>
       </c>
       <c r="V9" t="n">
         <v>17</v>
       </c>
       <c r="W9" t="n">
-        <v>16998.2</v>
+        <v>16843.53</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>130.49</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>99.26000000000001</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>31.47</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>108.59</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>20.17</v>
+        <v>-4.35</v>
       </c>
       <c r="I10" t="n">
-        <v>56.63</v>
+        <v>37.78</v>
       </c>
       <c r="J10" t="n">
-        <v>0.47</v>
+        <v>1.78</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>71.25</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>73.55</v>
+        <v>66.75</v>
       </c>
       <c r="N10" t="n">
-        <v>130.49</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>766</v>
+        <v>1424</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99955.34</v>
+        <v>99979.03999999999</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>117.44</v>
+        <v>63.19</v>
       </c>
       <c r="T10" t="n">
-        <v>9995.530000000001</v>
+        <v>9997.9</v>
       </c>
       <c r="U10" t="n">
-        <v>153.98</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>17991.96</v>
+        <v>17996.23</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GANDHITUBE</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>995.05</v>
+        <v>1522</v>
       </c>
       <c r="E11" t="n">
-        <v>838.36</v>
+        <v>1499.69</v>
       </c>
       <c r="F11" t="n">
-        <v>18.69</v>
+        <v>1.49</v>
       </c>
       <c r="G11" t="n">
-        <v>1031.8</v>
+        <v>1551.2</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.56</v>
+        <v>-1.88</v>
       </c>
       <c r="I11" t="n">
-        <v>73.53</v>
+        <v>36.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="K11" t="n">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>72.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>995.05</v>
+        <v>1522</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99505</v>
+        <v>98930</v>
       </c>
       <c r="R11" t="n">
-        <v>9.949999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>895.54</v>
+        <v>1369.8</v>
       </c>
       <c r="T11" t="n">
-        <v>9950.5</v>
+        <v>9893</v>
       </c>
       <c r="U11" t="n">
-        <v>1144.31</v>
+        <v>1765.52</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>14925.75</v>
+        <v>15828.8</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>224.98</v>
+        <v>630.3</v>
       </c>
       <c r="E2" t="n">
-        <v>204.63</v>
+        <v>499.88</v>
       </c>
       <c r="F2" t="n">
-        <v>9.949999999999999</v>
+        <v>26.09</v>
       </c>
       <c r="G2" t="n">
-        <v>221.5</v>
+        <v>539</v>
       </c>
       <c r="H2" t="n">
-        <v>1.57</v>
+        <v>16.94</v>
       </c>
       <c r="I2" t="n">
-        <v>45.83</v>
+        <v>69.56</v>
       </c>
       <c r="J2" t="n">
-        <v>4.24</v>
+        <v>1.37</v>
       </c>
       <c r="K2" t="n">
-        <v>66.25</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>79.75</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>224.98</v>
+        <v>630.3</v>
       </c>
       <c r="O2" t="n">
-        <v>444</v>
+        <v>158</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99891.12</v>
+        <v>99587.39999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>202.48</v>
+        <v>567.27</v>
       </c>
       <c r="T2" t="n">
-        <v>9989.110000000001</v>
+        <v>9958.74</v>
       </c>
       <c r="U2" t="n">
-        <v>260.98</v>
+        <v>750.0599999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W2" t="n">
-        <v>15982.58</v>
+        <v>18921.61</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>371.95</v>
+        <v>280.05</v>
       </c>
       <c r="E3" t="n">
-        <v>322.89</v>
+        <v>218.64</v>
       </c>
       <c r="F3" t="n">
-        <v>15.19</v>
+        <v>28.09</v>
       </c>
       <c r="G3" t="n">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.64</v>
+        <v>-1.74</v>
       </c>
       <c r="I3" t="n">
-        <v>53.31</v>
+        <v>63.57</v>
       </c>
       <c r="J3" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>67.5</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>77.3</v>
       </c>
       <c r="N3" t="n">
-        <v>371.95</v>
+        <v>280.05</v>
       </c>
       <c r="O3" t="n">
-        <v>268</v>
+        <v>357</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99682.60000000001</v>
+        <v>99977.85000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>334.76</v>
+        <v>252.04</v>
       </c>
       <c r="T3" t="n">
-        <v>9968.26</v>
+        <v>9997.780000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>435.18</v>
+        <v>333.26</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
-        <v>16946.04</v>
+        <v>18995.79</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>329.5</v>
+        <v>236.65</v>
       </c>
       <c r="E4" t="n">
-        <v>303.38</v>
+        <v>193.55</v>
       </c>
       <c r="F4" t="n">
-        <v>8.609999999999999</v>
+        <v>22.27</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>173.45</v>
       </c>
       <c r="H4" t="n">
-        <v>49.77</v>
+        <v>36.44</v>
       </c>
       <c r="I4" t="n">
-        <v>35.44</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="K4" t="n">
-        <v>56.25</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>73.75</v>
+        <v>77</v>
       </c>
       <c r="N4" t="n">
-        <v>329.5</v>
+        <v>236.65</v>
       </c>
       <c r="O4" t="n">
-        <v>303</v>
+        <v>422</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99838.5</v>
+        <v>99866.3</v>
       </c>
       <c r="R4" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>296.55</v>
+        <v>212.98</v>
       </c>
       <c r="T4" t="n">
-        <v>9983.85</v>
+        <v>9986.629999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>375.63</v>
+        <v>286.35</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>13977.39</v>
+        <v>20971.92</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.26</v>
+        <v>335.5</v>
       </c>
       <c r="E5" t="n">
-        <v>15.46</v>
+        <v>252.91</v>
       </c>
       <c r="F5" t="n">
-        <v>24.57</v>
+        <v>32.66</v>
       </c>
       <c r="G5" t="n">
-        <v>17.4</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>10.69</v>
+        <v>52.22</v>
       </c>
       <c r="I5" t="n">
-        <v>47.42</v>
+        <v>58.29</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>0.33</v>
       </c>
       <c r="K5" t="n">
-        <v>57.5</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>72.09999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>19.26</v>
+        <v>335.5</v>
       </c>
       <c r="O5" t="n">
-        <v>5192</v>
+        <v>298</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99997.92</v>
+        <v>99979</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>17.33</v>
+        <v>301.95</v>
       </c>
       <c r="T5" t="n">
-        <v>9999.790000000001</v>
+        <v>9997.9</v>
       </c>
       <c r="U5" t="n">
-        <v>22.15</v>
+        <v>395.89</v>
       </c>
       <c r="V5" t="n">
-        <v>15.01</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>15009.69</v>
+        <v>17996.22</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1868.3</v>
+        <v>84.88</v>
       </c>
       <c r="E6" t="n">
-        <v>1653.52</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>12.99</v>
+        <v>13.32</v>
       </c>
       <c r="G6" t="n">
-        <v>1876</v>
+        <v>58.79</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.41</v>
+        <v>44.38</v>
       </c>
       <c r="I6" t="n">
-        <v>58.49</v>
+        <v>56.23</v>
       </c>
       <c r="J6" t="n">
-        <v>1.68</v>
+        <v>0.83</v>
       </c>
       <c r="K6" t="n">
-        <v>71.25</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>69.95</v>
+        <v>76.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1868.3</v>
+        <v>84.88</v>
       </c>
       <c r="O6" t="n">
-        <v>53</v>
+        <v>1178</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99019.89999999999</v>
+        <v>99988.64</v>
       </c>
       <c r="R6" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>1681.47</v>
+        <v>76.39</v>
       </c>
       <c r="T6" t="n">
-        <v>9901.99</v>
+        <v>9998.860000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>2204.59</v>
+        <v>99.31</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W6" t="n">
-        <v>17823.58</v>
+        <v>16998.07</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>733.1</v>
+        <v>1261.7</v>
       </c>
       <c r="E7" t="n">
-        <v>644.99</v>
+        <v>698.83</v>
       </c>
       <c r="F7" t="n">
-        <v>13.66</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>629.9</v>
+        <v>720</v>
       </c>
       <c r="H7" t="n">
-        <v>16.38</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>45.92</v>
+        <v>69.48</v>
       </c>
       <c r="J7" t="n">
-        <v>0.63</v>
+        <v>1.82</v>
       </c>
       <c r="K7" t="n">
-        <v>52.5</v>
+        <v>72.5</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>69.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="N7" t="n">
-        <v>733.1</v>
+        <v>1261.7</v>
       </c>
       <c r="O7" t="n">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99701.60000000001</v>
+        <v>99674.3</v>
       </c>
       <c r="R7" t="n">
         <v>9.970000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>659.79</v>
+        <v>1135.53</v>
       </c>
       <c r="T7" t="n">
-        <v>9970.16</v>
+        <v>9967.43</v>
       </c>
       <c r="U7" t="n">
-        <v>835.73</v>
+        <v>1526.66</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W7" t="n">
-        <v>13958.22</v>
+        <v>20931.6</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LINCOLN</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>594.65</v>
+        <v>535.25</v>
       </c>
       <c r="E8" t="n">
-        <v>587.33</v>
+        <v>452.3</v>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>18.34</v>
       </c>
       <c r="G8" t="n">
-        <v>624.4</v>
+        <v>552.5</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.76</v>
+        <v>-3.12</v>
       </c>
       <c r="I8" t="n">
-        <v>42.51</v>
+        <v>50.88</v>
       </c>
       <c r="J8" t="n">
-        <v>0.46</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>57.5</v>
+        <v>63.75</v>
       </c>
       <c r="L8" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>67.3</v>
+        <v>75.05</v>
       </c>
       <c r="N8" t="n">
-        <v>594.65</v>
+        <v>535.25</v>
       </c>
       <c r="O8" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99901.2</v>
+        <v>99556.5</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>535.1799999999999</v>
+        <v>481.72</v>
       </c>
       <c r="T8" t="n">
-        <v>9990.120000000001</v>
+        <v>9955.65</v>
       </c>
       <c r="U8" t="n">
-        <v>701.6900000000001</v>
+        <v>626.24</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>17982.22</v>
+        <v>16924.6</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>ONELIFECAP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1478.8</v>
+        <v>36.05</v>
       </c>
       <c r="E9" t="n">
-        <v>1268.47</v>
+        <v>23.74</v>
       </c>
       <c r="F9" t="n">
-        <v>16.58</v>
+        <v>51.88</v>
       </c>
       <c r="G9" t="n">
-        <v>1513</v>
+        <v>18.59</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.26</v>
+        <v>93.92</v>
       </c>
       <c r="I9" t="n">
-        <v>49.66</v>
+        <v>64.84</v>
       </c>
       <c r="J9" t="n">
-        <v>1.97</v>
+        <v>2.57</v>
       </c>
       <c r="K9" t="n">
-        <v>58.75</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>67.25</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>1478.8</v>
+        <v>36.05</v>
       </c>
       <c r="O9" t="n">
-        <v>67</v>
+        <v>2773</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99079.60000000001</v>
+        <v>99966.64999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>1330.92</v>
+        <v>32.44</v>
       </c>
       <c r="T9" t="n">
-        <v>9907.959999999999</v>
+        <v>9996.67</v>
       </c>
       <c r="U9" t="n">
-        <v>1730.2</v>
+        <v>42.9</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>16843.53</v>
+        <v>18993.66</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70.20999999999999</v>
+        <v>209.05</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>172.89</v>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>20.92</v>
       </c>
       <c r="G10" t="n">
-        <v>73.40000000000001</v>
+        <v>204.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.35</v>
+        <v>2.27</v>
       </c>
       <c r="I10" t="n">
-        <v>37.78</v>
+        <v>58.94</v>
       </c>
       <c r="J10" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="K10" t="n">
-        <v>71.25</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>66.75</v>
+        <v>75</v>
       </c>
       <c r="N10" t="n">
-        <v>70.20999999999999</v>
+        <v>209.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1424</v>
+        <v>478</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99979.03999999999</v>
+        <v>99925.89999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>63.19</v>
+        <v>188.14</v>
       </c>
       <c r="T10" t="n">
-        <v>9997.9</v>
+        <v>9992.59</v>
       </c>
       <c r="U10" t="n">
-        <v>82.84999999999999</v>
+        <v>248.77</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>17996.23</v>
+        <v>18985.92</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1522</v>
+        <v>49.95</v>
       </c>
       <c r="E11" t="n">
-        <v>1499.69</v>
+        <v>42.47</v>
       </c>
       <c r="F11" t="n">
-        <v>1.49</v>
+        <v>17.61</v>
       </c>
       <c r="G11" t="n">
-        <v>1551.2</v>
+        <v>46.84</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.88</v>
+        <v>6.64</v>
       </c>
       <c r="I11" t="n">
-        <v>36.08</v>
+        <v>69.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="K11" t="n">
         <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>66.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1522</v>
+        <v>49.95</v>
       </c>
       <c r="O11" t="n">
-        <v>65</v>
+        <v>2002</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>98930</v>
+        <v>99999.89999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>1369.8</v>
+        <v>44.96</v>
       </c>
       <c r="T11" t="n">
-        <v>9893</v>
+        <v>9999.99</v>
       </c>
       <c r="U11" t="n">
-        <v>1765.52</v>
+        <v>58.94</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>15828.8</v>
+        <v>17999.98</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -1256,7 +1256,7 @@
         <v>58.94</v>
       </c>
       <c r="J10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
         <v>75</v>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>630.3</v>
+        <v>19.79</v>
       </c>
       <c r="E2" t="n">
-        <v>499.88</v>
+        <v>15.51</v>
       </c>
       <c r="F2" t="n">
-        <v>26.09</v>
+        <v>27.58</v>
       </c>
       <c r="G2" t="n">
-        <v>539</v>
+        <v>17.4</v>
       </c>
       <c r="H2" t="n">
-        <v>16.94</v>
+        <v>13.74</v>
       </c>
       <c r="I2" t="n">
-        <v>69.56</v>
+        <v>54.66</v>
       </c>
       <c r="J2" t="n">
-        <v>1.37</v>
+        <v>1.99</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>68.75</v>
       </c>
       <c r="L2" t="n">
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>79.59999999999999</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>630.3</v>
+        <v>19.79</v>
       </c>
       <c r="O2" t="n">
-        <v>158</v>
+        <v>5053</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99587.39999999999</v>
+        <v>99998.87</v>
       </c>
       <c r="R2" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>567.27</v>
+        <v>17.81</v>
       </c>
       <c r="T2" t="n">
-        <v>9958.74</v>
+        <v>9999.889999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>750.0599999999999</v>
+        <v>23.35</v>
       </c>
       <c r="V2" t="n">
-        <v>19</v>
+        <v>17.99</v>
       </c>
       <c r="W2" t="n">
-        <v>18921.61</v>
+        <v>17989.8</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>280.05</v>
+        <v>477.55</v>
       </c>
       <c r="E3" t="n">
-        <v>218.64</v>
+        <v>332.66</v>
       </c>
       <c r="F3" t="n">
-        <v>28.09</v>
+        <v>43.55</v>
       </c>
       <c r="G3" t="n">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.74</v>
+        <v>60.25</v>
       </c>
       <c r="I3" t="n">
-        <v>63.57</v>
+        <v>52.55</v>
       </c>
       <c r="J3" t="n">
-        <v>1.23</v>
+        <v>15.27</v>
       </c>
       <c r="K3" t="n">
-        <v>67.5</v>
+        <v>71.25</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M3" t="n">
-        <v>77.3</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>280.05</v>
+        <v>477.55</v>
       </c>
       <c r="O3" t="n">
-        <v>357</v>
+        <v>209</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99977.85000000001</v>
+        <v>99807.95</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>252.04</v>
+        <v>429.8</v>
       </c>
       <c r="T3" t="n">
-        <v>9997.780000000001</v>
+        <v>9980.799999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>333.26</v>
+        <v>563.51</v>
       </c>
       <c r="V3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>18995.79</v>
+        <v>17965.43</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -724,68 +724,68 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>236.65</v>
+        <v>234.4</v>
       </c>
       <c r="E4" t="n">
-        <v>193.55</v>
+        <v>194.04</v>
       </c>
       <c r="F4" t="n">
-        <v>22.27</v>
+        <v>20.8</v>
       </c>
       <c r="G4" t="n">
         <v>173.45</v>
       </c>
       <c r="H4" t="n">
-        <v>36.44</v>
+        <v>35.14</v>
       </c>
       <c r="I4" t="n">
-        <v>66.59999999999999</v>
+        <v>62.83</v>
       </c>
       <c r="J4" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
         <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>77</v>
+        <v>75.5</v>
       </c>
       <c r="N4" t="n">
-        <v>236.65</v>
+        <v>234.4</v>
       </c>
       <c r="O4" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99866.3</v>
+        <v>99854.39999999999</v>
       </c>
       <c r="R4" t="n">
         <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>212.98</v>
+        <v>210.96</v>
       </c>
       <c r="T4" t="n">
-        <v>9986.629999999999</v>
+        <v>9985.440000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>286.35</v>
+        <v>283.62</v>
       </c>
       <c r="V4" t="n">
         <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>20971.92</v>
+        <v>20969.42</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>335.5</v>
+        <v>325</v>
       </c>
       <c r="E5" t="n">
-        <v>252.91</v>
+        <v>304.02</v>
       </c>
       <c r="F5" t="n">
-        <v>32.66</v>
+        <v>6.9</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>220</v>
       </c>
       <c r="H5" t="n">
-        <v>52.22</v>
+        <v>47.73</v>
       </c>
       <c r="I5" t="n">
-        <v>58.29</v>
+        <v>34.32</v>
       </c>
       <c r="J5" t="n">
-        <v>0.33</v>
+        <v>1.53</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>58.75</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>75.25</v>
       </c>
       <c r="N5" t="n">
-        <v>335.5</v>
+        <v>325</v>
       </c>
       <c r="O5" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99979</v>
+        <v>99775</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>301.95</v>
+        <v>292.5</v>
       </c>
       <c r="T5" t="n">
-        <v>9997.9</v>
+        <v>9977.5</v>
       </c>
       <c r="U5" t="n">
-        <v>395.89</v>
+        <v>377</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>17996.22</v>
+        <v>15964</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>84.88</v>
+        <v>2194.6</v>
       </c>
       <c r="E6" t="n">
-        <v>74.90000000000001</v>
+        <v>1219.86</v>
       </c>
       <c r="F6" t="n">
-        <v>13.32</v>
+        <v>79.91</v>
       </c>
       <c r="G6" t="n">
-        <v>58.79</v>
+        <v>1250</v>
       </c>
       <c r="H6" t="n">
-        <v>44.38</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>56.23</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.83</v>
+        <v>2.29</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
-        <v>76.75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>84.88</v>
+        <v>2194.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1178</v>
+        <v>45</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99988.64</v>
+        <v>98757</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>76.39</v>
+        <v>1975.14</v>
       </c>
       <c r="T6" t="n">
-        <v>9998.860000000001</v>
+        <v>9875.700000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>99.31</v>
+        <v>2611.57</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>16998.07</v>
+        <v>18763.83</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>DIVGIITTS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1261.7</v>
+        <v>1218.6</v>
       </c>
       <c r="E7" t="n">
-        <v>698.83</v>
+        <v>823.76</v>
       </c>
       <c r="F7" t="n">
-        <v>80.54000000000001</v>
+        <v>47.93</v>
       </c>
       <c r="G7" t="n">
-        <v>720</v>
+        <v>807.4</v>
       </c>
       <c r="H7" t="n">
-        <v>75.23999999999999</v>
+        <v>50.93</v>
       </c>
       <c r="I7" t="n">
-        <v>69.48</v>
+        <v>59.33</v>
       </c>
       <c r="J7" t="n">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="K7" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
-        <v>75.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>1261.7</v>
+        <v>1218.6</v>
       </c>
       <c r="O7" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99674.3</v>
+        <v>99925.2</v>
       </c>
       <c r="R7" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>1135.53</v>
+        <v>1096.74</v>
       </c>
       <c r="T7" t="n">
-        <v>9967.43</v>
+        <v>9992.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1526.66</v>
+        <v>1450.13</v>
       </c>
       <c r="V7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>20931.6</v>
+        <v>18985.79</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>535.25</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>452.3</v>
+        <v>75.02</v>
       </c>
       <c r="F8" t="n">
-        <v>18.34</v>
+        <v>7.77</v>
       </c>
       <c r="G8" t="n">
-        <v>552.5</v>
+        <v>58.79</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.12</v>
+        <v>37.52</v>
       </c>
       <c r="I8" t="n">
-        <v>50.88</v>
+        <v>45.31</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="K8" t="n">
-        <v>63.75</v>
+        <v>57.5</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>75.05</v>
+        <v>74.5</v>
       </c>
       <c r="N8" t="n">
-        <v>535.25</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>186</v>
+        <v>1236</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99556.5</v>
+        <v>99930.60000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>481.72</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>9955.65</v>
+        <v>9993.059999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>626.24</v>
+        <v>91.36</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>16924.6</v>
+        <v>12990.98</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ONELIFECAP</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36.05</v>
+        <v>620.65</v>
       </c>
       <c r="E9" t="n">
-        <v>23.74</v>
+        <v>500.53</v>
       </c>
       <c r="F9" t="n">
-        <v>51.88</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>18.59</v>
+        <v>539</v>
       </c>
       <c r="H9" t="n">
-        <v>93.92</v>
+        <v>15.15</v>
       </c>
       <c r="I9" t="n">
-        <v>64.84</v>
+        <v>64.39</v>
       </c>
       <c r="J9" t="n">
-        <v>2.57</v>
+        <v>0.39</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>36.05</v>
+        <v>620.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2773</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99966.64999999999</v>
+        <v>99924.64999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>32.44</v>
+        <v>558.58</v>
       </c>
       <c r="T9" t="n">
-        <v>9996.67</v>
+        <v>9992.459999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>42.9</v>
+        <v>732.37</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>18993.66</v>
+        <v>17986.44</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>209.05</v>
+        <v>285.15</v>
       </c>
       <c r="E10" t="n">
-        <v>172.89</v>
+        <v>218.96</v>
       </c>
       <c r="F10" t="n">
-        <v>20.92</v>
+        <v>30.23</v>
       </c>
       <c r="G10" t="n">
-        <v>204.4</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>2.27</v>
+        <v>0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>58.94</v>
+        <v>65.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>0.85</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="M10" t="n">
-        <v>75</v>
+        <v>73.55</v>
       </c>
       <c r="N10" t="n">
-        <v>209.05</v>
+        <v>285.15</v>
       </c>
       <c r="O10" t="n">
-        <v>478</v>
+        <v>350</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99925.89999999999</v>
+        <v>99802.5</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S10" t="n">
-        <v>188.14</v>
+        <v>256.64</v>
       </c>
       <c r="T10" t="n">
-        <v>9992.59</v>
+        <v>9980.25</v>
       </c>
       <c r="U10" t="n">
-        <v>248.77</v>
+        <v>336.48</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>18985.92</v>
+        <v>17964.45</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49.95</v>
+        <v>369.35</v>
       </c>
       <c r="E11" t="n">
-        <v>42.47</v>
+        <v>323.07</v>
       </c>
       <c r="F11" t="n">
-        <v>17.61</v>
+        <v>14.33</v>
       </c>
       <c r="G11" t="n">
-        <v>46.84</v>
+        <v>386</v>
       </c>
       <c r="H11" t="n">
-        <v>6.64</v>
+        <v>-4.31</v>
       </c>
       <c r="I11" t="n">
-        <v>69.7</v>
+        <v>51.33</v>
       </c>
       <c r="J11" t="n">
-        <v>2.26</v>
+        <v>1.19</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="L11" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>73.8</v>
+        <v>73</v>
       </c>
       <c r="N11" t="n">
-        <v>49.95</v>
+        <v>369.35</v>
       </c>
       <c r="O11" t="n">
-        <v>2002</v>
+        <v>270</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99999.89999999999</v>
+        <v>99724.5</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>44.96</v>
+        <v>332.42</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.99</v>
+        <v>9972.450000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>58.94</v>
+        <v>421.06</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>17999.98</v>
+        <v>13961.43</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.79</v>
+        <v>375.65</v>
       </c>
       <c r="E2" t="n">
-        <v>15.51</v>
+        <v>323.21</v>
       </c>
       <c r="F2" t="n">
-        <v>27.58</v>
+        <v>16.23</v>
       </c>
       <c r="G2" t="n">
-        <v>17.4</v>
+        <v>386</v>
       </c>
       <c r="H2" t="n">
-        <v>13.74</v>
+        <v>-2.68</v>
       </c>
       <c r="I2" t="n">
-        <v>54.66</v>
+        <v>55.26</v>
       </c>
       <c r="J2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="K2" t="n">
-        <v>68.75</v>
+        <v>67.5</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>78.84999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="N2" t="n">
-        <v>19.79</v>
+        <v>375.65</v>
       </c>
       <c r="O2" t="n">
-        <v>5053</v>
+        <v>266</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99998.87</v>
+        <v>99922.89999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>17.81</v>
+        <v>338.08</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.889999999999</v>
+        <v>9992.290000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>23.35</v>
+        <v>450.78</v>
       </c>
       <c r="V2" t="n">
-        <v>17.99</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>17989.8</v>
+        <v>19984.58</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INDOBORAX</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>477.55</v>
+        <v>48.71</v>
       </c>
       <c r="E3" t="n">
-        <v>332.66</v>
+        <v>42.56</v>
       </c>
       <c r="F3" t="n">
-        <v>43.55</v>
+        <v>14.45</v>
       </c>
       <c r="G3" t="n">
-        <v>298</v>
+        <v>46.84</v>
       </c>
       <c r="H3" t="n">
-        <v>60.25</v>
+        <v>3.99</v>
       </c>
       <c r="I3" t="n">
-        <v>52.55</v>
+        <v>60.84</v>
       </c>
       <c r="J3" t="n">
-        <v>15.27</v>
+        <v>0.82</v>
       </c>
       <c r="K3" t="n">
-        <v>71.25</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>78.34999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>477.55</v>
+        <v>48.71</v>
       </c>
       <c r="O3" t="n">
-        <v>209</v>
+        <v>2052</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99807.95</v>
+        <v>99952.92</v>
       </c>
       <c r="R3" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>429.8</v>
+        <v>43.84</v>
       </c>
       <c r="T3" t="n">
-        <v>9980.799999999999</v>
+        <v>9995.290000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>563.51</v>
+        <v>56.99</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W3" t="n">
-        <v>17965.43</v>
+        <v>16992</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>234.4</v>
+        <v>320.2</v>
       </c>
       <c r="E4" t="n">
-        <v>194.04</v>
+        <v>304.31</v>
       </c>
       <c r="F4" t="n">
-        <v>20.8</v>
+        <v>5.22</v>
       </c>
       <c r="G4" t="n">
-        <v>173.45</v>
+        <v>220</v>
       </c>
       <c r="H4" t="n">
-        <v>35.14</v>
+        <v>45.55</v>
       </c>
       <c r="I4" t="n">
-        <v>62.83</v>
+        <v>30.95</v>
       </c>
       <c r="J4" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>58.75</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>75.5</v>
+        <v>75.25</v>
       </c>
       <c r="N4" t="n">
-        <v>234.4</v>
+        <v>320.2</v>
       </c>
       <c r="O4" t="n">
-        <v>426</v>
+        <v>312</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99854.39999999999</v>
+        <v>99902.39999999999</v>
       </c>
       <c r="R4" t="n">
         <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>210.96</v>
+        <v>288.18</v>
       </c>
       <c r="T4" t="n">
-        <v>9985.440000000001</v>
+        <v>9990.24</v>
       </c>
       <c r="U4" t="n">
-        <v>283.62</v>
+        <v>371.43</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>20969.42</v>
+        <v>15984.38</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,34 +804,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>325</v>
+        <v>79.16</v>
       </c>
       <c r="E5" t="n">
-        <v>304.02</v>
+        <v>75.13</v>
       </c>
       <c r="F5" t="n">
-        <v>6.9</v>
+        <v>5.36</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>58.79</v>
       </c>
       <c r="H5" t="n">
-        <v>47.73</v>
+        <v>34.65</v>
       </c>
       <c r="I5" t="n">
-        <v>34.32</v>
+        <v>41.66</v>
       </c>
       <c r="J5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="K5" t="n">
         <v>58.75</v>
@@ -843,34 +843,34 @@
         <v>75.25</v>
       </c>
       <c r="N5" t="n">
-        <v>325</v>
+        <v>79.16</v>
       </c>
       <c r="O5" t="n">
-        <v>307</v>
+        <v>1263</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99775</v>
+        <v>99979.08</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>292.5</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>9977.5</v>
+        <v>9997.91</v>
       </c>
       <c r="U5" t="n">
-        <v>377</v>
+        <v>91.83</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="W5" t="n">
-        <v>15964</v>
+        <v>16006.65</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2194.6</v>
+        <v>199.83</v>
       </c>
       <c r="E6" t="n">
-        <v>1219.86</v>
+        <v>185.69</v>
       </c>
       <c r="F6" t="n">
-        <v>79.91</v>
+        <v>7.62</v>
       </c>
       <c r="G6" t="n">
-        <v>1250</v>
+        <v>202.4</v>
       </c>
       <c r="H6" t="n">
-        <v>75.56999999999999</v>
+        <v>-1.27</v>
       </c>
       <c r="I6" t="n">
-        <v>67.20999999999999</v>
+        <v>66.17</v>
       </c>
       <c r="J6" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>74.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>2194.6</v>
+        <v>199.83</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>500</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>98757</v>
+        <v>99915</v>
       </c>
       <c r="R6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>1975.14</v>
+        <v>179.85</v>
       </c>
       <c r="T6" t="n">
-        <v>9875.700000000001</v>
+        <v>9991.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2611.57</v>
+        <v>233.8</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W6" t="n">
-        <v>18763.83</v>
+        <v>16985.55</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIVGIITTS</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1218.6</v>
+        <v>1435.5</v>
       </c>
       <c r="E7" t="n">
-        <v>823.76</v>
+        <v>999.86</v>
       </c>
       <c r="F7" t="n">
-        <v>47.93</v>
+        <v>43.57</v>
       </c>
       <c r="G7" t="n">
-        <v>807.4</v>
+        <v>993.8</v>
       </c>
       <c r="H7" t="n">
-        <v>50.93</v>
+        <v>44.45</v>
       </c>
       <c r="I7" t="n">
-        <v>59.33</v>
+        <v>59.86</v>
       </c>
       <c r="J7" t="n">
-        <v>2.49</v>
+        <v>0.62</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="M7" t="n">
-        <v>74.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="N7" t="n">
-        <v>1218.6</v>
+        <v>1435.5</v>
       </c>
       <c r="O7" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99925.2</v>
+        <v>99049.5</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1096.74</v>
+        <v>1291.95</v>
       </c>
       <c r="T7" t="n">
-        <v>9992.52</v>
+        <v>9904.950000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1450.13</v>
+        <v>1693.89</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>18985.79</v>
+        <v>17828.91</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80.84999999999999</v>
+        <v>872.5</v>
       </c>
       <c r="E8" t="n">
-        <v>75.02</v>
+        <v>576.38</v>
       </c>
       <c r="F8" t="n">
-        <v>7.77</v>
+        <v>51.38</v>
       </c>
       <c r="G8" t="n">
-        <v>58.79</v>
+        <v>659.2</v>
       </c>
       <c r="H8" t="n">
-        <v>37.52</v>
+        <v>32.36</v>
       </c>
       <c r="I8" t="n">
-        <v>45.31</v>
+        <v>59.34</v>
       </c>
       <c r="J8" t="n">
-        <v>1.12</v>
+        <v>0.74</v>
       </c>
       <c r="K8" t="n">
-        <v>57.5</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M8" t="n">
-        <v>74.5</v>
+        <v>71.95</v>
       </c>
       <c r="N8" t="n">
-        <v>80.84999999999999</v>
+        <v>872.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1236</v>
+        <v>114</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99930.60000000001</v>
+        <v>99465</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>72.76000000000001</v>
+        <v>785.25</v>
       </c>
       <c r="T8" t="n">
-        <v>9993.059999999999</v>
+        <v>9946.5</v>
       </c>
       <c r="U8" t="n">
-        <v>91.36</v>
+        <v>1029.55</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>12990.98</v>
+        <v>17903.7</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>620.65</v>
+        <v>324.25</v>
       </c>
       <c r="E9" t="n">
-        <v>500.53</v>
+        <v>254.1</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>27.61</v>
       </c>
       <c r="G9" t="n">
-        <v>539</v>
+        <v>220.4</v>
       </c>
       <c r="H9" t="n">
-        <v>15.15</v>
+        <v>47.12</v>
       </c>
       <c r="I9" t="n">
-        <v>64.39</v>
+        <v>49.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39</v>
+        <v>0.66</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>52.5</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="N9" t="n">
-        <v>620.65</v>
+        <v>324.25</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>308</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99924.64999999999</v>
+        <v>99869</v>
       </c>
       <c r="R9" t="n">
         <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>558.58</v>
+        <v>291.82</v>
       </c>
       <c r="T9" t="n">
-        <v>9992.459999999999</v>
+        <v>9986.9</v>
       </c>
       <c r="U9" t="n">
-        <v>732.37</v>
+        <v>372.89</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>17986.44</v>
+        <v>14980.35</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1234,68 +1234,68 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>285.15</v>
+        <v>288.9</v>
       </c>
       <c r="E10" t="n">
-        <v>218.96</v>
+        <v>219.3</v>
       </c>
       <c r="F10" t="n">
-        <v>30.23</v>
+        <v>31.74</v>
       </c>
       <c r="G10" t="n">
         <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05</v>
+        <v>1.37</v>
       </c>
       <c r="I10" t="n">
-        <v>65.5</v>
+        <v>66.88</v>
       </c>
       <c r="J10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>73.55</v>
+        <v>70.75</v>
       </c>
       <c r="N10" t="n">
-        <v>285.15</v>
+        <v>288.9</v>
       </c>
       <c r="O10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99802.5</v>
+        <v>99959.39999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>256.64</v>
+        <v>260.01</v>
       </c>
       <c r="T10" t="n">
-        <v>9980.25</v>
+        <v>9995.940000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>336.48</v>
+        <v>340.9</v>
       </c>
       <c r="V10" t="n">
         <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>17964.45</v>
+        <v>17992.69</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>369.35</v>
+        <v>1162.5</v>
       </c>
       <c r="E11" t="n">
-        <v>323.07</v>
+        <v>706.49</v>
       </c>
       <c r="F11" t="n">
-        <v>14.33</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>386</v>
+        <v>720</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.31</v>
+        <v>61.46</v>
       </c>
       <c r="I11" t="n">
-        <v>51.33</v>
+        <v>59.17</v>
       </c>
       <c r="J11" t="n">
-        <v>1.19</v>
+        <v>0.32</v>
       </c>
       <c r="K11" t="n">
-        <v>55</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M11" t="n">
-        <v>73</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>369.35</v>
+        <v>1162.5</v>
       </c>
       <c r="O11" t="n">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99724.5</v>
+        <v>99975</v>
       </c>
       <c r="R11" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>332.42</v>
+        <v>1046.25</v>
       </c>
       <c r="T11" t="n">
-        <v>9972.450000000001</v>
+        <v>9997.5</v>
       </c>
       <c r="U11" t="n">
-        <v>421.06</v>
+        <v>1371.75</v>
       </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>13961.43</v>
+        <v>17995.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>375.65</v>
+        <v>67.5</v>
       </c>
       <c r="E2" t="n">
-        <v>323.21</v>
+        <v>60.41</v>
       </c>
       <c r="F2" t="n">
-        <v>16.23</v>
+        <v>11.74</v>
       </c>
       <c r="G2" t="n">
-        <v>386</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.68</v>
+        <v>-0.74</v>
       </c>
       <c r="I2" t="n">
-        <v>55.26</v>
+        <v>55.12</v>
       </c>
       <c r="J2" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="K2" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>92</v>
+      </c>
+      <c r="M2" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="N2" t="n">
         <v>67.5</v>
       </c>
-      <c r="L2" t="n">
-        <v>100</v>
-      </c>
-      <c r="M2" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>375.65</v>
-      </c>
       <c r="O2" t="n">
-        <v>266</v>
+        <v>1481</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99922.89999999999</v>
+        <v>99967.5</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>338.08</v>
+        <v>60.75</v>
       </c>
       <c r="T2" t="n">
-        <v>9992.290000000001</v>
+        <v>9996.75</v>
       </c>
       <c r="U2" t="n">
-        <v>450.78</v>
+        <v>81</v>
       </c>
       <c r="V2" t="n">
         <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>19984.58</v>
+        <v>19993.5</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.71</v>
+        <v>21.8</v>
       </c>
       <c r="E3" t="n">
-        <v>42.56</v>
+        <v>15.58</v>
       </c>
       <c r="F3" t="n">
-        <v>14.45</v>
+        <v>39.93</v>
       </c>
       <c r="G3" t="n">
-        <v>46.84</v>
+        <v>17.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.99</v>
+        <v>25.29</v>
       </c>
       <c r="I3" t="n">
-        <v>60.84</v>
+        <v>71.48</v>
       </c>
       <c r="J3" t="n">
-        <v>0.82</v>
+        <v>3.48</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>48.71</v>
+        <v>21.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2052</v>
+        <v>4587</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99952.92</v>
+        <v>99996.60000000001</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>43.84</v>
+        <v>19.62</v>
       </c>
       <c r="T3" t="n">
-        <v>9995.290000000001</v>
+        <v>9999.66</v>
       </c>
       <c r="U3" t="n">
-        <v>56.99</v>
+        <v>25.72</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>17.98</v>
       </c>
       <c r="W3" t="n">
-        <v>16992</v>
+        <v>17979.39</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>320.2</v>
+        <v>232.2</v>
       </c>
       <c r="E4" t="n">
-        <v>304.31</v>
+        <v>194.97</v>
       </c>
       <c r="F4" t="n">
-        <v>5.22</v>
+        <v>19.1</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>173.45</v>
       </c>
       <c r="H4" t="n">
-        <v>45.55</v>
+        <v>33.87</v>
       </c>
       <c r="I4" t="n">
-        <v>30.95</v>
+        <v>57.43</v>
       </c>
       <c r="J4" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="K4" t="n">
-        <v>58.75</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="N4" t="n">
-        <v>320.2</v>
+        <v>232.2</v>
       </c>
       <c r="O4" t="n">
-        <v>312</v>
+        <v>430</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99902.39999999999</v>
+        <v>99846</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>288.18</v>
+        <v>208.98</v>
       </c>
       <c r="T4" t="n">
-        <v>9990.24</v>
+        <v>9984.6</v>
       </c>
       <c r="U4" t="n">
-        <v>371.43</v>
+        <v>278.64</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="W4" t="n">
-        <v>15984.38</v>
+        <v>19969.2</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,34 +804,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79.16</v>
+        <v>374.2</v>
       </c>
       <c r="E5" t="n">
-        <v>75.13</v>
+        <v>323.36</v>
       </c>
       <c r="F5" t="n">
-        <v>5.36</v>
+        <v>15.72</v>
       </c>
       <c r="G5" t="n">
-        <v>58.79</v>
+        <v>386</v>
       </c>
       <c r="H5" t="n">
-        <v>34.65</v>
+        <v>-3.06</v>
       </c>
       <c r="I5" t="n">
-        <v>41.66</v>
+        <v>54.17</v>
       </c>
       <c r="J5" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="K5" t="n">
         <v>58.75</v>
@@ -843,34 +843,34 @@
         <v>75.25</v>
       </c>
       <c r="N5" t="n">
-        <v>79.16</v>
+        <v>374.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1263</v>
+        <v>267</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99979.08</v>
+        <v>99911.39999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>71.23999999999999</v>
+        <v>336.78</v>
       </c>
       <c r="T5" t="n">
-        <v>9997.91</v>
+        <v>9991.139999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>91.83</v>
+        <v>430.33</v>
       </c>
       <c r="V5" t="n">
-        <v>16.01</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>16006.65</v>
+        <v>14986.71</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>199.83</v>
+        <v>329</v>
       </c>
       <c r="E6" t="n">
-        <v>185.69</v>
+        <v>254.74</v>
       </c>
       <c r="F6" t="n">
-        <v>7.62</v>
+        <v>29.15</v>
       </c>
       <c r="G6" t="n">
-        <v>202.4</v>
+        <v>220.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.27</v>
+        <v>49.27</v>
       </c>
       <c r="I6" t="n">
-        <v>66.17</v>
+        <v>53.06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.62</v>
+        <v>0.55</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>57.5</v>
       </c>
       <c r="L6" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>73.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="N6" t="n">
-        <v>199.83</v>
+        <v>329</v>
       </c>
       <c r="O6" t="n">
-        <v>500</v>
+        <v>303</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99915</v>
+        <v>99687</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>179.85</v>
+        <v>296.1</v>
       </c>
       <c r="T6" t="n">
-        <v>9991.5</v>
+        <v>9968.700000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>233.8</v>
+        <v>378.35</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>16985.55</v>
+        <v>14953.05</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1435.5</v>
+        <v>604.4</v>
       </c>
       <c r="E7" t="n">
-        <v>999.86</v>
+        <v>501.68</v>
       </c>
       <c r="F7" t="n">
-        <v>43.57</v>
+        <v>20.47</v>
       </c>
       <c r="G7" t="n">
-        <v>993.8</v>
+        <v>539</v>
       </c>
       <c r="H7" t="n">
-        <v>44.45</v>
+        <v>12.13</v>
       </c>
       <c r="I7" t="n">
-        <v>59.86</v>
+        <v>56.53</v>
       </c>
       <c r="J7" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="K7" t="n">
         <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>71.95</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>1435.5</v>
+        <v>604.4</v>
       </c>
       <c r="O7" t="n">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99049.5</v>
+        <v>99726</v>
       </c>
       <c r="R7" t="n">
-        <v>9.9</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1291.95</v>
+        <v>543.96</v>
       </c>
       <c r="T7" t="n">
-        <v>9904.950000000001</v>
+        <v>9972.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1693.89</v>
+        <v>713.1900000000001</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>17828.91</v>
+        <v>17950.68</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>872.5</v>
+        <v>734.35</v>
       </c>
       <c r="E8" t="n">
-        <v>576.38</v>
+        <v>649.72</v>
       </c>
       <c r="F8" t="n">
-        <v>51.38</v>
+        <v>13.02</v>
       </c>
       <c r="G8" t="n">
-        <v>659.2</v>
+        <v>629.9</v>
       </c>
       <c r="H8" t="n">
-        <v>32.36</v>
+        <v>16.58</v>
       </c>
       <c r="I8" t="n">
-        <v>59.34</v>
+        <v>47.76</v>
       </c>
       <c r="J8" t="n">
-        <v>0.74</v>
+        <v>1.38</v>
       </c>
       <c r="K8" t="n">
         <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>71.95</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>872.5</v>
+        <v>734.35</v>
       </c>
       <c r="O8" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99465</v>
+        <v>99871.60000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.949999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>785.25</v>
+        <v>660.92</v>
       </c>
       <c r="T8" t="n">
-        <v>9946.5</v>
+        <v>9987.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1029.55</v>
+        <v>844.5</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>17903.7</v>
+        <v>14980.74</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>324.25</v>
+        <v>79.37</v>
       </c>
       <c r="E9" t="n">
-        <v>254.1</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>27.61</v>
+        <v>5.49</v>
       </c>
       <c r="G9" t="n">
-        <v>220.4</v>
+        <v>58.79</v>
       </c>
       <c r="H9" t="n">
-        <v>47.12</v>
+        <v>35.01</v>
       </c>
       <c r="I9" t="n">
-        <v>49.9</v>
+        <v>42.28</v>
       </c>
       <c r="J9" t="n">
-        <v>0.66</v>
+        <v>1.27</v>
       </c>
       <c r="K9" t="n">
-        <v>52.5</v>
+        <v>56.25</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>71.5</v>
+        <v>73.75</v>
       </c>
       <c r="N9" t="n">
-        <v>324.25</v>
+        <v>79.37</v>
       </c>
       <c r="O9" t="n">
-        <v>308</v>
+        <v>1259</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99869</v>
+        <v>99926.83</v>
       </c>
       <c r="R9" t="n">
         <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>291.82</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>9986.9</v>
+        <v>9992.68</v>
       </c>
       <c r="U9" t="n">
-        <v>372.89</v>
+        <v>90.48</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>14980.35</v>
+        <v>13989.76</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>SYNCOMF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>288.9</v>
+        <v>25.08</v>
       </c>
       <c r="E10" t="n">
-        <v>219.3</v>
+        <v>14.51</v>
       </c>
       <c r="F10" t="n">
-        <v>31.74</v>
+        <v>72.86</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>18.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.37</v>
+        <v>34.12</v>
       </c>
       <c r="I10" t="n">
-        <v>66.88</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>3.43</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>70.75</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>288.9</v>
+        <v>25.08</v>
       </c>
       <c r="O10" t="n">
-        <v>346</v>
+        <v>3987</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99959.39999999999</v>
+        <v>99993.96000000001</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>260.01</v>
+        <v>22.57</v>
       </c>
       <c r="T10" t="n">
-        <v>9995.940000000001</v>
+        <v>9999.4</v>
       </c>
       <c r="U10" t="n">
-        <v>340.9</v>
+        <v>29.09</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>15.99</v>
       </c>
       <c r="W10" t="n">
-        <v>17992.69</v>
+        <v>15989.03</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1162.5</v>
+        <v>7015.5</v>
       </c>
       <c r="E11" t="n">
-        <v>706.49</v>
+        <v>5208.16</v>
       </c>
       <c r="F11" t="n">
-        <v>64.54000000000001</v>
+        <v>34.7</v>
       </c>
       <c r="G11" t="n">
-        <v>720</v>
+        <v>4488.9</v>
       </c>
       <c r="H11" t="n">
-        <v>61.46</v>
+        <v>56.29</v>
       </c>
       <c r="I11" t="n">
-        <v>59.17</v>
+        <v>56</v>
       </c>
       <c r="J11" t="n">
-        <v>0.32</v>
+        <v>1.41</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>70.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>1162.5</v>
+        <v>7015.5</v>
       </c>
       <c r="O11" t="n">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99975</v>
+        <v>98217</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="S11" t="n">
-        <v>1046.25</v>
+        <v>6313.95</v>
       </c>
       <c r="T11" t="n">
-        <v>9997.5</v>
+        <v>9821.700000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1371.75</v>
+        <v>8208.139999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>17995.5</v>
+        <v>16696.89</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67.5</v>
+        <v>8133.5</v>
       </c>
       <c r="E2" t="n">
-        <v>60.41</v>
+        <v>8046.56</v>
       </c>
       <c r="F2" t="n">
-        <v>11.74</v>
+        <v>1.08</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>8099.5</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.74</v>
+        <v>0.42</v>
       </c>
       <c r="I2" t="n">
-        <v>55.12</v>
+        <v>29.66</v>
       </c>
       <c r="J2" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="K2" t="n">
-        <v>73.75</v>
+        <v>81.25</v>
       </c>
       <c r="L2" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>81.05</v>
+        <v>48.75</v>
       </c>
       <c r="N2" t="n">
-        <v>67.5</v>
+        <v>8133.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1481</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99967.5</v>
+        <v>97602</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="S2" t="n">
-        <v>60.75</v>
+        <v>7320.15</v>
       </c>
       <c r="T2" t="n">
-        <v>9996.75</v>
+        <v>9760.200000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>81</v>
+        <v>9597.530000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>19993.5</v>
+        <v>17568.36</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -634,82 +634,82 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.8</v>
+        <v>1326.4</v>
       </c>
       <c r="E3" t="n">
-        <v>15.58</v>
+        <v>1292.07</v>
       </c>
       <c r="F3" t="n">
-        <v>39.93</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>17.4</v>
+        <v>1067.7</v>
       </c>
       <c r="H3" t="n">
-        <v>25.29</v>
+        <v>24.23</v>
       </c>
       <c r="I3" t="n">
-        <v>71.48</v>
+        <v>37.97</v>
       </c>
       <c r="J3" t="n">
-        <v>3.48</v>
+        <v>4.29</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>81.25</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>79.59999999999999</v>
+        <v>48.75</v>
       </c>
       <c r="N3" t="n">
-        <v>21.8</v>
+        <v>1326.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4587</v>
+        <v>75</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99996.60000000001</v>
+        <v>99480</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>19.62</v>
+        <v>1193.76</v>
       </c>
       <c r="T3" t="n">
-        <v>9999.66</v>
+        <v>9948</v>
       </c>
       <c r="U3" t="n">
-        <v>25.72</v>
+        <v>1565.15</v>
       </c>
       <c r="V3" t="n">
-        <v>17.98</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>17979.39</v>
+        <v>17906.4</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -719,82 +719,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>232.2</v>
+        <v>375.05</v>
       </c>
       <c r="E4" t="n">
-        <v>194.97</v>
+        <v>364.98</v>
       </c>
       <c r="F4" t="n">
-        <v>19.1</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>173.45</v>
+        <v>369.3</v>
       </c>
       <c r="H4" t="n">
-        <v>33.87</v>
+        <v>1.56</v>
       </c>
       <c r="I4" t="n">
-        <v>57.43</v>
+        <v>37.95</v>
       </c>
       <c r="J4" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>78.75</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>75.5</v>
+        <v>47.25</v>
       </c>
       <c r="N4" t="n">
-        <v>232.2</v>
+        <v>375.05</v>
       </c>
       <c r="O4" t="n">
-        <v>430</v>
+        <v>266</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99846</v>
+        <v>99763.3</v>
       </c>
       <c r="R4" t="n">
         <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>208.98</v>
+        <v>337.54</v>
       </c>
       <c r="T4" t="n">
-        <v>9984.6</v>
+        <v>9976.33</v>
       </c>
       <c r="U4" t="n">
-        <v>278.64</v>
+        <v>442.56</v>
       </c>
       <c r="V4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>19969.2</v>
+        <v>17957.39</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -804,82 +804,82 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>374.2</v>
+        <v>1875</v>
       </c>
       <c r="E5" t="n">
-        <v>323.36</v>
+        <v>1861.84</v>
       </c>
       <c r="F5" t="n">
-        <v>15.72</v>
+        <v>0.71</v>
       </c>
       <c r="G5" t="n">
-        <v>386</v>
+        <v>1362.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.06</v>
+        <v>37.66</v>
       </c>
       <c r="I5" t="n">
-        <v>54.17</v>
+        <v>34.65</v>
       </c>
       <c r="J5" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="K5" t="n">
-        <v>58.75</v>
+        <v>76.25</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>75.25</v>
+        <v>45.75</v>
       </c>
       <c r="N5" t="n">
-        <v>374.2</v>
+        <v>1875</v>
       </c>
       <c r="O5" t="n">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99911.39999999999</v>
+        <v>99375</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.94</v>
       </c>
       <c r="S5" t="n">
-        <v>336.78</v>
+        <v>1687.5</v>
       </c>
       <c r="T5" t="n">
-        <v>9991.139999999999</v>
+        <v>9937.5</v>
       </c>
       <c r="U5" t="n">
-        <v>430.33</v>
+        <v>2175</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>14986.71</v>
+        <v>15900</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>329</v>
+        <v>1967.2</v>
       </c>
       <c r="E6" t="n">
-        <v>254.74</v>
+        <v>1440.47</v>
       </c>
       <c r="F6" t="n">
-        <v>29.15</v>
+        <v>36.57</v>
       </c>
       <c r="G6" t="n">
-        <v>220.4</v>
+        <v>1893</v>
       </c>
       <c r="H6" t="n">
-        <v>49.27</v>
+        <v>3.92</v>
       </c>
       <c r="I6" t="n">
-        <v>53.06</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.55</v>
+        <v>2.38</v>
       </c>
       <c r="K6" t="n">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>74.5</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>329</v>
+        <v>1967.2</v>
       </c>
       <c r="O6" t="n">
-        <v>303</v>
+        <v>50</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99687</v>
+        <v>98360</v>
       </c>
       <c r="R6" t="n">
-        <v>9.970000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="S6" t="n">
-        <v>296.1</v>
+        <v>1770.48</v>
       </c>
       <c r="T6" t="n">
-        <v>9968.700000000001</v>
+        <v>9836</v>
       </c>
       <c r="U6" t="n">
-        <v>378.35</v>
+        <v>2281.95</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>14953.05</v>
+        <v>15737.6</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ROLEXRINGS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>604.4</v>
+        <v>196.36</v>
       </c>
       <c r="E7" t="n">
-        <v>501.68</v>
+        <v>143.92</v>
       </c>
       <c r="F7" t="n">
-        <v>20.47</v>
+        <v>36.44</v>
       </c>
       <c r="G7" t="n">
-        <v>539</v>
+        <v>154.09</v>
       </c>
       <c r="H7" t="n">
-        <v>12.13</v>
+        <v>27.43</v>
       </c>
       <c r="I7" t="n">
-        <v>56.53</v>
+        <v>69.31</v>
       </c>
       <c r="J7" t="n">
-        <v>0.76</v>
+        <v>2.63</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>74.34999999999999</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>604.4</v>
+        <v>196.36</v>
       </c>
       <c r="O7" t="n">
-        <v>165</v>
+        <v>509</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99726</v>
+        <v>99947.24000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>543.96</v>
+        <v>176.72</v>
       </c>
       <c r="T7" t="n">
-        <v>9972.6</v>
+        <v>9994.719999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>713.1900000000001</v>
+        <v>227.78</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>17950.68</v>
+        <v>15991.56</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>HITECHCORP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>734.35</v>
+        <v>340.25</v>
       </c>
       <c r="E8" t="n">
-        <v>649.72</v>
+        <v>226.94</v>
       </c>
       <c r="F8" t="n">
-        <v>13.02</v>
+        <v>49.93</v>
       </c>
       <c r="G8" t="n">
-        <v>629.9</v>
+        <v>223.44</v>
       </c>
       <c r="H8" t="n">
-        <v>16.58</v>
+        <v>52.28</v>
       </c>
       <c r="I8" t="n">
-        <v>47.76</v>
+        <v>58.17</v>
       </c>
       <c r="J8" t="n">
-        <v>1.38</v>
+        <v>2.11</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>74.34999999999999</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>734.35</v>
+        <v>340.25</v>
       </c>
       <c r="O8" t="n">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99871.60000000001</v>
+        <v>99693.25</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>660.92</v>
+        <v>306.23</v>
       </c>
       <c r="T8" t="n">
-        <v>9987.16</v>
+        <v>9969.33</v>
       </c>
       <c r="U8" t="n">
-        <v>844.5</v>
+        <v>394.69</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>14980.74</v>
+        <v>15950.92</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>HARSHA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79.37</v>
+        <v>474.5</v>
       </c>
       <c r="E9" t="n">
-        <v>75.23999999999999</v>
+        <v>399.76</v>
       </c>
       <c r="F9" t="n">
-        <v>5.49</v>
+        <v>18.7</v>
       </c>
       <c r="G9" t="n">
-        <v>58.79</v>
+        <v>428.9</v>
       </c>
       <c r="H9" t="n">
-        <v>35.01</v>
+        <v>10.63</v>
       </c>
       <c r="I9" t="n">
-        <v>42.28</v>
+        <v>64.64</v>
       </c>
       <c r="J9" t="n">
-        <v>1.27</v>
+        <v>2.24</v>
       </c>
       <c r="K9" t="n">
-        <v>56.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>73.75</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>79.37</v>
+        <v>474.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1259</v>
+        <v>210</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99926.83</v>
+        <v>99645</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>71.43000000000001</v>
+        <v>427.05</v>
       </c>
       <c r="T9" t="n">
-        <v>9992.68</v>
+        <v>9964.5</v>
       </c>
       <c r="U9" t="n">
-        <v>90.48</v>
+        <v>545.67</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>13989.76</v>
+        <v>14946.75</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SYNCOMF</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.08</v>
+        <v>400.8</v>
       </c>
       <c r="E10" t="n">
-        <v>14.51</v>
+        <v>257.03</v>
       </c>
       <c r="F10" t="n">
-        <v>72.86</v>
+        <v>55.93</v>
       </c>
       <c r="G10" t="n">
-        <v>18.7</v>
+        <v>255.87</v>
       </c>
       <c r="H10" t="n">
-        <v>34.12</v>
+        <v>56.64</v>
       </c>
       <c r="I10" t="n">
-        <v>73.48999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="J10" t="n">
-        <v>3.43</v>
+        <v>11.64</v>
       </c>
       <c r="K10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>72.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>25.08</v>
+        <v>400.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3987</v>
+        <v>249</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99993.96000000001</v>
+        <v>99799.2</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S10" t="n">
-        <v>22.57</v>
+        <v>360.72</v>
       </c>
       <c r="T10" t="n">
-        <v>9999.4</v>
+        <v>9979.92</v>
       </c>
       <c r="U10" t="n">
-        <v>29.09</v>
+        <v>464.93</v>
       </c>
       <c r="V10" t="n">
-        <v>15.99</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>15989.03</v>
+        <v>15967.87</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7015.5</v>
+        <v>136.51</v>
       </c>
       <c r="E11" t="n">
-        <v>5208.16</v>
+        <v>102.34</v>
       </c>
       <c r="F11" t="n">
-        <v>34.7</v>
+        <v>33.39</v>
       </c>
       <c r="G11" t="n">
-        <v>4488.9</v>
+        <v>73.5</v>
       </c>
       <c r="H11" t="n">
-        <v>56.29</v>
+        <v>85.73</v>
       </c>
       <c r="I11" t="n">
-        <v>56</v>
+        <v>67.33</v>
       </c>
       <c r="J11" t="n">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>72.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>7015.5</v>
+        <v>136.51</v>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>732</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>98217</v>
+        <v>99925.32000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>9.82</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>6313.95</v>
+        <v>122.86</v>
       </c>
       <c r="T11" t="n">
-        <v>9821.700000000001</v>
+        <v>9992.530000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>8208.139999999999</v>
+        <v>158.35</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>16696.89</v>
+        <v>15988.05</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ARIES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8133.5</v>
+        <v>501.25</v>
       </c>
       <c r="E2" t="n">
-        <v>8046.56</v>
+        <v>364.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.08</v>
+        <v>37.65</v>
       </c>
       <c r="G2" t="n">
-        <v>8099.5</v>
+        <v>445</v>
       </c>
       <c r="H2" t="n">
-        <v>0.42</v>
+        <v>12.64</v>
       </c>
       <c r="I2" t="n">
-        <v>29.66</v>
+        <v>66.23</v>
       </c>
       <c r="J2" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="K2" t="n">
-        <v>81.25</v>
+        <v>72.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>48.75</v>
+        <v>83.5</v>
       </c>
       <c r="N2" t="n">
-        <v>8133.5</v>
+        <v>501.25</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>199</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>97602</v>
+        <v>99748.75</v>
       </c>
       <c r="R2" t="n">
-        <v>9.76</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>7320.15</v>
+        <v>451.12</v>
       </c>
       <c r="T2" t="n">
-        <v>9760.200000000001</v>
+        <v>9974.879999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>9597.530000000001</v>
+        <v>606.51</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>17568.36</v>
+        <v>20947.24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -634,82 +634,82 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1326.4</v>
+        <v>886.25</v>
       </c>
       <c r="E3" t="n">
-        <v>1292.07</v>
+        <v>722.8200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>22.61</v>
       </c>
       <c r="G3" t="n">
-        <v>1067.7</v>
+        <v>513.55</v>
       </c>
       <c r="H3" t="n">
-        <v>24.23</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>37.97</v>
+        <v>50.32</v>
       </c>
       <c r="J3" t="n">
-        <v>4.29</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>81.25</v>
+        <v>71.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M3" t="n">
-        <v>48.75</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1326.4</v>
+        <v>886.25</v>
       </c>
       <c r="O3" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99480</v>
+        <v>99260</v>
       </c>
       <c r="R3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="S3" t="n">
-        <v>1193.76</v>
+        <v>797.62</v>
       </c>
       <c r="T3" t="n">
-        <v>9948</v>
+        <v>9926</v>
       </c>
       <c r="U3" t="n">
-        <v>1565.15</v>
+        <v>1045.77</v>
       </c>
       <c r="V3" t="n">
         <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>17906.4</v>
+        <v>17866.8</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>375.05</v>
+        <v>2039.6</v>
       </c>
       <c r="E4" t="n">
-        <v>364.98</v>
+        <v>1995.24</v>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>369.3</v>
+        <v>1930</v>
       </c>
       <c r="H4" t="n">
-        <v>1.56</v>
+        <v>5.68</v>
       </c>
       <c r="I4" t="n">
-        <v>37.95</v>
+        <v>30.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="K4" t="n">
-        <v>78.75</v>
+        <v>81.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M4" t="n">
-        <v>47.25</v>
+        <v>75.95</v>
       </c>
       <c r="N4" t="n">
-        <v>375.05</v>
+        <v>2039.6</v>
       </c>
       <c r="O4" t="n">
-        <v>266</v>
+        <v>49</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99763.3</v>
+        <v>99940.39999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>337.54</v>
+        <v>1835.64</v>
       </c>
       <c r="T4" t="n">
-        <v>9976.33</v>
+        <v>9994.040000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>442.56</v>
+        <v>2467.92</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>17957.39</v>
+        <v>20987.48</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,82 +804,82 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1875</v>
+        <v>326.75</v>
       </c>
       <c r="E5" t="n">
-        <v>1861.84</v>
+        <v>256.61</v>
       </c>
       <c r="F5" t="n">
-        <v>0.71</v>
+        <v>27.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1362.1</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>37.66</v>
+        <v>48.25</v>
       </c>
       <c r="I5" t="n">
-        <v>34.65</v>
+        <v>51.71</v>
       </c>
       <c r="J5" t="n">
-        <v>1.33</v>
+        <v>0.62</v>
       </c>
       <c r="K5" t="n">
-        <v>76.25</v>
+        <v>57.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>45.75</v>
+        <v>74.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1875</v>
+        <v>326.75</v>
       </c>
       <c r="O5" t="n">
-        <v>53</v>
+        <v>306</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99375</v>
+        <v>99985.5</v>
       </c>
       <c r="R5" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>1687.5</v>
+        <v>294.08</v>
       </c>
       <c r="T5" t="n">
-        <v>9937.5</v>
+        <v>9998.549999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>2175</v>
+        <v>375.76</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>15900</v>
+        <v>14997.82</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1967.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1440.47</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>36.57</v>
+        <v>7.01</v>
       </c>
       <c r="G6" t="n">
-        <v>1893</v>
+        <v>58.79</v>
       </c>
       <c r="H6" t="n">
-        <v>3.92</v>
+        <v>37.61</v>
       </c>
       <c r="I6" t="n">
-        <v>68.76000000000001</v>
+        <v>46.91</v>
       </c>
       <c r="J6" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>57.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>74.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1967.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>1236</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>98360</v>
+        <v>99992.39999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>1770.48</v>
+        <v>72.81</v>
       </c>
       <c r="T6" t="n">
-        <v>9836</v>
+        <v>9999.24</v>
       </c>
       <c r="U6" t="n">
-        <v>2281.95</v>
+        <v>91.42</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>15737.6</v>
+        <v>12999.01</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ROLEXRINGS</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>196.36</v>
+        <v>23.98</v>
       </c>
       <c r="E7" t="n">
-        <v>143.92</v>
+        <v>15.67</v>
       </c>
       <c r="F7" t="n">
-        <v>36.44</v>
+        <v>53.04</v>
       </c>
       <c r="G7" t="n">
-        <v>154.09</v>
+        <v>17.4</v>
       </c>
       <c r="H7" t="n">
-        <v>27.43</v>
+        <v>37.82</v>
       </c>
       <c r="I7" t="n">
-        <v>69.31</v>
+        <v>80.55</v>
       </c>
       <c r="J7" t="n">
-        <v>2.63</v>
+        <v>3.23</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>196.36</v>
+        <v>23.98</v>
       </c>
       <c r="O7" t="n">
-        <v>509</v>
+        <v>4170</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99947.24000000001</v>
+        <v>99996.60000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>176.72</v>
+        <v>21.58</v>
       </c>
       <c r="T7" t="n">
-        <v>9994.719999999999</v>
+        <v>9999.66</v>
       </c>
       <c r="U7" t="n">
-        <v>227.78</v>
+        <v>27.82</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="W7" t="n">
-        <v>15991.56</v>
+        <v>16009.46</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>340.25</v>
+        <v>327.35</v>
       </c>
       <c r="E8" t="n">
-        <v>226.94</v>
+        <v>305.43</v>
       </c>
       <c r="F8" t="n">
-        <v>49.93</v>
+        <v>7.18</v>
       </c>
       <c r="G8" t="n">
-        <v>223.44</v>
+        <v>220</v>
       </c>
       <c r="H8" t="n">
-        <v>52.28</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>58.17</v>
+        <v>43.55</v>
       </c>
       <c r="J8" t="n">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>56.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>73.75</v>
       </c>
       <c r="N8" t="n">
-        <v>340.25</v>
+        <v>327.35</v>
       </c>
       <c r="O8" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99693.25</v>
+        <v>99841.75</v>
       </c>
       <c r="R8" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>306.23</v>
+        <v>294.62</v>
       </c>
       <c r="T8" t="n">
-        <v>9969.33</v>
+        <v>9984.17</v>
       </c>
       <c r="U8" t="n">
-        <v>394.69</v>
+        <v>373.18</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>15950.92</v>
+        <v>13977.84</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>474.5</v>
+        <v>66.59</v>
       </c>
       <c r="E9" t="n">
-        <v>399.76</v>
+        <v>60.59</v>
       </c>
       <c r="F9" t="n">
-        <v>18.7</v>
+        <v>9.9</v>
       </c>
       <c r="G9" t="n">
-        <v>428.9</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>10.63</v>
+        <v>-2.07</v>
       </c>
       <c r="I9" t="n">
-        <v>64.64</v>
+        <v>52.52</v>
       </c>
       <c r="J9" t="n">
-        <v>2.24</v>
+        <v>1.48</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>73.55</v>
       </c>
       <c r="N9" t="n">
-        <v>474.5</v>
+        <v>66.59</v>
       </c>
       <c r="O9" t="n">
-        <v>210</v>
+        <v>1501</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99645</v>
+        <v>99951.59</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>427.05</v>
+        <v>59.93</v>
       </c>
       <c r="T9" t="n">
-        <v>9964.5</v>
+        <v>9995.16</v>
       </c>
       <c r="U9" t="n">
-        <v>545.67</v>
+        <v>75.91</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>14946.75</v>
+        <v>13993.22</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>ORIENTBELL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>400.8</v>
+        <v>417.1</v>
       </c>
       <c r="E10" t="n">
-        <v>257.03</v>
+        <v>318.69</v>
       </c>
       <c r="F10" t="n">
-        <v>55.93</v>
+        <v>30.88</v>
       </c>
       <c r="G10" t="n">
-        <v>255.87</v>
+        <v>339.7</v>
       </c>
       <c r="H10" t="n">
-        <v>56.64</v>
+        <v>22.78</v>
       </c>
       <c r="I10" t="n">
-        <v>67.36</v>
+        <v>65.14</v>
       </c>
       <c r="J10" t="n">
-        <v>11.64</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="N10" t="n">
-        <v>400.8</v>
+        <v>417.1</v>
       </c>
       <c r="O10" t="n">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99799.2</v>
+        <v>99686.89999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>360.72</v>
+        <v>375.39</v>
       </c>
       <c r="T10" t="n">
-        <v>9979.92</v>
+        <v>9968.690000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>464.93</v>
+        <v>496.35</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>15967.87</v>
+        <v>18940.51</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>PREMIERPOL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>136.51</v>
+        <v>101.54</v>
       </c>
       <c r="E11" t="n">
-        <v>102.34</v>
+        <v>63.02</v>
       </c>
       <c r="F11" t="n">
-        <v>33.39</v>
+        <v>61.13</v>
       </c>
       <c r="G11" t="n">
-        <v>73.5</v>
+        <v>62.02</v>
       </c>
       <c r="H11" t="n">
-        <v>85.73</v>
+        <v>63.72</v>
       </c>
       <c r="I11" t="n">
-        <v>67.33</v>
+        <v>63.84</v>
       </c>
       <c r="J11" t="n">
-        <v>2.31</v>
+        <v>4.51</v>
       </c>
       <c r="K11" t="n">
         <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="N11" t="n">
-        <v>136.51</v>
+        <v>101.54</v>
       </c>
       <c r="O11" t="n">
-        <v>732</v>
+        <v>984</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99925.32000000001</v>
+        <v>99915.36</v>
       </c>
       <c r="R11" t="n">
         <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>122.86</v>
+        <v>91.39</v>
       </c>
       <c r="T11" t="n">
-        <v>9992.530000000001</v>
+        <v>9991.540000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>158.35</v>
+        <v>120.83</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>15988.05</v>
+        <v>18983.92</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARIES</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>501.25</v>
+        <v>22.95</v>
       </c>
       <c r="E2" t="n">
-        <v>364.15</v>
+        <v>15.71</v>
       </c>
       <c r="F2" t="n">
-        <v>37.65</v>
+        <v>46.06</v>
       </c>
       <c r="G2" t="n">
-        <v>445</v>
+        <v>17.4</v>
       </c>
       <c r="H2" t="n">
-        <v>12.64</v>
+        <v>31.9</v>
       </c>
       <c r="I2" t="n">
-        <v>66.23</v>
+        <v>68.98</v>
       </c>
       <c r="J2" t="n">
-        <v>1.61</v>
+        <v>2.43</v>
       </c>
       <c r="K2" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>83.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>501.25</v>
+        <v>22.95</v>
       </c>
       <c r="O2" t="n">
-        <v>199</v>
+        <v>4357</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99748.75</v>
+        <v>99993.14999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>451.12</v>
+        <v>20.66</v>
       </c>
       <c r="T2" t="n">
-        <v>9974.879999999999</v>
+        <v>9999.32</v>
       </c>
       <c r="U2" t="n">
-        <v>606.51</v>
+        <v>27.77</v>
       </c>
       <c r="V2" t="n">
         <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>20947.24</v>
+        <v>20998.56</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>886.25</v>
+        <v>629.5</v>
       </c>
       <c r="E3" t="n">
-        <v>722.8200000000001</v>
+        <v>503.88</v>
       </c>
       <c r="F3" t="n">
-        <v>22.61</v>
+        <v>24.93</v>
       </c>
       <c r="G3" t="n">
-        <v>513.55</v>
+        <v>539</v>
       </c>
       <c r="H3" t="n">
-        <v>72.56999999999999</v>
+        <v>16.79</v>
       </c>
       <c r="I3" t="n">
-        <v>50.32</v>
+        <v>63.31</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="K3" t="n">
-        <v>71.25</v>
+        <v>72.5</v>
       </c>
       <c r="L3" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>76.34999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>886.25</v>
+        <v>629.5</v>
       </c>
       <c r="O3" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99260</v>
+        <v>99461</v>
       </c>
       <c r="R3" t="n">
-        <v>9.93</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>797.62</v>
+        <v>566.55</v>
       </c>
       <c r="T3" t="n">
-        <v>9926</v>
+        <v>9946.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1045.77</v>
+        <v>761.6900000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>17866.8</v>
+        <v>20886.81</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,82 +719,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2039.6</v>
+        <v>761.15</v>
       </c>
       <c r="E4" t="n">
-        <v>1995.24</v>
+        <v>653.3200000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>16.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1930</v>
+        <v>629.9</v>
       </c>
       <c r="H4" t="n">
-        <v>5.68</v>
+        <v>20.84</v>
       </c>
       <c r="I4" t="n">
-        <v>30.8</v>
+        <v>56.35</v>
       </c>
       <c r="J4" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="K4" t="n">
-        <v>81.25</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>75.95</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>2039.6</v>
+        <v>761.15</v>
       </c>
       <c r="O4" t="n">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99940.39999999999</v>
+        <v>99710.64999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1835.64</v>
+        <v>685.04</v>
       </c>
       <c r="T4" t="n">
-        <v>9994.040000000001</v>
+        <v>9971.059999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>2467.92</v>
+        <v>913.38</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W4" t="n">
-        <v>20987.48</v>
+        <v>19942.13</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>326.75</v>
+        <v>128.63</v>
       </c>
       <c r="E5" t="n">
-        <v>256.61</v>
+        <v>100.92</v>
       </c>
       <c r="F5" t="n">
-        <v>27.33</v>
+        <v>27.46</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>108.59</v>
       </c>
       <c r="H5" t="n">
-        <v>48.25</v>
+        <v>18.45</v>
       </c>
       <c r="I5" t="n">
-        <v>51.71</v>
+        <v>55.57</v>
       </c>
       <c r="J5" t="n">
-        <v>0.62</v>
+        <v>1.52</v>
       </c>
       <c r="K5" t="n">
-        <v>57.5</v>
+        <v>72.5</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>74.5</v>
+        <v>80.3</v>
       </c>
       <c r="N5" t="n">
-        <v>326.75</v>
+        <v>128.63</v>
       </c>
       <c r="O5" t="n">
-        <v>306</v>
+        <v>777</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99985.5</v>
+        <v>99945.50999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>294.08</v>
+        <v>115.77</v>
       </c>
       <c r="T5" t="n">
-        <v>9998.549999999999</v>
+        <v>9994.549999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>375.76</v>
+        <v>155.64</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="W5" t="n">
-        <v>14997.82</v>
+        <v>20988.56</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80.90000000000001</v>
+        <v>431.9</v>
       </c>
       <c r="E6" t="n">
-        <v>75.59999999999999</v>
+        <v>399.14</v>
       </c>
       <c r="F6" t="n">
-        <v>7.01</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>58.79</v>
+        <v>453.2</v>
       </c>
       <c r="H6" t="n">
-        <v>37.61</v>
+        <v>-4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>46.91</v>
+        <v>66.59</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="K6" t="n">
-        <v>57.5</v>
+        <v>67.5</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>74.5</v>
+        <v>77.3</v>
       </c>
       <c r="N6" t="n">
-        <v>80.90000000000001</v>
+        <v>431.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1236</v>
+        <v>231</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99992.39999999999</v>
+        <v>99768.89999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>72.81</v>
+        <v>388.71</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.24</v>
+        <v>9976.889999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>91.42</v>
+        <v>513.96</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>12999.01</v>
+        <v>18956.09</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23.98</v>
+        <v>228.35</v>
       </c>
       <c r="E7" t="n">
-        <v>15.67</v>
+        <v>196.63</v>
       </c>
       <c r="F7" t="n">
-        <v>53.04</v>
+        <v>16.13</v>
       </c>
       <c r="G7" t="n">
-        <v>17.4</v>
+        <v>173.45</v>
       </c>
       <c r="H7" t="n">
-        <v>37.82</v>
+        <v>31.65</v>
       </c>
       <c r="I7" t="n">
-        <v>80.55</v>
+        <v>52.26</v>
       </c>
       <c r="J7" t="n">
-        <v>3.23</v>
+        <v>10.03</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>71.25</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>74.34999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="N7" t="n">
-        <v>23.98</v>
+        <v>228.35</v>
       </c>
       <c r="O7" t="n">
-        <v>4170</v>
+        <v>437</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99996.60000000001</v>
+        <v>99788.95</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S7" t="n">
-        <v>21.58</v>
+        <v>205.52</v>
       </c>
       <c r="T7" t="n">
-        <v>9999.66</v>
+        <v>9978.9</v>
       </c>
       <c r="U7" t="n">
-        <v>27.82</v>
+        <v>267.17</v>
       </c>
       <c r="V7" t="n">
-        <v>16.01</v>
+        <v>17</v>
       </c>
       <c r="W7" t="n">
-        <v>16009.46</v>
+        <v>16964.12</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>327.35</v>
+        <v>154.53</v>
       </c>
       <c r="E8" t="n">
-        <v>305.43</v>
+        <v>106.76</v>
       </c>
       <c r="F8" t="n">
-        <v>7.18</v>
+        <v>44.75</v>
       </c>
       <c r="G8" t="n">
-        <v>220</v>
+        <v>133.9</v>
       </c>
       <c r="H8" t="n">
-        <v>48.8</v>
+        <v>15.41</v>
       </c>
       <c r="I8" t="n">
-        <v>43.55</v>
+        <v>62.38</v>
       </c>
       <c r="J8" t="n">
-        <v>1.36</v>
+        <v>6.59</v>
       </c>
       <c r="K8" t="n">
-        <v>56.25</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>73.75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>327.35</v>
+        <v>154.53</v>
       </c>
       <c r="O8" t="n">
-        <v>305</v>
+        <v>647</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99841.75</v>
+        <v>99980.91</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>294.62</v>
+        <v>139.08</v>
       </c>
       <c r="T8" t="n">
-        <v>9984.17</v>
+        <v>9998.09</v>
       </c>
       <c r="U8" t="n">
-        <v>373.18</v>
+        <v>183.89</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>13977.84</v>
+        <v>18996.37</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66.59</v>
+        <v>504.1</v>
       </c>
       <c r="E9" t="n">
-        <v>60.59</v>
+        <v>361.84</v>
       </c>
       <c r="F9" t="n">
-        <v>9.9</v>
+        <v>39.31</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>342.2</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.07</v>
+        <v>47.31</v>
       </c>
       <c r="I9" t="n">
-        <v>52.52</v>
+        <v>61.56</v>
       </c>
       <c r="J9" t="n">
-        <v>1.48</v>
+        <v>3.01</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="M9" t="n">
-        <v>73.55</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>66.59</v>
+        <v>504.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1501</v>
+        <v>198</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99951.59</v>
+        <v>99811.8</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S9" t="n">
-        <v>59.93</v>
+        <v>453.69</v>
       </c>
       <c r="T9" t="n">
-        <v>9995.16</v>
+        <v>9981.18</v>
       </c>
       <c r="U9" t="n">
-        <v>75.91</v>
+        <v>599.88</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>13993.22</v>
+        <v>18964.24</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORIENTBELL</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>417.1</v>
+        <v>59.2</v>
       </c>
       <c r="E10" t="n">
-        <v>318.69</v>
+        <v>34.11</v>
       </c>
       <c r="F10" t="n">
-        <v>30.88</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>339.7</v>
+        <v>35.79</v>
       </c>
       <c r="H10" t="n">
-        <v>22.78</v>
+        <v>65.41</v>
       </c>
       <c r="I10" t="n">
-        <v>65.14</v>
+        <v>60.12</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L10" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>73</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>417.1</v>
+        <v>59.2</v>
       </c>
       <c r="O10" t="n">
-        <v>239</v>
+        <v>1689</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99686.89999999999</v>
+        <v>99988.8</v>
       </c>
       <c r="R10" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>375.39</v>
+        <v>53.28</v>
       </c>
       <c r="T10" t="n">
-        <v>9968.690000000001</v>
+        <v>9998.879999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>496.35</v>
+        <v>70.45</v>
       </c>
       <c r="V10" t="n">
         <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>18940.51</v>
+        <v>18997.87</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PREMIERPOL</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>101.54</v>
+        <v>7102.5</v>
       </c>
       <c r="E11" t="n">
-        <v>63.02</v>
+        <v>5259.35</v>
       </c>
       <c r="F11" t="n">
-        <v>61.13</v>
+        <v>35.05</v>
       </c>
       <c r="G11" t="n">
-        <v>62.02</v>
+        <v>4488.9</v>
       </c>
       <c r="H11" t="n">
-        <v>63.72</v>
+        <v>58.22</v>
       </c>
       <c r="I11" t="n">
-        <v>63.84</v>
+        <v>56.85</v>
       </c>
       <c r="J11" t="n">
-        <v>4.51</v>
+        <v>1.74</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>73</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>101.54</v>
+        <v>7102.5</v>
       </c>
       <c r="O11" t="n">
-        <v>984</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99915.36</v>
+        <v>99435</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>91.39</v>
+        <v>6392.25</v>
       </c>
       <c r="T11" t="n">
-        <v>9991.540000000001</v>
+        <v>9943.5</v>
       </c>
       <c r="U11" t="n">
-        <v>120.83</v>
+        <v>8451.98</v>
       </c>
       <c r="V11" t="n">
         <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>18983.92</v>
+        <v>18892.65</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.95</v>
+        <v>372.1</v>
       </c>
       <c r="E2" t="n">
-        <v>15.71</v>
+        <v>365.57</v>
       </c>
       <c r="F2" t="n">
-        <v>46.06</v>
+        <v>1.79</v>
       </c>
       <c r="G2" t="n">
-        <v>17.4</v>
+        <v>369.3</v>
       </c>
       <c r="H2" t="n">
-        <v>31.9</v>
+        <v>0.76</v>
       </c>
       <c r="I2" t="n">
-        <v>68.98</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.43</v>
+        <v>1.66</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>78.75</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>82.59999999999999</v>
+        <v>47.25</v>
       </c>
       <c r="N2" t="n">
-        <v>22.95</v>
+        <v>372.1</v>
       </c>
       <c r="O2" t="n">
-        <v>4357</v>
+        <v>268</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99993.14999999999</v>
+        <v>99722.8</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>20.66</v>
+        <v>334.89</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.32</v>
+        <v>9972.280000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>27.77</v>
+        <v>439.08</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>20998.56</v>
+        <v>17950.1</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>629.5</v>
+        <v>24685</v>
       </c>
       <c r="E3" t="n">
-        <v>503.88</v>
+        <v>18330.56</v>
       </c>
       <c r="F3" t="n">
-        <v>24.93</v>
+        <v>34.67</v>
       </c>
       <c r="G3" t="n">
-        <v>539</v>
+        <v>19851</v>
       </c>
       <c r="H3" t="n">
-        <v>16.79</v>
+        <v>24.35</v>
       </c>
       <c r="I3" t="n">
-        <v>63.31</v>
+        <v>69.11</v>
       </c>
       <c r="J3" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>81.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>629.5</v>
+        <v>24685</v>
       </c>
       <c r="O3" t="n">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99461</v>
+        <v>98740</v>
       </c>
       <c r="R3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>566.55</v>
+        <v>22216.5</v>
       </c>
       <c r="T3" t="n">
-        <v>9946.1</v>
+        <v>9874</v>
       </c>
       <c r="U3" t="n">
-        <v>761.6900000000001</v>
+        <v>28634.6</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>20886.81</v>
+        <v>15798.4</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>761.15</v>
+        <v>3150.6</v>
       </c>
       <c r="E4" t="n">
-        <v>653.3200000000001</v>
+        <v>2186.65</v>
       </c>
       <c r="F4" t="n">
-        <v>16.5</v>
+        <v>44.08</v>
       </c>
       <c r="G4" t="n">
-        <v>629.9</v>
+        <v>2131</v>
       </c>
       <c r="H4" t="n">
-        <v>20.84</v>
+        <v>47.85</v>
       </c>
       <c r="I4" t="n">
-        <v>56.35</v>
+        <v>68.83</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6</v>
+        <v>3.31</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>81.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>761.15</v>
+        <v>3150.6</v>
       </c>
       <c r="O4" t="n">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99710.64999999999</v>
+        <v>97668.60000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="S4" t="n">
-        <v>685.04</v>
+        <v>2835.54</v>
       </c>
       <c r="T4" t="n">
-        <v>9971.059999999999</v>
+        <v>9766.860000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>913.38</v>
+        <v>3654.7</v>
       </c>
       <c r="V4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>19942.13</v>
+        <v>15626.98</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>128.63</v>
+        <v>498.8</v>
       </c>
       <c r="E5" t="n">
-        <v>100.92</v>
+        <v>293.64</v>
       </c>
       <c r="F5" t="n">
-        <v>27.46</v>
+        <v>69.87</v>
       </c>
       <c r="G5" t="n">
-        <v>108.59</v>
+        <v>319.98</v>
       </c>
       <c r="H5" t="n">
-        <v>18.45</v>
+        <v>55.88</v>
       </c>
       <c r="I5" t="n">
-        <v>55.57</v>
+        <v>66.59</v>
       </c>
       <c r="J5" t="n">
-        <v>1.52</v>
+        <v>2.31</v>
       </c>
       <c r="K5" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>80.3</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>128.63</v>
+        <v>498.8</v>
       </c>
       <c r="O5" t="n">
-        <v>777</v>
+        <v>200</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99945.50999999999</v>
+        <v>99760</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>115.77</v>
+        <v>448.92</v>
       </c>
       <c r="T5" t="n">
-        <v>9994.549999999999</v>
+        <v>9976</v>
       </c>
       <c r="U5" t="n">
-        <v>155.64</v>
+        <v>578.61</v>
       </c>
       <c r="V5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>20988.56</v>
+        <v>15961.6</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HITECHCORP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>431.9</v>
+        <v>349.1</v>
       </c>
       <c r="E6" t="n">
-        <v>399.14</v>
+        <v>229.56</v>
       </c>
       <c r="F6" t="n">
-        <v>8.210000000000001</v>
+        <v>52.07</v>
       </c>
       <c r="G6" t="n">
-        <v>453.2</v>
+        <v>223.44</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.7</v>
+        <v>56.24</v>
       </c>
       <c r="I6" t="n">
-        <v>66.59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.24</v>
+        <v>7.23</v>
       </c>
       <c r="K6" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>77.3</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>431.9</v>
+        <v>349.1</v>
       </c>
       <c r="O6" t="n">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99768.89999999999</v>
+        <v>99842.60000000001</v>
       </c>
       <c r="R6" t="n">
         <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>388.71</v>
+        <v>314.19</v>
       </c>
       <c r="T6" t="n">
-        <v>9976.889999999999</v>
+        <v>9984.26</v>
       </c>
       <c r="U6" t="n">
-        <v>513.96</v>
+        <v>404.96</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>18956.09</v>
+        <v>15974.82</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SATIN</t>
+          <t>ORIENTBELL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>228.35</v>
+        <v>432.55</v>
       </c>
       <c r="E7" t="n">
-        <v>196.63</v>
+        <v>320.27</v>
       </c>
       <c r="F7" t="n">
-        <v>16.13</v>
+        <v>35.06</v>
       </c>
       <c r="G7" t="n">
-        <v>173.45</v>
+        <v>339.7</v>
       </c>
       <c r="H7" t="n">
-        <v>31.65</v>
+        <v>27.33</v>
       </c>
       <c r="I7" t="n">
-        <v>52.26</v>
+        <v>69.73</v>
       </c>
       <c r="J7" t="n">
-        <v>10.03</v>
+        <v>2.22</v>
       </c>
       <c r="K7" t="n">
-        <v>71.25</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>74.75</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>228.35</v>
+        <v>432.55</v>
       </c>
       <c r="O7" t="n">
-        <v>437</v>
+        <v>231</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99788.95</v>
+        <v>99919.05</v>
       </c>
       <c r="R7" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>205.52</v>
+        <v>389.3</v>
       </c>
       <c r="T7" t="n">
-        <v>9978.9</v>
+        <v>9991.91</v>
       </c>
       <c r="U7" t="n">
-        <v>267.17</v>
+        <v>501.76</v>
       </c>
       <c r="V7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>16964.12</v>
+        <v>15987.05</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>154.53</v>
+        <v>1343.8</v>
       </c>
       <c r="E8" t="n">
-        <v>106.76</v>
+        <v>1054.93</v>
       </c>
       <c r="F8" t="n">
-        <v>44.75</v>
+        <v>27.38</v>
       </c>
       <c r="G8" t="n">
-        <v>133.9</v>
+        <v>1249.7</v>
       </c>
       <c r="H8" t="n">
-        <v>15.41</v>
+        <v>7.53</v>
       </c>
       <c r="I8" t="n">
-        <v>62.38</v>
+        <v>62.89</v>
       </c>
       <c r="J8" t="n">
-        <v>6.59</v>
+        <v>7.16</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1343.8</v>
+      </c>
+      <c r="O8" t="n">
         <v>74</v>
-      </c>
-      <c r="M8" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="N8" t="n">
-        <v>154.53</v>
-      </c>
-      <c r="O8" t="n">
-        <v>647</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99980.91</v>
+        <v>99441.2</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="S8" t="n">
-        <v>139.08</v>
+        <v>1209.42</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.09</v>
+        <v>9944.120000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>183.89</v>
+        <v>1558.81</v>
       </c>
       <c r="V8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>18996.37</v>
+        <v>15910.59</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>504.1</v>
+        <v>988.3</v>
       </c>
       <c r="E9" t="n">
-        <v>361.84</v>
+        <v>511.48</v>
       </c>
       <c r="F9" t="n">
-        <v>39.31</v>
+        <v>93.22</v>
       </c>
       <c r="G9" t="n">
-        <v>342.2</v>
+        <v>540</v>
       </c>
       <c r="H9" t="n">
-        <v>47.31</v>
+        <v>83.02</v>
       </c>
       <c r="I9" t="n">
-        <v>61.56</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
         <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>74.59999999999999</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>504.1</v>
+        <v>988.3</v>
       </c>
       <c r="O9" t="n">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99811.8</v>
+        <v>99818.3</v>
       </c>
       <c r="R9" t="n">
         <v>9.98</v>
       </c>
       <c r="S9" t="n">
-        <v>453.69</v>
+        <v>889.47</v>
       </c>
       <c r="T9" t="n">
-        <v>9981.18</v>
+        <v>9981.83</v>
       </c>
       <c r="U9" t="n">
-        <v>599.88</v>
+        <v>1146.43</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>18964.24</v>
+        <v>15970.93</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FCL</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59.2</v>
+        <v>795.6</v>
       </c>
       <c r="E10" t="n">
-        <v>34.11</v>
+        <v>506.08</v>
       </c>
       <c r="F10" t="n">
-        <v>73.54000000000001</v>
+        <v>57.21</v>
       </c>
       <c r="G10" t="n">
-        <v>35.79</v>
+        <v>543.4</v>
       </c>
       <c r="H10" t="n">
-        <v>65.41</v>
+        <v>46.41</v>
       </c>
       <c r="I10" t="n">
-        <v>60.12</v>
+        <v>62.61</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="K10" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>73.90000000000001</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>59.2</v>
+        <v>795.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1689</v>
+        <v>125</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99988.8</v>
+        <v>99450</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="S10" t="n">
-        <v>53.28</v>
+        <v>716.04</v>
       </c>
       <c r="T10" t="n">
-        <v>9998.879999999999</v>
+        <v>9945</v>
       </c>
       <c r="U10" t="n">
-        <v>70.45</v>
+        <v>922.9</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>18997.87</v>
+        <v>15912</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ZIMLAB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7102.5</v>
+        <v>146.61</v>
       </c>
       <c r="E11" t="n">
-        <v>5259.35</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>35.05</v>
+        <v>50.09</v>
       </c>
       <c r="G11" t="n">
-        <v>4488.9</v>
+        <v>128</v>
       </c>
       <c r="H11" t="n">
-        <v>58.22</v>
+        <v>14.54</v>
       </c>
       <c r="I11" t="n">
-        <v>56.85</v>
+        <v>69.48</v>
       </c>
       <c r="J11" t="n">
-        <v>1.74</v>
+        <v>5.06</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>73.90000000000001</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>7102.5</v>
+        <v>146.61</v>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>682</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99435</v>
+        <v>99988.02</v>
       </c>
       <c r="R11" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>6392.25</v>
+        <v>131.95</v>
       </c>
       <c r="T11" t="n">
-        <v>9943.5</v>
+        <v>9998.799999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>8451.98</v>
+        <v>170.07</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>18892.65</v>
+        <v>15998.08</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>372.1</v>
+        <v>1235.7</v>
       </c>
       <c r="E2" t="n">
-        <v>365.57</v>
+        <v>1202.16</v>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>2.79</v>
       </c>
       <c r="G2" t="n">
-        <v>369.3</v>
+        <v>1177.55</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76</v>
+        <v>4.94</v>
       </c>
       <c r="I2" t="n">
-        <v>37.3</v>
+        <v>41.81</v>
       </c>
       <c r="J2" t="n">
-        <v>1.66</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>78.75</v>
+        <v>81.25</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>47.25</v>
+        <v>48.75</v>
       </c>
       <c r="N2" t="n">
-        <v>372.1</v>
+        <v>1235.7</v>
       </c>
       <c r="O2" t="n">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99722.8</v>
+        <v>98856</v>
       </c>
       <c r="R2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>334.89</v>
+        <v>1112.13</v>
       </c>
       <c r="T2" t="n">
-        <v>9972.280000000001</v>
+        <v>9885.6</v>
       </c>
       <c r="U2" t="n">
-        <v>439.08</v>
+        <v>1458.13</v>
       </c>
       <c r="V2" t="n">
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>17950.1</v>
+        <v>17794.08</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24685</v>
+        <v>368.65</v>
       </c>
       <c r="E3" t="n">
-        <v>18330.56</v>
+        <v>364.99</v>
       </c>
       <c r="F3" t="n">
-        <v>34.67</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>19851</v>
+        <v>369.3</v>
       </c>
       <c r="H3" t="n">
-        <v>24.35</v>
+        <v>-0.18</v>
       </c>
       <c r="I3" t="n">
-        <v>69.11</v>
+        <v>35.73</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>1.54</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>46.5</v>
       </c>
       <c r="N3" t="n">
-        <v>24685</v>
+        <v>368.65</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>271</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>98740</v>
+        <v>99904.14999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>9.869999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>22216.5</v>
+        <v>331.78</v>
       </c>
       <c r="T3" t="n">
-        <v>9874</v>
+        <v>9990.42</v>
       </c>
       <c r="U3" t="n">
-        <v>28634.6</v>
+        <v>435.01</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>15798.4</v>
+        <v>17982.75</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -719,34 +719,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>HITECHCORP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3150.6</v>
+        <v>350.55</v>
       </c>
       <c r="E4" t="n">
-        <v>2186.65</v>
+        <v>229.48</v>
       </c>
       <c r="F4" t="n">
-        <v>44.08</v>
+        <v>52.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2131</v>
+        <v>223.44</v>
       </c>
       <c r="H4" t="n">
-        <v>47.85</v>
+        <v>56.89</v>
       </c>
       <c r="I4" t="n">
-        <v>68.83</v>
+        <v>67.61</v>
       </c>
       <c r="J4" t="n">
-        <v>3.31</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
         <v>75</v>
@@ -758,34 +758,34 @@
         <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>3150.6</v>
+        <v>350.55</v>
       </c>
       <c r="O4" t="n">
-        <v>31</v>
+        <v>285</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>97668.60000000001</v>
+        <v>99906.75</v>
       </c>
       <c r="R4" t="n">
-        <v>9.77</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>2835.54</v>
+        <v>315.5</v>
       </c>
       <c r="T4" t="n">
-        <v>9766.860000000001</v>
+        <v>9990.67</v>
       </c>
       <c r="U4" t="n">
-        <v>3654.7</v>
+        <v>406.64</v>
       </c>
       <c r="V4" t="n">
         <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>15626.98</v>
+        <v>15985.08</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -809,29 +809,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>498.8</v>
+        <v>483.25</v>
       </c>
       <c r="E5" t="n">
-        <v>293.64</v>
+        <v>293.5</v>
       </c>
       <c r="F5" t="n">
-        <v>69.87</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>319.98</v>
       </c>
       <c r="H5" t="n">
-        <v>55.88</v>
+        <v>51.03</v>
       </c>
       <c r="I5" t="n">
-        <v>66.59</v>
+        <v>60.42</v>
       </c>
       <c r="J5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="K5" t="n">
         <v>75</v>
@@ -843,34 +843,34 @@
         <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>498.8</v>
+        <v>483.25</v>
       </c>
       <c r="O5" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99760</v>
+        <v>99549.5</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>448.92</v>
+        <v>434.92</v>
       </c>
       <c r="T5" t="n">
-        <v>9976</v>
+        <v>9954.950000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>578.61</v>
+        <v>560.5700000000001</v>
       </c>
       <c r="V5" t="n">
         <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>15961.6</v>
+        <v>15927.92</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,34 +889,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>349.1</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="n">
-        <v>229.56</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>52.07</v>
+        <v>39.67</v>
       </c>
       <c r="G6" t="n">
-        <v>223.44</v>
+        <v>11.38</v>
       </c>
       <c r="H6" t="n">
-        <v>56.24</v>
+        <v>22.14</v>
       </c>
       <c r="I6" t="n">
-        <v>66.43000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="J6" t="n">
-        <v>7.23</v>
+        <v>2.09</v>
       </c>
       <c r="K6" t="n">
         <v>75</v>
@@ -928,34 +928,34 @@
         <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>349.1</v>
+        <v>13.9</v>
       </c>
       <c r="O6" t="n">
-        <v>286</v>
+        <v>7194</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99842.60000000001</v>
+        <v>99996.60000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>314.19</v>
+        <v>12.51</v>
       </c>
       <c r="T6" t="n">
-        <v>9984.26</v>
+        <v>9999.66</v>
       </c>
       <c r="U6" t="n">
-        <v>404.96</v>
+        <v>16.12</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>15.97</v>
       </c>
       <c r="W6" t="n">
-        <v>15974.82</v>
+        <v>15969.46</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -979,29 +979,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>432.55</v>
+        <v>413</v>
       </c>
       <c r="E7" t="n">
-        <v>320.27</v>
+        <v>318.73</v>
       </c>
       <c r="F7" t="n">
-        <v>35.06</v>
+        <v>29.58</v>
       </c>
       <c r="G7" t="n">
         <v>339.7</v>
       </c>
       <c r="H7" t="n">
-        <v>27.33</v>
+        <v>21.58</v>
       </c>
       <c r="I7" t="n">
-        <v>69.73</v>
+        <v>57.37</v>
       </c>
       <c r="J7" t="n">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
         <v>75</v>
@@ -1013,34 +1013,34 @@
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>432.55</v>
+        <v>413</v>
       </c>
       <c r="O7" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99919.05</v>
+        <v>99946</v>
       </c>
       <c r="R7" t="n">
         <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>389.3</v>
+        <v>371.7</v>
       </c>
       <c r="T7" t="n">
-        <v>9991.91</v>
+        <v>9994.6</v>
       </c>
       <c r="U7" t="n">
-        <v>501.76</v>
+        <v>479.08</v>
       </c>
       <c r="V7" t="n">
         <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>15987.05</v>
+        <v>15991.36</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,34 +1059,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1343.8</v>
+        <v>816.45</v>
       </c>
       <c r="E8" t="n">
-        <v>1054.93</v>
+        <v>572.53</v>
       </c>
       <c r="F8" t="n">
-        <v>27.38</v>
+        <v>42.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1249.7</v>
+        <v>500</v>
       </c>
       <c r="H8" t="n">
-        <v>7.53</v>
+        <v>63.29</v>
       </c>
       <c r="I8" t="n">
-        <v>62.89</v>
+        <v>69.77</v>
       </c>
       <c r="J8" t="n">
-        <v>7.16</v>
+        <v>2.11</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
@@ -1098,34 +1098,34 @@
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>1343.8</v>
+        <v>816.45</v>
       </c>
       <c r="O8" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99441.2</v>
+        <v>99606.89999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>9.94</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1209.42</v>
+        <v>734.8</v>
       </c>
       <c r="T8" t="n">
-        <v>9944.120000000001</v>
+        <v>9960.690000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1558.81</v>
+        <v>947.08</v>
       </c>
       <c r="V8" t="n">
         <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>15910.59</v>
+        <v>15937.1</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,34 +1144,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>988.3</v>
+        <v>856.55</v>
       </c>
       <c r="E9" t="n">
-        <v>511.48</v>
+        <v>704.34</v>
       </c>
       <c r="F9" t="n">
-        <v>93.22</v>
+        <v>21.61</v>
       </c>
       <c r="G9" t="n">
-        <v>540</v>
+        <v>613.8</v>
       </c>
       <c r="H9" t="n">
-        <v>83.02</v>
+        <v>39.55</v>
       </c>
       <c r="I9" t="n">
-        <v>65.65000000000001</v>
+        <v>60.18</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>75</v>
@@ -1183,34 +1183,34 @@
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>988.3</v>
+        <v>856.55</v>
       </c>
       <c r="O9" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99818.3</v>
+        <v>99359.8</v>
       </c>
       <c r="R9" t="n">
-        <v>9.98</v>
+        <v>9.94</v>
       </c>
       <c r="S9" t="n">
-        <v>889.47</v>
+        <v>770.9</v>
       </c>
       <c r="T9" t="n">
-        <v>9981.83</v>
+        <v>9935.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1146.43</v>
+        <v>993.6</v>
       </c>
       <c r="V9" t="n">
         <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>15970.93</v>
+        <v>15897.57</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>795.6</v>
+        <v>2596</v>
       </c>
       <c r="E10" t="n">
-        <v>506.08</v>
+        <v>2578</v>
       </c>
       <c r="F10" t="n">
-        <v>57.21</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>543.4</v>
+        <v>2695</v>
       </c>
       <c r="H10" t="n">
-        <v>46.41</v>
+        <v>-3.67</v>
       </c>
       <c r="I10" t="n">
-        <v>62.61</v>
+        <v>31.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>73.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>44.25</v>
       </c>
       <c r="N10" t="n">
-        <v>795.6</v>
+        <v>2596</v>
       </c>
       <c r="O10" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99450</v>
+        <v>98648</v>
       </c>
       <c r="R10" t="n">
-        <v>9.94</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>716.04</v>
+        <v>2336.4</v>
       </c>
       <c r="T10" t="n">
-        <v>9945</v>
+        <v>9864.799999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>922.9</v>
+        <v>3063.28</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>15912</v>
+        <v>17756.64</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZIMLAB</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>146.61</v>
+        <v>140.43</v>
       </c>
       <c r="E11" t="n">
-        <v>97.68000000000001</v>
+        <v>107.46</v>
       </c>
       <c r="F11" t="n">
-        <v>50.09</v>
+        <v>30.68</v>
       </c>
       <c r="G11" t="n">
-        <v>128</v>
+        <v>104.9</v>
       </c>
       <c r="H11" t="n">
-        <v>14.54</v>
+        <v>33.87</v>
       </c>
       <c r="I11" t="n">
-        <v>69.48</v>
+        <v>69.7</v>
       </c>
       <c r="J11" t="n">
-        <v>5.06</v>
+        <v>1.62</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="N11" t="n">
-        <v>146.61</v>
+        <v>140.43</v>
       </c>
       <c r="O11" t="n">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99988.02</v>
+        <v>99986.16</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>131.95</v>
+        <v>126.39</v>
       </c>
       <c r="T11" t="n">
-        <v>9998.799999999999</v>
+        <v>9998.620000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>170.07</v>
+        <v>162.9</v>
       </c>
       <c r="V11" t="n">
         <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>15998.08</v>
+        <v>15997.79</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1235.7</v>
+        <v>788.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1202.16</v>
+        <v>653.29</v>
       </c>
       <c r="F2" t="n">
-        <v>2.79</v>
+        <v>20.68</v>
       </c>
       <c r="G2" t="n">
-        <v>1177.55</v>
+        <v>629.9</v>
       </c>
       <c r="H2" t="n">
-        <v>4.94</v>
+        <v>25.16</v>
       </c>
       <c r="I2" t="n">
-        <v>41.81</v>
+        <v>61.19</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>2.01</v>
       </c>
       <c r="K2" t="n">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>48.75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>1235.7</v>
+        <v>788.4</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>98856</v>
+        <v>99338.39999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="S2" t="n">
-        <v>1112.13</v>
+        <v>709.5599999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>9885.6</v>
+        <v>9933.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1458.13</v>
+        <v>953.96</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>17794.08</v>
+        <v>20861.06</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -634,82 +634,82 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>VHL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>368.65</v>
+        <v>3650</v>
       </c>
       <c r="E3" t="n">
-        <v>364.99</v>
+        <v>3421.63</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>6.67</v>
       </c>
       <c r="G3" t="n">
-        <v>369.3</v>
+        <v>3799.8</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.18</v>
+        <v>-3.94</v>
       </c>
       <c r="I3" t="n">
-        <v>35.73</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.54</v>
+        <v>2.78</v>
       </c>
       <c r="K3" t="n">
-        <v>77.5</v>
+        <v>67.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>46.5</v>
+        <v>80.5</v>
       </c>
       <c r="N3" t="n">
-        <v>368.65</v>
+        <v>3650</v>
       </c>
       <c r="O3" t="n">
-        <v>271</v>
+        <v>27</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99904.14999999999</v>
+        <v>98550</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>331.78</v>
+        <v>3285</v>
       </c>
       <c r="T3" t="n">
-        <v>9990.42</v>
+        <v>9855</v>
       </c>
       <c r="U3" t="n">
-        <v>435.01</v>
+        <v>4343.5</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
-        <v>17982.75</v>
+        <v>18724.5</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HITECHCORP</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>350.55</v>
+        <v>231.42</v>
       </c>
       <c r="E4" t="n">
-        <v>229.48</v>
+        <v>208.46</v>
       </c>
       <c r="F4" t="n">
-        <v>52.76</v>
+        <v>11.01</v>
       </c>
       <c r="G4" t="n">
-        <v>223.44</v>
+        <v>243.07</v>
       </c>
       <c r="H4" t="n">
-        <v>56.89</v>
+        <v>-4.79</v>
       </c>
       <c r="I4" t="n">
-        <v>67.61</v>
+        <v>55.22</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>1.46</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>77.5</v>
       </c>
       <c r="N4" t="n">
-        <v>350.55</v>
+        <v>231.42</v>
       </c>
       <c r="O4" t="n">
-        <v>285</v>
+        <v>432</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99906.75</v>
+        <v>99973.44</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>315.5</v>
+        <v>208.28</v>
       </c>
       <c r="T4" t="n">
-        <v>9990.67</v>
+        <v>9997.34</v>
       </c>
       <c r="U4" t="n">
-        <v>406.64</v>
+        <v>273.08</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>15985.08</v>
+        <v>17995.22</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>483.25</v>
+        <v>441</v>
       </c>
       <c r="E5" t="n">
-        <v>293.5</v>
+        <v>399.95</v>
       </c>
       <c r="F5" t="n">
-        <v>64.65000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="G5" t="n">
-        <v>319.98</v>
+        <v>453.2</v>
       </c>
       <c r="H5" t="n">
-        <v>51.03</v>
+        <v>-2.69</v>
       </c>
       <c r="I5" t="n">
-        <v>60.42</v>
+        <v>67.94</v>
       </c>
       <c r="J5" t="n">
-        <v>2.28</v>
+        <v>1.44</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>75.8</v>
       </c>
       <c r="N5" t="n">
-        <v>483.25</v>
+        <v>441</v>
       </c>
       <c r="O5" t="n">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99549.5</v>
+        <v>99666</v>
       </c>
       <c r="R5" t="n">
-        <v>9.949999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>434.92</v>
+        <v>396.9</v>
       </c>
       <c r="T5" t="n">
-        <v>9954.950000000001</v>
+        <v>9966.6</v>
       </c>
       <c r="U5" t="n">
-        <v>560.5700000000001</v>
+        <v>520.38</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>15927.92</v>
+        <v>17939.88</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>124.89</v>
       </c>
       <c r="E6" t="n">
-        <v>9.949999999999999</v>
+        <v>100.95</v>
       </c>
       <c r="F6" t="n">
-        <v>39.67</v>
+        <v>23.71</v>
       </c>
       <c r="G6" t="n">
-        <v>11.38</v>
+        <v>108.59</v>
       </c>
       <c r="H6" t="n">
-        <v>22.14</v>
+        <v>15.01</v>
       </c>
       <c r="I6" t="n">
-        <v>61.75</v>
+        <v>48.47</v>
       </c>
       <c r="J6" t="n">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>63.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>75.05</v>
       </c>
       <c r="N6" t="n">
-        <v>13.9</v>
+        <v>124.89</v>
       </c>
       <c r="O6" t="n">
-        <v>7194</v>
+        <v>800</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99996.60000000001</v>
+        <v>99912</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>12.51</v>
+        <v>112.4</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.66</v>
+        <v>9991.200000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>16.12</v>
+        <v>147.37</v>
       </c>
       <c r="V6" t="n">
-        <v>15.97</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>15969.46</v>
+        <v>17984.16</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORIENTBELL</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>413</v>
+        <v>203.79</v>
       </c>
       <c r="E7" t="n">
-        <v>318.73</v>
+        <v>188.59</v>
       </c>
       <c r="F7" t="n">
-        <v>29.58</v>
+        <v>8.06</v>
       </c>
       <c r="G7" t="n">
-        <v>339.7</v>
+        <v>150.79</v>
       </c>
       <c r="H7" t="n">
-        <v>21.58</v>
+        <v>35.15</v>
       </c>
       <c r="I7" t="n">
-        <v>57.37</v>
+        <v>45.48</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>1.69</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>63.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>75.05</v>
       </c>
       <c r="N7" t="n">
-        <v>413</v>
+        <v>203.79</v>
       </c>
       <c r="O7" t="n">
-        <v>242</v>
+        <v>490</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99946</v>
+        <v>99857.10000000001</v>
       </c>
       <c r="R7" t="n">
         <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>371.7</v>
+        <v>183.41</v>
       </c>
       <c r="T7" t="n">
-        <v>9994.6</v>
+        <v>9985.709999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>479.08</v>
+        <v>236.4</v>
       </c>
       <c r="V7" t="n">
         <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>15991.36</v>
+        <v>15977.14</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>816.45</v>
+        <v>14.81</v>
       </c>
       <c r="E8" t="n">
-        <v>572.53</v>
+        <v>9.98</v>
       </c>
       <c r="F8" t="n">
-        <v>42.6</v>
+        <v>48.45</v>
       </c>
       <c r="G8" t="n">
-        <v>500</v>
+        <v>11.38</v>
       </c>
       <c r="H8" t="n">
-        <v>63.29</v>
+        <v>30.14</v>
       </c>
       <c r="I8" t="n">
-        <v>69.77</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>816.45</v>
+        <v>14.81</v>
       </c>
       <c r="O8" t="n">
-        <v>122</v>
+        <v>6752</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99606.89999999999</v>
+        <v>99997.12</v>
       </c>
       <c r="R8" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>734.8</v>
+        <v>13.33</v>
       </c>
       <c r="T8" t="n">
-        <v>9960.690000000001</v>
+        <v>9999.709999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>947.08</v>
+        <v>17.62</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>18.97</v>
       </c>
       <c r="W8" t="n">
-        <v>15937.1</v>
+        <v>18969.45</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>AVTNPL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>856.55</v>
+        <v>94.78</v>
       </c>
       <c r="E9" t="n">
-        <v>704.34</v>
+        <v>71.17</v>
       </c>
       <c r="F9" t="n">
-        <v>21.61</v>
+        <v>33.17</v>
       </c>
       <c r="G9" t="n">
-        <v>613.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>39.55</v>
+        <v>18.62</v>
       </c>
       <c r="I9" t="n">
-        <v>60.18</v>
+        <v>57.99</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>10.01</v>
       </c>
       <c r="K9" t="n">
         <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>856.55</v>
+        <v>94.78</v>
       </c>
       <c r="O9" t="n">
-        <v>116</v>
+        <v>1055</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99359.8</v>
+        <v>99992.89999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>770.9</v>
+        <v>85.3</v>
       </c>
       <c r="T9" t="n">
-        <v>9935.98</v>
+        <v>9999.290000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>993.6</v>
+        <v>112.79</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>15897.57</v>
+        <v>18998.65</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,82 +1229,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2596</v>
+        <v>328.2</v>
       </c>
       <c r="E10" t="n">
-        <v>2578</v>
+        <v>256.84</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>27.78</v>
       </c>
       <c r="G10" t="n">
-        <v>2695</v>
+        <v>220.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.67</v>
+        <v>48.91</v>
       </c>
       <c r="I10" t="n">
-        <v>31.12</v>
+        <v>52.52</v>
       </c>
       <c r="J10" t="n">
-        <v>2.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>73.75</v>
+        <v>57.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>44.25</v>
+        <v>74.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2596</v>
+        <v>328.2</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>304</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>98648</v>
+        <v>99772.8</v>
       </c>
       <c r="R10" t="n">
-        <v>9.859999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="S10" t="n">
-        <v>2336.4</v>
+        <v>295.38</v>
       </c>
       <c r="T10" t="n">
-        <v>9864.799999999999</v>
+        <v>9977.280000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>3063.28</v>
+        <v>377.43</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>17756.64</v>
+        <v>14965.92</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DBOL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>140.43</v>
+        <v>83.16</v>
       </c>
       <c r="E11" t="n">
-        <v>107.46</v>
+        <v>75.47</v>
       </c>
       <c r="F11" t="n">
-        <v>30.68</v>
+        <v>10.18</v>
       </c>
       <c r="G11" t="n">
-        <v>104.9</v>
+        <v>58.79</v>
       </c>
       <c r="H11" t="n">
-        <v>33.87</v>
+        <v>41.45</v>
       </c>
       <c r="I11" t="n">
-        <v>69.7</v>
+        <v>52.82</v>
       </c>
       <c r="J11" t="n">
-        <v>1.62</v>
+        <v>0.76</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>57.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>43.5</v>
+        <v>74.5</v>
       </c>
       <c r="N11" t="n">
-        <v>140.43</v>
+        <v>83.16</v>
       </c>
       <c r="O11" t="n">
-        <v>712</v>
+        <v>1202</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99986.16</v>
+        <v>99958.32000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>126.39</v>
+        <v>74.84</v>
       </c>
       <c r="T11" t="n">
-        <v>9998.620000000001</v>
+        <v>9995.83</v>
       </c>
       <c r="U11" t="n">
-        <v>162.9</v>
+        <v>94.8</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>15997.79</v>
+        <v>13994.16</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>788.4</v>
+        <v>337.65</v>
       </c>
       <c r="E2" t="n">
-        <v>653.29</v>
+        <v>257.53</v>
       </c>
       <c r="F2" t="n">
-        <v>20.68</v>
+        <v>31.11</v>
       </c>
       <c r="G2" t="n">
-        <v>629.9</v>
+        <v>220.4</v>
       </c>
       <c r="H2" t="n">
-        <v>25.16</v>
+        <v>53.2</v>
       </c>
       <c r="I2" t="n">
-        <v>61.19</v>
+        <v>58.19</v>
       </c>
       <c r="J2" t="n">
-        <v>2.01</v>
+        <v>1.2</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>82.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="N2" t="n">
-        <v>788.4</v>
+        <v>337.65</v>
       </c>
       <c r="O2" t="n">
-        <v>126</v>
+        <v>296</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99338.39999999999</v>
+        <v>99944.39999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.93</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>709.5599999999999</v>
+        <v>303.88</v>
       </c>
       <c r="T2" t="n">
-        <v>9933.84</v>
+        <v>9994.440000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>953.96</v>
+        <v>401.8</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W2" t="n">
-        <v>20861.06</v>
+        <v>18989.44</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VHL</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3650</v>
+        <v>214.89</v>
       </c>
       <c r="E3" t="n">
-        <v>3421.63</v>
+        <v>188.82</v>
       </c>
       <c r="F3" t="n">
-        <v>6.67</v>
+        <v>13.81</v>
       </c>
       <c r="G3" t="n">
-        <v>3799.8</v>
+        <v>150.79</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.94</v>
+        <v>42.51</v>
       </c>
       <c r="I3" t="n">
-        <v>67.09999999999999</v>
+        <v>56.15</v>
       </c>
       <c r="J3" t="n">
-        <v>2.78</v>
+        <v>3.29</v>
       </c>
       <c r="K3" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>80.5</v>
+        <v>81.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3650</v>
+        <v>214.89</v>
       </c>
       <c r="O3" t="n">
-        <v>27</v>
+        <v>465</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>98550</v>
+        <v>99923.85000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>3285</v>
+        <v>193.4</v>
       </c>
       <c r="T3" t="n">
-        <v>9855</v>
+        <v>9992.379999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>4343.5</v>
+        <v>257.87</v>
       </c>
       <c r="V3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W3" t="n">
-        <v>18724.5</v>
+        <v>19984.77</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>231.42</v>
+        <v>806.1</v>
       </c>
       <c r="E4" t="n">
-        <v>208.46</v>
+        <v>654.9</v>
       </c>
       <c r="F4" t="n">
-        <v>11.01</v>
+        <v>23.09</v>
       </c>
       <c r="G4" t="n">
-        <v>243.07</v>
+        <v>629.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.79</v>
+        <v>27.97</v>
       </c>
       <c r="I4" t="n">
-        <v>55.22</v>
+        <v>64.38</v>
       </c>
       <c r="J4" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="K4" t="n">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>77.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>231.42</v>
+        <v>806.1</v>
       </c>
       <c r="O4" t="n">
-        <v>432</v>
+        <v>124</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99973.44</v>
+        <v>99956.39999999999</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>208.28</v>
+        <v>725.49</v>
       </c>
       <c r="T4" t="n">
-        <v>9997.34</v>
+        <v>9995.639999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>273.08</v>
+        <v>975.38</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>17995.22</v>
+        <v>20990.84</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>441</v>
+        <v>292.25</v>
       </c>
       <c r="E5" t="n">
-        <v>399.95</v>
+        <v>222.02</v>
       </c>
       <c r="F5" t="n">
-        <v>10.26</v>
+        <v>31.63</v>
       </c>
       <c r="G5" t="n">
-        <v>453.2</v>
+        <v>285</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.69</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>67.94</v>
+        <v>60.99</v>
       </c>
       <c r="J5" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="M5" t="n">
-        <v>75.8</v>
+        <v>77.5</v>
       </c>
       <c r="N5" t="n">
-        <v>441</v>
+        <v>292.25</v>
       </c>
       <c r="O5" t="n">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99666</v>
+        <v>99949.5</v>
       </c>
       <c r="R5" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>396.9</v>
+        <v>263.03</v>
       </c>
       <c r="T5" t="n">
-        <v>9966.6</v>
+        <v>9994.950000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>520.38</v>
+        <v>353.62</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W5" t="n">
-        <v>17939.88</v>
+        <v>20989.4</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>VHL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>124.89</v>
+        <v>3627.6</v>
       </c>
       <c r="E6" t="n">
-        <v>100.95</v>
+        <v>3421.93</v>
       </c>
       <c r="F6" t="n">
-        <v>23.71</v>
+        <v>6.01</v>
       </c>
       <c r="G6" t="n">
-        <v>108.59</v>
+        <v>3799.8</v>
       </c>
       <c r="H6" t="n">
-        <v>15.01</v>
+        <v>-4.53</v>
       </c>
       <c r="I6" t="n">
-        <v>48.47</v>
+        <v>64.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>63.75</v>
+        <v>58.75</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>75.05</v>
+        <v>75.25</v>
       </c>
       <c r="N6" t="n">
-        <v>124.89</v>
+        <v>3627.6</v>
       </c>
       <c r="O6" t="n">
-        <v>800</v>
+        <v>27</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99912</v>
+        <v>97945.2</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>112.4</v>
+        <v>3264.84</v>
       </c>
       <c r="T6" t="n">
-        <v>9991.200000000001</v>
+        <v>9794.52</v>
       </c>
       <c r="U6" t="n">
-        <v>147.37</v>
+        <v>4208.02</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>17984.16</v>
+        <v>15671.23</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>CPCAP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>203.79</v>
+        <v>175.66</v>
       </c>
       <c r="E7" t="n">
-        <v>188.59</v>
+        <v>107.64</v>
       </c>
       <c r="F7" t="n">
-        <v>8.06</v>
+        <v>63.19</v>
       </c>
       <c r="G7" t="n">
-        <v>150.79</v>
+        <v>133.9</v>
       </c>
       <c r="H7" t="n">
-        <v>35.15</v>
+        <v>31.19</v>
       </c>
       <c r="I7" t="n">
-        <v>45.48</v>
+        <v>69.59</v>
       </c>
       <c r="J7" t="n">
-        <v>1.69</v>
+        <v>4.18</v>
       </c>
       <c r="K7" t="n">
-        <v>63.75</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
-        <v>75.05</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>203.79</v>
+        <v>175.66</v>
       </c>
       <c r="O7" t="n">
-        <v>490</v>
+        <v>569</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99857.10000000001</v>
+        <v>99950.53999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>183.41</v>
+        <v>158.09</v>
       </c>
       <c r="T7" t="n">
-        <v>9985.709999999999</v>
+        <v>9995.049999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>236.4</v>
+        <v>209.04</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>15977.14</v>
+        <v>18990.6</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,34 +1059,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>AEROENTER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.81</v>
+        <v>136.68</v>
       </c>
       <c r="E8" t="n">
-        <v>9.98</v>
+        <v>103.55</v>
       </c>
       <c r="F8" t="n">
-        <v>48.45</v>
+        <v>31.99</v>
       </c>
       <c r="G8" t="n">
-        <v>11.38</v>
+        <v>113.9</v>
       </c>
       <c r="H8" t="n">
-        <v>30.14</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>67.81999999999999</v>
+        <v>56.78</v>
       </c>
       <c r="J8" t="n">
-        <v>2.13</v>
+        <v>4.78</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
@@ -1098,34 +1098,34 @@
         <v>74.59999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>14.81</v>
+        <v>136.68</v>
       </c>
       <c r="O8" t="n">
-        <v>6752</v>
+        <v>731</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99997.12</v>
+        <v>99913.08</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>13.33</v>
+        <v>123.01</v>
       </c>
       <c r="T8" t="n">
-        <v>9999.709999999999</v>
+        <v>9991.309999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>17.62</v>
+        <v>162.65</v>
       </c>
       <c r="V8" t="n">
-        <v>18.97</v>
+        <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>18969.45</v>
+        <v>18983.49</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AVTNPL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>94.78</v>
+        <v>83</v>
       </c>
       <c r="E9" t="n">
-        <v>71.17</v>
+        <v>75.61</v>
       </c>
       <c r="F9" t="n">
-        <v>33.17</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>79.90000000000001</v>
+        <v>58.79</v>
       </c>
       <c r="H9" t="n">
-        <v>18.62</v>
+        <v>41.18</v>
       </c>
       <c r="I9" t="n">
-        <v>57.99</v>
+        <v>52.37</v>
       </c>
       <c r="J9" t="n">
-        <v>10.01</v>
+        <v>0.78</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>57.5</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>74.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="N9" t="n">
-        <v>94.78</v>
+        <v>83</v>
       </c>
       <c r="O9" t="n">
-        <v>1055</v>
+        <v>1204</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99992.89999999999</v>
+        <v>99932</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>85.3</v>
+        <v>74.7</v>
       </c>
       <c r="T9" t="n">
-        <v>9999.290000000001</v>
+        <v>9993.200000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>112.79</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>18998.65</v>
+        <v>12991.16</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>328.2</v>
+        <v>25.88</v>
       </c>
       <c r="E10" t="n">
-        <v>256.84</v>
+        <v>15.91</v>
       </c>
       <c r="F10" t="n">
-        <v>27.78</v>
+        <v>62.62</v>
       </c>
       <c r="G10" t="n">
-        <v>220.4</v>
+        <v>17.4</v>
       </c>
       <c r="H10" t="n">
-        <v>48.91</v>
+        <v>48.74</v>
       </c>
       <c r="I10" t="n">
-        <v>52.52</v>
+        <v>79.42</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>57.5</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M10" t="n">
-        <v>74.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>328.2</v>
+        <v>25.88</v>
       </c>
       <c r="O10" t="n">
-        <v>304</v>
+        <v>3863</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99772.8</v>
+        <v>99974.44</v>
       </c>
       <c r="R10" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>295.38</v>
+        <v>23.29</v>
       </c>
       <c r="T10" t="n">
-        <v>9977.280000000001</v>
+        <v>9997.440000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>377.43</v>
+        <v>30.02</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>14965.92</v>
+        <v>15995.91</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83.16</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>75.47</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.18</v>
+        <v>49.97</v>
       </c>
       <c r="G11" t="n">
-        <v>58.79</v>
+        <v>11.38</v>
       </c>
       <c r="H11" t="n">
-        <v>41.45</v>
+        <v>31.81</v>
       </c>
       <c r="I11" t="n">
-        <v>52.82</v>
+        <v>68.92</v>
       </c>
       <c r="J11" t="n">
-        <v>0.76</v>
+        <v>1.42</v>
       </c>
       <c r="K11" t="n">
-        <v>57.5</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
-        <v>74.5</v>
+        <v>74</v>
       </c>
       <c r="N11" t="n">
-        <v>83.16</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>1202</v>
+        <v>6666</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99958.32000000001</v>
+        <v>99990</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>74.84</v>
+        <v>13.5</v>
       </c>
       <c r="T11" t="n">
-        <v>9995.83</v>
+        <v>9999</v>
       </c>
       <c r="U11" t="n">
-        <v>94.8</v>
+        <v>17.85</v>
       </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>13994.16</v>
+        <v>18998.1</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>337.65</v>
+        <v>464</v>
       </c>
       <c r="E2" t="n">
-        <v>257.53</v>
+        <v>352.77</v>
       </c>
       <c r="F2" t="n">
-        <v>31.11</v>
+        <v>31.53</v>
       </c>
       <c r="G2" t="n">
-        <v>220.4</v>
+        <v>305.9</v>
       </c>
       <c r="H2" t="n">
-        <v>53.2</v>
+        <v>51.68</v>
       </c>
       <c r="I2" t="n">
-        <v>58.19</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="N2" t="n">
-        <v>337.65</v>
+        <v>464</v>
       </c>
       <c r="O2" t="n">
-        <v>296</v>
+        <v>215</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99944.39999999999</v>
+        <v>99760</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S2" t="n">
-        <v>303.88</v>
+        <v>417.6</v>
       </c>
       <c r="T2" t="n">
-        <v>9994.440000000001</v>
+        <v>9976</v>
       </c>
       <c r="U2" t="n">
-        <v>401.8</v>
+        <v>538.24</v>
       </c>
       <c r="V2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W2" t="n">
-        <v>18989.44</v>
+        <v>15961.6</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>MODISONLTD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>214.89</v>
+        <v>545.3</v>
       </c>
       <c r="E3" t="n">
-        <v>188.82</v>
+        <v>254.45</v>
       </c>
       <c r="F3" t="n">
-        <v>13.81</v>
+        <v>114.3</v>
       </c>
       <c r="G3" t="n">
-        <v>150.79</v>
+        <v>197.45</v>
       </c>
       <c r="H3" t="n">
-        <v>42.51</v>
+        <v>176.17</v>
       </c>
       <c r="I3" t="n">
-        <v>56.15</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.29</v>
+        <v>2.48</v>
       </c>
       <c r="K3" t="n">
         <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>81.8</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>214.89</v>
+        <v>545.3</v>
       </c>
       <c r="O3" t="n">
-        <v>465</v>
+        <v>183</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99923.85000000001</v>
+        <v>99789.89999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>193.4</v>
+        <v>490.77</v>
       </c>
       <c r="T3" t="n">
-        <v>9992.379999999999</v>
+        <v>9978.99</v>
       </c>
       <c r="U3" t="n">
-        <v>257.87</v>
+        <v>632.55</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>19984.77</v>
+        <v>15966.38</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>EIMCOELECO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>806.1</v>
+        <v>2454.2</v>
       </c>
       <c r="E4" t="n">
-        <v>654.9</v>
+        <v>1774.9</v>
       </c>
       <c r="F4" t="n">
-        <v>23.09</v>
+        <v>38.27</v>
       </c>
       <c r="G4" t="n">
-        <v>629.9</v>
+        <v>2380</v>
       </c>
       <c r="H4" t="n">
-        <v>27.97</v>
+        <v>3.12</v>
       </c>
       <c r="I4" t="n">
-        <v>64.38</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>4.25</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>81.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>806.1</v>
+        <v>2454.2</v>
       </c>
       <c r="O4" t="n">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99956.39999999999</v>
+        <v>98168</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="S4" t="n">
-        <v>725.49</v>
+        <v>2208.78</v>
       </c>
       <c r="T4" t="n">
-        <v>9995.639999999999</v>
+        <v>9816.799999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>975.38</v>
+        <v>2846.87</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>20990.84</v>
+        <v>15706.88</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>RUBYMILLS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>292.25</v>
+        <v>541.25</v>
       </c>
       <c r="E5" t="n">
-        <v>222.02</v>
+        <v>301.38</v>
       </c>
       <c r="F5" t="n">
-        <v>31.63</v>
+        <v>79.59</v>
       </c>
       <c r="G5" t="n">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>101.21</v>
       </c>
       <c r="I5" t="n">
-        <v>60.99</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.96</v>
+        <v>4.95</v>
       </c>
       <c r="K5" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>77.5</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>292.25</v>
+        <v>541.25</v>
       </c>
       <c r="O5" t="n">
-        <v>342</v>
+        <v>184</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99949.5</v>
+        <v>99590</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>263.03</v>
+        <v>487.12</v>
       </c>
       <c r="T5" t="n">
-        <v>9994.950000000001</v>
+        <v>9959</v>
       </c>
       <c r="U5" t="n">
-        <v>353.62</v>
+        <v>627.85</v>
       </c>
       <c r="V5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>20989.4</v>
+        <v>15934.4</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VHL</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3627.6</v>
+        <v>206.47</v>
       </c>
       <c r="E6" t="n">
-        <v>3421.93</v>
+        <v>137.14</v>
       </c>
       <c r="F6" t="n">
-        <v>6.01</v>
+        <v>50.55</v>
       </c>
       <c r="G6" t="n">
-        <v>3799.8</v>
+        <v>123.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.53</v>
+        <v>66.78</v>
       </c>
       <c r="I6" t="n">
-        <v>64.3</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="n">
-        <v>58.75</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>75.25</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>3627.6</v>
+        <v>206.47</v>
       </c>
       <c r="O6" t="n">
-        <v>27</v>
+        <v>484</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>97945.2</v>
+        <v>99931.48</v>
       </c>
       <c r="R6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>3264.84</v>
+        <v>185.82</v>
       </c>
       <c r="T6" t="n">
-        <v>9794.52</v>
+        <v>9993.15</v>
       </c>
       <c r="U6" t="n">
-        <v>4208.02</v>
+        <v>239.51</v>
       </c>
       <c r="V6" t="n">
         <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>15671.23</v>
+        <v>15989.04</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CPCAP</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>175.66</v>
+        <v>508.65</v>
       </c>
       <c r="E7" t="n">
-        <v>107.64</v>
+        <v>298.49</v>
       </c>
       <c r="F7" t="n">
-        <v>63.19</v>
+        <v>70.41</v>
       </c>
       <c r="G7" t="n">
-        <v>133.9</v>
+        <v>319.98</v>
       </c>
       <c r="H7" t="n">
-        <v>31.19</v>
+        <v>58.96</v>
       </c>
       <c r="I7" t="n">
-        <v>69.59</v>
+        <v>63.88</v>
       </c>
       <c r="J7" t="n">
-        <v>4.18</v>
+        <v>2.21</v>
       </c>
       <c r="K7" t="n">
         <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>74.59999999999999</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>175.66</v>
+        <v>508.65</v>
       </c>
       <c r="O7" t="n">
-        <v>569</v>
+        <v>196</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99950.53999999999</v>
+        <v>99695.39999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>158.09</v>
+        <v>457.78</v>
       </c>
       <c r="T7" t="n">
-        <v>9995.049999999999</v>
+        <v>9969.540000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>209.04</v>
+        <v>590.03</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>18990.6</v>
+        <v>15951.26</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEROENTER</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>136.68</v>
+        <v>1489.1</v>
       </c>
       <c r="E8" t="n">
-        <v>103.55</v>
+        <v>951.8099999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>31.99</v>
+        <v>56.45</v>
       </c>
       <c r="G8" t="n">
-        <v>113.9</v>
+        <v>944.6</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>57.64</v>
       </c>
       <c r="I8" t="n">
-        <v>56.78</v>
+        <v>59.11</v>
       </c>
       <c r="J8" t="n">
-        <v>4.78</v>
+        <v>3.88</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>74.59999999999999</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>136.68</v>
+        <v>1489.1</v>
       </c>
       <c r="O8" t="n">
-        <v>731</v>
+        <v>67</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99913.08</v>
+        <v>99769.7</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>123.01</v>
+        <v>1340.19</v>
       </c>
       <c r="T8" t="n">
-        <v>9991.309999999999</v>
+        <v>9976.969999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>162.65</v>
+        <v>1727.36</v>
       </c>
       <c r="V8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>18983.49</v>
+        <v>15963.15</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>SANATHAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>548.15</v>
       </c>
       <c r="E9" t="n">
-        <v>75.61</v>
+        <v>441.3</v>
       </c>
       <c r="F9" t="n">
-        <v>9.779999999999999</v>
+        <v>24.21</v>
       </c>
       <c r="G9" t="n">
-        <v>58.79</v>
+        <v>512</v>
       </c>
       <c r="H9" t="n">
-        <v>41.18</v>
+        <v>7.06</v>
       </c>
       <c r="I9" t="n">
-        <v>52.37</v>
+        <v>66.62</v>
       </c>
       <c r="J9" t="n">
-        <v>0.78</v>
+        <v>3.19</v>
       </c>
       <c r="K9" t="n">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>74.5</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>83</v>
+        <v>548.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1204</v>
+        <v>182</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99932</v>
+        <v>99763.3</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S9" t="n">
-        <v>74.7</v>
+        <v>493.34</v>
       </c>
       <c r="T9" t="n">
-        <v>9993.200000000001</v>
+        <v>9976.33</v>
       </c>
       <c r="U9" t="n">
-        <v>93.79000000000001</v>
+        <v>635.85</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>12991.16</v>
+        <v>15962.13</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.88</v>
+        <v>850.8</v>
       </c>
       <c r="E10" t="n">
-        <v>15.91</v>
+        <v>645.47</v>
       </c>
       <c r="F10" t="n">
-        <v>62.62</v>
+        <v>31.81</v>
       </c>
       <c r="G10" t="n">
-        <v>17.4</v>
+        <v>820</v>
       </c>
       <c r="H10" t="n">
-        <v>48.74</v>
+        <v>3.76</v>
       </c>
       <c r="I10" t="n">
-        <v>79.42</v>
+        <v>61.62</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>74.34999999999999</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>25.88</v>
+        <v>850.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3863</v>
+        <v>117</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99974.44</v>
+        <v>99543.60000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>23.29</v>
+        <v>765.72</v>
       </c>
       <c r="T10" t="n">
-        <v>9997.440000000001</v>
+        <v>9954.360000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>30.02</v>
+        <v>986.9299999999999</v>
       </c>
       <c r="V10" t="n">
         <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>15995.91</v>
+        <v>15926.98</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>178.98</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>152.54</v>
       </c>
       <c r="F11" t="n">
-        <v>49.97</v>
+        <v>17.33</v>
       </c>
       <c r="G11" t="n">
-        <v>11.38</v>
+        <v>130.75</v>
       </c>
       <c r="H11" t="n">
-        <v>31.81</v>
+        <v>36.89</v>
       </c>
       <c r="I11" t="n">
-        <v>68.92</v>
+        <v>66.03</v>
       </c>
       <c r="J11" t="n">
-        <v>1.42</v>
+        <v>2.48</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>178.98</v>
       </c>
       <c r="O11" t="n">
-        <v>6666</v>
+        <v>558</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99990</v>
+        <v>99870.84</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>13.5</v>
+        <v>161.08</v>
       </c>
       <c r="T11" t="n">
-        <v>9999</v>
+        <v>9987.08</v>
       </c>
       <c r="U11" t="n">
-        <v>17.85</v>
+        <v>205.83</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>18998.1</v>
+        <v>14980.63</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>464</v>
+        <v>447.95</v>
       </c>
       <c r="E2" t="n">
-        <v>352.77</v>
+        <v>400.15</v>
       </c>
       <c r="F2" t="n">
-        <v>31.53</v>
+        <v>11.94</v>
       </c>
       <c r="G2" t="n">
-        <v>305.9</v>
+        <v>453.2</v>
       </c>
       <c r="H2" t="n">
-        <v>51.68</v>
+        <v>-1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>65.26000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>1.34</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>77.3</v>
       </c>
       <c r="N2" t="n">
-        <v>464</v>
+        <v>447.95</v>
       </c>
       <c r="O2" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99760</v>
+        <v>99892.85000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>417.6</v>
+        <v>403.16</v>
       </c>
       <c r="T2" t="n">
-        <v>9976</v>
+        <v>9989.280000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>538.24</v>
+        <v>528.58</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>15961.6</v>
+        <v>17980.71</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>545.3</v>
+        <v>335.95</v>
       </c>
       <c r="E3" t="n">
-        <v>254.45</v>
+        <v>259.55</v>
       </c>
       <c r="F3" t="n">
-        <v>114.3</v>
+        <v>29.44</v>
       </c>
       <c r="G3" t="n">
-        <v>197.45</v>
+        <v>220.4</v>
       </c>
       <c r="H3" t="n">
-        <v>176.17</v>
+        <v>52.43</v>
       </c>
       <c r="I3" t="n">
-        <v>67.56999999999999</v>
+        <v>55.59</v>
       </c>
       <c r="J3" t="n">
-        <v>2.48</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>545.3</v>
+        <v>335.95</v>
       </c>
       <c r="O3" t="n">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99789.89999999999</v>
+        <v>99777.14999999999</v>
       </c>
       <c r="R3" t="n">
         <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>490.77</v>
+        <v>302.36</v>
       </c>
       <c r="T3" t="n">
-        <v>9978.99</v>
+        <v>9977.719999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>632.55</v>
+        <v>396.42</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>15966.38</v>
+        <v>17959.89</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EIMCOELECO</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2454.2</v>
+        <v>80.16</v>
       </c>
       <c r="E4" t="n">
-        <v>1774.9</v>
+        <v>75.98</v>
       </c>
       <c r="F4" t="n">
-        <v>38.27</v>
+        <v>5.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2380</v>
+        <v>58.79</v>
       </c>
       <c r="H4" t="n">
-        <v>3.12</v>
+        <v>36.35</v>
       </c>
       <c r="I4" t="n">
-        <v>65.51000000000001</v>
+        <v>44.29</v>
       </c>
       <c r="J4" t="n">
-        <v>4.25</v>
+        <v>1.54</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>58.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>75.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2454.2</v>
+        <v>80.16</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>1247</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>98168</v>
+        <v>99959.52</v>
       </c>
       <c r="R4" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>2208.78</v>
+        <v>72.14</v>
       </c>
       <c r="T4" t="n">
-        <v>9816.799999999999</v>
+        <v>9995.950000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>2846.87</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="W4" t="n">
-        <v>15706.88</v>
+        <v>16003.52</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RUBYMILLS</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>541.25</v>
+        <v>335</v>
       </c>
       <c r="E5" t="n">
-        <v>301.38</v>
+        <v>306.69</v>
       </c>
       <c r="F5" t="n">
-        <v>79.59</v>
+        <v>9.23</v>
       </c>
       <c r="G5" t="n">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="H5" t="n">
-        <v>101.21</v>
+        <v>52.27</v>
       </c>
       <c r="I5" t="n">
-        <v>68.54000000000001</v>
+        <v>53.66</v>
       </c>
       <c r="J5" t="n">
-        <v>4.95</v>
+        <v>0.58</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>57.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>74.5</v>
       </c>
       <c r="N5" t="n">
-        <v>541.25</v>
+        <v>335</v>
       </c>
       <c r="O5" t="n">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99590</v>
+        <v>99830</v>
       </c>
       <c r="R5" t="n">
-        <v>9.960000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>487.12</v>
+        <v>301.5</v>
       </c>
       <c r="T5" t="n">
-        <v>9959</v>
+        <v>9983</v>
       </c>
       <c r="U5" t="n">
-        <v>627.85</v>
+        <v>378.55</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>15934.4</v>
+        <v>12977.9</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>206.47</v>
+        <v>24.79</v>
       </c>
       <c r="E6" t="n">
-        <v>137.14</v>
+        <v>16.08</v>
       </c>
       <c r="F6" t="n">
-        <v>50.55</v>
+        <v>54.15</v>
       </c>
       <c r="G6" t="n">
-        <v>123.8</v>
+        <v>17.4</v>
       </c>
       <c r="H6" t="n">
-        <v>66.78</v>
+        <v>42.47</v>
       </c>
       <c r="I6" t="n">
-        <v>67.95999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>0.37</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>206.47</v>
+        <v>24.79</v>
       </c>
       <c r="O6" t="n">
-        <v>484</v>
+        <v>4033</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99931.48</v>
+        <v>99978.07000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>185.82</v>
+        <v>22.31</v>
       </c>
       <c r="T6" t="n">
-        <v>9993.15</v>
+        <v>9997.809999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>239.51</v>
+        <v>29.25</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>17.99</v>
       </c>
       <c r="W6" t="n">
-        <v>15989.04</v>
+        <v>17986.05</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>508.65</v>
+        <v>790.65</v>
       </c>
       <c r="E7" t="n">
-        <v>298.49</v>
+        <v>659.5</v>
       </c>
       <c r="F7" t="n">
-        <v>70.41</v>
+        <v>19.89</v>
       </c>
       <c r="G7" t="n">
-        <v>319.98</v>
+        <v>629.9</v>
       </c>
       <c r="H7" t="n">
-        <v>58.96</v>
+        <v>25.52</v>
       </c>
       <c r="I7" t="n">
-        <v>63.88</v>
+        <v>58.01</v>
       </c>
       <c r="J7" t="n">
-        <v>2.21</v>
+        <v>0.61</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>508.65</v>
+        <v>790.65</v>
       </c>
       <c r="O7" t="n">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99695.39999999999</v>
+        <v>99621.89999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>457.78</v>
+        <v>711.58</v>
       </c>
       <c r="T7" t="n">
-        <v>9969.540000000001</v>
+        <v>9962.190000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>590.03</v>
+        <v>925.0599999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W7" t="n">
-        <v>15951.26</v>
+        <v>16935.72</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1489.1</v>
+        <v>307.65</v>
       </c>
       <c r="E8" t="n">
-        <v>951.8099999999999</v>
+        <v>223.45</v>
       </c>
       <c r="F8" t="n">
-        <v>56.45</v>
+        <v>37.68</v>
       </c>
       <c r="G8" t="n">
-        <v>944.6</v>
+        <v>285</v>
       </c>
       <c r="H8" t="n">
-        <v>57.64</v>
+        <v>7.95</v>
       </c>
       <c r="I8" t="n">
-        <v>59.11</v>
+        <v>62.58</v>
       </c>
       <c r="J8" t="n">
-        <v>3.88</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>73.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1489.1</v>
+        <v>307.65</v>
       </c>
       <c r="O8" t="n">
-        <v>67</v>
+        <v>325</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99769.7</v>
+        <v>99986.25</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>1340.19</v>
+        <v>276.88</v>
       </c>
       <c r="T8" t="n">
-        <v>9976.969999999999</v>
+        <v>9998.620000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1727.36</v>
+        <v>363.03</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>15963.15</v>
+        <v>17997.53</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANATHAN</t>
+          <t>VHL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>548.15</v>
+        <v>3694.4</v>
       </c>
       <c r="E9" t="n">
-        <v>441.3</v>
+        <v>3423.27</v>
       </c>
       <c r="F9" t="n">
-        <v>24.21</v>
+        <v>7.92</v>
       </c>
       <c r="G9" t="n">
-        <v>512</v>
+        <v>3799.8</v>
       </c>
       <c r="H9" t="n">
-        <v>7.06</v>
+        <v>-2.77</v>
       </c>
       <c r="I9" t="n">
-        <v>66.62</v>
+        <v>67.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>56.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>73.75</v>
       </c>
       <c r="N9" t="n">
-        <v>548.15</v>
+        <v>3694.4</v>
       </c>
       <c r="O9" t="n">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99763.3</v>
+        <v>99748.8</v>
       </c>
       <c r="R9" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>493.34</v>
+        <v>3324.96</v>
       </c>
       <c r="T9" t="n">
-        <v>9976.33</v>
+        <v>9974.879999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>635.85</v>
+        <v>4285.5</v>
       </c>
       <c r="V9" t="n">
         <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>15962.13</v>
+        <v>15959.81</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>850.8</v>
+        <v>14.45</v>
       </c>
       <c r="E10" t="n">
-        <v>645.47</v>
+        <v>10.07</v>
       </c>
       <c r="F10" t="n">
-        <v>31.81</v>
+        <v>43.48</v>
       </c>
       <c r="G10" t="n">
-        <v>820</v>
+        <v>11.38</v>
       </c>
       <c r="H10" t="n">
-        <v>3.76</v>
+        <v>26.98</v>
       </c>
       <c r="I10" t="n">
-        <v>61.62</v>
+        <v>60.98</v>
       </c>
       <c r="J10" t="n">
-        <v>3.34</v>
+        <v>1.12</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>71.75</v>
       </c>
       <c r="N10" t="n">
-        <v>850.8</v>
+        <v>14.45</v>
       </c>
       <c r="O10" t="n">
-        <v>117</v>
+        <v>6920</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99543.60000000001</v>
+        <v>99994</v>
       </c>
       <c r="R10" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>765.72</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>9954.360000000001</v>
+        <v>9999.4</v>
       </c>
       <c r="U10" t="n">
-        <v>986.9299999999999</v>
+        <v>17.05</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>17.99</v>
       </c>
       <c r="W10" t="n">
-        <v>15926.98</v>
+        <v>17988.92</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>178.98</v>
+        <v>128.03</v>
       </c>
       <c r="E11" t="n">
-        <v>152.54</v>
+        <v>101.77</v>
       </c>
       <c r="F11" t="n">
-        <v>17.33</v>
+        <v>25.8</v>
       </c>
       <c r="G11" t="n">
-        <v>130.75</v>
+        <v>108.59</v>
       </c>
       <c r="H11" t="n">
-        <v>36.89</v>
+        <v>17.9</v>
       </c>
       <c r="I11" t="n">
-        <v>66.03</v>
+        <v>52.97</v>
       </c>
       <c r="J11" t="n">
-        <v>2.48</v>
+        <v>0.71</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>57.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>71.3</v>
       </c>
       <c r="N11" t="n">
-        <v>178.98</v>
+        <v>128.03</v>
       </c>
       <c r="O11" t="n">
-        <v>558</v>
+        <v>781</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99870.84</v>
+        <v>99991.42999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>161.08</v>
+        <v>115.23</v>
       </c>
       <c r="T11" t="n">
-        <v>9987.08</v>
+        <v>9999.139999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>205.83</v>
+        <v>147.23</v>
       </c>
       <c r="V11" t="n">
         <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>14980.63</v>
+        <v>14998.71</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>447.95</v>
+        <v>338</v>
       </c>
       <c r="E2" t="n">
-        <v>400.15</v>
+        <v>307.08</v>
       </c>
       <c r="F2" t="n">
-        <v>11.94</v>
+        <v>10.07</v>
       </c>
       <c r="G2" t="n">
-        <v>453.2</v>
+        <v>220</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.16</v>
+        <v>53.64</v>
       </c>
       <c r="I2" t="n">
-        <v>68.84</v>
+        <v>56.36</v>
       </c>
       <c r="J2" t="n">
-        <v>1.34</v>
+        <v>3.59</v>
       </c>
       <c r="K2" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>77.3</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>447.95</v>
+        <v>338</v>
       </c>
       <c r="O2" t="n">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99892.85000000001</v>
+        <v>99710</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>403.16</v>
+        <v>304.2</v>
       </c>
       <c r="T2" t="n">
-        <v>9989.280000000001</v>
+        <v>9971</v>
       </c>
       <c r="U2" t="n">
-        <v>528.58</v>
+        <v>405.6</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>17980.71</v>
+        <v>19942</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>335.95</v>
+        <v>61.32</v>
       </c>
       <c r="E3" t="n">
-        <v>259.55</v>
+        <v>49.48</v>
       </c>
       <c r="F3" t="n">
-        <v>29.44</v>
+        <v>23.93</v>
       </c>
       <c r="G3" t="n">
-        <v>220.4</v>
+        <v>62.84</v>
       </c>
       <c r="H3" t="n">
-        <v>52.43</v>
+        <v>-2.42</v>
       </c>
       <c r="I3" t="n">
-        <v>55.59</v>
+        <v>64.62</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>2.91</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>82</v>
       </c>
       <c r="N3" t="n">
-        <v>335.95</v>
+        <v>61.32</v>
       </c>
       <c r="O3" t="n">
-        <v>297</v>
+        <v>1630</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99777.14999999999</v>
+        <v>99951.60000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>302.36</v>
+        <v>55.19</v>
       </c>
       <c r="T3" t="n">
-        <v>9977.719999999999</v>
+        <v>9995.16</v>
       </c>
       <c r="U3" t="n">
-        <v>396.42</v>
+        <v>74.2</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>17959.89</v>
+        <v>20989.84</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>VHL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80.16</v>
+        <v>3740.4</v>
       </c>
       <c r="E4" t="n">
-        <v>75.98</v>
+        <v>3424.05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.5</v>
+        <v>9.24</v>
       </c>
       <c r="G4" t="n">
-        <v>58.79</v>
+        <v>3799.8</v>
       </c>
       <c r="H4" t="n">
-        <v>36.35</v>
+        <v>-1.56</v>
       </c>
       <c r="I4" t="n">
-        <v>44.29</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="K4" t="n">
-        <v>58.75</v>
+        <v>67.5</v>
       </c>
       <c r="L4" t="n">
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>75.25</v>
+        <v>80.5</v>
       </c>
       <c r="N4" t="n">
-        <v>80.16</v>
+        <v>3740.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1247</v>
+        <v>26</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99959.52</v>
+        <v>97250.39999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="S4" t="n">
-        <v>72.14</v>
+        <v>3366.36</v>
       </c>
       <c r="T4" t="n">
-        <v>9995.950000000001</v>
+        <v>9725.040000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>92.98999999999999</v>
+        <v>4376.27</v>
       </c>
       <c r="V4" t="n">
-        <v>16.01</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>16003.52</v>
+        <v>16532.57</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>335</v>
+        <v>329.85</v>
       </c>
       <c r="E5" t="n">
-        <v>306.69</v>
+        <v>260.17</v>
       </c>
       <c r="F5" t="n">
-        <v>9.23</v>
+        <v>26.78</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>52.27</v>
+        <v>49.66</v>
       </c>
       <c r="I5" t="n">
-        <v>53.66</v>
+        <v>51.05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.58</v>
+        <v>1.28</v>
       </c>
       <c r="K5" t="n">
-        <v>57.5</v>
+        <v>66.25</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>74.5</v>
+        <v>79.75</v>
       </c>
       <c r="N5" t="n">
-        <v>335</v>
+        <v>329.85</v>
       </c>
       <c r="O5" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99830</v>
+        <v>99944.55</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>301.5</v>
+        <v>296.86</v>
       </c>
       <c r="T5" t="n">
-        <v>9983</v>
+        <v>9994.459999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>378.55</v>
+        <v>382.63</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>12977.9</v>
+        <v>15991.13</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.79</v>
+        <v>51.45</v>
       </c>
       <c r="E6" t="n">
-        <v>16.08</v>
+        <v>43.04</v>
       </c>
       <c r="F6" t="n">
-        <v>54.15</v>
+        <v>19.53</v>
       </c>
       <c r="G6" t="n">
-        <v>17.4</v>
+        <v>46.84</v>
       </c>
       <c r="H6" t="n">
-        <v>42.47</v>
+        <v>9.84</v>
       </c>
       <c r="I6" t="n">
-        <v>68.72</v>
+        <v>66.78</v>
       </c>
       <c r="J6" t="n">
-        <v>0.37</v>
+        <v>1.86</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>72.5</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>74.34999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>24.79</v>
+        <v>51.45</v>
       </c>
       <c r="O6" t="n">
-        <v>4033</v>
+        <v>1943</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99978.07000000001</v>
+        <v>99967.35000000001</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>22.31</v>
+        <v>46.31</v>
       </c>
       <c r="T6" t="n">
-        <v>9997.809999999999</v>
+        <v>9996.74</v>
       </c>
       <c r="U6" t="n">
-        <v>29.25</v>
+        <v>61.74</v>
       </c>
       <c r="V6" t="n">
-        <v>17.99</v>
+        <v>20</v>
       </c>
       <c r="W6" t="n">
-        <v>17986.05</v>
+        <v>19993.47</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>790.65</v>
+        <v>25.09</v>
       </c>
       <c r="E7" t="n">
-        <v>659.5</v>
+        <v>16.14</v>
       </c>
       <c r="F7" t="n">
-        <v>19.89</v>
+        <v>55.49</v>
       </c>
       <c r="G7" t="n">
-        <v>629.9</v>
+        <v>17.4</v>
       </c>
       <c r="H7" t="n">
-        <v>25.52</v>
+        <v>44.2</v>
       </c>
       <c r="I7" t="n">
-        <v>58.01</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.61</v>
+        <v>1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>65</v>
       </c>
       <c r="L7" t="n">
         <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>74.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>790.65</v>
+        <v>25.09</v>
       </c>
       <c r="O7" t="n">
-        <v>126</v>
+        <v>3985</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99621.89999999999</v>
+        <v>99983.64999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>711.58</v>
+        <v>22.58</v>
       </c>
       <c r="T7" t="n">
-        <v>9962.190000000001</v>
+        <v>9998.360000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>925.0599999999999</v>
+        <v>29.1</v>
       </c>
       <c r="V7" t="n">
-        <v>17</v>
+        <v>15.98</v>
       </c>
       <c r="W7" t="n">
-        <v>16935.72</v>
+        <v>15977.39</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>307.65</v>
+        <v>447.4</v>
       </c>
       <c r="E8" t="n">
-        <v>223.45</v>
+        <v>400.23</v>
       </c>
       <c r="F8" t="n">
-        <v>37.68</v>
+        <v>11.79</v>
       </c>
       <c r="G8" t="n">
-        <v>285</v>
+        <v>453.2</v>
       </c>
       <c r="H8" t="n">
-        <v>7.95</v>
+        <v>-1.28</v>
       </c>
       <c r="I8" t="n">
-        <v>62.58</v>
+        <v>68.25</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>66.25</v>
+        <v>63.75</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>73.75</v>
+        <v>75.05</v>
       </c>
       <c r="N8" t="n">
-        <v>307.65</v>
+        <v>447.4</v>
       </c>
       <c r="O8" t="n">
-        <v>325</v>
+        <v>223</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99986.25</v>
+        <v>99770.2</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>276.88</v>
+        <v>402.66</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.620000000001</v>
+        <v>9977.02</v>
       </c>
       <c r="U8" t="n">
-        <v>363.03</v>
+        <v>523.46</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>17997.53</v>
+        <v>16960.93</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VHL</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3694.4</v>
+        <v>794.2</v>
       </c>
       <c r="E9" t="n">
-        <v>3423.27</v>
+        <v>660.99</v>
       </c>
       <c r="F9" t="n">
-        <v>7.92</v>
+        <v>20.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3799.8</v>
+        <v>629.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.77</v>
+        <v>26.08</v>
       </c>
       <c r="I9" t="n">
-        <v>67.05</v>
+        <v>58.72</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="K9" t="n">
-        <v>56.25</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>73.75</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>3694.4</v>
+        <v>794.2</v>
       </c>
       <c r="O9" t="n">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99748.8</v>
+        <v>99275</v>
       </c>
       <c r="R9" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="S9" t="n">
-        <v>3324.96</v>
+        <v>714.78</v>
       </c>
       <c r="T9" t="n">
-        <v>9974.879999999999</v>
+        <v>9927.5</v>
       </c>
       <c r="U9" t="n">
-        <v>4285.5</v>
+        <v>937.16</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>15959.81</v>
+        <v>17869.5</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.45</v>
+        <v>293.95</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07</v>
+        <v>223.84</v>
       </c>
       <c r="F10" t="n">
-        <v>43.48</v>
+        <v>31.32</v>
       </c>
       <c r="G10" t="n">
-        <v>11.38</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>26.98</v>
+        <v>3.14</v>
       </c>
       <c r="I10" t="n">
-        <v>60.98</v>
+        <v>55.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="K10" t="n">
-        <v>66.25</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M10" t="n">
-        <v>71.75</v>
+        <v>73.55</v>
       </c>
       <c r="N10" t="n">
-        <v>14.45</v>
+        <v>293.95</v>
       </c>
       <c r="O10" t="n">
-        <v>6920</v>
+        <v>340</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99994</v>
+        <v>99943</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>264.56</v>
       </c>
       <c r="T10" t="n">
-        <v>9999.4</v>
+        <v>9994.299999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>17.05</v>
+        <v>346.86</v>
       </c>
       <c r="V10" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>17988.92</v>
+        <v>17989.74</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>AVTNPL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>128.03</v>
+        <v>101</v>
       </c>
       <c r="E11" t="n">
-        <v>101.77</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>25.8</v>
+        <v>40.29</v>
       </c>
       <c r="G11" t="n">
-        <v>108.59</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>17.9</v>
+        <v>26.41</v>
       </c>
       <c r="I11" t="n">
-        <v>52.97</v>
+        <v>64.44</v>
       </c>
       <c r="J11" t="n">
-        <v>0.71</v>
+        <v>1.75</v>
       </c>
       <c r="K11" t="n">
-        <v>57.5</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="M11" t="n">
-        <v>71.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>128.03</v>
+        <v>101</v>
       </c>
       <c r="O11" t="n">
-        <v>781</v>
+        <v>990</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99991.42999999999</v>
+        <v>99990</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>115.23</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.139999999999</v>
+        <v>9999</v>
       </c>
       <c r="U11" t="n">
-        <v>147.23</v>
+        <v>120.19</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>14998.71</v>
+        <v>18998.1</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,64 +558,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>338</v>
+        <v>61.32</v>
       </c>
       <c r="E2" t="n">
-        <v>307.08</v>
+        <v>49.48</v>
       </c>
       <c r="F2" t="n">
-        <v>10.07</v>
+        <v>23.93</v>
       </c>
       <c r="G2" t="n">
-        <v>220</v>
+        <v>62.84</v>
       </c>
       <c r="H2" t="n">
-        <v>53.64</v>
+        <v>-2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>56.36</v>
+        <v>64.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.59</v>
+        <v>2.91</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N2" t="n">
-        <v>338</v>
+        <v>61.32</v>
       </c>
       <c r="O2" t="n">
-        <v>295</v>
+        <v>1630</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99710</v>
+        <v>99951.60000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>304.2</v>
+        <v>55.19</v>
       </c>
       <c r="T2" t="n">
-        <v>9971</v>
+        <v>9995.16</v>
       </c>
       <c r="U2" t="n">
-        <v>405.6</v>
+        <v>74.2</v>
       </c>
       <c r="V2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>19942</v>
+        <v>20989.84</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -643,64 +643,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61.32</v>
+        <v>338</v>
       </c>
       <c r="E3" t="n">
-        <v>49.48</v>
+        <v>307.08</v>
       </c>
       <c r="F3" t="n">
-        <v>23.93</v>
+        <v>10.07</v>
       </c>
       <c r="G3" t="n">
-        <v>62.84</v>
+        <v>220</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.42</v>
+        <v>53.64</v>
       </c>
       <c r="I3" t="n">
-        <v>64.62</v>
+        <v>56.36</v>
       </c>
       <c r="J3" t="n">
-        <v>2.91</v>
+        <v>3.59</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N3" t="n">
-        <v>61.32</v>
+        <v>338</v>
       </c>
       <c r="O3" t="n">
-        <v>1630</v>
+        <v>295</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99951.60000000001</v>
+        <v>99710</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>55.19</v>
+        <v>304.2</v>
       </c>
       <c r="T3" t="n">
-        <v>9995.16</v>
+        <v>9971</v>
       </c>
       <c r="U3" t="n">
-        <v>74.2</v>
+        <v>405.6</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W3" t="n">
-        <v>20989.84</v>
+        <v>19942</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1238,64 +1238,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>293.95</v>
+        <v>1811.5</v>
       </c>
       <c r="E10" t="n">
-        <v>223.84</v>
+        <v>1092.51</v>
       </c>
       <c r="F10" t="n">
-        <v>31.32</v>
+        <v>65.81</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>1065.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.14</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>55.8</v>
+        <v>55.38</v>
       </c>
       <c r="J10" t="n">
-        <v>0.53</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>72.5</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>73.55</v>
+        <v>74.3</v>
       </c>
       <c r="N10" t="n">
-        <v>293.95</v>
+        <v>1811.5</v>
       </c>
       <c r="O10" t="n">
-        <v>340</v>
+        <v>55</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99943</v>
+        <v>99632.5</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>264.56</v>
+        <v>1630.35</v>
       </c>
       <c r="T10" t="n">
-        <v>9994.299999999999</v>
+        <v>9963.25</v>
       </c>
       <c r="U10" t="n">
-        <v>346.86</v>
+        <v>2155.68</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>17989.74</v>
+        <v>18930.18</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AVTNPL</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1323,64 +1323,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>101</v>
+        <v>293.95</v>
       </c>
       <c r="E11" t="n">
-        <v>71.98999999999999</v>
+        <v>223.84</v>
       </c>
       <c r="F11" t="n">
-        <v>40.29</v>
+        <v>31.32</v>
       </c>
       <c r="G11" t="n">
-        <v>79.90000000000001</v>
+        <v>285</v>
       </c>
       <c r="H11" t="n">
-        <v>26.41</v>
+        <v>3.14</v>
       </c>
       <c r="I11" t="n">
-        <v>64.44</v>
+        <v>55.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.75</v>
+        <v>0.53</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>73.09999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="N11" t="n">
-        <v>101</v>
+        <v>293.95</v>
       </c>
       <c r="O11" t="n">
-        <v>990</v>
+        <v>340</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99990</v>
+        <v>99943</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>90.90000000000001</v>
+        <v>264.56</v>
       </c>
       <c r="T11" t="n">
-        <v>9999</v>
+        <v>9994.299999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>120.19</v>
+        <v>346.86</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>18998.1</v>
+        <v>17989.74</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61.32</v>
+        <v>605.85</v>
       </c>
       <c r="E2" t="n">
-        <v>49.48</v>
+        <v>591.84</v>
       </c>
       <c r="F2" t="n">
-        <v>23.93</v>
+        <v>2.37</v>
       </c>
       <c r="G2" t="n">
-        <v>62.84</v>
+        <v>527.9</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.42</v>
+        <v>14.77</v>
       </c>
       <c r="I2" t="n">
-        <v>64.62</v>
+        <v>26.83</v>
       </c>
       <c r="J2" t="n">
-        <v>2.91</v>
+        <v>3.44</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>81.25</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>82</v>
+        <v>48.75</v>
       </c>
       <c r="N2" t="n">
-        <v>61.32</v>
+        <v>605.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1630</v>
+        <v>165</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99951.60000000001</v>
+        <v>99965.25</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>55.19</v>
+        <v>545.26</v>
       </c>
       <c r="T2" t="n">
-        <v>9995.16</v>
+        <v>9996.52</v>
       </c>
       <c r="U2" t="n">
-        <v>74.2</v>
+        <v>714.9</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>20989.84</v>
+        <v>17993.74</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>RBZJEWEL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>338</v>
+        <v>209.28</v>
       </c>
       <c r="E3" t="n">
-        <v>307.08</v>
+        <v>144.43</v>
       </c>
       <c r="F3" t="n">
-        <v>10.07</v>
+        <v>44.9</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>165.44</v>
       </c>
       <c r="H3" t="n">
-        <v>53.64</v>
+        <v>26.5</v>
       </c>
       <c r="I3" t="n">
-        <v>56.36</v>
+        <v>64.64</v>
       </c>
       <c r="J3" t="n">
-        <v>3.59</v>
+        <v>2.6</v>
       </c>
       <c r="K3" t="n">
         <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>338</v>
+        <v>209.28</v>
       </c>
       <c r="O3" t="n">
-        <v>295</v>
+        <v>477</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99710</v>
+        <v>99826.56</v>
       </c>
       <c r="R3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>304.2</v>
+        <v>188.35</v>
       </c>
       <c r="T3" t="n">
-        <v>9971</v>
+        <v>9982.66</v>
       </c>
       <c r="U3" t="n">
-        <v>405.6</v>
+        <v>242.76</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>19942</v>
+        <v>15972.25</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VHL</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3740.4</v>
+        <v>256.98</v>
       </c>
       <c r="E4" t="n">
-        <v>3424.05</v>
+        <v>165.95</v>
       </c>
       <c r="F4" t="n">
-        <v>9.24</v>
+        <v>54.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3799.8</v>
+        <v>163.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.56</v>
+        <v>56.79</v>
       </c>
       <c r="I4" t="n">
-        <v>69.81999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.25</v>
+        <v>16.3</v>
       </c>
       <c r="K4" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>80.5</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>3740.4</v>
+        <v>256.98</v>
       </c>
       <c r="O4" t="n">
-        <v>26</v>
+        <v>389</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>97250.39999999999</v>
+        <v>99965.22</v>
       </c>
       <c r="R4" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>3366.36</v>
+        <v>231.28</v>
       </c>
       <c r="T4" t="n">
-        <v>9725.040000000001</v>
+        <v>9996.52</v>
       </c>
       <c r="U4" t="n">
-        <v>4376.27</v>
+        <v>298.1</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>16532.57</v>
+        <v>15994.44</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>329.85</v>
+        <v>268.81</v>
       </c>
       <c r="E5" t="n">
-        <v>260.17</v>
+        <v>151.59</v>
       </c>
       <c r="F5" t="n">
-        <v>26.78</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>49.66</v>
+        <v>203.98</v>
       </c>
       <c r="I5" t="n">
-        <v>51.05</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="K5" t="n">
-        <v>66.25</v>
+        <v>75</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>79.75</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>329.85</v>
+        <v>268.81</v>
       </c>
       <c r="O5" t="n">
-        <v>303</v>
+        <v>372</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99944.55</v>
+        <v>99997.32000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>296.86</v>
+        <v>241.93</v>
       </c>
       <c r="T5" t="n">
-        <v>9994.459999999999</v>
+        <v>9999.73</v>
       </c>
       <c r="U5" t="n">
-        <v>382.63</v>
+        <v>311.82</v>
       </c>
       <c r="V5" t="n">
         <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>15991.13</v>
+        <v>15999.57</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.45</v>
+        <v>348.85</v>
       </c>
       <c r="E6" t="n">
-        <v>43.04</v>
+        <v>307.51</v>
       </c>
       <c r="F6" t="n">
-        <v>19.53</v>
+        <v>13.44</v>
       </c>
       <c r="G6" t="n">
-        <v>46.84</v>
+        <v>220</v>
       </c>
       <c r="H6" t="n">
-        <v>9.84</v>
+        <v>58.57</v>
       </c>
       <c r="I6" t="n">
-        <v>66.78</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.86</v>
+        <v>3.54</v>
       </c>
       <c r="K6" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>77.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>51.45</v>
+        <v>348.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1943</v>
+        <v>286</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99967.35000000001</v>
+        <v>99771.10000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>46.31</v>
+        <v>313.97</v>
       </c>
       <c r="T6" t="n">
-        <v>9996.74</v>
+        <v>9977.110000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>61.74</v>
+        <v>401.18</v>
       </c>
       <c r="V6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>19993.47</v>
+        <v>14965.66</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.09</v>
+        <v>1486.1</v>
       </c>
       <c r="E7" t="n">
-        <v>16.14</v>
+        <v>1145.54</v>
       </c>
       <c r="F7" t="n">
-        <v>55.49</v>
+        <v>29.73</v>
       </c>
       <c r="G7" t="n">
-        <v>17.4</v>
+        <v>1388</v>
       </c>
       <c r="H7" t="n">
-        <v>44.2</v>
+        <v>7.07</v>
       </c>
       <c r="I7" t="n">
-        <v>70.01000000000001</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.25</v>
+        <v>3.37</v>
       </c>
       <c r="K7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>76.59999999999999</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>25.09</v>
+        <v>1486.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3985</v>
+        <v>67</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99983.64999999999</v>
+        <v>99568.7</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>22.58</v>
+        <v>1337.49</v>
       </c>
       <c r="T7" t="n">
-        <v>9998.360000000001</v>
+        <v>9956.870000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>29.1</v>
+        <v>1723.88</v>
       </c>
       <c r="V7" t="n">
-        <v>15.98</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>15977.39</v>
+        <v>15930.99</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>SHREEPUSHK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>447.4</v>
+        <v>505.4</v>
       </c>
       <c r="E8" t="n">
-        <v>400.23</v>
+        <v>386.63</v>
       </c>
       <c r="F8" t="n">
-        <v>11.79</v>
+        <v>30.72</v>
       </c>
       <c r="G8" t="n">
-        <v>453.2</v>
+        <v>476</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.28</v>
+        <v>6.18</v>
       </c>
       <c r="I8" t="n">
-        <v>68.25</v>
+        <v>55.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>63.75</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>75.05</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>447.4</v>
+        <v>505.4</v>
       </c>
       <c r="O8" t="n">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99770.2</v>
+        <v>99563.8</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>402.66</v>
+        <v>454.86</v>
       </c>
       <c r="T8" t="n">
-        <v>9977.02</v>
+        <v>9956.379999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>523.46</v>
+        <v>586.26</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>16960.93</v>
+        <v>15930.21</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>794.2</v>
+        <v>295.6</v>
       </c>
       <c r="E9" t="n">
-        <v>660.99</v>
+        <v>234.37</v>
       </c>
       <c r="F9" t="n">
-        <v>20.15</v>
+        <v>26.13</v>
       </c>
       <c r="G9" t="n">
-        <v>629.9</v>
+        <v>230.44</v>
       </c>
       <c r="H9" t="n">
-        <v>26.08</v>
+        <v>28.28</v>
       </c>
       <c r="I9" t="n">
-        <v>58.72</v>
+        <v>55.77</v>
       </c>
       <c r="J9" t="n">
-        <v>0.46</v>
+        <v>2.24</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>794.2</v>
+        <v>295.6</v>
       </c>
       <c r="O9" t="n">
-        <v>125</v>
+        <v>338</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99275</v>
+        <v>99912.8</v>
       </c>
       <c r="R9" t="n">
-        <v>9.93</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>714.78</v>
+        <v>266.04</v>
       </c>
       <c r="T9" t="n">
-        <v>9927.5</v>
+        <v>9991.280000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>937.16</v>
+        <v>342.9</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>17869.5</v>
+        <v>15986.05</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>SANATHAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1811.5</v>
+        <v>548.1</v>
       </c>
       <c r="E10" t="n">
-        <v>1092.51</v>
+        <v>443</v>
       </c>
       <c r="F10" t="n">
-        <v>65.81</v>
+        <v>23.72</v>
       </c>
       <c r="G10" t="n">
-        <v>1065.5</v>
+        <v>512</v>
       </c>
       <c r="H10" t="n">
-        <v>70.01000000000001</v>
+        <v>7.05</v>
       </c>
       <c r="I10" t="n">
-        <v>55.38</v>
+        <v>64.11</v>
       </c>
       <c r="J10" t="n">
-        <v>1.56</v>
+        <v>2.83</v>
       </c>
       <c r="K10" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>74.3</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>1811.5</v>
+        <v>548.1</v>
       </c>
       <c r="O10" t="n">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99632.5</v>
+        <v>99754.2</v>
       </c>
       <c r="R10" t="n">
-        <v>9.960000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S10" t="n">
-        <v>1630.35</v>
+        <v>493.29</v>
       </c>
       <c r="T10" t="n">
-        <v>9963.25</v>
+        <v>9975.42</v>
       </c>
       <c r="U10" t="n">
-        <v>2155.68</v>
+        <v>635.8</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>18930.18</v>
+        <v>15960.67</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>MAHASTEEL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>293.95</v>
+        <v>1292.8</v>
       </c>
       <c r="E11" t="n">
-        <v>223.84</v>
+        <v>939.58</v>
       </c>
       <c r="F11" t="n">
-        <v>31.32</v>
+        <v>37.59</v>
       </c>
       <c r="G11" t="n">
-        <v>285</v>
+        <v>1050</v>
       </c>
       <c r="H11" t="n">
-        <v>3.14</v>
+        <v>23.12</v>
       </c>
       <c r="I11" t="n">
-        <v>55.8</v>
+        <v>63.06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.53</v>
+        <v>3.96</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>73.55</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>293.95</v>
+        <v>1292.8</v>
       </c>
       <c r="O11" t="n">
-        <v>340</v>
+        <v>77</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99943</v>
+        <v>99545.60000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>264.56</v>
+        <v>1163.52</v>
       </c>
       <c r="T11" t="n">
-        <v>9994.299999999999</v>
+        <v>9954.559999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>346.86</v>
+        <v>1499.65</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>17989.74</v>
+        <v>15927.3</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>605.85</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>591.84</v>
+        <v>16.23</v>
       </c>
       <c r="F2" t="n">
-        <v>2.37</v>
+        <v>41.74</v>
       </c>
       <c r="G2" t="n">
-        <v>527.9</v>
+        <v>17.4</v>
       </c>
       <c r="H2" t="n">
-        <v>14.77</v>
+        <v>32.18</v>
       </c>
       <c r="I2" t="n">
-        <v>26.83</v>
+        <v>53.03</v>
       </c>
       <c r="J2" t="n">
-        <v>3.44</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>81.25</v>
+        <v>71.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>48.75</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>605.85</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>165</v>
+        <v>4347</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99965.25</v>
+        <v>99981</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>545.26</v>
+        <v>20.7</v>
       </c>
       <c r="T2" t="n">
-        <v>9996.52</v>
+        <v>9998.1</v>
       </c>
       <c r="U2" t="n">
-        <v>714.9</v>
+        <v>27.14</v>
       </c>
       <c r="V2" t="n">
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>17993.74</v>
+        <v>17996.58</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RBZJEWEL</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>209.28</v>
+        <v>110.87</v>
       </c>
       <c r="E3" t="n">
-        <v>144.43</v>
+        <v>102.21</v>
       </c>
       <c r="F3" t="n">
-        <v>44.9</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>165.44</v>
+        <v>108.59</v>
       </c>
       <c r="H3" t="n">
-        <v>26.5</v>
+        <v>2.1</v>
       </c>
       <c r="I3" t="n">
-        <v>64.64</v>
+        <v>32.09</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>74.75</v>
       </c>
       <c r="N3" t="n">
-        <v>209.28</v>
+        <v>110.87</v>
       </c>
       <c r="O3" t="n">
-        <v>477</v>
+        <v>901</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99826.56</v>
+        <v>99893.87</v>
       </c>
       <c r="R3" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>188.35</v>
+        <v>99.78</v>
       </c>
       <c r="T3" t="n">
-        <v>9982.66</v>
+        <v>9989.389999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>242.76</v>
+        <v>128.61</v>
       </c>
       <c r="V3" t="n">
         <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>15972.25</v>
+        <v>15983.02</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>256.98</v>
+        <v>687.5</v>
       </c>
       <c r="E4" t="n">
-        <v>165.95</v>
+        <v>596.38</v>
       </c>
       <c r="F4" t="n">
-        <v>54.86</v>
+        <v>15.28</v>
       </c>
       <c r="G4" t="n">
-        <v>163.9</v>
+        <v>659.2</v>
       </c>
       <c r="H4" t="n">
-        <v>56.79</v>
+        <v>4.29</v>
       </c>
       <c r="I4" t="n">
-        <v>68.40000000000001</v>
+        <v>25.73</v>
       </c>
       <c r="J4" t="n">
-        <v>16.3</v>
+        <v>2.42</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>256.98</v>
+        <v>687.5</v>
       </c>
       <c r="O4" t="n">
-        <v>389</v>
+        <v>145</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99965.22</v>
+        <v>99687.5</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>231.28</v>
+        <v>618.75</v>
       </c>
       <c r="T4" t="n">
-        <v>9996.52</v>
+        <v>9968.75</v>
       </c>
       <c r="U4" t="n">
-        <v>298.1</v>
+        <v>804.38</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>15994.44</v>
+        <v>16946.88</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>268.81</v>
+        <v>319.15</v>
       </c>
       <c r="E5" t="n">
-        <v>151.59</v>
+        <v>261.4</v>
       </c>
       <c r="F5" t="n">
-        <v>77.31999999999999</v>
+        <v>22.09</v>
       </c>
       <c r="G5" t="n">
-        <v>88.43000000000001</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>203.98</v>
+        <v>44.8</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>43.78</v>
       </c>
       <c r="J5" t="n">
-        <v>2.03</v>
+        <v>1.21</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>56.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>73.75</v>
       </c>
       <c r="N5" t="n">
-        <v>268.81</v>
+        <v>319.15</v>
       </c>
       <c r="O5" t="n">
-        <v>372</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99997.32000000001</v>
+        <v>99893.95</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>241.93</v>
+        <v>287.24</v>
       </c>
       <c r="T5" t="n">
-        <v>9999.73</v>
+        <v>9989.4</v>
       </c>
       <c r="U5" t="n">
-        <v>311.82</v>
+        <v>370.21</v>
       </c>
       <c r="V5" t="n">
         <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>15999.57</v>
+        <v>15983.03</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>348.85</v>
+        <v>34.57</v>
       </c>
       <c r="E6" t="n">
-        <v>307.51</v>
+        <v>20.81</v>
       </c>
       <c r="F6" t="n">
-        <v>13.44</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>220</v>
+        <v>21.25</v>
       </c>
       <c r="H6" t="n">
-        <v>58.57</v>
+        <v>62.68</v>
       </c>
       <c r="I6" t="n">
-        <v>64.43000000000001</v>
+        <v>59.11</v>
       </c>
       <c r="J6" t="n">
-        <v>3.54</v>
+        <v>1.78</v>
       </c>
       <c r="K6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="L6" t="n">
         <v>75</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>73.5</v>
       </c>
       <c r="N6" t="n">
-        <v>348.85</v>
+        <v>34.57</v>
       </c>
       <c r="O6" t="n">
-        <v>286</v>
+        <v>2892</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99771.10000000001</v>
+        <v>99976.44</v>
       </c>
       <c r="R6" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>313.97</v>
+        <v>31.11</v>
       </c>
       <c r="T6" t="n">
-        <v>9977.110000000001</v>
+        <v>9997.639999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>401.18</v>
+        <v>41.14</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>14965.66</v>
+        <v>18995.52</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1486.1</v>
+        <v>225.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1145.54</v>
+        <v>166.42</v>
       </c>
       <c r="F7" t="n">
-        <v>29.73</v>
+        <v>35.26</v>
       </c>
       <c r="G7" t="n">
-        <v>1388</v>
+        <v>163.9</v>
       </c>
       <c r="H7" t="n">
-        <v>7.07</v>
+        <v>37.34</v>
       </c>
       <c r="I7" t="n">
-        <v>64.31999999999999</v>
+        <v>51.89</v>
       </c>
       <c r="J7" t="n">
-        <v>3.37</v>
+        <v>5.1</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>71.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>1486.1</v>
+        <v>225.1</v>
       </c>
       <c r="O7" t="n">
-        <v>67</v>
+        <v>444</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99568.7</v>
+        <v>99944.39999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>1337.49</v>
+        <v>202.59</v>
       </c>
       <c r="T7" t="n">
-        <v>9956.870000000001</v>
+        <v>9994.440000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1723.88</v>
+        <v>261.12</v>
       </c>
       <c r="V7" t="n">
         <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>15930.99</v>
+        <v>15991.1</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SHREEPUSHK</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>505.4</v>
+        <v>264.78</v>
       </c>
       <c r="E8" t="n">
-        <v>386.63</v>
+        <v>152.59</v>
       </c>
       <c r="F8" t="n">
-        <v>30.72</v>
+        <v>73.52</v>
       </c>
       <c r="G8" t="n">
-        <v>476</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>6.18</v>
+        <v>199.42</v>
       </c>
       <c r="I8" t="n">
-        <v>55.6</v>
+        <v>59.74</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.09</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="N8" t="n">
-        <v>505.4</v>
+        <v>264.78</v>
       </c>
       <c r="O8" t="n">
-        <v>197</v>
+        <v>377</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99563.8</v>
+        <v>99822.06</v>
       </c>
       <c r="R8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>454.86</v>
+        <v>238.3</v>
       </c>
       <c r="T8" t="n">
-        <v>9956.379999999999</v>
+        <v>9982.209999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>586.26</v>
+        <v>315.09</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>15930.21</v>
+        <v>18966.19</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>295.6</v>
+        <v>344</v>
       </c>
       <c r="E9" t="n">
-        <v>234.37</v>
+        <v>307.92</v>
       </c>
       <c r="F9" t="n">
-        <v>26.13</v>
+        <v>11.72</v>
       </c>
       <c r="G9" t="n">
-        <v>230.44</v>
+        <v>220</v>
       </c>
       <c r="H9" t="n">
-        <v>28.28</v>
+        <v>56.36</v>
       </c>
       <c r="I9" t="n">
-        <v>55.77</v>
+        <v>59.16</v>
       </c>
       <c r="J9" t="n">
-        <v>2.24</v>
+        <v>0.67</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>72.75</v>
       </c>
       <c r="N9" t="n">
-        <v>295.6</v>
+        <v>344</v>
       </c>
       <c r="O9" t="n">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99912.8</v>
+        <v>99760</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S9" t="n">
-        <v>266.04</v>
+        <v>309.6</v>
       </c>
       <c r="T9" t="n">
-        <v>9991.280000000001</v>
+        <v>9976</v>
       </c>
       <c r="U9" t="n">
-        <v>342.9</v>
+        <v>402.48</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W9" t="n">
-        <v>15986.05</v>
+        <v>16959.2</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANATHAN</t>
+          <t>MVGJL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>548.1</v>
+        <v>220.36</v>
       </c>
       <c r="E10" t="n">
-        <v>443</v>
+        <v>169.5</v>
       </c>
       <c r="F10" t="n">
-        <v>23.72</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>512</v>
+        <v>208.5</v>
       </c>
       <c r="H10" t="n">
-        <v>7.05</v>
+        <v>5.69</v>
       </c>
       <c r="I10" t="n">
-        <v>64.11</v>
+        <v>56.19</v>
       </c>
       <c r="J10" t="n">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="K10" t="n">
         <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>72.2</v>
       </c>
       <c r="N10" t="n">
-        <v>548.1</v>
+        <v>220.36</v>
       </c>
       <c r="O10" t="n">
-        <v>182</v>
+        <v>453</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99754.2</v>
+        <v>99823.08</v>
       </c>
       <c r="R10" t="n">
         <v>9.98</v>
       </c>
       <c r="S10" t="n">
-        <v>493.29</v>
+        <v>198.32</v>
       </c>
       <c r="T10" t="n">
-        <v>9975.42</v>
+        <v>9982.309999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>635.8</v>
+        <v>262.23</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>15960.67</v>
+        <v>18966.39</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1292.8</v>
+        <v>283.75</v>
       </c>
       <c r="E11" t="n">
-        <v>939.58</v>
+        <v>220.17</v>
       </c>
       <c r="F11" t="n">
-        <v>37.59</v>
+        <v>28.88</v>
       </c>
       <c r="G11" t="n">
-        <v>1050</v>
+        <v>241.57</v>
       </c>
       <c r="H11" t="n">
-        <v>23.12</v>
+        <v>17.46</v>
       </c>
       <c r="I11" t="n">
-        <v>63.06</v>
+        <v>50.67</v>
       </c>
       <c r="J11" t="n">
-        <v>3.96</v>
+        <v>0.57</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>57.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1292.8</v>
+        <v>283.75</v>
       </c>
       <c r="O11" t="n">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99545.60000000001</v>
+        <v>99880</v>
       </c>
       <c r="R11" t="n">
-        <v>9.949999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>1163.52</v>
+        <v>255.38</v>
       </c>
       <c r="T11" t="n">
-        <v>9954.559999999999</v>
+        <v>9988</v>
       </c>
       <c r="U11" t="n">
-        <v>1499.65</v>
+        <v>326.31</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>15927.3</v>
+        <v>14982</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>78.48</v>
       </c>
       <c r="E2" t="n">
-        <v>16.23</v>
+        <v>76.41</v>
       </c>
       <c r="F2" t="n">
-        <v>41.74</v>
+        <v>2.71</v>
       </c>
       <c r="G2" t="n">
-        <v>17.4</v>
+        <v>58.79</v>
       </c>
       <c r="H2" t="n">
-        <v>32.18</v>
+        <v>33.49</v>
       </c>
       <c r="I2" t="n">
-        <v>53.03</v>
+        <v>40.89</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>0.85</v>
       </c>
       <c r="K2" t="n">
-        <v>71.25</v>
+        <v>65</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>80.34999999999999</v>
+        <v>79</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>78.48</v>
       </c>
       <c r="O2" t="n">
-        <v>4347</v>
+        <v>1274</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99981</v>
+        <v>99983.52</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>20.7</v>
+        <v>70.63</v>
       </c>
       <c r="T2" t="n">
-        <v>9998.1</v>
+        <v>9998.35</v>
       </c>
       <c r="U2" t="n">
-        <v>27.14</v>
+        <v>92.61</v>
       </c>
       <c r="V2" t="n">
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>17996.58</v>
+        <v>17997.03</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>110.87</v>
+        <v>23.57</v>
       </c>
       <c r="E3" t="n">
-        <v>102.21</v>
+        <v>16.27</v>
       </c>
       <c r="F3" t="n">
-        <v>8.470000000000001</v>
+        <v>44.83</v>
       </c>
       <c r="G3" t="n">
-        <v>108.59</v>
+        <v>17.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1</v>
+        <v>35.46</v>
       </c>
       <c r="I3" t="n">
-        <v>32.09</v>
+        <v>56.28</v>
       </c>
       <c r="J3" t="n">
-        <v>2.16</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>66.25</v>
       </c>
       <c r="L3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>74.75</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>110.87</v>
+        <v>23.57</v>
       </c>
       <c r="O3" t="n">
-        <v>901</v>
+        <v>4242</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99893.87</v>
+        <v>99983.94</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>99.78</v>
+        <v>21.21</v>
       </c>
       <c r="T3" t="n">
-        <v>9989.389999999999</v>
+        <v>9998.389999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>128.61</v>
+        <v>27.81</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>17.99</v>
       </c>
       <c r="W3" t="n">
-        <v>15983.02</v>
+        <v>17987.11</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>687.5</v>
+        <v>18.07</v>
       </c>
       <c r="E4" t="n">
-        <v>596.38</v>
+        <v>10.24</v>
       </c>
       <c r="F4" t="n">
-        <v>15.28</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>659.2</v>
+        <v>11.38</v>
       </c>
       <c r="H4" t="n">
-        <v>4.29</v>
+        <v>58.79</v>
       </c>
       <c r="I4" t="n">
-        <v>25.73</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.42</v>
+        <v>3.61</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L4" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>74.34999999999999</v>
+        <v>74</v>
       </c>
       <c r="N4" t="n">
-        <v>687.5</v>
+        <v>18.07</v>
       </c>
       <c r="O4" t="n">
-        <v>145</v>
+        <v>5534</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99687.5</v>
+        <v>99999.38</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>618.75</v>
+        <v>16.26</v>
       </c>
       <c r="T4" t="n">
-        <v>9968.75</v>
+        <v>9999.940000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>804.38</v>
+        <v>21.32</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>17.99</v>
       </c>
       <c r="W4" t="n">
-        <v>16946.88</v>
+        <v>17989.89</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>319.15</v>
+        <v>347.8</v>
       </c>
       <c r="E5" t="n">
-        <v>261.4</v>
+        <v>308.32</v>
       </c>
       <c r="F5" t="n">
-        <v>22.09</v>
+        <v>12.81</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>220</v>
       </c>
       <c r="H5" t="n">
-        <v>44.8</v>
+        <v>58.09</v>
       </c>
       <c r="I5" t="n">
-        <v>43.78</v>
+        <v>61.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1.21</v>
+        <v>0.89</v>
       </c>
       <c r="K5" t="n">
-        <v>56.25</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M5" t="n">
-        <v>73.75</v>
+        <v>72.75</v>
       </c>
       <c r="N5" t="n">
-        <v>319.15</v>
+        <v>347.8</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99893.95</v>
+        <v>99818.60000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>287.24</v>
+        <v>313.02</v>
       </c>
       <c r="T5" t="n">
-        <v>9989.4</v>
+        <v>9981.860000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>370.21</v>
+        <v>406.93</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>15983.03</v>
+        <v>16969.16</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34.57</v>
+        <v>1139.9</v>
       </c>
       <c r="E6" t="n">
-        <v>20.81</v>
+        <v>1038.48</v>
       </c>
       <c r="F6" t="n">
-        <v>66.09999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="G6" t="n">
-        <v>21.25</v>
+        <v>993.8</v>
       </c>
       <c r="H6" t="n">
-        <v>62.68</v>
+        <v>14.7</v>
       </c>
       <c r="I6" t="n">
-        <v>59.11</v>
+        <v>28.95</v>
       </c>
       <c r="J6" t="n">
-        <v>1.78</v>
+        <v>2.79</v>
       </c>
       <c r="K6" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M6" t="n">
-        <v>73.5</v>
+        <v>71.95</v>
       </c>
       <c r="N6" t="n">
-        <v>34.57</v>
+        <v>1139.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2892</v>
+        <v>87</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99976.44</v>
+        <v>99171.3</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="S6" t="n">
-        <v>31.11</v>
+        <v>1025.91</v>
       </c>
       <c r="T6" t="n">
-        <v>9997.639999999999</v>
+        <v>9917.129999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>41.14</v>
+        <v>1322.28</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>18995.52</v>
+        <v>15867.41</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>225.1</v>
+        <v>313.75</v>
       </c>
       <c r="E7" t="n">
-        <v>166.42</v>
+        <v>261.94</v>
       </c>
       <c r="F7" t="n">
-        <v>35.26</v>
+        <v>19.78</v>
       </c>
       <c r="G7" t="n">
-        <v>163.9</v>
+        <v>220.4</v>
       </c>
       <c r="H7" t="n">
-        <v>37.34</v>
+        <v>42.35</v>
       </c>
       <c r="I7" t="n">
-        <v>51.89</v>
+        <v>40.63</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>71.25</v>
+        <v>52.5</v>
       </c>
       <c r="L7" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>73.15000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="N7" t="n">
-        <v>225.1</v>
+        <v>313.75</v>
       </c>
       <c r="O7" t="n">
-        <v>444</v>
+        <v>318</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99944.39999999999</v>
+        <v>99772.5</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S7" t="n">
-        <v>202.59</v>
+        <v>282.38</v>
       </c>
       <c r="T7" t="n">
-        <v>9994.440000000001</v>
+        <v>9977.25</v>
       </c>
       <c r="U7" t="n">
-        <v>261.12</v>
+        <v>357.68</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>15991.1</v>
+        <v>13968.15</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>264.78</v>
+        <v>294.55</v>
       </c>
       <c r="E8" t="n">
-        <v>152.59</v>
+        <v>203.88</v>
       </c>
       <c r="F8" t="n">
-        <v>73.52</v>
+        <v>44.47</v>
       </c>
       <c r="G8" t="n">
-        <v>88.43000000000001</v>
+        <v>231</v>
       </c>
       <c r="H8" t="n">
-        <v>199.42</v>
+        <v>27.51</v>
       </c>
       <c r="I8" t="n">
-        <v>59.74</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M8" t="n">
-        <v>73</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>264.78</v>
+        <v>294.55</v>
       </c>
       <c r="O8" t="n">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99822.06</v>
+        <v>99852.45</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>238.3</v>
+        <v>265.1</v>
       </c>
       <c r="T8" t="n">
-        <v>9982.209999999999</v>
+        <v>9985.25</v>
       </c>
       <c r="U8" t="n">
-        <v>315.09</v>
+        <v>350.51</v>
       </c>
       <c r="V8" t="n">
         <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>18966.19</v>
+        <v>18971.97</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>344</v>
+        <v>513.1</v>
       </c>
       <c r="E9" t="n">
-        <v>307.92</v>
+        <v>507.19</v>
       </c>
       <c r="F9" t="n">
-        <v>11.72</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
-        <v>220</v>
+        <v>539</v>
       </c>
       <c r="H9" t="n">
-        <v>56.36</v>
+        <v>-4.81</v>
       </c>
       <c r="I9" t="n">
-        <v>59.16</v>
+        <v>28.73</v>
       </c>
       <c r="J9" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>56.25</v>
       </c>
       <c r="L9" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>72.75</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>344</v>
+        <v>513.1</v>
       </c>
       <c r="O9" t="n">
-        <v>290</v>
+        <v>194</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99760</v>
+        <v>99541.39999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>309.6</v>
+        <v>461.79</v>
       </c>
       <c r="T9" t="n">
-        <v>9976</v>
+        <v>9954.139999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>402.48</v>
+        <v>605.46</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>16959.2</v>
+        <v>17917.45</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MVGJL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>220.36</v>
+        <v>11293</v>
       </c>
       <c r="E10" t="n">
-        <v>169.5</v>
+        <v>10667.65</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>5.86</v>
       </c>
       <c r="G10" t="n">
-        <v>208.5</v>
+        <v>11644</v>
       </c>
       <c r="H10" t="n">
-        <v>5.69</v>
+        <v>-3.01</v>
       </c>
       <c r="I10" t="n">
-        <v>56.19</v>
+        <v>57.25</v>
       </c>
       <c r="J10" t="n">
-        <v>2.17</v>
+        <v>3.06</v>
       </c>
       <c r="K10" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="L10" t="n">
         <v>75</v>
       </c>
-      <c r="L10" t="n">
-        <v>68</v>
-      </c>
       <c r="M10" t="n">
-        <v>72.2</v>
+        <v>70.5</v>
       </c>
       <c r="N10" t="n">
-        <v>220.36</v>
+        <v>11293</v>
       </c>
       <c r="O10" t="n">
-        <v>453</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99823.08</v>
+        <v>90344</v>
       </c>
       <c r="R10" t="n">
-        <v>9.98</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>198.32</v>
+        <v>10163.7</v>
       </c>
       <c r="T10" t="n">
-        <v>9982.309999999999</v>
+        <v>9034.4</v>
       </c>
       <c r="U10" t="n">
-        <v>262.23</v>
+        <v>13212.81</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W10" t="n">
-        <v>18966.39</v>
+        <v>15358.48</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>283.75</v>
+        <v>9162</v>
       </c>
       <c r="E11" t="n">
-        <v>220.17</v>
+        <v>7224.28</v>
       </c>
       <c r="F11" t="n">
-        <v>28.88</v>
+        <v>26.82</v>
       </c>
       <c r="G11" t="n">
-        <v>241.57</v>
+        <v>7071.5</v>
       </c>
       <c r="H11" t="n">
-        <v>17.46</v>
+        <v>29.56</v>
       </c>
       <c r="I11" t="n">
-        <v>50.67</v>
+        <v>47.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.57</v>
+        <v>1.85</v>
       </c>
       <c r="K11" t="n">
-        <v>57.5</v>
+        <v>63.75</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
-        <v>72.09999999999999</v>
+        <v>70.25</v>
       </c>
       <c r="N11" t="n">
-        <v>283.75</v>
+        <v>9162</v>
       </c>
       <c r="O11" t="n">
-        <v>352</v>
+        <v>10</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99880</v>
+        <v>91620</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>9.16</v>
       </c>
       <c r="S11" t="n">
-        <v>255.38</v>
+        <v>8245.799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>9988</v>
+        <v>9162</v>
       </c>
       <c r="U11" t="n">
-        <v>326.31</v>
+        <v>10811.16</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>14982</v>
+        <v>16491.6</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78.48</v>
+        <v>813.35</v>
       </c>
       <c r="E2" t="n">
-        <v>76.41</v>
+        <v>806.39</v>
       </c>
       <c r="F2" t="n">
-        <v>2.71</v>
+        <v>0.86</v>
       </c>
       <c r="G2" t="n">
-        <v>58.79</v>
+        <v>797.55</v>
       </c>
       <c r="H2" t="n">
-        <v>33.49</v>
+        <v>1.98</v>
       </c>
       <c r="I2" t="n">
-        <v>40.89</v>
+        <v>38.78</v>
       </c>
       <c r="J2" t="n">
-        <v>0.85</v>
+        <v>3.14</v>
       </c>
       <c r="K2" t="n">
-        <v>65</v>
+        <v>81.25</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>79</v>
+        <v>48.75</v>
       </c>
       <c r="N2" t="n">
-        <v>78.48</v>
+        <v>813.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1274</v>
+        <v>122</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99983.52</v>
+        <v>99228.7</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="S2" t="n">
-        <v>70.63</v>
+        <v>732.02</v>
       </c>
       <c r="T2" t="n">
-        <v>9998.35</v>
+        <v>9922.870000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>92.61</v>
+        <v>959.75</v>
       </c>
       <c r="V2" t="n">
         <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>17997.03</v>
+        <v>17861.17</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -634,82 +634,82 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.57</v>
+        <v>153.83</v>
       </c>
       <c r="E3" t="n">
-        <v>16.27</v>
+        <v>153.6</v>
       </c>
       <c r="F3" t="n">
-        <v>44.83</v>
+        <v>0.15</v>
       </c>
       <c r="G3" t="n">
-        <v>17.4</v>
+        <v>130.75</v>
       </c>
       <c r="H3" t="n">
-        <v>35.46</v>
+        <v>17.65</v>
       </c>
       <c r="I3" t="n">
-        <v>56.28</v>
+        <v>39.05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="K3" t="n">
-        <v>66.25</v>
+        <v>78.75</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>77.34999999999999</v>
+        <v>47.25</v>
       </c>
       <c r="N3" t="n">
-        <v>23.57</v>
+        <v>153.83</v>
       </c>
       <c r="O3" t="n">
-        <v>4242</v>
+        <v>650</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99983.94</v>
+        <v>99989.5</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>21.21</v>
+        <v>138.45</v>
       </c>
       <c r="T3" t="n">
-        <v>9998.389999999999</v>
+        <v>9998.950000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>27.81</v>
+        <v>181.52</v>
       </c>
       <c r="V3" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>17987.11</v>
+        <v>17998.11</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -719,82 +719,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>RSWM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.07</v>
+        <v>177.14</v>
       </c>
       <c r="E4" t="n">
-        <v>10.24</v>
+        <v>177.06</v>
       </c>
       <c r="F4" t="n">
-        <v>76.43000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="G4" t="n">
-        <v>11.38</v>
+        <v>171.18</v>
       </c>
       <c r="H4" t="n">
-        <v>58.79</v>
+        <v>3.48</v>
       </c>
       <c r="I4" t="n">
-        <v>74.29000000000001</v>
+        <v>29.51</v>
       </c>
       <c r="J4" t="n">
-        <v>3.61</v>
+        <v>1.24</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>76.25</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>74</v>
+        <v>45.75</v>
       </c>
       <c r="N4" t="n">
-        <v>18.07</v>
+        <v>177.14</v>
       </c>
       <c r="O4" t="n">
-        <v>5534</v>
+        <v>564</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99999.38</v>
+        <v>99906.96000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>16.26</v>
+        <v>159.43</v>
       </c>
       <c r="T4" t="n">
-        <v>9999.940000000001</v>
+        <v>9990.700000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>21.32</v>
+        <v>205.48</v>
       </c>
       <c r="V4" t="n">
-        <v>17.99</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>17989.89</v>
+        <v>15985.11</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -804,82 +804,82 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>KERNEX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>347.8</v>
+        <v>1587.2</v>
       </c>
       <c r="E5" t="n">
-        <v>308.32</v>
+        <v>1578.69</v>
       </c>
       <c r="F5" t="n">
-        <v>12.81</v>
+        <v>0.54</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>1425</v>
       </c>
       <c r="H5" t="n">
-        <v>58.09</v>
+        <v>11.38</v>
       </c>
       <c r="I5" t="n">
-        <v>61.8</v>
+        <v>38.45</v>
       </c>
       <c r="J5" t="n">
-        <v>0.89</v>
+        <v>1.35</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>76.25</v>
       </c>
       <c r="L5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>72.75</v>
+        <v>45.75</v>
       </c>
       <c r="N5" t="n">
-        <v>347.8</v>
+        <v>1587.2</v>
       </c>
       <c r="O5" t="n">
-        <v>287</v>
+        <v>63</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99818.60000000001</v>
+        <v>99993.60000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>313.02</v>
+        <v>1428.48</v>
       </c>
       <c r="T5" t="n">
-        <v>9981.860000000001</v>
+        <v>9999.360000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>406.93</v>
+        <v>1841.15</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>16969.16</v>
+        <v>15998.98</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1139.9</v>
+        <v>306.55</v>
       </c>
       <c r="E6" t="n">
-        <v>1038.48</v>
+        <v>204.49</v>
       </c>
       <c r="F6" t="n">
-        <v>9.77</v>
+        <v>49.91</v>
       </c>
       <c r="G6" t="n">
-        <v>993.8</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
-        <v>14.7</v>
+        <v>32.71</v>
       </c>
       <c r="I6" t="n">
-        <v>28.95</v>
+        <v>68.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>71.95</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>1139.9</v>
+        <v>306.55</v>
       </c>
       <c r="O6" t="n">
-        <v>87</v>
+        <v>326</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99171.3</v>
+        <v>99935.3</v>
       </c>
       <c r="R6" t="n">
-        <v>9.92</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>1025.91</v>
+        <v>275.9</v>
       </c>
       <c r="T6" t="n">
-        <v>9917.129999999999</v>
+        <v>9993.530000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1322.28</v>
+        <v>355.6</v>
       </c>
       <c r="V6" t="n">
         <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>15867.41</v>
+        <v>15989.65</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>313.75</v>
+        <v>1136.4</v>
       </c>
       <c r="E7" t="n">
-        <v>261.94</v>
+        <v>750.91</v>
       </c>
       <c r="F7" t="n">
-        <v>19.78</v>
+        <v>51.34</v>
       </c>
       <c r="G7" t="n">
-        <v>220.4</v>
+        <v>720</v>
       </c>
       <c r="H7" t="n">
-        <v>42.35</v>
+        <v>57.83</v>
       </c>
       <c r="I7" t="n">
-        <v>40.63</v>
+        <v>57.66</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.59</v>
       </c>
       <c r="K7" t="n">
-        <v>52.5</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>71.5</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>313.75</v>
+        <v>1136.4</v>
       </c>
       <c r="O7" t="n">
-        <v>318</v>
+        <v>87</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99772.5</v>
+        <v>98866.8</v>
       </c>
       <c r="R7" t="n">
-        <v>9.98</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>282.38</v>
+        <v>1022.76</v>
       </c>
       <c r="T7" t="n">
-        <v>9977.25</v>
+        <v>9886.68</v>
       </c>
       <c r="U7" t="n">
-        <v>357.68</v>
+        <v>1318.22</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>13968.15</v>
+        <v>15818.69</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KROSS</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>294.55</v>
+        <v>687.4</v>
       </c>
       <c r="E8" t="n">
-        <v>203.88</v>
+        <v>595.75</v>
       </c>
       <c r="F8" t="n">
-        <v>44.47</v>
+        <v>15.38</v>
       </c>
       <c r="G8" t="n">
-        <v>231</v>
+        <v>684</v>
       </c>
       <c r="H8" t="n">
-        <v>27.51</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
-        <v>65.20999999999999</v>
+        <v>56.23</v>
       </c>
       <c r="J8" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="K8" t="n">
         <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>71.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>294.55</v>
+        <v>687.4</v>
       </c>
       <c r="O8" t="n">
-        <v>339</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99852.45</v>
+        <v>99673</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>265.1</v>
+        <v>618.66</v>
       </c>
       <c r="T8" t="n">
-        <v>9985.25</v>
+        <v>9967.299999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>350.51</v>
+        <v>790.51</v>
       </c>
       <c r="V8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>18971.97</v>
+        <v>14950.95</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,82 +1144,82 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>KOLTEPATIL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>513.1</v>
+        <v>458.3</v>
       </c>
       <c r="E9" t="n">
-        <v>507.19</v>
+        <v>385.79</v>
       </c>
       <c r="F9" t="n">
-        <v>1.17</v>
+        <v>18.8</v>
       </c>
       <c r="G9" t="n">
-        <v>539</v>
+        <v>451.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.81</v>
+        <v>1.42</v>
       </c>
       <c r="I9" t="n">
-        <v>28.73</v>
+        <v>62.74</v>
       </c>
       <c r="J9" t="n">
-        <v>0.61</v>
+        <v>3.86</v>
       </c>
       <c r="K9" t="n">
-        <v>56.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>71.34999999999999</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>513.1</v>
+        <v>458.3</v>
       </c>
       <c r="O9" t="n">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99541.39999999999</v>
+        <v>99909.39999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.949999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>461.79</v>
+        <v>412.47</v>
       </c>
       <c r="T9" t="n">
-        <v>9954.139999999999</v>
+        <v>9990.940000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>605.46</v>
+        <v>527.04</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>17917.45</v>
+        <v>14986.41</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11293</v>
+        <v>402.15</v>
       </c>
       <c r="E10" t="n">
-        <v>10667.65</v>
+        <v>302.7</v>
       </c>
       <c r="F10" t="n">
-        <v>5.86</v>
+        <v>32.85</v>
       </c>
       <c r="G10" t="n">
-        <v>11644</v>
+        <v>363.25</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.01</v>
+        <v>10.71</v>
       </c>
       <c r="I10" t="n">
-        <v>57.25</v>
+        <v>58.24</v>
       </c>
       <c r="J10" t="n">
-        <v>3.06</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>67.5</v>
+        <v>72.5</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>70.5</v>
+        <v>43.5</v>
       </c>
       <c r="N10" t="n">
-        <v>11293</v>
+        <v>402.15</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>248</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>90344</v>
+        <v>99733.2</v>
       </c>
       <c r="R10" t="n">
-        <v>9.029999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>10163.7</v>
+        <v>361.94</v>
       </c>
       <c r="T10" t="n">
-        <v>9034.4</v>
+        <v>9973.32</v>
       </c>
       <c r="U10" t="n">
-        <v>13212.81</v>
+        <v>466.49</v>
       </c>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>15358.48</v>
+        <v>15957.31</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9162</v>
+        <v>293</v>
       </c>
       <c r="E11" t="n">
-        <v>7224.28</v>
+        <v>190.05</v>
       </c>
       <c r="F11" t="n">
-        <v>26.82</v>
+        <v>54.17</v>
       </c>
       <c r="G11" t="n">
-        <v>7071.5</v>
+        <v>178.95</v>
       </c>
       <c r="H11" t="n">
-        <v>29.56</v>
+        <v>63.73</v>
       </c>
       <c r="I11" t="n">
-        <v>47.9</v>
+        <v>55.27</v>
       </c>
       <c r="J11" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="K11" t="n">
-        <v>63.75</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>70.25</v>
+        <v>43.5</v>
       </c>
       <c r="N11" t="n">
-        <v>9162</v>
+        <v>293</v>
       </c>
       <c r="O11" t="n">
-        <v>10</v>
+        <v>341</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>91620</v>
+        <v>99913</v>
       </c>
       <c r="R11" t="n">
-        <v>9.16</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>8245.799999999999</v>
+        <v>263.7</v>
       </c>
       <c r="T11" t="n">
-        <v>9162</v>
+        <v>9991.299999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>10811.16</v>
+        <v>339.88</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>16491.6</v>
+        <v>15986.08</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>KERNEX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,68 +558,68 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>813.35</v>
+        <v>1587.2</v>
       </c>
       <c r="E2" t="n">
-        <v>806.39</v>
+        <v>1578.69</v>
       </c>
       <c r="F2" t="n">
-        <v>0.86</v>
+        <v>0.54</v>
       </c>
       <c r="G2" t="n">
-        <v>797.55</v>
+        <v>1425</v>
       </c>
       <c r="H2" t="n">
-        <v>1.98</v>
+        <v>11.38</v>
       </c>
       <c r="I2" t="n">
-        <v>38.78</v>
+        <v>38.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.14</v>
+        <v>1.35</v>
       </c>
       <c r="K2" t="n">
-        <v>81.25</v>
+        <v>76.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>48.75</v>
+        <v>77.75</v>
       </c>
       <c r="N2" t="n">
-        <v>813.35</v>
+        <v>1587.2</v>
       </c>
       <c r="O2" t="n">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99228.7</v>
+        <v>99993.60000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>732.02</v>
+        <v>1428.48</v>
       </c>
       <c r="T2" t="n">
-        <v>9922.870000000001</v>
+        <v>9999.360000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>959.75</v>
+        <v>1920.51</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>17861.17</v>
+        <v>20998.66</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -643,73 +643,73 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>153.83</v>
+        <v>1136.4</v>
       </c>
       <c r="E3" t="n">
-        <v>153.6</v>
+        <v>750.91</v>
       </c>
       <c r="F3" t="n">
-        <v>0.15</v>
+        <v>51.34</v>
       </c>
       <c r="G3" t="n">
-        <v>130.75</v>
+        <v>720</v>
       </c>
       <c r="H3" t="n">
-        <v>17.65</v>
+        <v>57.83</v>
       </c>
       <c r="I3" t="n">
-        <v>39.05</v>
+        <v>57.66</v>
       </c>
       <c r="J3" t="n">
-        <v>1.63</v>
+        <v>3.59</v>
       </c>
       <c r="K3" t="n">
-        <v>78.75</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>47.25</v>
+        <v>77</v>
       </c>
       <c r="N3" t="n">
-        <v>153.83</v>
+        <v>1136.4</v>
       </c>
       <c r="O3" t="n">
-        <v>650</v>
+        <v>87</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99989.5</v>
+        <v>98866.8</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>138.45</v>
+        <v>1022.76</v>
       </c>
       <c r="T3" t="n">
-        <v>9998.950000000001</v>
+        <v>9886.68</v>
       </c>
       <c r="U3" t="n">
-        <v>181.52</v>
+        <v>1375.04</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>17998.11</v>
+        <v>20762.03</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RSWM</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -728,73 +728,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>177.14</v>
+        <v>300.55</v>
       </c>
       <c r="E4" t="n">
-        <v>177.06</v>
+        <v>262.41</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05</v>
+        <v>14.53</v>
       </c>
       <c r="G4" t="n">
-        <v>171.18</v>
+        <v>220.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.48</v>
+        <v>36.37</v>
       </c>
       <c r="I4" t="n">
-        <v>29.51</v>
+        <v>34.16</v>
       </c>
       <c r="J4" t="n">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="K4" t="n">
-        <v>76.25</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>45.75</v>
+        <v>76.75</v>
       </c>
       <c r="N4" t="n">
-        <v>177.14</v>
+        <v>300.55</v>
       </c>
       <c r="O4" t="n">
-        <v>564</v>
+        <v>332</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99906.96000000001</v>
+        <v>99782.60000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S4" t="n">
-        <v>159.43</v>
+        <v>270.5</v>
       </c>
       <c r="T4" t="n">
-        <v>9990.700000000001</v>
+        <v>9978.26</v>
       </c>
       <c r="U4" t="n">
-        <v>205.48</v>
+        <v>351.64</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>15985.11</v>
+        <v>16963.04</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KERNEX</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -813,73 +813,73 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1587.2</v>
+        <v>7034</v>
       </c>
       <c r="E5" t="n">
-        <v>1578.69</v>
+        <v>5433.98</v>
       </c>
       <c r="F5" t="n">
-        <v>0.54</v>
+        <v>29.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1425</v>
+        <v>4488.9</v>
       </c>
       <c r="H5" t="n">
-        <v>11.38</v>
+        <v>56.7</v>
       </c>
       <c r="I5" t="n">
-        <v>38.45</v>
+        <v>53.39</v>
       </c>
       <c r="J5" t="n">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="K5" t="n">
-        <v>76.25</v>
+        <v>71.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M5" t="n">
-        <v>45.75</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1587.2</v>
+        <v>7034</v>
       </c>
       <c r="O5" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99993.60000000001</v>
+        <v>98476</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.85</v>
       </c>
       <c r="S5" t="n">
-        <v>1428.48</v>
+        <v>6330.6</v>
       </c>
       <c r="T5" t="n">
-        <v>9999.360000000001</v>
+        <v>9847.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1841.15</v>
+        <v>8300.120000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>15998.98</v>
+        <v>17725.68</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KROSS</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,73 +898,73 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>306.55</v>
+        <v>813.35</v>
       </c>
       <c r="E6" t="n">
-        <v>204.49</v>
+        <v>806.39</v>
       </c>
       <c r="F6" t="n">
-        <v>49.91</v>
+        <v>0.86</v>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>797.55</v>
       </c>
       <c r="H6" t="n">
-        <v>32.71</v>
+        <v>1.98</v>
       </c>
       <c r="I6" t="n">
-        <v>68.3</v>
+        <v>38.78</v>
       </c>
       <c r="J6" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>81.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>75.55</v>
       </c>
       <c r="N6" t="n">
-        <v>306.55</v>
+        <v>813.35</v>
       </c>
       <c r="O6" t="n">
-        <v>326</v>
+        <v>122</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99935.3</v>
+        <v>99228.7</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.92</v>
       </c>
       <c r="S6" t="n">
-        <v>275.9</v>
+        <v>732.02</v>
       </c>
       <c r="T6" t="n">
-        <v>9993.530000000001</v>
+        <v>9922.870000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>355.6</v>
+        <v>984.15</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W6" t="n">
-        <v>15989.65</v>
+        <v>20838.03</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -983,73 +983,73 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1136.4</v>
+        <v>153.83</v>
       </c>
       <c r="E7" t="n">
-        <v>750.91</v>
+        <v>153.6</v>
       </c>
       <c r="F7" t="n">
-        <v>51.34</v>
+        <v>0.15</v>
       </c>
       <c r="G7" t="n">
-        <v>720</v>
+        <v>130.75</v>
       </c>
       <c r="H7" t="n">
-        <v>57.83</v>
+        <v>17.65</v>
       </c>
       <c r="I7" t="n">
-        <v>57.66</v>
+        <v>39.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.59</v>
+        <v>1.64</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>78.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>74.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1136.4</v>
+        <v>153.83</v>
       </c>
       <c r="O7" t="n">
-        <v>87</v>
+        <v>650</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>98866.8</v>
+        <v>99989.5</v>
       </c>
       <c r="R7" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>1022.76</v>
+        <v>138.45</v>
       </c>
       <c r="T7" t="n">
-        <v>9886.68</v>
+        <v>9998.950000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1318.22</v>
+        <v>186.13</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W7" t="n">
-        <v>15818.69</v>
+        <v>20997.8</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PREMEXPLN</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1068,68 +1068,68 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>687.4</v>
+        <v>24.05</v>
       </c>
       <c r="E8" t="n">
-        <v>595.75</v>
+        <v>16.32</v>
       </c>
       <c r="F8" t="n">
-        <v>15.38</v>
+        <v>47.33</v>
       </c>
       <c r="G8" t="n">
-        <v>684</v>
+        <v>17.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>38.22</v>
       </c>
       <c r="I8" t="n">
-        <v>56.23</v>
+        <v>58.85</v>
       </c>
       <c r="J8" t="n">
-        <v>2.25</v>
+        <v>0.92</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>687.4</v>
+        <v>24.05</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>4158</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99673</v>
+        <v>99999.89999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>618.66</v>
+        <v>21.64</v>
       </c>
       <c r="T8" t="n">
-        <v>9967.299999999999</v>
+        <v>9999.99</v>
       </c>
       <c r="U8" t="n">
-        <v>790.51</v>
+        <v>28.38</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>14950.95</v>
+        <v>17999.98</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KOLTEPATIL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1153,68 +1153,68 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>458.3</v>
+        <v>340.9</v>
       </c>
       <c r="E9" t="n">
-        <v>385.79</v>
+        <v>308.69</v>
       </c>
       <c r="F9" t="n">
-        <v>18.8</v>
+        <v>10.44</v>
       </c>
       <c r="G9" t="n">
-        <v>451.9</v>
+        <v>220</v>
       </c>
       <c r="H9" t="n">
-        <v>1.42</v>
+        <v>54.95</v>
       </c>
       <c r="I9" t="n">
-        <v>62.74</v>
+        <v>54.87</v>
       </c>
       <c r="J9" t="n">
-        <v>3.86</v>
+        <v>1.16</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>73.5</v>
       </c>
       <c r="N9" t="n">
-        <v>458.3</v>
+        <v>340.9</v>
       </c>
       <c r="O9" t="n">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99909.39999999999</v>
+        <v>99883.7</v>
       </c>
       <c r="R9" t="n">
         <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>412.47</v>
+        <v>306.81</v>
       </c>
       <c r="T9" t="n">
-        <v>9990.940000000001</v>
+        <v>9988.370000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>527.04</v>
+        <v>388.63</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>14986.41</v>
+        <v>13983.72</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1238,68 +1238,68 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>402.15</v>
+        <v>52.57</v>
       </c>
       <c r="E10" t="n">
-        <v>302.7</v>
+        <v>43.38</v>
       </c>
       <c r="F10" t="n">
-        <v>32.85</v>
+        <v>21.19</v>
       </c>
       <c r="G10" t="n">
-        <v>363.25</v>
+        <v>46.84</v>
       </c>
       <c r="H10" t="n">
-        <v>10.71</v>
+        <v>12.23</v>
       </c>
       <c r="I10" t="n">
-        <v>58.24</v>
+        <v>60.47</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>72.5</v>
+        <v>66.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>43.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>402.15</v>
+        <v>52.57</v>
       </c>
       <c r="O10" t="n">
-        <v>248</v>
+        <v>1902</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99733.2</v>
+        <v>99988.14</v>
       </c>
       <c r="R10" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>361.94</v>
+        <v>47.31</v>
       </c>
       <c r="T10" t="n">
-        <v>9973.32</v>
+        <v>9998.809999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>466.49</v>
+        <v>62.03</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>15957.31</v>
+        <v>17997.87</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1323,73 +1323,73 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>293</v>
+        <v>505.8</v>
       </c>
       <c r="E11" t="n">
-        <v>190.05</v>
+        <v>494.76</v>
       </c>
       <c r="F11" t="n">
-        <v>54.17</v>
+        <v>2.23</v>
       </c>
       <c r="G11" t="n">
-        <v>178.95</v>
+        <v>520.6</v>
       </c>
       <c r="H11" t="n">
-        <v>63.73</v>
+        <v>-2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>55.27</v>
+        <v>32.18</v>
       </c>
       <c r="J11" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>71.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>43.5</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>293</v>
+        <v>505.8</v>
       </c>
       <c r="O11" t="n">
-        <v>341</v>
+        <v>197</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99913</v>
+        <v>99642.60000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>263.7</v>
+        <v>455.22</v>
       </c>
       <c r="T11" t="n">
-        <v>9991.299999999999</v>
+        <v>9964.26</v>
       </c>
       <c r="U11" t="n">
-        <v>339.88</v>
+        <v>601.9</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>15986.08</v>
+        <v>18932.09</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KERNEX</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1587.2</v>
+        <v>192.41</v>
       </c>
       <c r="E2" t="n">
-        <v>1578.69</v>
+        <v>190.37</v>
       </c>
       <c r="F2" t="n">
-        <v>0.54</v>
+        <v>1.07</v>
       </c>
       <c r="G2" t="n">
-        <v>1425</v>
+        <v>150.79</v>
       </c>
       <c r="H2" t="n">
-        <v>11.38</v>
+        <v>27.6</v>
       </c>
       <c r="I2" t="n">
-        <v>38.45</v>
+        <v>34.25</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="K2" t="n">
-        <v>76.25</v>
+        <v>78.75</v>
       </c>
       <c r="L2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M2" t="n">
-        <v>77.75</v>
+        <v>83.25</v>
       </c>
       <c r="N2" t="n">
-        <v>1587.2</v>
+        <v>192.41</v>
       </c>
       <c r="O2" t="n">
-        <v>63</v>
+        <v>519</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99993.60000000001</v>
+        <v>99860.78999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>1428.48</v>
+        <v>173.17</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.360000000001</v>
+        <v>9986.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1920.51</v>
+        <v>236.66</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="W2" t="n">
-        <v>20998.66</v>
+        <v>22967.98</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1136.4</v>
+        <v>25.25</v>
       </c>
       <c r="E3" t="n">
-        <v>750.91</v>
+        <v>16.38</v>
       </c>
       <c r="F3" t="n">
-        <v>51.34</v>
+        <v>54.17</v>
       </c>
       <c r="G3" t="n">
-        <v>720</v>
+        <v>17.4</v>
       </c>
       <c r="H3" t="n">
-        <v>57.83</v>
+        <v>45.11</v>
       </c>
       <c r="I3" t="n">
-        <v>57.66</v>
+        <v>64.48</v>
       </c>
       <c r="J3" t="n">
-        <v>3.59</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>77</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1136.4</v>
+        <v>25.25</v>
       </c>
       <c r="O3" t="n">
-        <v>87</v>
+        <v>3960</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>98866.8</v>
+        <v>99990</v>
       </c>
       <c r="R3" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>1022.76</v>
+        <v>22.72</v>
       </c>
       <c r="T3" t="n">
-        <v>9886.68</v>
+        <v>9999</v>
       </c>
       <c r="U3" t="n">
-        <v>1375.04</v>
+        <v>29.79</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>17.98</v>
       </c>
       <c r="W3" t="n">
-        <v>20762.03</v>
+        <v>17978.2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300.55</v>
+        <v>6977</v>
       </c>
       <c r="E4" t="n">
-        <v>262.41</v>
+        <v>5453.37</v>
       </c>
       <c r="F4" t="n">
-        <v>14.53</v>
+        <v>27.94</v>
       </c>
       <c r="G4" t="n">
-        <v>220.4</v>
+        <v>4488.9</v>
       </c>
       <c r="H4" t="n">
-        <v>36.37</v>
+        <v>55.43</v>
       </c>
       <c r="I4" t="n">
-        <v>34.16</v>
+        <v>51.78</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>66.25</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M4" t="n">
-        <v>76.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>300.55</v>
+        <v>6977</v>
       </c>
       <c r="O4" t="n">
-        <v>332</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99782.60000000001</v>
+        <v>97678</v>
       </c>
       <c r="R4" t="n">
-        <v>9.98</v>
+        <v>9.77</v>
       </c>
       <c r="S4" t="n">
-        <v>270.5</v>
+        <v>6279.3</v>
       </c>
       <c r="T4" t="n">
-        <v>9978.26</v>
+        <v>9767.799999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>351.64</v>
+        <v>8093.32</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>16963.04</v>
+        <v>15628.48</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7034</v>
+        <v>1188.8</v>
       </c>
       <c r="E5" t="n">
-        <v>5433.98</v>
+        <v>754.8</v>
       </c>
       <c r="F5" t="n">
-        <v>29.44</v>
+        <v>57.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4488.9</v>
+        <v>720</v>
       </c>
       <c r="H5" t="n">
-        <v>56.7</v>
+        <v>65.11</v>
       </c>
       <c r="I5" t="n">
-        <v>53.39</v>
+        <v>61.84</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>1.14</v>
       </c>
       <c r="K5" t="n">
-        <v>71.25</v>
+        <v>66.25</v>
       </c>
       <c r="L5" t="n">
         <v>84</v>
       </c>
       <c r="M5" t="n">
-        <v>76.34999999999999</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>7034</v>
+        <v>1188.8</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>98476</v>
+        <v>99859.2</v>
       </c>
       <c r="R5" t="n">
-        <v>9.85</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>6330.6</v>
+        <v>1069.92</v>
       </c>
       <c r="T5" t="n">
-        <v>9847.6</v>
+        <v>9985.92</v>
       </c>
       <c r="U5" t="n">
-        <v>8300.120000000001</v>
+        <v>1402.78</v>
       </c>
       <c r="V5" t="n">
         <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>17725.68</v>
+        <v>17974.66</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>813.35</v>
+        <v>509.7</v>
       </c>
       <c r="E6" t="n">
-        <v>806.39</v>
+        <v>495.04</v>
       </c>
       <c r="F6" t="n">
-        <v>0.86</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>797.55</v>
+        <v>520.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.98</v>
+        <v>-2.09</v>
       </c>
       <c r="I6" t="n">
-        <v>38.78</v>
+        <v>34.09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>1.38</v>
       </c>
       <c r="K6" t="n">
-        <v>81.25</v>
+        <v>71.25</v>
       </c>
       <c r="L6" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>75.55</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>813.35</v>
+        <v>509.7</v>
       </c>
       <c r="O6" t="n">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99228.7</v>
+        <v>99901.2</v>
       </c>
       <c r="R6" t="n">
-        <v>9.92</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>732.02</v>
+        <v>458.73</v>
       </c>
       <c r="T6" t="n">
-        <v>9922.870000000001</v>
+        <v>9990.120000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>984.15</v>
+        <v>606.54</v>
       </c>
       <c r="V6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>20838.03</v>
+        <v>18981.23</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>153.83</v>
+        <v>344.4</v>
       </c>
       <c r="E7" t="n">
-        <v>153.6</v>
+        <v>309.08</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15</v>
+        <v>11.43</v>
       </c>
       <c r="G7" t="n">
-        <v>130.75</v>
+        <v>220</v>
       </c>
       <c r="H7" t="n">
-        <v>17.65</v>
+        <v>56.55</v>
       </c>
       <c r="I7" t="n">
-        <v>39.05</v>
+        <v>57.48</v>
       </c>
       <c r="J7" t="n">
-        <v>1.64</v>
+        <v>0.76</v>
       </c>
       <c r="K7" t="n">
-        <v>78.75</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="M7" t="n">
-        <v>74.45</v>
+        <v>72.75</v>
       </c>
       <c r="N7" t="n">
-        <v>153.83</v>
+        <v>344.4</v>
       </c>
       <c r="O7" t="n">
-        <v>650</v>
+        <v>290</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99989.5</v>
+        <v>99876</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>138.45</v>
+        <v>309.96</v>
       </c>
       <c r="T7" t="n">
-        <v>9998.950000000001</v>
+        <v>9987.6</v>
       </c>
       <c r="U7" t="n">
-        <v>186.13</v>
+        <v>402.95</v>
       </c>
       <c r="V7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W7" t="n">
-        <v>20997.8</v>
+        <v>16978.92</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.05</v>
+        <v>440.75</v>
       </c>
       <c r="E8" t="n">
-        <v>16.32</v>
+        <v>400.27</v>
       </c>
       <c r="F8" t="n">
-        <v>47.33</v>
+        <v>10.11</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
+        <v>453.2</v>
       </c>
       <c r="H8" t="n">
-        <v>38.22</v>
+        <v>-2.75</v>
       </c>
       <c r="I8" t="n">
-        <v>58.85</v>
+        <v>58.95</v>
       </c>
       <c r="J8" t="n">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M8" t="n">
-        <v>74.34999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>24.05</v>
+        <v>440.75</v>
       </c>
       <c r="O8" t="n">
-        <v>4158</v>
+        <v>226</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99999.89999999999</v>
+        <v>99609.5</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>21.64</v>
+        <v>396.68</v>
       </c>
       <c r="T8" t="n">
-        <v>9999.99</v>
+        <v>9960.950000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>28.38</v>
+        <v>520.08</v>
       </c>
       <c r="V8" t="n">
         <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>17999.98</v>
+        <v>17929.71</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>340.9</v>
+        <v>1904.1</v>
       </c>
       <c r="E9" t="n">
-        <v>308.69</v>
+        <v>1300</v>
       </c>
       <c r="F9" t="n">
-        <v>10.44</v>
+        <v>46.47</v>
       </c>
       <c r="G9" t="n">
-        <v>220</v>
+        <v>1250</v>
       </c>
       <c r="H9" t="n">
-        <v>54.95</v>
+        <v>52.33</v>
       </c>
       <c r="I9" t="n">
-        <v>54.87</v>
+        <v>48.97</v>
       </c>
       <c r="J9" t="n">
-        <v>1.16</v>
+        <v>2.33</v>
       </c>
       <c r="K9" t="n">
-        <v>62.5</v>
+        <v>66.25</v>
       </c>
       <c r="L9" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>73.5</v>
+        <v>72.55</v>
       </c>
       <c r="N9" t="n">
-        <v>340.9</v>
+        <v>1904.1</v>
       </c>
       <c r="O9" t="n">
-        <v>293</v>
+        <v>52</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99883.7</v>
+        <v>99013.2</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>9.9</v>
       </c>
       <c r="S9" t="n">
-        <v>306.81</v>
+        <v>1713.69</v>
       </c>
       <c r="T9" t="n">
-        <v>9988.370000000001</v>
+        <v>9901.32</v>
       </c>
       <c r="U9" t="n">
-        <v>388.63</v>
+        <v>2246.84</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>13983.72</v>
+        <v>17822.38</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52.57</v>
+        <v>299.85</v>
       </c>
       <c r="E10" t="n">
-        <v>43.38</v>
+        <v>262.88</v>
       </c>
       <c r="F10" t="n">
-        <v>21.19</v>
+        <v>14.06</v>
       </c>
       <c r="G10" t="n">
-        <v>46.84</v>
+        <v>220.4</v>
       </c>
       <c r="H10" t="n">
-        <v>12.23</v>
+        <v>36.05</v>
       </c>
       <c r="I10" t="n">
-        <v>60.47</v>
+        <v>33.85</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>66.25</v>
+        <v>52.5</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>73.34999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="N10" t="n">
-        <v>52.57</v>
+        <v>299.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1902</v>
+        <v>333</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99988.14</v>
+        <v>99850.05</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>47.31</v>
+        <v>269.86</v>
       </c>
       <c r="T10" t="n">
-        <v>9998.809999999999</v>
+        <v>9985</v>
       </c>
       <c r="U10" t="n">
-        <v>62.03</v>
+        <v>341.83</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>17997.87</v>
+        <v>13979.01</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>PIXTRANS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>505.8</v>
+        <v>1648.7</v>
       </c>
       <c r="E11" t="n">
-        <v>494.76</v>
+        <v>1606.44</v>
       </c>
       <c r="F11" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="G11" t="n">
-        <v>520.6</v>
+        <v>1624</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.84</v>
+        <v>1.52</v>
       </c>
       <c r="I11" t="n">
-        <v>32.18</v>
+        <v>35.36</v>
       </c>
       <c r="J11" t="n">
-        <v>1.35</v>
+        <v>0.1</v>
       </c>
       <c r="K11" t="n">
-        <v>71.25</v>
+        <v>65</v>
       </c>
       <c r="L11" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
-        <v>73.15000000000001</v>
+        <v>71</v>
       </c>
       <c r="N11" t="n">
-        <v>505.8</v>
+        <v>1648.7</v>
       </c>
       <c r="O11" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99642.60000000001</v>
+        <v>98922</v>
       </c>
       <c r="R11" t="n">
-        <v>9.960000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>455.22</v>
+        <v>1483.83</v>
       </c>
       <c r="T11" t="n">
-        <v>9964.26</v>
+        <v>9892.200000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>601.9</v>
+        <v>1945.47</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>18932.09</v>
+        <v>17805.96</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>192.41</v>
+        <v>16.65</v>
       </c>
       <c r="E2" t="n">
-        <v>190.37</v>
+        <v>10.36</v>
       </c>
       <c r="F2" t="n">
-        <v>1.07</v>
+        <v>60.77</v>
       </c>
       <c r="G2" t="n">
-        <v>150.79</v>
+        <v>11.38</v>
       </c>
       <c r="H2" t="n">
-        <v>27.6</v>
+        <v>46.31</v>
       </c>
       <c r="I2" t="n">
-        <v>34.25</v>
+        <v>61.28</v>
       </c>
       <c r="J2" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="K2" t="n">
-        <v>78.75</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>83.25</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>192.41</v>
+        <v>16.65</v>
       </c>
       <c r="O2" t="n">
-        <v>519</v>
+        <v>6006</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99860.78999999999</v>
+        <v>99999.89999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>173.17</v>
+        <v>14.98</v>
       </c>
       <c r="T2" t="n">
-        <v>9986.08</v>
+        <v>9999.99</v>
       </c>
       <c r="U2" t="n">
-        <v>236.66</v>
+        <v>19.81</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>18.98</v>
       </c>
       <c r="W2" t="n">
-        <v>22967.98</v>
+        <v>18979.98</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.25</v>
+        <v>556.05</v>
       </c>
       <c r="E3" t="n">
-        <v>16.38</v>
+        <v>554.3200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>54.17</v>
+        <v>0.31</v>
       </c>
       <c r="G3" t="n">
-        <v>17.4</v>
+        <v>582.45</v>
       </c>
       <c r="H3" t="n">
-        <v>45.11</v>
+        <v>-4.53</v>
       </c>
       <c r="I3" t="n">
-        <v>64.48</v>
+        <v>23.08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>4.07</v>
       </c>
       <c r="K3" t="n">
-        <v>66.25</v>
+        <v>73.75</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>77.34999999999999</v>
+        <v>76.25</v>
       </c>
       <c r="N3" t="n">
-        <v>25.25</v>
+        <v>556.05</v>
       </c>
       <c r="O3" t="n">
-        <v>3960</v>
+        <v>179</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99990</v>
+        <v>99532.95</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>22.72</v>
+        <v>500.44</v>
       </c>
       <c r="T3" t="n">
-        <v>9999</v>
+        <v>9953.299999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>29.79</v>
+        <v>683.9400000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>17.98</v>
+        <v>23</v>
       </c>
       <c r="W3" t="n">
-        <v>17978.2</v>
+        <v>22892.58</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6977</v>
+        <v>194.9</v>
       </c>
       <c r="E4" t="n">
-        <v>5453.37</v>
+        <v>190.46</v>
       </c>
       <c r="F4" t="n">
-        <v>27.94</v>
+        <v>2.33</v>
       </c>
       <c r="G4" t="n">
-        <v>4488.9</v>
+        <v>150.79</v>
       </c>
       <c r="H4" t="n">
-        <v>55.43</v>
+        <v>29.25</v>
       </c>
       <c r="I4" t="n">
-        <v>51.78</v>
+        <v>37.61</v>
       </c>
       <c r="J4" t="n">
-        <v>1.35</v>
+        <v>0.36</v>
       </c>
       <c r="K4" t="n">
-        <v>66.25</v>
+        <v>65</v>
       </c>
       <c r="L4" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M4" t="n">
-        <v>73.34999999999999</v>
+        <v>75</v>
       </c>
       <c r="N4" t="n">
-        <v>6977</v>
+        <v>194.9</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>513</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>97678</v>
+        <v>99983.7</v>
       </c>
       <c r="R4" t="n">
-        <v>9.77</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>6279.3</v>
+        <v>175.41</v>
       </c>
       <c r="T4" t="n">
-        <v>9767.799999999999</v>
+        <v>9998.370000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>8093.32</v>
+        <v>229.98</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>15628.48</v>
+        <v>17997.07</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1188.8</v>
+        <v>26.51</v>
       </c>
       <c r="E5" t="n">
-        <v>754.8</v>
+        <v>16.44</v>
       </c>
       <c r="F5" t="n">
-        <v>57.5</v>
+        <v>61.25</v>
       </c>
       <c r="G5" t="n">
-        <v>720</v>
+        <v>17.4</v>
       </c>
       <c r="H5" t="n">
-        <v>65.11</v>
+        <v>52.36</v>
       </c>
       <c r="I5" t="n">
-        <v>61.84</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.14</v>
+        <v>0.47</v>
       </c>
       <c r="K5" t="n">
-        <v>66.25</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>73.34999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1188.8</v>
+        <v>26.51</v>
       </c>
       <c r="O5" t="n">
-        <v>84</v>
+        <v>3772</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99859.2</v>
+        <v>99995.72</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>1069.92</v>
+        <v>23.86</v>
       </c>
       <c r="T5" t="n">
-        <v>9985.92</v>
+        <v>9999.57</v>
       </c>
       <c r="U5" t="n">
-        <v>1402.78</v>
+        <v>31.28</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="W5" t="n">
-        <v>17974.66</v>
+        <v>17989.23</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>509.7</v>
+        <v>9505.5</v>
       </c>
       <c r="E6" t="n">
-        <v>495.04</v>
+        <v>7266.17</v>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>30.82</v>
       </c>
       <c r="G6" t="n">
-        <v>520.6</v>
+        <v>7071.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.09</v>
+        <v>34.42</v>
       </c>
       <c r="I6" t="n">
-        <v>34.09</v>
+        <v>58.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="K6" t="n">
-        <v>71.25</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>73.15000000000001</v>
+        <v>74</v>
       </c>
       <c r="N6" t="n">
-        <v>509.7</v>
+        <v>9505.5</v>
       </c>
       <c r="O6" t="n">
-        <v>196</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99901.2</v>
+        <v>95055</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.51</v>
       </c>
       <c r="S6" t="n">
-        <v>458.73</v>
+        <v>8554.950000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>9990.120000000001</v>
+        <v>9505.5</v>
       </c>
       <c r="U6" t="n">
-        <v>606.54</v>
+        <v>11311.55</v>
       </c>
       <c r="V6" t="n">
         <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>18981.23</v>
+        <v>18060.45</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>344.4</v>
+        <v>1091.2</v>
       </c>
       <c r="E7" t="n">
-        <v>309.08</v>
+        <v>758.22</v>
       </c>
       <c r="F7" t="n">
-        <v>11.43</v>
+        <v>43.92</v>
       </c>
       <c r="G7" t="n">
-        <v>220</v>
+        <v>720</v>
       </c>
       <c r="H7" t="n">
-        <v>56.55</v>
+        <v>51.56</v>
       </c>
       <c r="I7" t="n">
-        <v>57.48</v>
+        <v>51.61</v>
       </c>
       <c r="J7" t="n">
-        <v>0.76</v>
+        <v>1.44</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>66.25</v>
       </c>
       <c r="L7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="N7" t="n">
-        <v>344.4</v>
+        <v>1091.2</v>
       </c>
       <c r="O7" t="n">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99876</v>
+        <v>99299.2</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.93</v>
       </c>
       <c r="S7" t="n">
-        <v>309.96</v>
+        <v>982.08</v>
       </c>
       <c r="T7" t="n">
-        <v>9987.6</v>
+        <v>9929.92</v>
       </c>
       <c r="U7" t="n">
-        <v>402.95</v>
+        <v>1265.79</v>
       </c>
       <c r="V7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
-        <v>16978.92</v>
+        <v>15887.87</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>440.75</v>
+        <v>341.6</v>
       </c>
       <c r="E8" t="n">
-        <v>400.27</v>
+        <v>309.45</v>
       </c>
       <c r="F8" t="n">
-        <v>10.11</v>
+        <v>10.39</v>
       </c>
       <c r="G8" t="n">
-        <v>453.2</v>
+        <v>220</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.75</v>
+        <v>55.27</v>
       </c>
       <c r="I8" t="n">
-        <v>58.95</v>
+        <v>54.75</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="L8" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="N8" t="n">
-        <v>440.75</v>
+        <v>341.6</v>
       </c>
       <c r="O8" t="n">
-        <v>226</v>
+        <v>292</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99609.5</v>
+        <v>99747.2</v>
       </c>
       <c r="R8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>396.68</v>
+        <v>307.44</v>
       </c>
       <c r="T8" t="n">
-        <v>9960.950000000001</v>
+        <v>9974.719999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>520.08</v>
+        <v>389.42</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>17929.71</v>
+        <v>13964.61</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1904.1</v>
+        <v>314.9</v>
       </c>
       <c r="E9" t="n">
-        <v>1300</v>
+        <v>191.6</v>
       </c>
       <c r="F9" t="n">
-        <v>46.47</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>1250</v>
+        <v>178.95</v>
       </c>
       <c r="H9" t="n">
-        <v>52.33</v>
+        <v>75.97</v>
       </c>
       <c r="I9" t="n">
-        <v>48.97</v>
+        <v>65.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="K9" t="n">
-        <v>66.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>72.55</v>
+        <v>72.2</v>
       </c>
       <c r="N9" t="n">
-        <v>1904.1</v>
+        <v>314.9</v>
       </c>
       <c r="O9" t="n">
-        <v>52</v>
+        <v>317</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99013.2</v>
+        <v>99823.3</v>
       </c>
       <c r="R9" t="n">
-        <v>9.9</v>
+        <v>9.98</v>
       </c>
       <c r="S9" t="n">
-        <v>1713.69</v>
+        <v>283.41</v>
       </c>
       <c r="T9" t="n">
-        <v>9901.32</v>
+        <v>9982.33</v>
       </c>
       <c r="U9" t="n">
-        <v>2246.84</v>
+        <v>374.73</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>17822.38</v>
+        <v>18966.43</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>299.85</v>
+        <v>54.31</v>
       </c>
       <c r="E10" t="n">
-        <v>262.88</v>
+        <v>43.53</v>
       </c>
       <c r="F10" t="n">
-        <v>14.06</v>
+        <v>24.77</v>
       </c>
       <c r="G10" t="n">
-        <v>220.4</v>
+        <v>46.84</v>
       </c>
       <c r="H10" t="n">
-        <v>36.05</v>
+        <v>15.95</v>
       </c>
       <c r="I10" t="n">
-        <v>33.85</v>
+        <v>65.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52.5</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>71.5</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>299.85</v>
+        <v>54.31</v>
       </c>
       <c r="O10" t="n">
-        <v>333</v>
+        <v>1841</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99850.05</v>
+        <v>99984.71000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>269.86</v>
+        <v>48.88</v>
       </c>
       <c r="T10" t="n">
-        <v>9985</v>
+        <v>9998.469999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>341.83</v>
+        <v>64.09</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>18.01</v>
       </c>
       <c r="W10" t="n">
-        <v>13979.01</v>
+        <v>18007.25</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIXTRANS</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1648.7</v>
+        <v>7160</v>
       </c>
       <c r="E11" t="n">
-        <v>1606.44</v>
+        <v>5473.32</v>
       </c>
       <c r="F11" t="n">
-        <v>2.63</v>
+        <v>30.82</v>
       </c>
       <c r="G11" t="n">
-        <v>1624</v>
+        <v>4488.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.52</v>
+        <v>59.5</v>
       </c>
       <c r="I11" t="n">
-        <v>35.36</v>
+        <v>56.34</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="K11" t="n">
-        <v>65</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1648.7</v>
+        <v>7160</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>98922</v>
+        <v>93080</v>
       </c>
       <c r="R11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="S11" t="n">
-        <v>1483.83</v>
+        <v>6444</v>
       </c>
       <c r="T11" t="n">
-        <v>9892.200000000001</v>
+        <v>9308</v>
       </c>
       <c r="U11" t="n">
-        <v>1945.47</v>
+        <v>8448.799999999999</v>
       </c>
       <c r="V11" t="n">
         <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>17805.96</v>
+        <v>16754.4</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.65</v>
+        <v>346</v>
       </c>
       <c r="E2" t="n">
-        <v>10.36</v>
+        <v>309.86</v>
       </c>
       <c r="F2" t="n">
-        <v>60.77</v>
+        <v>11.66</v>
       </c>
       <c r="G2" t="n">
-        <v>11.38</v>
+        <v>220</v>
       </c>
       <c r="H2" t="n">
-        <v>46.31</v>
+        <v>57.27</v>
       </c>
       <c r="I2" t="n">
-        <v>61.28</v>
+        <v>58.11</v>
       </c>
       <c r="J2" t="n">
-        <v>2.01</v>
+        <v>0.63</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L2" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>76.59999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N2" t="n">
-        <v>16.65</v>
+        <v>346</v>
       </c>
       <c r="O2" t="n">
-        <v>6006</v>
+        <v>289</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99999.89999999999</v>
+        <v>99994</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>14.98</v>
+        <v>311.4</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.99</v>
+        <v>9999.4</v>
       </c>
       <c r="U2" t="n">
-        <v>19.81</v>
+        <v>404.82</v>
       </c>
       <c r="V2" t="n">
-        <v>18.98</v>
+        <v>17</v>
       </c>
       <c r="W2" t="n">
-        <v>18979.98</v>
+        <v>16998.98</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>556.05</v>
+        <v>191.73</v>
       </c>
       <c r="E3" t="n">
-        <v>554.3200000000001</v>
+        <v>190.52</v>
       </c>
       <c r="F3" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="G3" t="n">
-        <v>582.45</v>
+        <v>150.79</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.53</v>
+        <v>27.15</v>
       </c>
       <c r="I3" t="n">
-        <v>23.08</v>
+        <v>35.15</v>
       </c>
       <c r="J3" t="n">
-        <v>4.07</v>
+        <v>0.32</v>
       </c>
       <c r="K3" t="n">
-        <v>73.75</v>
+        <v>65</v>
       </c>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M3" t="n">
-        <v>76.25</v>
+        <v>75</v>
       </c>
       <c r="N3" t="n">
-        <v>556.05</v>
+        <v>191.73</v>
       </c>
       <c r="O3" t="n">
-        <v>179</v>
+        <v>521</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99532.95</v>
+        <v>99891.33</v>
       </c>
       <c r="R3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>500.44</v>
+        <v>172.56</v>
       </c>
       <c r="T3" t="n">
-        <v>9953.299999999999</v>
+        <v>9989.129999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>683.9400000000001</v>
+        <v>226.24</v>
       </c>
       <c r="V3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>22892.58</v>
+        <v>17980.44</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>194.9</v>
+        <v>7140</v>
       </c>
       <c r="E4" t="n">
-        <v>190.46</v>
+        <v>5493.36</v>
       </c>
       <c r="F4" t="n">
-        <v>2.33</v>
+        <v>29.98</v>
       </c>
       <c r="G4" t="n">
-        <v>150.79</v>
+        <v>4488.9</v>
       </c>
       <c r="H4" t="n">
-        <v>29.25</v>
+        <v>59.06</v>
       </c>
       <c r="I4" t="n">
-        <v>37.61</v>
+        <v>55.72</v>
       </c>
       <c r="J4" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>65</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>194.9</v>
+        <v>7140</v>
       </c>
       <c r="O4" t="n">
-        <v>513</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99983.7</v>
+        <v>99960</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>175.41</v>
+        <v>6426</v>
       </c>
       <c r="T4" t="n">
-        <v>9998.370000000001</v>
+        <v>9996</v>
       </c>
       <c r="U4" t="n">
-        <v>229.98</v>
+        <v>8425.200000000001</v>
       </c>
       <c r="V4" t="n">
         <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>17997.07</v>
+        <v>17992.8</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>ORBTEXP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.51</v>
+        <v>267.15</v>
       </c>
       <c r="E5" t="n">
-        <v>16.44</v>
+        <v>201.89</v>
       </c>
       <c r="F5" t="n">
-        <v>61.25</v>
+        <v>32.33</v>
       </c>
       <c r="G5" t="n">
-        <v>17.4</v>
+        <v>265</v>
       </c>
       <c r="H5" t="n">
-        <v>52.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>69.23999999999999</v>
+        <v>61.74</v>
       </c>
       <c r="J5" t="n">
-        <v>0.47</v>
+        <v>1.45</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="M5" t="n">
-        <v>74.34999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="N5" t="n">
-        <v>26.51</v>
+        <v>267.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3772</v>
+        <v>374</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99995.72</v>
+        <v>99914.10000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>23.86</v>
+        <v>240.43</v>
       </c>
       <c r="T5" t="n">
-        <v>9999.57</v>
+        <v>9991.41</v>
       </c>
       <c r="U5" t="n">
-        <v>31.28</v>
+        <v>312.57</v>
       </c>
       <c r="V5" t="n">
-        <v>17.99</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>17989.23</v>
+        <v>16985.4</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MAYURUNIQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9505.5</v>
+        <v>731.25</v>
       </c>
       <c r="E6" t="n">
-        <v>7266.17</v>
+        <v>668.8200000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>30.82</v>
+        <v>9.33</v>
       </c>
       <c r="G6" t="n">
-        <v>7071.5</v>
+        <v>629.9</v>
       </c>
       <c r="H6" t="n">
-        <v>34.42</v>
+        <v>16.09</v>
       </c>
       <c r="I6" t="n">
-        <v>58.3</v>
+        <v>46.76</v>
       </c>
       <c r="J6" t="n">
-        <v>1.37</v>
+        <v>0.28</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>52.5</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
-        <v>74</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>9505.5</v>
+        <v>731.25</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>95055</v>
+        <v>99450</v>
       </c>
       <c r="R6" t="n">
-        <v>9.51</v>
+        <v>9.94</v>
       </c>
       <c r="S6" t="n">
-        <v>8554.950000000001</v>
+        <v>658.12</v>
       </c>
       <c r="T6" t="n">
-        <v>9505.5</v>
+        <v>9945</v>
       </c>
       <c r="U6" t="n">
-        <v>11311.55</v>
+        <v>826.3099999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>18060.45</v>
+        <v>12928.5</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1091.2</v>
+        <v>9986</v>
       </c>
       <c r="E7" t="n">
-        <v>758.22</v>
+        <v>9437.440000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>43.92</v>
+        <v>5.81</v>
       </c>
       <c r="G7" t="n">
-        <v>720</v>
+        <v>9950</v>
       </c>
       <c r="H7" t="n">
-        <v>51.56</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="n">
-        <v>51.61</v>
+        <v>38.51</v>
       </c>
       <c r="J7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="K7" t="n">
-        <v>66.25</v>
+        <v>56.25</v>
       </c>
       <c r="L7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M7" t="n">
-        <v>73.75</v>
+        <v>68.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1091.2</v>
+        <v>9986</v>
       </c>
       <c r="O7" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99299.2</v>
+        <v>99860</v>
       </c>
       <c r="R7" t="n">
-        <v>9.93</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>982.08</v>
+        <v>8987.4</v>
       </c>
       <c r="T7" t="n">
-        <v>9929.92</v>
+        <v>9986</v>
       </c>
       <c r="U7" t="n">
-        <v>1265.79</v>
+        <v>11384.04</v>
       </c>
       <c r="V7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>15887.87</v>
+        <v>13980.4</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>341.6</v>
+        <v>231.66</v>
       </c>
       <c r="E8" t="n">
-        <v>309.45</v>
+        <v>209.23</v>
       </c>
       <c r="F8" t="n">
-        <v>10.39</v>
+        <v>10.72</v>
       </c>
       <c r="G8" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H8" t="n">
-        <v>55.27</v>
+        <v>8.25</v>
       </c>
       <c r="I8" t="n">
-        <v>54.75</v>
+        <v>35.35</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="K8" t="n">
-        <v>62.5</v>
+        <v>58.75</v>
       </c>
       <c r="L8" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="M8" t="n">
-        <v>73.5</v>
+        <v>68.45</v>
       </c>
       <c r="N8" t="n">
-        <v>341.6</v>
+        <v>231.66</v>
       </c>
       <c r="O8" t="n">
-        <v>292</v>
+        <v>431</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99747.2</v>
+        <v>99845.46000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>307.44</v>
+        <v>208.49</v>
       </c>
       <c r="T8" t="n">
-        <v>9974.719999999999</v>
+        <v>9984.549999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>389.42</v>
+        <v>271.04</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>13964.61</v>
+        <v>16973.73</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>314.9</v>
+        <v>114.96</v>
       </c>
       <c r="E9" t="n">
-        <v>191.6</v>
+        <v>99.77</v>
       </c>
       <c r="F9" t="n">
-        <v>64.34999999999999</v>
+        <v>15.23</v>
       </c>
       <c r="G9" t="n">
-        <v>178.95</v>
+        <v>114</v>
       </c>
       <c r="H9" t="n">
-        <v>75.97</v>
+        <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>65.25</v>
+        <v>48.91</v>
       </c>
       <c r="J9" t="n">
-        <v>2.63</v>
+        <v>0.98</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>52.5</v>
       </c>
       <c r="L9" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="M9" t="n">
-        <v>72.2</v>
+        <v>68.3</v>
       </c>
       <c r="N9" t="n">
-        <v>314.9</v>
+        <v>114.96</v>
       </c>
       <c r="O9" t="n">
-        <v>317</v>
+        <v>869</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99823.3</v>
+        <v>99900.24000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>283.41</v>
+        <v>103.46</v>
       </c>
       <c r="T9" t="n">
-        <v>9982.33</v>
+        <v>9990.02</v>
       </c>
       <c r="U9" t="n">
-        <v>374.73</v>
+        <v>131.05</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>18966.43</v>
+        <v>13986.03</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54.31</v>
+        <v>512.25</v>
       </c>
       <c r="E10" t="n">
-        <v>43.53</v>
+        <v>454.96</v>
       </c>
       <c r="F10" t="n">
-        <v>24.77</v>
+        <v>12.59</v>
       </c>
       <c r="G10" t="n">
-        <v>46.84</v>
+        <v>404</v>
       </c>
       <c r="H10" t="n">
-        <v>15.95</v>
+        <v>26.79</v>
       </c>
       <c r="I10" t="n">
-        <v>65.2</v>
+        <v>47.59</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>6.82</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>66.25</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="M10" t="n">
-        <v>70.34999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="N10" t="n">
-        <v>54.31</v>
+        <v>512.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1841</v>
+        <v>195</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99984.71000000001</v>
+        <v>99888.75</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>48.88</v>
+        <v>461.02</v>
       </c>
       <c r="T10" t="n">
-        <v>9998.469999999999</v>
+        <v>9988.879999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>64.09</v>
+        <v>589.09</v>
       </c>
       <c r="V10" t="n">
-        <v>18.01</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>18007.25</v>
+        <v>14983.31</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7160</v>
+        <v>260.65</v>
       </c>
       <c r="E11" t="n">
-        <v>5473.32</v>
+        <v>192.07</v>
       </c>
       <c r="F11" t="n">
-        <v>30.82</v>
+        <v>35.71</v>
       </c>
       <c r="G11" t="n">
-        <v>4488.9</v>
+        <v>178.95</v>
       </c>
       <c r="H11" t="n">
-        <v>59.5</v>
+        <v>45.66</v>
       </c>
       <c r="I11" t="n">
-        <v>56.34</v>
+        <v>40.54</v>
       </c>
       <c r="J11" t="n">
-        <v>0.52</v>
+        <v>5.99</v>
       </c>
       <c r="K11" t="n">
         <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>70.34999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="N11" t="n">
-        <v>7160</v>
+        <v>260.65</v>
       </c>
       <c r="O11" t="n">
-        <v>13</v>
+        <v>383</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>93080</v>
+        <v>99828.95</v>
       </c>
       <c r="R11" t="n">
-        <v>9.31</v>
+        <v>9.98</v>
       </c>
       <c r="S11" t="n">
-        <v>6444</v>
+        <v>234.58</v>
       </c>
       <c r="T11" t="n">
-        <v>9308</v>
+        <v>9982.9</v>
       </c>
       <c r="U11" t="n">
-        <v>8448.799999999999</v>
+        <v>302.35</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>16754.4</v>
+        <v>15972.63</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>346</v>
+        <v>120.7</v>
       </c>
       <c r="E2" t="n">
-        <v>309.86</v>
+        <v>99.87</v>
       </c>
       <c r="F2" t="n">
-        <v>11.66</v>
+        <v>20.86</v>
       </c>
       <c r="G2" t="n">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="H2" t="n">
-        <v>57.27</v>
+        <v>5.88</v>
       </c>
       <c r="I2" t="n">
-        <v>58.11</v>
+        <v>55.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.63</v>
+        <v>1.36</v>
       </c>
       <c r="K2" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M2" t="n">
-        <v>76.75</v>
+        <v>78.8</v>
       </c>
       <c r="N2" t="n">
-        <v>346</v>
+        <v>120.7</v>
       </c>
       <c r="O2" t="n">
-        <v>289</v>
+        <v>828</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99994</v>
+        <v>99939.60000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>311.4</v>
+        <v>108.63</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.4</v>
+        <v>9993.959999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>404.82</v>
+        <v>143.63</v>
       </c>
       <c r="V2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W2" t="n">
-        <v>16998.98</v>
+        <v>18988.52</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SATIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>191.73</v>
+        <v>251.18</v>
       </c>
       <c r="E3" t="n">
-        <v>190.52</v>
+        <v>201.96</v>
       </c>
       <c r="F3" t="n">
-        <v>0.64</v>
+        <v>24.37</v>
       </c>
       <c r="G3" t="n">
-        <v>150.79</v>
+        <v>173.45</v>
       </c>
       <c r="H3" t="n">
-        <v>27.15</v>
+        <v>44.81</v>
       </c>
       <c r="I3" t="n">
-        <v>35.15</v>
+        <v>67.91</v>
       </c>
       <c r="J3" t="n">
-        <v>0.32</v>
+        <v>8.82</v>
       </c>
       <c r="K3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="M3" t="n">
-        <v>75</v>
+        <v>78.2</v>
       </c>
       <c r="N3" t="n">
-        <v>191.73</v>
+        <v>251.18</v>
       </c>
       <c r="O3" t="n">
-        <v>521</v>
+        <v>398</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99891.33</v>
+        <v>99969.64</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>172.56</v>
+        <v>226.06</v>
       </c>
       <c r="T3" t="n">
-        <v>9989.129999999999</v>
+        <v>9996.959999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>226.24</v>
+        <v>303.93</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>17980.44</v>
+        <v>20993.62</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7140</v>
+        <v>459</v>
       </c>
       <c r="E4" t="n">
-        <v>5493.36</v>
+        <v>400.45</v>
       </c>
       <c r="F4" t="n">
-        <v>29.98</v>
+        <v>14.62</v>
       </c>
       <c r="G4" t="n">
-        <v>4488.9</v>
+        <v>453.2</v>
       </c>
       <c r="H4" t="n">
-        <v>59.06</v>
+        <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>55.72</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3</v>
+        <v>1.64</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
         <v>84</v>
       </c>
       <c r="M4" t="n">
-        <v>70.34999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>7140</v>
+        <v>459</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99960</v>
+        <v>99603</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>6426</v>
+        <v>413.1</v>
       </c>
       <c r="T4" t="n">
-        <v>9996</v>
+        <v>9960.299999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>8425.200000000001</v>
+        <v>550.8</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W4" t="n">
-        <v>17992.8</v>
+        <v>19920.6</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORBTEXP</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>267.15</v>
+        <v>15.97</v>
       </c>
       <c r="E5" t="n">
-        <v>201.89</v>
+        <v>10.41</v>
       </c>
       <c r="F5" t="n">
-        <v>32.33</v>
+        <v>53.37</v>
       </c>
       <c r="G5" t="n">
-        <v>265</v>
+        <v>11.38</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8100000000000001</v>
+        <v>40.33</v>
       </c>
       <c r="I5" t="n">
-        <v>61.74</v>
+        <v>55.95</v>
       </c>
       <c r="J5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="K5" t="n">
         <v>70</v>
       </c>
       <c r="L5" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>69.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>267.15</v>
+        <v>15.97</v>
       </c>
       <c r="O5" t="n">
-        <v>374</v>
+        <v>6261</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99914.10000000001</v>
+        <v>99988.17</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>240.43</v>
+        <v>14.37</v>
       </c>
       <c r="T5" t="n">
-        <v>9991.41</v>
+        <v>9998.82</v>
       </c>
       <c r="U5" t="n">
-        <v>312.57</v>
+        <v>18.68</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>16.97</v>
       </c>
       <c r="W5" t="n">
-        <v>16985.4</v>
+        <v>16967.99</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAYURUNIQ</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>731.25</v>
+        <v>291.3</v>
       </c>
       <c r="E6" t="n">
-        <v>668.8200000000001</v>
+        <v>226.11</v>
       </c>
       <c r="F6" t="n">
-        <v>9.33</v>
+        <v>28.83</v>
       </c>
       <c r="G6" t="n">
-        <v>629.9</v>
+        <v>285</v>
       </c>
       <c r="H6" t="n">
-        <v>16.09</v>
+        <v>2.21</v>
       </c>
       <c r="I6" t="n">
-        <v>46.76</v>
+        <v>55.34</v>
       </c>
       <c r="J6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="K6" t="n">
-        <v>52.5</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>69.09999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="N6" t="n">
-        <v>731.25</v>
+        <v>291.3</v>
       </c>
       <c r="O6" t="n">
-        <v>136</v>
+        <v>343</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99450</v>
+        <v>99915.89999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>9.94</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>658.12</v>
+        <v>262.17</v>
       </c>
       <c r="T6" t="n">
-        <v>9945</v>
+        <v>9991.59</v>
       </c>
       <c r="U6" t="n">
-        <v>826.3099999999999</v>
+        <v>343.73</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>12928.5</v>
+        <v>17984.86</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>MANCREDIT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9986</v>
+        <v>239.94</v>
       </c>
       <c r="E7" t="n">
-        <v>9437.440000000001</v>
+        <v>198.84</v>
       </c>
       <c r="F7" t="n">
-        <v>5.81</v>
+        <v>20.67</v>
       </c>
       <c r="G7" t="n">
-        <v>9950</v>
+        <v>215.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.36</v>
+        <v>11.21</v>
       </c>
       <c r="I7" t="n">
-        <v>38.51</v>
+        <v>63.76</v>
       </c>
       <c r="J7" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="K7" t="n">
-        <v>56.25</v>
+        <v>72.5</v>
       </c>
       <c r="L7" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
-        <v>68.55</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>9986</v>
+        <v>239.94</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>416</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99860</v>
+        <v>99815.03999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S7" t="n">
-        <v>8987.4</v>
+        <v>215.95</v>
       </c>
       <c r="T7" t="n">
-        <v>9986</v>
+        <v>9981.5</v>
       </c>
       <c r="U7" t="n">
-        <v>11384.04</v>
+        <v>285.53</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>13980.4</v>
+        <v>18964.86</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CONSOFINVT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>231.66</v>
+        <v>302.95</v>
       </c>
       <c r="E8" t="n">
-        <v>209.23</v>
+        <v>243.26</v>
       </c>
       <c r="F8" t="n">
-        <v>10.72</v>
+        <v>24.54</v>
       </c>
       <c r="G8" t="n">
-        <v>214</v>
+        <v>245.09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.25</v>
+        <v>23.61</v>
       </c>
       <c r="I8" t="n">
-        <v>35.35</v>
+        <v>61.03</v>
       </c>
       <c r="J8" t="n">
-        <v>1.59</v>
+        <v>5.81</v>
       </c>
       <c r="K8" t="n">
-        <v>58.75</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="M8" t="n">
-        <v>68.45</v>
+        <v>73</v>
       </c>
       <c r="N8" t="n">
-        <v>231.66</v>
+        <v>302.95</v>
       </c>
       <c r="O8" t="n">
-        <v>431</v>
+        <v>330</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99845.46000000001</v>
+        <v>99973.5</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>208.49</v>
+        <v>272.65</v>
       </c>
       <c r="T8" t="n">
-        <v>9984.549999999999</v>
+        <v>9997.35</v>
       </c>
       <c r="U8" t="n">
-        <v>271.04</v>
+        <v>360.51</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W8" t="n">
-        <v>16973.73</v>
+        <v>18994.96</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>114.96</v>
+        <v>1397.4</v>
       </c>
       <c r="E9" t="n">
-        <v>99.77</v>
+        <v>1120.62</v>
       </c>
       <c r="F9" t="n">
-        <v>15.23</v>
+        <v>24.7</v>
       </c>
       <c r="G9" t="n">
-        <v>114</v>
+        <v>1102.7</v>
       </c>
       <c r="H9" t="n">
-        <v>0.84</v>
+        <v>26.73</v>
       </c>
       <c r="I9" t="n">
-        <v>48.91</v>
+        <v>60.46</v>
       </c>
       <c r="J9" t="n">
-        <v>0.98</v>
+        <v>2.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52.5</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="M9" t="n">
-        <v>68.3</v>
+        <v>73</v>
       </c>
       <c r="N9" t="n">
-        <v>114.96</v>
+        <v>1397.4</v>
       </c>
       <c r="O9" t="n">
-        <v>869</v>
+        <v>71</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99900.24000000001</v>
+        <v>99215.39999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>9.92</v>
       </c>
       <c r="S9" t="n">
-        <v>103.46</v>
+        <v>1257.66</v>
       </c>
       <c r="T9" t="n">
-        <v>9990.02</v>
+        <v>9921.540000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>131.05</v>
+        <v>1662.91</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>13986.03</v>
+        <v>18850.93</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>512.25</v>
+        <v>29.14</v>
       </c>
       <c r="E10" t="n">
-        <v>454.96</v>
+        <v>16.58</v>
       </c>
       <c r="F10" t="n">
-        <v>12.59</v>
+        <v>75.72</v>
       </c>
       <c r="G10" t="n">
-        <v>404</v>
+        <v>17.4</v>
       </c>
       <c r="H10" t="n">
-        <v>26.79</v>
+        <v>67.47</v>
       </c>
       <c r="I10" t="n">
-        <v>47.59</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>6.82</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="n">
-        <v>66.25</v>
+        <v>58.75</v>
       </c>
       <c r="L10" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="M10" t="n">
-        <v>67.75</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>512.25</v>
+        <v>29.14</v>
       </c>
       <c r="O10" t="n">
-        <v>195</v>
+        <v>3431</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99888.75</v>
+        <v>99979.34</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>461.02</v>
+        <v>26.23</v>
       </c>
       <c r="T10" t="n">
-        <v>9988.879999999999</v>
+        <v>9997.93</v>
       </c>
       <c r="U10" t="n">
-        <v>589.09</v>
+        <v>33.8</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>15.99</v>
       </c>
       <c r="W10" t="n">
-        <v>14983.31</v>
+        <v>15986.7</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>260.65</v>
+        <v>347.75</v>
       </c>
       <c r="E11" t="n">
-        <v>192.07</v>
+        <v>310.32</v>
       </c>
       <c r="F11" t="n">
-        <v>35.71</v>
+        <v>12.06</v>
       </c>
       <c r="G11" t="n">
-        <v>178.95</v>
+        <v>220</v>
       </c>
       <c r="H11" t="n">
-        <v>45.66</v>
+        <v>58.07</v>
       </c>
       <c r="I11" t="n">
-        <v>40.54</v>
+        <v>59.4</v>
       </c>
       <c r="J11" t="n">
-        <v>5.99</v>
+        <v>0.53</v>
       </c>
       <c r="K11" t="n">
         <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
-        <v>67.55</v>
+        <v>72.75</v>
       </c>
       <c r="N11" t="n">
-        <v>260.65</v>
+        <v>347.75</v>
       </c>
       <c r="O11" t="n">
-        <v>383</v>
+        <v>287</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99828.95</v>
+        <v>99804.25</v>
       </c>
       <c r="R11" t="n">
         <v>9.98</v>
       </c>
       <c r="S11" t="n">
-        <v>234.58</v>
+        <v>312.98</v>
       </c>
       <c r="T11" t="n">
-        <v>9982.9</v>
+        <v>9980.42</v>
       </c>
       <c r="U11" t="n">
-        <v>302.35</v>
+        <v>406.87</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>15972.63</v>
+        <v>16966.72</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
